--- a/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
+++ b/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
@@ -36914,7 +36914,7 @@
         </is>
       </c>
       <c r="B5" s="334">
-        <f>'申請内容'!C134</f>
+        <f>'申請内容'!C143</f>
         <v/>
       </c>
       <c r="C5" s="327" t="inlineStr">
@@ -36945,7 +36945,7 @@
         </is>
       </c>
       <c r="B6" s="334">
-        <f>'申請内容'!C135</f>
+        <f>'申請内容'!C144</f>
         <v/>
       </c>
       <c r="C6" s="327" t="inlineStr">
@@ -36972,7 +36972,7 @@
         </is>
       </c>
       <c r="B7" s="334">
-        <f>'申請内容'!C136</f>
+        <f>'申請内容'!C145</f>
         <v/>
       </c>
       <c r="C7" s="327" t="inlineStr">
@@ -36999,7 +36999,7 @@
         </is>
       </c>
       <c r="B8" s="334">
-        <f>'申請内容'!C137</f>
+        <f>'申請内容'!C146</f>
         <v/>
       </c>
       <c r="C8" s="327" t="inlineStr">
@@ -37022,7 +37022,7 @@
         </is>
       </c>
       <c r="B9" s="334">
-        <f>'申請内容'!C138</f>
+        <f>'申請内容'!C147</f>
         <v/>
       </c>
       <c r="C9" s="327" t="inlineStr">
@@ -37097,7 +37097,7 @@
       </c>
       <c r="F11" s="508" t="n"/>
       <c r="H11" s="343">
-        <f>H1/(B5+B6+B7)</f>
+        <f>H10/(B5+B6+B7)</f>
         <v/>
       </c>
       <c r="J11" s="323" t="inlineStr">

--- a/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
+++ b/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="転記" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="申請内容" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="給与支給総額計算" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="給与支給総額計算 (旧)" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="申請金額" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="小規模事業者確認" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="分類表" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet name="商品マスタ" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet name="プルダウン用" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet name="実績報告" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet name="編集用" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="転記" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="申請内容" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="給与支給総額計算" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="給与支給総額計算 (旧)" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="申請金額" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="小規模事業者確認" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分類表" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品マスタ" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プルダウン用" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実績報告" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="編集用" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -626,7 +626,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="66">
+  <borders count="68">
     <border/>
     <border>
       <left style="thin">
@@ -1240,11 +1240,26 @@
         <color rgb="FF000000"/>
       </left>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="521">
+  <cellXfs count="525">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1272,23 +1287,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
@@ -1299,18 +1308,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -1318,28 +1323,16 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1352,12 +1345,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1386,9 +1375,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
@@ -1741,9 +1728,7 @@
     <xf numFmtId="3" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -2399,24 +2384,16 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="170" fontId="67" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="28" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="28" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="67" fillId="28" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="28" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -2598,6 +2575,14 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="170" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2754,7 +2739,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -2769,17 +2754,17 @@
         <cNvPicPr preferRelativeResize="0"/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3181,7 +3166,7 @@
           <t>項目</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>記入欄</t>
         </is>
@@ -3195,7 +3180,7 @@
     <row r="5">
       <c r="A5" s="19" t="n"/>
       <c r="B5" s="41" t="n"/>
-      <c r="C5" s="10" t="n"/>
+      <c r="C5" s="41" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -3209,7 +3194,7 @@
     <row r="7">
       <c r="A7" s="19" t="n"/>
       <c r="B7" s="41" t="n"/>
-      <c r="C7" s="10" t="n"/>
+      <c r="C7" s="41" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -3217,7 +3202,7 @@
           <t>企業名</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
+      <c r="B8" s="58" t="n"/>
       <c r="C8" s="26" t="n"/>
     </row>
     <row r="9">
@@ -3231,13 +3216,13 @@
           <t>企業名（フリガナ）</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n"/>
+      <c r="B10" s="58" t="n"/>
       <c r="C10" s="26" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="41" t="n"/>
-      <c r="C11" s="10" t="n"/>
+      <c r="C11" s="41" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
@@ -3251,7 +3236,7 @@
     <row r="13">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="41" t="n"/>
-      <c r="C13" s="10" t="n"/>
+      <c r="C13" s="41" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -3260,7 +3245,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
-      <c r="C14" s="23" t="n"/>
+      <c r="C14" s="26" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="52" t="n"/>
@@ -3351,7 +3336,7 @@
     <row r="25">
       <c r="A25" s="19" t="n"/>
       <c r="B25" s="41" t="n"/>
-      <c r="C25" s="10" t="n"/>
+      <c r="C25" s="41" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -3365,7 +3350,7 @@
     <row r="27">
       <c r="A27" s="19" t="n"/>
       <c r="B27" s="41" t="n"/>
-      <c r="C27" s="10" t="n"/>
+      <c r="C27" s="41" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -3373,13 +3358,13 @@
           <t>担当者氏名</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
+      <c r="B28" s="58" t="n"/>
       <c r="C28" s="26" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="41" t="n"/>
-      <c r="C29" s="10" t="n"/>
+      <c r="C29" s="41" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -3387,13 +3372,13 @@
           <t>担当者氏名フリガナ</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
+      <c r="B30" s="58" t="n"/>
       <c r="C30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="19" t="n"/>
       <c r="B31" s="41" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="C31" s="41" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -3402,12 +3387,12 @@
         </is>
       </c>
       <c r="B32" s="22" t="n"/>
-      <c r="C32" s="29" t="n"/>
+      <c r="C32" s="59" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="19" t="n"/>
       <c r="B33" s="41" t="n"/>
-      <c r="C33" s="10" t="n"/>
+      <c r="C33" s="41" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -3421,7 +3406,7 @@
     <row r="35">
       <c r="A35" s="19" t="n"/>
       <c r="B35" s="41" t="n"/>
-      <c r="C35" s="10" t="n"/>
+      <c r="C35" s="41" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -3435,7 +3420,7 @@
     <row r="37">
       <c r="A37" s="19" t="n"/>
       <c r="B37" s="41" t="n"/>
-      <c r="C37" s="10" t="n"/>
+      <c r="C37" s="41" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -3443,7 +3428,7 @@
           <t>従業員数：正規雇用</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n"/>
+      <c r="B38" s="58" t="n"/>
       <c r="C38" s="30" t="n"/>
     </row>
     <row r="39">
@@ -3457,7 +3442,7 @@
           <t>従業員数：契約社員</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n"/>
+      <c r="B40" s="58" t="n"/>
       <c r="C40" s="30" t="n"/>
     </row>
     <row r="41">
@@ -3471,7 +3456,7 @@
           <t>従業員数：パートアルバイト</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n"/>
+      <c r="B42" s="58" t="n"/>
       <c r="C42" s="30" t="n"/>
     </row>
     <row r="43">
@@ -3485,13 +3470,13 @@
           <t>従業員数：派遣社員</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n"/>
+      <c r="B44" s="58" t="n"/>
       <c r="C44" s="30" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
       <c r="B45" s="41" t="n"/>
-      <c r="C45" s="10" t="n"/>
+      <c r="C45" s="41" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -3499,13 +3484,13 @@
           <t>従業員数：その他</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n"/>
+      <c r="B46" s="58" t="n"/>
       <c r="C46" s="26" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="19" t="n"/>
       <c r="B47" s="41" t="n"/>
-      <c r="C47" s="10" t="n"/>
+      <c r="C47" s="41" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="32" t="inlineStr">
@@ -3527,7 +3512,7 @@
           <t>⇨「有」の場合、下記についてお教えください</t>
         </is>
       </c>
-      <c r="B49" s="34" t="n"/>
+      <c r="B49" s="49" t="n"/>
       <c r="C49" s="41" t="n"/>
     </row>
     <row r="50">
@@ -3632,7 +3617,7 @@
           <t>SECURITY ACTION自己宣言ID</t>
         </is>
       </c>
-      <c r="B61" s="15" t="n"/>
+      <c r="B61" s="58" t="n"/>
       <c r="C61" s="46" t="n"/>
     </row>
     <row r="62">
@@ -3719,7 +3704,7 @@
           <t>賃金引上げ計画を、従業員へ表明しましたか？</t>
         </is>
       </c>
-      <c r="B72" s="55" t="n"/>
+      <c r="B72" s="56" t="n"/>
       <c r="C72" s="56" t="inlineStr">
         <is>
           <t>賃上げ表明を行わない場合は、弊社までご相談ください。</t>
@@ -3779,7 +3764,7 @@
     <row r="79">
       <c r="A79" s="52" t="n"/>
       <c r="B79" s="41" t="n"/>
-      <c r="C79" s="10" t="n"/>
+      <c r="C79" s="41" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="61" t="inlineStr">
@@ -3788,7 +3773,7 @@
         </is>
       </c>
       <c r="B80" s="66" t="n"/>
-      <c r="C80" s="10" t="n"/>
+      <c r="C80" s="41" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="63" t="inlineStr">
@@ -8061,7 +8046,7 @@
           <t>ファイル添付</t>
         </is>
       </c>
-      <c r="C20" s="220" t="n"/>
+      <c r="C20" s="253" t="n"/>
       <c r="F20" s="140" t="n"/>
       <c r="G20" s="140" t="n"/>
       <c r="H20" s="462" t="n"/>
@@ -8713,9 +8698,9 @@
           <t>ファイル添付</t>
         </is>
       </c>
-      <c r="C44" s="220" t="n"/>
-      <c r="D44" s="220" t="n"/>
-      <c r="E44" s="220" t="n"/>
+      <c r="C44" s="253" t="n"/>
+      <c r="D44" s="253" t="n"/>
+      <c r="E44" s="253" t="n"/>
       <c r="F44" s="140" t="n"/>
       <c r="G44" s="140" t="n"/>
       <c r="H44" s="462" t="n"/>
@@ -8854,9 +8839,9 @@
           <t>ファイル添付</t>
         </is>
       </c>
-      <c r="C50" s="220" t="n"/>
-      <c r="D50" s="220" t="n"/>
-      <c r="E50" s="220" t="n"/>
+      <c r="C50" s="253" t="n"/>
+      <c r="D50" s="253" t="n"/>
+      <c r="E50" s="253" t="n"/>
       <c r="F50" s="140" t="n"/>
       <c r="G50" s="140" t="n"/>
       <c r="H50" s="462" t="n"/>
@@ -8894,9 +8879,9 @@
           <t>ファイル添付</t>
         </is>
       </c>
-      <c r="C52" s="220" t="n"/>
-      <c r="D52" s="220" t="n"/>
-      <c r="E52" s="220" t="n"/>
+      <c r="C52" s="253" t="n"/>
+      <c r="D52" s="253" t="n"/>
+      <c r="E52" s="253" t="n"/>
       <c r="F52" s="140" t="n"/>
       <c r="G52" s="140" t="n"/>
       <c r="H52" s="462" t="n"/>
@@ -9035,9 +9020,9 @@
           <t>ファイル添付</t>
         </is>
       </c>
-      <c r="C58" s="220" t="n"/>
-      <c r="D58" s="220" t="n"/>
-      <c r="E58" s="220" t="n"/>
+      <c r="C58" s="253" t="n"/>
+      <c r="D58" s="253" t="n"/>
+      <c r="E58" s="253" t="n"/>
       <c r="F58" s="140" t="n"/>
       <c r="G58" s="140" t="n"/>
       <c r="H58" s="462" t="n"/>
@@ -9463,9 +9448,9 @@
           <t>ファイル添付</t>
         </is>
       </c>
-      <c r="C76" s="220" t="n"/>
-      <c r="D76" s="220" t="n"/>
-      <c r="E76" s="220" t="n"/>
+      <c r="C76" s="253" t="n"/>
+      <c r="D76" s="253" t="n"/>
+      <c r="E76" s="253" t="n"/>
       <c r="F76" s="140" t="n"/>
       <c r="G76" s="140" t="n"/>
       <c r="H76" s="462" t="n"/>
@@ -21850,7 +21835,7 @@
           <t>本店所在地　住所</t>
         </is>
       </c>
-      <c r="C45" s="224" t="n"/>
+      <c r="C45" s="499" t="n"/>
       <c r="D45" s="190" t="inlineStr">
         <is>
           <t>『履歴事項全部証明書』より記入
@@ -22001,7 +21986,7 @@
           <t>資本金</t>
         </is>
       </c>
-      <c r="C49" s="224" t="n"/>
+      <c r="C49" s="499" t="n"/>
       <c r="D49" s="190" t="inlineStr">
         <is>
           <t>『履歴事項全部証明書』より記入
@@ -22822,7 +22807,7 @@
           <t>代表者・役員数</t>
         </is>
       </c>
-      <c r="C71" s="224" t="n"/>
+      <c r="C71" s="499" t="n"/>
       <c r="D71" s="190" t="inlineStr">
         <is>
           <t>代表者を含めた役員数
@@ -22860,7 +22845,7 @@
           <t>代表者役職</t>
         </is>
       </c>
-      <c r="C72" s="224" t="n"/>
+      <c r="C72" s="499" t="n"/>
       <c r="D72" s="226" t="n"/>
       <c r="E72" s="191" t="n"/>
       <c r="F72" s="140" t="n"/>
@@ -23022,12 +23007,12 @@
     </row>
     <row r="77">
       <c r="A77" s="197" t="n"/>
-      <c r="B77" s="204" t="inlineStr">
+      <c r="B77" s="498" t="inlineStr">
         <is>
           <t>役員（1）役職</t>
         </is>
       </c>
-      <c r="C77" s="224" t="n"/>
+      <c r="C77" s="499" t="n"/>
       <c r="D77" s="460" t="n"/>
       <c r="E77" s="191" t="n"/>
       <c r="F77" s="199" t="n"/>
@@ -23054,12 +23039,12 @@
     </row>
     <row r="78">
       <c r="A78" s="200" t="n"/>
-      <c r="B78" s="204" t="inlineStr">
+      <c r="B78" s="498" t="inlineStr">
         <is>
           <t>役員（1）氏名</t>
         </is>
       </c>
-      <c r="C78" s="224" t="n"/>
+      <c r="C78" s="499" t="n"/>
       <c r="D78" s="460" t="n"/>
       <c r="E78" s="191" t="n"/>
       <c r="F78" s="140" t="n"/>
@@ -23086,12 +23071,12 @@
     </row>
     <row r="79">
       <c r="A79" s="69" t="n"/>
-      <c r="B79" s="204" t="inlineStr">
+      <c r="B79" s="498" t="inlineStr">
         <is>
           <t>役員（1）氏名フリガナ</t>
         </is>
       </c>
-      <c r="C79" s="224" t="n"/>
+      <c r="C79" s="499" t="n"/>
       <c r="D79" s="190" t="inlineStr">
         <is>
           <t>フリガナは申請時に担当者へ確認</t>
@@ -23127,7 +23112,7 @@
           <t>役員（2）役職</t>
         </is>
       </c>
-      <c r="C80" s="224" t="n"/>
+      <c r="C80" s="499" t="n"/>
       <c r="D80" s="203" t="n"/>
       <c r="E80" s="159" t="n"/>
       <c r="F80" s="140" t="n"/>
@@ -23159,7 +23144,7 @@
           <t>役員（2）氏名</t>
         </is>
       </c>
-      <c r="C81" s="224" t="n"/>
+      <c r="C81" s="499" t="n"/>
       <c r="D81" s="203" t="n"/>
       <c r="E81" s="159" t="n"/>
       <c r="F81" s="140" t="n"/>
@@ -23191,7 +23176,7 @@
           <t>役員（2）氏名フリガナ</t>
         </is>
       </c>
-      <c r="C82" s="224" t="n"/>
+      <c r="C82" s="499" t="n"/>
       <c r="D82" s="203" t="n"/>
       <c r="E82" s="159" t="n"/>
       <c r="F82" s="140" t="n"/>
@@ -23218,12 +23203,12 @@
     </row>
     <row r="83">
       <c r="A83" s="69" t="n"/>
-      <c r="B83" s="204" t="inlineStr">
+      <c r="B83" s="498" t="inlineStr">
         <is>
           <t>役員（3）役職</t>
         </is>
       </c>
-      <c r="C83" s="224" t="n"/>
+      <c r="C83" s="499" t="n"/>
       <c r="D83" s="203" t="n"/>
       <c r="E83" s="159" t="n"/>
       <c r="F83" s="140" t="n"/>
@@ -23250,12 +23235,12 @@
     </row>
     <row r="84">
       <c r="A84" s="69" t="n"/>
-      <c r="B84" s="204" t="inlineStr">
+      <c r="B84" s="498" t="inlineStr">
         <is>
           <t>役員（3）氏名</t>
         </is>
       </c>
-      <c r="C84" s="224" t="n"/>
+      <c r="C84" s="499" t="n"/>
       <c r="D84" s="203" t="n"/>
       <c r="E84" s="159" t="n"/>
       <c r="F84" s="140" t="n"/>
@@ -23282,12 +23267,12 @@
     </row>
     <row r="85">
       <c r="A85" s="69" t="n"/>
-      <c r="B85" s="204" t="inlineStr">
+      <c r="B85" s="498" t="inlineStr">
         <is>
           <t>役員（3）氏名フリガナ</t>
         </is>
       </c>
-      <c r="C85" s="224" t="n"/>
+      <c r="C85" s="499" t="n"/>
       <c r="D85" s="203" t="n"/>
       <c r="E85" s="159" t="n"/>
       <c r="F85" s="140" t="n"/>
@@ -23319,7 +23304,7 @@
           <t>役員（4）役職</t>
         </is>
       </c>
-      <c r="C86" s="224" t="n"/>
+      <c r="C86" s="499" t="n"/>
       <c r="D86" s="203" t="n"/>
       <c r="E86" s="159" t="n"/>
       <c r="F86" s="140" t="n"/>
@@ -23351,7 +23336,7 @@
           <t>役員（4）氏名</t>
         </is>
       </c>
-      <c r="C87" s="224" t="n"/>
+      <c r="C87" s="499" t="n"/>
       <c r="D87" s="203" t="n"/>
       <c r="E87" s="159" t="n"/>
       <c r="F87" s="140" t="n"/>
@@ -23383,7 +23368,7 @@
           <t>役員（4）氏名フリガナ</t>
         </is>
       </c>
-      <c r="C88" s="224" t="n"/>
+      <c r="C88" s="499" t="n"/>
       <c r="D88" s="203" t="n"/>
       <c r="E88" s="159" t="n"/>
       <c r="F88" s="140" t="n"/>
@@ -23410,12 +23395,12 @@
     </row>
     <row r="89">
       <c r="A89" s="69" t="n"/>
-      <c r="B89" s="204" t="inlineStr">
+      <c r="B89" s="498" t="inlineStr">
         <is>
           <t>役員（5）役職</t>
         </is>
       </c>
-      <c r="C89" s="224" t="n"/>
+      <c r="C89" s="499" t="n"/>
       <c r="D89" s="203" t="n"/>
       <c r="E89" s="191" t="n"/>
       <c r="F89" s="202" t="n"/>
@@ -23442,12 +23427,12 @@
     </row>
     <row r="90">
       <c r="A90" s="69" t="n"/>
-      <c r="B90" s="204" t="inlineStr">
+      <c r="B90" s="498" t="inlineStr">
         <is>
           <t>役員（5）氏名</t>
         </is>
       </c>
-      <c r="C90" s="224" t="n"/>
+      <c r="C90" s="499" t="n"/>
       <c r="D90" s="203" t="n"/>
       <c r="E90" s="191" t="n"/>
       <c r="F90" s="202" t="n"/>
@@ -23474,12 +23459,12 @@
     </row>
     <row r="91">
       <c r="A91" s="69" t="n"/>
-      <c r="B91" s="204" t="inlineStr">
+      <c r="B91" s="498" t="inlineStr">
         <is>
           <t>役員（5）氏名フリガナ</t>
         </is>
       </c>
-      <c r="C91" s="224" t="n"/>
+      <c r="C91" s="499" t="n"/>
       <c r="D91" s="203" t="n"/>
       <c r="E91" s="191" t="n"/>
       <c r="F91" s="202" t="n"/>
@@ -23511,7 +23496,7 @@
           <t>役員（6）役職</t>
         </is>
       </c>
-      <c r="C92" s="224" t="n"/>
+      <c r="C92" s="499" t="n"/>
       <c r="D92" s="203" t="n"/>
       <c r="E92" s="159" t="n"/>
       <c r="F92" s="140" t="n"/>
@@ -23543,7 +23528,7 @@
           <t>役員（6）氏名</t>
         </is>
       </c>
-      <c r="C93" s="224" t="n"/>
+      <c r="C93" s="499" t="n"/>
       <c r="D93" s="203" t="n"/>
       <c r="E93" s="159" t="n"/>
       <c r="F93" s="140" t="n"/>
@@ -23575,7 +23560,7 @@
           <t>役員（6）氏名フリガナ</t>
         </is>
       </c>
-      <c r="C94" s="224" t="n"/>
+      <c r="C94" s="499" t="n"/>
       <c r="D94" s="203" t="n"/>
       <c r="E94" s="159" t="n"/>
       <c r="F94" s="140" t="n"/>
@@ -23602,12 +23587,12 @@
     </row>
     <row r="95">
       <c r="A95" s="69" t="n"/>
-      <c r="B95" s="204" t="inlineStr">
+      <c r="B95" s="498" t="inlineStr">
         <is>
           <t>役員（7）役職</t>
         </is>
       </c>
-      <c r="C95" s="224" t="n"/>
+      <c r="C95" s="499" t="n"/>
       <c r="D95" s="203" t="n"/>
       <c r="E95" s="191" t="n"/>
       <c r="F95" s="202" t="n"/>
@@ -23634,12 +23619,12 @@
     </row>
     <row r="96">
       <c r="A96" s="69" t="n"/>
-      <c r="B96" s="204" t="inlineStr">
+      <c r="B96" s="498" t="inlineStr">
         <is>
           <t>役員（7）氏名</t>
         </is>
       </c>
-      <c r="C96" s="224" t="n"/>
+      <c r="C96" s="499" t="n"/>
       <c r="D96" s="203" t="n"/>
       <c r="E96" s="191" t="n"/>
       <c r="F96" s="202" t="n"/>
@@ -23666,12 +23651,12 @@
     </row>
     <row r="97">
       <c r="A97" s="69" t="n"/>
-      <c r="B97" s="204" t="inlineStr">
+      <c r="B97" s="498" t="inlineStr">
         <is>
           <t>役員（7）氏名フリガナ</t>
         </is>
       </c>
-      <c r="C97" s="224" t="n"/>
+      <c r="C97" s="499" t="n"/>
       <c r="D97" s="203" t="n"/>
       <c r="E97" s="191" t="n"/>
       <c r="F97" s="202" t="n"/>
@@ -23707,14 +23692,14 @@
       <c r="D98" s="203" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>役員（8）氏名</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="0" t="inlineStr">
         <is>
           <t>役員（8）氏名フリガナ</t>
         </is>
@@ -23731,14 +23716,14 @@
       <c r="D101" s="203" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>役員（9）氏名</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>役員（9）氏名フリガナ</t>
         </is>
@@ -23755,14 +23740,14 @@
       <c r="D104" s="203" t="n"/>
     </row>
     <row r="105" outlineLevel="1" s="477">
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>役員（10）氏名</t>
         </is>
       </c>
     </row>
     <row r="106" outlineLevel="1" s="477">
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
         <is>
           <t>役員（10）氏名フリガナ</t>
         </is>
@@ -24010,12 +23995,9 @@
           <t>申請年度</t>
         </is>
       </c>
-      <c r="C113" s="210">
-        <f>'転記'!B50</f>
-        <v/>
-      </c>
-      <c r="D113" s="210" t="n"/>
-      <c r="E113" s="211" t="n"/>
+      <c r="C113" s="482" t="n"/>
+      <c r="D113" s="482" t="n"/>
+      <c r="E113" s="510" t="n"/>
       <c r="F113" s="140" t="n"/>
       <c r="G113" s="462" t="n"/>
       <c r="H113" s="462" t="n"/>
@@ -24215,9 +24197,6 @@
     <row r="119">
       <c r="A119" s="69" t="n"/>
       <c r="B119" s="124" t="n"/>
-      <c r="C119" s="113" t="n"/>
-      <c r="D119" s="114" t="n"/>
-      <c r="E119" s="113" t="n"/>
       <c r="F119" s="69" t="n"/>
     </row>
     <row r="120" ht="6" customHeight="1" s="477">
@@ -24371,18 +24350,11 @@
     </row>
     <row r="126">
       <c r="A126" s="69" t="n"/>
-      <c r="B126" s="141" t="inlineStr">
+      <c r="B126" s="521" t="inlineStr">
         <is>
           <t>『  次へ  』</t>
         </is>
       </c>
-      <c r="C126" s="142" t="inlineStr">
-        <is>
-          <t>をクリック</t>
-        </is>
-      </c>
-      <c r="D126" s="73" t="n"/>
-      <c r="E126" s="73" t="n"/>
       <c r="F126" s="69" t="n"/>
     </row>
     <row r="127" ht="6" customHeight="1" s="477">
@@ -24479,7 +24451,7 @@
         </is>
       </c>
       <c r="C130" s="219" t="n"/>
-      <c r="D130" s="220" t="n"/>
+      <c r="D130" s="253" t="n"/>
       <c r="E130" s="73" t="n"/>
       <c r="F130" s="140" t="n"/>
       <c r="G130" s="462" t="n"/>
@@ -24510,13 +24482,13 @@
           <t>ファイル添付</t>
         </is>
       </c>
-      <c r="C131" s="220" t="inlineStr">
+      <c r="C131" s="253" t="inlineStr">
         <is>
           <t>※添付資料のアドレスとgBizIDプライムの一致を確認
 　ファイル名に空白（スペース）が入っていないか確認</t>
         </is>
       </c>
-      <c r="D131" s="220" t="n"/>
+      <c r="D131" s="253" t="n"/>
       <c r="E131" s="223" t="inlineStr">
         <is>
           <t>資料リンクを貼る</t>
@@ -24547,9 +24519,6 @@
     <row r="132">
       <c r="A132" s="69" t="n"/>
       <c r="B132" s="72" t="n"/>
-      <c r="C132" s="73" t="n"/>
-      <c r="D132" s="69" t="n"/>
-      <c r="E132" s="73" t="n"/>
       <c r="F132" s="69" t="n"/>
     </row>
     <row r="133" ht="6" customHeight="1" s="477">
@@ -24660,7 +24629,7 @@
           <t>行っている事業に該当するものすべて選択</t>
         </is>
       </c>
-      <c r="C137" s="224" t="n"/>
+      <c r="C137" s="499" t="n"/>
       <c r="D137" s="225" t="inlineStr">
         <is>
           <t>※複数選択</t>
@@ -24709,7 +24678,7 @@
           <t>をクリック</t>
         </is>
       </c>
-      <c r="D139" s="73" t="n"/>
+      <c r="D139" s="522" t="n"/>
       <c r="E139" s="73" t="n"/>
       <c r="F139" s="69" t="n"/>
     </row>
@@ -24717,7 +24686,7 @@
       <c r="A140" s="69" t="n"/>
       <c r="B140" s="72" t="n"/>
       <c r="C140" s="73" t="n"/>
-      <c r="D140" s="69" t="n"/>
+      <c r="D140" s="523" t="n"/>
       <c r="E140" s="73" t="n"/>
       <c r="F140" s="69" t="n"/>
       <c r="G140" s="69" t="n"/>
@@ -24748,6 +24717,7 @@
           <t>財務情報入力</t>
         </is>
       </c>
+      <c r="D141" s="523" t="n"/>
       <c r="F141" s="69" t="n"/>
       <c r="G141" s="462" t="n"/>
       <c r="H141" s="462" t="n"/>
@@ -24774,7 +24744,7 @@
       <c r="A142" s="69" t="n"/>
       <c r="B142" s="72" t="n"/>
       <c r="C142" s="73" t="n"/>
-      <c r="D142" s="69" t="n"/>
+      <c r="D142" s="523" t="n"/>
       <c r="E142" s="73" t="n"/>
       <c r="F142" s="69" t="n"/>
       <c r="G142" s="462" t="n"/>
@@ -24809,11 +24779,7 @@
         <f>'転記'!B64</f>
         <v/>
       </c>
-      <c r="D143" s="226" t="inlineStr">
-        <is>
-          <t>前期決算期末の人数</t>
-        </is>
-      </c>
+      <c r="D143" s="523" t="n"/>
       <c r="E143" s="159" t="n"/>
       <c r="F143" s="140" t="n"/>
       <c r="G143" s="462" t="n"/>
@@ -24848,11 +24814,7 @@
         <f>'転記'!B65</f>
         <v/>
       </c>
-      <c r="D144" s="226" t="inlineStr">
-        <is>
-          <t>前期決算期末の人数</t>
-        </is>
-      </c>
+      <c r="D144" s="523" t="n"/>
       <c r="E144" s="159" t="n"/>
       <c r="F144" s="140" t="n"/>
       <c r="G144" s="462" t="n"/>
@@ -24887,11 +24849,7 @@
         <f>'転記'!B66</f>
         <v/>
       </c>
-      <c r="D145" s="226" t="inlineStr">
-        <is>
-          <t>前期決算期末の人数</t>
-        </is>
-      </c>
+      <c r="D145" s="524" t="n"/>
       <c r="E145" s="159" t="n"/>
       <c r="F145" s="140" t="n"/>
       <c r="G145" s="462" t="n"/>
@@ -25401,15 +25359,8 @@
           <t>セキュリティの状況</t>
         </is>
       </c>
-      <c r="C161" s="237" t="inlineStr">
-        <is>
-          <t>□緊急時の対応マニュアルや手順を定め、定期的に訓練を行っている
-■パソコンやサーバなどには、IDやパスワードを設け情報セキュリティ管理を行っている
-□セキュリティ対策は講じていないため、対策を講じていく
-□セキュリティ対策を講じておらず、今後もその予定はない</t>
-        </is>
-      </c>
-      <c r="D161" s="242" t="n"/>
+      <c r="C161" s="235" t="n"/>
+      <c r="D161" s="236" t="n"/>
       <c r="E161" s="159" t="n"/>
       <c r="F161" s="140" t="n"/>
       <c r="G161" s="462" t="n"/>
@@ -25813,9 +25764,6 @@
     <row r="173">
       <c r="A173" s="69" t="n"/>
       <c r="B173" s="72" t="n"/>
-      <c r="C173" s="73" t="n"/>
-      <c r="D173" s="250" t="n"/>
-      <c r="E173" s="73" t="n"/>
       <c r="F173" s="69" t="n"/>
       <c r="G173" s="462" t="n"/>
       <c r="H173" s="462" t="n"/>
@@ -26049,9 +25997,6 @@
     <row r="181">
       <c r="A181" s="69" t="n"/>
       <c r="B181" s="258" t="n"/>
-      <c r="C181" s="472" t="n"/>
-      <c r="D181" s="123" t="n"/>
-      <c r="E181" s="248" t="n"/>
       <c r="F181" s="140" t="n"/>
       <c r="G181" s="123" t="n"/>
       <c r="H181" s="462" t="n"/>
@@ -26194,20 +26139,9 @@
           <t>支援事業者入力</t>
         </is>
       </c>
-      <c r="C187" s="255" t="inlineStr">
-        <is>
-          <t>・申請者入力内容の確認
-①ITツールの選択、金額入力
-②入力した金額をお客様に画面共有し、確認
-③申請</t>
-        </is>
-      </c>
-      <c r="D187" s="256" t="inlineStr">
-        <is>
-          <t>完了後、再度お客様に画面共有をしていただく</t>
-        </is>
-      </c>
-      <c r="E187" s="257" t="n"/>
+      <c r="C187" s="482" t="n"/>
+      <c r="D187" s="482" t="n"/>
+      <c r="E187" s="510" t="n"/>
       <c r="F187" s="140" t="n"/>
       <c r="G187" s="462" t="n"/>
       <c r="H187" s="462" t="n"/>
@@ -26266,7 +26200,11 @@
       <c r="A189" s="69" t="n"/>
       <c r="B189" s="72" t="n"/>
       <c r="C189" s="73" t="n"/>
-      <c r="D189" s="69" t="n"/>
+      <c r="D189" s="69" t="inlineStr">
+        <is>
+          <t>https://www.mhlw.go.jp/content/11200000/001557915.pdf</t>
+        </is>
+      </c>
       <c r="E189" s="73" t="n"/>
       <c r="F189" s="69" t="n"/>
       <c r="G189" s="123" t="n"/>
@@ -26387,7 +26325,7 @@
       <c r="A193" s="69" t="n"/>
       <c r="B193" s="72" t="n"/>
       <c r="C193" s="73" t="n"/>
-      <c r="D193" s="69" t="n"/>
+      <c r="D193" s="501" t="n"/>
       <c r="E193" s="73" t="n"/>
       <c r="F193" s="69" t="n"/>
       <c r="G193" s="462" t="n"/>
@@ -26423,7 +26361,7 @@
           <t>をクリック</t>
         </is>
       </c>
-      <c r="D194" s="73" t="n"/>
+      <c r="D194" s="501" t="n"/>
       <c r="E194" s="73" t="n"/>
       <c r="F194" s="69" t="n"/>
     </row>
@@ -26431,7 +26369,7 @@
       <c r="A195" s="260" t="n"/>
       <c r="B195" s="261" t="n"/>
       <c r="C195" s="247" t="n"/>
-      <c r="D195" s="123" t="n"/>
+      <c r="D195" s="502" t="n"/>
       <c r="E195" s="248" t="n"/>
       <c r="F195" s="140" t="n"/>
       <c r="G195" s="462" t="n"/>
@@ -26984,17 +26922,9 @@
           <t>従業員代表者</t>
         </is>
       </c>
-      <c r="C211" s="286">
-        <f>'転記'!B76</f>
-        <v/>
-      </c>
-      <c r="D211" s="287" t="inlineStr">
-        <is>
-          <t>代表者・取締役以外の、従業員
- ※漢字フルネーム</t>
-        </is>
-      </c>
-      <c r="E211" s="159" t="n"/>
+      <c r="C211" s="482" t="n"/>
+      <c r="D211" s="482" t="n"/>
+      <c r="E211" s="510" t="n"/>
       <c r="F211" s="140" t="n"/>
       <c r="G211" s="462" t="n"/>
       <c r="H211" s="462" t="n"/>
@@ -27064,16 +26994,9 @@
           <t>事業所内最低賃金者</t>
         </is>
       </c>
-      <c r="C213" s="286">
-        <f>'転記'!B78</f>
-        <v/>
-      </c>
-      <c r="D213" s="289" t="inlineStr">
-        <is>
-          <t>代表者・取締役以外の、従業員（パートアルバイト不在の場合は、新入社員など社員も可）※漢字フルネーム</t>
-        </is>
-      </c>
-      <c r="E213" s="159" t="n"/>
+      <c r="C213" s="482" t="n"/>
+      <c r="D213" s="482" t="n"/>
+      <c r="E213" s="510" t="n"/>
       <c r="F213" s="140" t="n"/>
       <c r="G213" s="462" t="n"/>
       <c r="H213" s="462" t="n"/>
@@ -27205,7 +27128,11 @@
           <t>＋50円</t>
         </is>
       </c>
-      <c r="D217" s="190" t="n"/>
+      <c r="D217" s="190" t="inlineStr">
+        <is>
+          <t>https://it-shien.smrj.go.jp/pdf/it2026_chingin_houkoku1_katen.xlsx</t>
+        </is>
+      </c>
       <c r="E217" s="159" t="n"/>
       <c r="F217" s="140" t="n"/>
       <c r="G217" s="462" t="n"/>
@@ -27407,14 +27334,9 @@
           <t>指定する一定期間において、3ヶ月以上、R7年度改定の地域別最低賃金未満で雇用していた従業員数が全従業員の30%以上であり、加点を希望する</t>
         </is>
       </c>
-      <c r="C224" s="298" t="inlineStr">
-        <is>
-          <t>□はい
-□いいえ</t>
-        </is>
-      </c>
-      <c r="D224" s="299" t="n"/>
-      <c r="E224" s="299" t="n"/>
+      <c r="C224" s="482" t="n"/>
+      <c r="D224" s="482" t="n"/>
+      <c r="E224" s="510" t="n"/>
       <c r="F224" s="125" t="n"/>
       <c r="G224" s="169" t="n"/>
       <c r="H224" s="169" t="n"/>
@@ -27542,7 +27464,11 @@
       <c r="A228" s="125" t="n"/>
       <c r="B228" s="293" t="n"/>
       <c r="C228" s="125" t="n"/>
-      <c r="D228" s="125" t="n"/>
+      <c r="D228" s="125" t="inlineStr">
+        <is>
+          <t>https://it-shien.smrj.go.jp/pdf/it2026_chingin_houkoku2_katen.xlsx</t>
+        </is>
+      </c>
       <c r="E228" s="125" t="n"/>
       <c r="F228" s="125" t="n"/>
       <c r="G228" s="169" t="n"/>
@@ -27887,9 +27813,6 @@
     <row r="239">
       <c r="A239" s="69" t="n"/>
       <c r="B239" s="72" t="n"/>
-      <c r="C239" s="73" t="n"/>
-      <c r="D239" s="69" t="n"/>
-      <c r="E239" s="73" t="n"/>
       <c r="F239" s="69" t="n"/>
       <c r="G239" s="462" t="n"/>
       <c r="H239" s="462" t="n"/>
@@ -28338,7 +28261,6 @@
       <c r="Y255" s="462" t="n"/>
       <c r="Z255" s="462" t="n"/>
     </row>
-    <row r="256"/>
     <row r="257">
       <c r="A257" s="69" t="n"/>
       <c r="B257" s="72" t="n"/>
@@ -36699,7 +36621,7 @@
       <c r="E1135" s="355" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="26">
     <mergeCell ref="B211:E211"/>
     <mergeCell ref="B187:E187"/>
     <mergeCell ref="B239:E239"/>
@@ -36716,8 +36638,6 @@
     <mergeCell ref="B173:E173"/>
     <mergeCell ref="B224:E224"/>
     <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B161:E161"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C24:E24"/>
@@ -37676,7 +37596,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="380" t="inlineStr">
+      <c r="A25" s="383" t="inlineStr">
         <is>
           <t>給与支給総額</t>
         </is>
@@ -37975,7 +37895,7 @@
       <c r="C8" s="404" t="n"/>
       <c r="D8" s="404" t="inlineStr">
         <is>
-          <t>　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E8" s="405" t="inlineStr">
@@ -38039,7 +37959,7 @@
       <c r="C11" s="404" t="n"/>
       <c r="D11" s="404" t="inlineStr">
         <is>
-          <t>　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E11" s="408" t="inlineStr">
@@ -38097,7 +38017,7 @@
     <row r="19">
       <c r="I19" s="454" t="inlineStr">
         <is>
-          <t>　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
     </row>

--- a/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
+++ b/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
@@ -26915,16 +26915,24 @@
       <c r="Y210" s="462" t="n"/>
       <c r="Z210" s="462" t="n"/>
     </row>
-    <row r="211">
+    <row r="211" ht="6" customHeight="1" s="477">
       <c r="A211" s="200" t="n"/>
       <c r="B211" s="265" t="inlineStr">
         <is>
           <t>従業員代表者</t>
         </is>
       </c>
-      <c r="C211" s="482" t="n"/>
-      <c r="D211" s="482" t="n"/>
-      <c r="E211" s="510" t="n"/>
+      <c r="C211" s="286">
+        <f>'転記'!B76</f>
+        <v/>
+      </c>
+      <c r="D211" s="288" t="inlineStr">
+        <is>
+          <t>代表者・取締役以外の、従業員
+ ※漢字フルネーム</t>
+        </is>
+      </c>
+      <c r="E211" s="159" t="n"/>
       <c r="F211" s="140" t="n"/>
       <c r="G211" s="462" t="n"/>
       <c r="H211" s="462" t="n"/>
@@ -26987,16 +26995,23 @@
       <c r="Y212" s="462" t="n"/>
       <c r="Z212" s="462" t="n"/>
     </row>
-    <row r="213">
+    <row r="213" ht="6" customHeight="1" s="477">
       <c r="A213" s="69" t="n"/>
       <c r="B213" s="265" t="inlineStr">
         <is>
           <t>事業所内最低賃金者</t>
         </is>
       </c>
-      <c r="C213" s="482" t="n"/>
-      <c r="D213" s="482" t="n"/>
-      <c r="E213" s="510" t="n"/>
+      <c r="C213" s="286">
+        <f>'転記'!B78</f>
+        <v/>
+      </c>
+      <c r="D213" s="288" t="inlineStr">
+        <is>
+          <t>代表者・取締役以外の、従業員（パートアルバイト不在の場合は、新入社員など社員も可）※漢字フルネーム</t>
+        </is>
+      </c>
+      <c r="E213" s="159" t="n"/>
       <c r="F213" s="140" t="n"/>
       <c r="G213" s="462" t="n"/>
       <c r="H213" s="462" t="n"/>
@@ -36621,8 +36636,7 @@
       <c r="E1135" s="355" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="B211:E211"/>
+  <mergeCells count="24">
     <mergeCell ref="B187:E187"/>
     <mergeCell ref="B239:E239"/>
     <mergeCell ref="B8:D8"/>
@@ -36631,7 +36645,6 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B222:E222"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B213:E213"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="B126:E126"/>
     <mergeCell ref="B113:E113"/>

--- a/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
+++ b/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
@@ -38037,7 +38037,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="D3:D6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>'商品マスタ'!$B$3:$B$28</formula1>
+      <formula1>'商品マスタ'!$B$3:$B$45</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -47056,28 +47056,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="437" t="n"/>
+      <c r="A3" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
       <c r="B3" s="438" t="inlineStr">
         <is>
-          <t>目標管理クラウドcbox_ベーシック</t>
+          <t>貿易クラウド_利用料</t>
         </is>
       </c>
       <c r="C3" s="439" t="inlineStr">
         <is>
-          <t>DL04-0028197-002</t>
+          <t>DL06-0000792-001</t>
         </is>
       </c>
       <c r="D3" s="440" t="n"/>
       <c r="E3" s="438" t="inlineStr">
         <is>
-          <t>cbox001</t>
+          <t>貿易001</t>
         </is>
       </c>
       <c r="F3" s="514" t="n">
-        <v>2040</v>
+        <v>600000</v>
       </c>
       <c r="G3" s="514" t="n">
-        <v>14400</v>
+        <v>3000000</v>
       </c>
       <c r="H3" s="438" t="inlineStr">
         <is>
@@ -47086,859 +47090,1359 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="437" t="n"/>
-      <c r="B4" s="442" t="inlineStr">
+      <c r="A4" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B4" s="438" t="inlineStr">
+        <is>
+          <t>カンリル_利用料</t>
+        </is>
+      </c>
+      <c r="C4" s="439" t="inlineStr">
+        <is>
+          <t>DL06-0029228-001</t>
+        </is>
+      </c>
+      <c r="D4" s="440" t="n"/>
+      <c r="E4" s="438" t="inlineStr">
+        <is>
+          <t>カンリル001</t>
+        </is>
+      </c>
+      <c r="F4" s="514" t="n">
+        <v>32509</v>
+      </c>
+      <c r="G4" s="514" t="n">
+        <v>325091</v>
+      </c>
+      <c r="H4" s="442" t="inlineStr">
         <is>
           <t>目標管理クラウドcbox_スタンダード</t>
         </is>
       </c>
-      <c r="C4" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0000658</t>
-        </is>
-      </c>
-      <c r="D4" s="444" t="n"/>
-      <c r="E4" s="442" t="inlineStr">
-        <is>
-          <t>cbox009</t>
-        </is>
-      </c>
-      <c r="F4" s="515" t="n">
-        <v>3240</v>
-      </c>
-      <c r="G4" s="515" t="n">
-        <v>38400</v>
-      </c>
-      <c r="H4" s="442" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_スタンダード</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="437" t="n"/>
+      <c r="A5" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
       <c r="B5" s="438" t="inlineStr">
         <is>
+          <t>社長メシ_スタンダードプラン</t>
+        </is>
+      </c>
+      <c r="C5" s="439" t="inlineStr">
+        <is>
+          <t>DL06-0029652-001</t>
+        </is>
+      </c>
+      <c r="D5" s="440" t="n"/>
+      <c r="E5" s="438" t="inlineStr">
+        <is>
+          <t>社長メシ001</t>
+        </is>
+      </c>
+      <c r="F5" s="514" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G5" s="514" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H5" s="438" t="inlineStr">
+        <is>
           <t>目標管理クラウドcbox_プレミアム</t>
         </is>
       </c>
-      <c r="C5" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0000675</t>
-        </is>
-      </c>
-      <c r="D5" s="444" t="n"/>
-      <c r="E5" s="438" t="inlineStr">
-        <is>
-          <t>cbox010</t>
-        </is>
-      </c>
-      <c r="F5" s="514" t="n">
-        <v>4440</v>
-      </c>
-      <c r="G5" s="514" t="n">
-        <v>62400</v>
-      </c>
-      <c r="H5" s="438" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_プレミアム</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="437" t="n"/>
-      <c r="B6" s="442" t="inlineStr">
+      <c r="A6" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B6" s="438" t="inlineStr">
+        <is>
+          <t>せきなび_スタンダード</t>
+        </is>
+      </c>
+      <c r="C6" s="439" t="inlineStr">
+        <is>
+          <t>DL06-0002760-001</t>
+        </is>
+      </c>
+      <c r="D6" s="440" t="n"/>
+      <c r="E6" s="438" t="inlineStr">
+        <is>
+          <t>seknavi01</t>
+        </is>
+      </c>
+      <c r="F6" s="514" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G6" s="514" t="n">
+        <v>360000</v>
+      </c>
+      <c r="H6" s="442" t="inlineStr">
         <is>
           <t>目標管理クラウドcbox_ベーシック_初期設定</t>
         </is>
       </c>
-      <c r="C6" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0000291-001</t>
-        </is>
-      </c>
-      <c r="D6" s="444" t="n"/>
-      <c r="E6" s="442" t="inlineStr">
-        <is>
-          <t>cbox005</t>
-        </is>
-      </c>
-      <c r="F6" s="515" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B7" s="438" t="inlineStr">
+        <is>
+          <t>カンリル_導入・活用コンサルティング</t>
+        </is>
+      </c>
+      <c r="C7" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0001708</t>
+        </is>
+      </c>
+      <c r="D7" s="440" t="n"/>
+      <c r="E7" s="438" t="inlineStr">
+        <is>
+          <t>カンリル003</t>
+        </is>
+      </c>
+      <c r="F7" s="514" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G7" s="514" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H7" s="438" t="inlineStr">
+        <is>
+          <t>目標管理クラウドcbox_ベーシック_保守・サポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B8" s="438" t="inlineStr">
+        <is>
+          <t>カンリル_初期設定</t>
+        </is>
+      </c>
+      <c r="C8" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0001738</t>
+        </is>
+      </c>
+      <c r="D8" s="440" t="n"/>
+      <c r="E8" s="438" t="inlineStr">
+        <is>
+          <t>カンリル002</t>
+        </is>
+      </c>
+      <c r="F8" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G8" s="514" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H8" s="442" t="inlineStr">
+        <is>
+          <t>目標管理クラウドcbox_導入・活用コンサルティング</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B9" s="438" t="inlineStr">
+        <is>
+          <t>Scale人事評価_スタンダードプラン</t>
+        </is>
+      </c>
+      <c r="C9" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0002412</t>
+        </is>
+      </c>
+      <c r="D9" s="440" t="n"/>
+      <c r="E9" s="438" t="inlineStr">
+        <is>
+          <t>Scale001</t>
+        </is>
+      </c>
+      <c r="F9" s="514" t="n">
+        <v>1920</v>
+      </c>
+      <c r="G9" s="514" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H9" s="438" t="inlineStr">
+        <is>
+          <t>目標管理クラウドcbox_スタンダード_初期設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B10" s="438" t="inlineStr">
+        <is>
+          <t>AI Works_保守・サポート</t>
+        </is>
+      </c>
+      <c r="C10" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0001726</t>
+        </is>
+      </c>
+      <c r="D10" s="440" t="n"/>
+      <c r="E10" s="438" t="inlineStr">
+        <is>
+          <t>AIWorks005</t>
+        </is>
+      </c>
+      <c r="F10" s="514" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G10" s="514" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H10" s="442" t="inlineStr">
+        <is>
+          <t>目標管理クラウドcbox_スタンダード_保守・サポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B11" s="438" t="inlineStr">
+        <is>
+          <t>AI Works_利用料</t>
+        </is>
+      </c>
+      <c r="C11" s="439" t="inlineStr">
+        <is>
+          <t>DL06-0001191-001</t>
+        </is>
+      </c>
+      <c r="D11" s="440" t="n"/>
+      <c r="E11" s="438" t="inlineStr">
+        <is>
+          <t>AIWorks001</t>
+        </is>
+      </c>
+      <c r="F11" s="514" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G11" s="514" t="n">
+        <v>360000</v>
+      </c>
+      <c r="H11" s="438" t="inlineStr">
+        <is>
+          <t>目標管理クラウドcbox_プレミアム_初期設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B12" s="438" t="inlineStr">
+        <is>
+          <t>カンリル_保守サポート</t>
+        </is>
+      </c>
+      <c r="C12" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0001733</t>
+        </is>
+      </c>
+      <c r="D12" s="440" t="n"/>
+      <c r="E12" s="438" t="inlineStr">
+        <is>
+          <t>カンリル004</t>
+        </is>
+      </c>
+      <c r="F12" s="514" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G12" s="514" t="n">
+        <v>125000</v>
+      </c>
+      <c r="H12" s="442" t="inlineStr">
+        <is>
+          <t>目標管理クラウドcbox_プレミアム_保守・サポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B13" s="438" t="inlineStr">
+        <is>
+          <t>freee会計_スタータープラン</t>
+        </is>
+      </c>
+      <c r="C13" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0007357</t>
+        </is>
+      </c>
+      <c r="D13" s="440" t="n"/>
+      <c r="E13" s="438" t="inlineStr">
+        <is>
+          <t>freee会計001</t>
+        </is>
+      </c>
+      <c r="F13" s="514" t="n">
+        <v>65760</v>
+      </c>
+      <c r="G13" s="514" t="n">
+        <v>65760</v>
+      </c>
+      <c r="H13" s="438" t="inlineStr">
+        <is>
+          <t>貿易クラウド_利用料</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B14" s="438" t="inlineStr">
+        <is>
+          <t>Scale人事評価スタンダードプラン_初期設定</t>
+        </is>
+      </c>
+      <c r="C14" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0020657</t>
+        </is>
+      </c>
+      <c r="D14" s="440" t="n"/>
+      <c r="E14" s="438" t="inlineStr">
+        <is>
+          <t>Scale002</t>
+        </is>
+      </c>
+      <c r="F14" s="514" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G14" s="514" t="n">
+        <v>160000</v>
+      </c>
+      <c r="H14" s="442" t="inlineStr">
+        <is>
+          <t>AI Works_利用料</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B15" s="438" t="inlineStr">
+        <is>
+          <t>AI Works_初期設定</t>
+        </is>
+      </c>
+      <c r="C15" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0003894</t>
+        </is>
+      </c>
+      <c r="D15" s="440" t="n"/>
+      <c r="E15" s="438" t="inlineStr">
+        <is>
+          <t>AIWorks003</t>
+        </is>
+      </c>
+      <c r="F15" s="514" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G15" s="514" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H15" s="438" t="inlineStr">
+        <is>
+          <t>AI Works_利用料_初期設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B16" s="438" t="inlineStr">
+        <is>
+          <t>PCセキュリティみまもりパック</t>
+        </is>
+      </c>
+      <c r="C16" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0002804</t>
+        </is>
+      </c>
+      <c r="D16" s="440" t="n"/>
+      <c r="E16" s="438" t="inlineStr">
+        <is>
+          <t>pcsecurity</t>
+        </is>
+      </c>
+      <c r="F16" s="514" t="n"/>
+      <c r="G16" s="514" t="n"/>
+      <c r="H16" s="442" t="inlineStr">
+        <is>
+          <t>AI Works_利用料_保守・サポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B17" s="438" t="inlineStr">
+        <is>
+          <t>Scale人事評価_導入・活用コンサルティング</t>
+        </is>
+      </c>
+      <c r="C17" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0020659</t>
+        </is>
+      </c>
+      <c r="D17" s="440" t="n"/>
+      <c r="E17" s="438" t="inlineStr">
+        <is>
+          <t>Scale003</t>
+        </is>
+      </c>
+      <c r="F17" s="514" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G17" s="514" t="n">
+        <v>900000</v>
+      </c>
+      <c r="H17" s="438" t="inlineStr">
+        <is>
+          <t>AI Works_導入活用コンサルティング</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B18" s="438" t="inlineStr">
+        <is>
+          <t>AI Works_導入活用コンサルティング</t>
+        </is>
+      </c>
+      <c r="C18" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0003887</t>
+        </is>
+      </c>
+      <c r="D18" s="440" t="n"/>
+      <c r="E18" s="438" t="inlineStr">
+        <is>
+          <t>AIWorks002</t>
+        </is>
+      </c>
+      <c r="F18" s="514" t="n">
         <v>100000</v>
       </c>
-      <c r="G6" s="515" t="n">
+      <c r="G18" s="514" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H18" s="442" t="inlineStr">
+        <is>
+          <t>LINE公式アカウント_ライトプラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="437" t="inlineStr">
+        <is>
+          <t>カラフルボックスコンソーシアム</t>
+        </is>
+      </c>
+      <c r="B19" s="438" t="inlineStr">
+        <is>
+          <t>Scale人事評価スタンダードプラン_保守サポート</t>
+        </is>
+      </c>
+      <c r="C19" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0020660</t>
+        </is>
+      </c>
+      <c r="D19" s="440" t="n"/>
+      <c r="E19" s="438" t="inlineStr">
+        <is>
+          <t>Scale004</t>
+        </is>
+      </c>
+      <c r="F19" s="514" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G19" s="514" t="n">
+        <v>480000</v>
+      </c>
+      <c r="H19" s="438" t="inlineStr">
+        <is>
+          <t>LINE公式アカウント_スタンダードプラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B20" s="438" t="inlineStr">
+        <is>
+          <t>クラフトバンクオフィス プロフェッショナルプラン</t>
+        </is>
+      </c>
+      <c r="C20" s="439" t="inlineStr">
+        <is>
+          <t>DL04-0029552-004</t>
+        </is>
+      </c>
+      <c r="D20" s="440" t="n"/>
+      <c r="E20" s="438" t="inlineStr">
+        <is>
+          <t>クラフトバンクオフィス プロフェッショナルプラン</t>
+        </is>
+      </c>
+      <c r="F20" s="514" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="G20" s="514" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="H20" s="442" t="inlineStr">
+        <is>
+          <t>Lステップ_スタートプラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B21" s="438" t="inlineStr">
+        <is>
+          <t>クラフトバンクオフィス エンタープライズプラン</t>
+        </is>
+      </c>
+      <c r="C21" s="439" t="inlineStr">
+        <is>
+          <t>DL04-0029554-004</t>
+        </is>
+      </c>
+      <c r="D21" s="440" t="n"/>
+      <c r="E21" s="438" t="inlineStr">
+        <is>
+          <t>クラフトバンクオフィス エンタープライズプラン</t>
+        </is>
+      </c>
+      <c r="F21" s="514" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="G21" s="514" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="H21" s="438" t="inlineStr">
+        <is>
+          <t>Lステップ_スタンダードプラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B22" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
+        </is>
+      </c>
+      <c r="C22" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0000180</t>
+        </is>
+      </c>
+      <c r="D22" s="440" t="n"/>
+      <c r="E22" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
+        </is>
+      </c>
+      <c r="F22" s="514" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G22" s="514" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="H22" s="442" t="inlineStr">
+        <is>
+          <t>Lステップ_プロプラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B23" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）</t>
+        </is>
+      </c>
+      <c r="C23" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0000059</t>
+        </is>
+      </c>
+      <c r="D23" s="440" t="n"/>
+      <c r="E23" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）</t>
+        </is>
+      </c>
+      <c r="F23" s="514" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G23" s="514" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="H23" s="438" t="inlineStr">
+        <is>
+          <t>UTAGE_ライトプラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B24" s="438" t="inlineStr">
+        <is>
+          <t>クラフトバンクオフィス スタンダードプラン</t>
+        </is>
+      </c>
+      <c r="C24" s="439" t="inlineStr">
+        <is>
+          <t>DL04-0029553-003</t>
+        </is>
+      </c>
+      <c r="D24" s="440" t="n"/>
+      <c r="E24" s="438" t="inlineStr">
+        <is>
+          <t>クラフトバンクオフィス スタンダードプラン</t>
+        </is>
+      </c>
+      <c r="F24" s="514" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G24" s="514" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H24" s="442" t="inlineStr">
+        <is>
+          <t>UTAGE_スタンダードプラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B25" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
+        </is>
+      </c>
+      <c r="C25" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0000025</t>
+        </is>
+      </c>
+      <c r="D25" s="440" t="n"/>
+      <c r="E25" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
+        </is>
+      </c>
+      <c r="F25" s="514" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G25" s="514" t="n">
+        <v>800000</v>
+      </c>
+      <c r="H25" s="438" t="inlineStr">
+        <is>
+          <t>せきなび_スタンダード</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B26" s="438" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）</t>
+        </is>
+      </c>
+      <c r="C26" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0000070</t>
+        </is>
+      </c>
+      <c r="D26" s="440" t="n"/>
+      <c r="E26" s="438" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）</t>
+        </is>
+      </c>
+      <c r="F26" s="514" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G26" s="514" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="H26" s="442" t="inlineStr">
+        <is>
+          <t>CRS人材募集管理システム_ベーシック</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B27" s="438" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）</t>
+        </is>
+      </c>
+      <c r="C27" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0000036</t>
+        </is>
+      </c>
+      <c r="D27" s="440" t="n"/>
+      <c r="E27" s="438" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）</t>
+        </is>
+      </c>
+      <c r="F27" s="514" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G27" s="514" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H27" s="438" t="inlineStr">
+        <is>
+          <t>CRS人材募集管理システム_ベーシック_初期導入</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B28" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス プロフェッショナルプラン</t>
+        </is>
+      </c>
+      <c r="C28" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0001646</t>
+        </is>
+      </c>
+      <c r="D28" s="440" t="n"/>
+      <c r="E28" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス プロフェッショナルプラン</t>
+        </is>
+      </c>
+      <c r="F28" s="514" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G28" s="514" t="n">
+        <v>1805000</v>
+      </c>
+      <c r="H28" s="442" t="inlineStr">
+        <is>
+          <t>CRS人材募集管理システム_ベーシック_保守・サポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="437" t="inlineStr">
+        <is>
+          <t>クラフトバンク</t>
+        </is>
+      </c>
+      <c r="B29" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング活用コンサルティング（プロフェッショナルプラン）</t>
+        </is>
+      </c>
+      <c r="C29" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0004098</t>
+        </is>
+      </c>
+      <c r="D29" s="440" t="n"/>
+      <c r="E29" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング活用コンサルティング（プロフェッショナルプラン）</t>
+        </is>
+      </c>
+      <c r="F29" s="514" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G29" s="514" t="n">
+        <v>1920000</v>
+      </c>
+      <c r="H29" s="450" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="437" t="inlineStr">
+        <is>
+          <t>ピスケス</t>
+        </is>
+      </c>
+      <c r="B30" s="438" t="inlineStr">
+        <is>
+          <t>着信ポップアップCTI</t>
+        </is>
+      </c>
+      <c r="C30" s="439" t="inlineStr">
+        <is>
+          <t>DL06-0034655-001</t>
+        </is>
+      </c>
+      <c r="D30" s="440" t="n"/>
+      <c r="E30" s="438" t="inlineStr">
+        <is>
+          <t>PSA003</t>
+        </is>
+      </c>
+      <c r="F30" s="514" t="n">
+        <v>108000</v>
+      </c>
+      <c r="G30" s="514" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H30" s="450" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="437" t="inlineStr">
+        <is>
+          <t>ピスケス</t>
+        </is>
+      </c>
+      <c r="B31" s="438" t="inlineStr">
+        <is>
+          <t>LINEコネクト</t>
+        </is>
+      </c>
+      <c r="C31" s="439" t="inlineStr">
+        <is>
+          <t>DL06-0033682-001</t>
+        </is>
+      </c>
+      <c r="D31" s="440" t="n"/>
+      <c r="E31" s="438" t="inlineStr">
+        <is>
+          <t>PLINE</t>
+        </is>
+      </c>
+      <c r="F31" s="514" t="n">
+        <v>64000</v>
+      </c>
+      <c r="G31" s="514" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H31" s="450" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="437" t="inlineStr">
+        <is>
+          <t>ピスケス</t>
+        </is>
+      </c>
+      <c r="B32" s="438" t="inlineStr">
+        <is>
+          <t>ピスケスアポ</t>
+        </is>
+      </c>
+      <c r="C32" s="439" t="inlineStr">
+        <is>
+          <t>DL05-0024072-002</t>
+        </is>
+      </c>
+      <c r="D32" s="440" t="n"/>
+      <c r="E32" s="438" t="inlineStr">
+        <is>
+          <t>piscesapo2024</t>
+        </is>
+      </c>
+      <c r="F32" s="514" t="n">
+        <v>408000</v>
+      </c>
+      <c r="G32" s="514" t="n">
+        <v>480000</v>
+      </c>
+      <c r="H32" s="385" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="437" t="inlineStr">
+        <is>
+          <t>ピスケス</t>
+        </is>
+      </c>
+      <c r="B33" s="438" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="C33" s="439" t="inlineStr">
+        <is>
+          <t>DL06-0034634-001</t>
+        </is>
+      </c>
+      <c r="D33" s="440" t="n"/>
+      <c r="E33" s="438" t="inlineStr">
+        <is>
+          <t>PKA002</t>
+        </is>
+      </c>
+      <c r="F33" s="514" t="n">
+        <v>64000</v>
+      </c>
+      <c r="G33" s="514" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H33" s="385" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B34" s="438" t="inlineStr">
+        <is>
+          <t>irohana study スモール</t>
+        </is>
+      </c>
+      <c r="C34" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0024780</t>
+        </is>
+      </c>
+      <c r="D34" s="440" t="n"/>
+      <c r="E34" s="438" t="inlineStr">
+        <is>
+          <t>study_s</t>
+        </is>
+      </c>
+      <c r="F34" s="514" t="n">
+        <v>237600</v>
+      </c>
+      <c r="G34" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="H34" s="385" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B35" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa スモール</t>
+        </is>
+      </c>
+      <c r="C35" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0014825</t>
+        </is>
+      </c>
+      <c r="D35" s="440" t="n"/>
+      <c r="E35" s="438" t="inlineStr">
+        <is>
+          <t>visa_s</t>
+        </is>
+      </c>
+      <c r="F35" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="G35" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="H35" s="385" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B36" s="438" t="inlineStr">
+        <is>
+          <t>irohana study スタンダード</t>
+        </is>
+      </c>
+      <c r="C36" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0024781</t>
+        </is>
+      </c>
+      <c r="D36" s="440" t="n"/>
+      <c r="E36" s="438" t="inlineStr">
+        <is>
+          <t>study_m</t>
+        </is>
+      </c>
+      <c r="F36" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="G36" s="514" t="n">
+        <v>477600</v>
+      </c>
+      <c r="H36" s="385" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B37" s="438" t="inlineStr">
+        <is>
+          <t>irohana 導入コンサルティング等</t>
+        </is>
+      </c>
+      <c r="C37" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019039</t>
+        </is>
+      </c>
+      <c r="D37" s="440" t="n"/>
+      <c r="E37" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング等</t>
+        </is>
+      </c>
+      <c r="F37" s="514" t="n">
         <v>200000</v>
       </c>
-      <c r="H6" s="442" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_ベーシック_初期設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="437" t="n"/>
-      <c r="B7" s="438" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_ベーシック_保守・サポート</t>
-        </is>
-      </c>
-      <c r="C7" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0000622-001</t>
-        </is>
-      </c>
-      <c r="D7" s="444" t="n"/>
-      <c r="E7" s="438" t="inlineStr">
-        <is>
-          <t>cbox007</t>
-        </is>
-      </c>
-      <c r="F7" s="516" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G7" s="516" t="n">
-        <v>480000</v>
-      </c>
-      <c r="H7" s="438" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_ベーシック_保守・サポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="437" t="n"/>
-      <c r="B8" s="442" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_導入・活用コンサルティング</t>
-        </is>
-      </c>
-      <c r="C8" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0000623</t>
-        </is>
-      </c>
-      <c r="D8" s="444" t="n"/>
-      <c r="E8" s="442" t="inlineStr">
-        <is>
-          <t>cbox008</t>
-        </is>
-      </c>
-      <c r="F8" s="515" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G8" s="515" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="H8" s="442" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_導入・活用コンサルティング</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="437" t="n"/>
-      <c r="B9" s="438" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_スタンダード_初期設定</t>
-        </is>
-      </c>
-      <c r="C9" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0008895</t>
-        </is>
-      </c>
-      <c r="D9" s="444" t="n"/>
-      <c r="E9" s="438" t="inlineStr">
-        <is>
-          <t>cbox011</t>
-        </is>
-      </c>
-      <c r="F9" s="514" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G9" s="514" t="n">
+      <c r="G37" s="514" t="n">
         <v>200000</v>
       </c>
-      <c r="H9" s="438" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_スタンダード_初期設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="437" t="n"/>
-      <c r="B10" s="442" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_スタンダード_保守・サポート</t>
-        </is>
-      </c>
-      <c r="C10" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0008910</t>
-        </is>
-      </c>
-      <c r="D10" s="444" t="n"/>
-      <c r="E10" s="442" t="inlineStr">
-        <is>
-          <t>cbox012</t>
-        </is>
-      </c>
-      <c r="F10" s="515" t="n">
-        <v>240000</v>
-      </c>
-      <c r="G10" s="517" t="n">
-        <v>480000</v>
-      </c>
-      <c r="H10" s="442" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_スタンダード_保守・サポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="385" t="n"/>
-      <c r="B11" s="438" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_プレミアム_初期設定</t>
-        </is>
-      </c>
-      <c r="C11" s="439" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DL06-0008947	</t>
-        </is>
-      </c>
-      <c r="D11" s="444" t="n"/>
-      <c r="E11" s="438" t="inlineStr">
-        <is>
-          <t>cbox013</t>
-        </is>
-      </c>
-      <c r="F11" s="514" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G11" s="514" t="n">
-        <v>200000</v>
-      </c>
-      <c r="H11" s="438" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_プレミアム_初期設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="437" t="n"/>
-      <c r="B12" s="442" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_プレミアム_保守・サポート</t>
-        </is>
-      </c>
-      <c r="C12" s="443" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DL06-0008953	</t>
-        </is>
-      </c>
-      <c r="D12" s="444" t="n"/>
-      <c r="E12" s="442" t="inlineStr">
-        <is>
-          <t>cbox014</t>
-        </is>
-      </c>
-      <c r="F12" s="516" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G12" s="516" t="n">
-        <v>480000</v>
-      </c>
-      <c r="H12" s="442" t="inlineStr">
-        <is>
-          <t>目標管理クラウドcbox_プレミアム_保守・サポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="385" t="n"/>
-      <c r="B13" s="438" t="inlineStr">
-        <is>
-          <t>貿易クラウド_利用料</t>
-        </is>
-      </c>
-      <c r="C13" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0000792</t>
-        </is>
-      </c>
-      <c r="D13" s="448" t="n"/>
-      <c r="E13" s="438" t="inlineStr">
-        <is>
-          <t>貿易001</t>
-        </is>
-      </c>
-      <c r="F13" s="518" t="n"/>
-      <c r="G13" s="518" t="n"/>
-      <c r="H13" s="438" t="inlineStr">
-        <is>
-          <t>貿易クラウド_利用料</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="437" t="n"/>
-      <c r="B14" s="442" t="inlineStr">
-        <is>
-          <t>AI Works_利用料</t>
-        </is>
-      </c>
-      <c r="C14" s="443" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DL06-0001191	</t>
-        </is>
-      </c>
-      <c r="D14" s="444" t="n"/>
-      <c r="E14" s="442" t="inlineStr">
-        <is>
-          <t>AIWorks001</t>
-        </is>
-      </c>
-      <c r="F14" s="518" t="n"/>
-      <c r="G14" s="518" t="n"/>
-      <c r="H14" s="442" t="inlineStr">
-        <is>
-          <t>AI Works_利用料</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="437" t="n"/>
-      <c r="B15" s="438" t="inlineStr">
-        <is>
-          <t>AI Works_利用料_初期設定</t>
-        </is>
-      </c>
-      <c r="C15" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0008993</t>
-        </is>
-      </c>
-      <c r="D15" s="444" t="n"/>
-      <c r="E15" s="438" t="inlineStr">
-        <is>
-          <t>AIWorks002</t>
-        </is>
-      </c>
-      <c r="F15" s="518" t="n"/>
-      <c r="G15" s="518" t="n"/>
-      <c r="H15" s="438" t="inlineStr">
-        <is>
-          <t>AI Works_利用料_初期設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="437" t="n"/>
-      <c r="B16" s="442" t="inlineStr">
-        <is>
-          <t>AI Works_利用料_保守・サポート</t>
-        </is>
-      </c>
-      <c r="C16" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0009167</t>
-        </is>
-      </c>
-      <c r="D16" s="444" t="n"/>
-      <c r="E16" s="442" t="inlineStr">
-        <is>
-          <t>AIWorks003</t>
-        </is>
-      </c>
-      <c r="F16" s="518" t="n"/>
-      <c r="G16" s="518" t="n"/>
-      <c r="H16" s="442" t="inlineStr">
-        <is>
-          <t>AI Works_利用料_保守・サポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="437" t="n"/>
-      <c r="B17" s="438" t="inlineStr">
-        <is>
-          <t>AI Works_導入活用コンサルティング</t>
-        </is>
-      </c>
-      <c r="C17" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0009576</t>
-        </is>
-      </c>
-      <c r="D17" s="444" t="n"/>
-      <c r="E17" s="438" t="inlineStr">
-        <is>
-          <t>AIWorks004</t>
-        </is>
-      </c>
-      <c r="F17" s="518" t="n"/>
-      <c r="G17" s="518" t="n"/>
-      <c r="H17" s="438" t="inlineStr">
-        <is>
-          <t>AI Works_導入活用コンサルティング</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="437" t="n"/>
-      <c r="B18" s="442" t="inlineStr">
-        <is>
-          <t>LINE公式アカウント_ライトプラン</t>
-        </is>
-      </c>
-      <c r="C18" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0001270</t>
-        </is>
-      </c>
-      <c r="D18" s="448" t="n"/>
-      <c r="E18" s="442" t="inlineStr">
-        <is>
-          <t>LINE公式アカウント001</t>
-        </is>
-      </c>
-      <c r="F18" s="518" t="n"/>
-      <c r="G18" s="518" t="n"/>
-      <c r="H18" s="442" t="inlineStr">
-        <is>
-          <t>LINE公式アカウント_ライトプラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="437" t="n"/>
-      <c r="B19" s="438" t="inlineStr">
-        <is>
-          <t>LINE公式アカウント_スタンダードプラン</t>
-        </is>
-      </c>
-      <c r="C19" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0001831</t>
-        </is>
-      </c>
-      <c r="D19" s="444" t="n"/>
-      <c r="E19" s="438" t="inlineStr">
-        <is>
-          <t>LINE公式アカウント002</t>
-        </is>
-      </c>
-      <c r="F19" s="518" t="n"/>
-      <c r="G19" s="518" t="n"/>
-      <c r="H19" s="438" t="inlineStr">
-        <is>
-          <t>LINE公式アカウント_スタンダードプラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="437" t="n"/>
-      <c r="B20" s="442" t="inlineStr">
-        <is>
-          <t>Lステップ_スタートプラン</t>
-        </is>
-      </c>
-      <c r="C20" s="443" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DL06-0001835	</t>
-        </is>
-      </c>
-      <c r="D20" s="444" t="n"/>
-      <c r="E20" s="442" t="inlineStr">
-        <is>
-          <t>Lステップ001</t>
-        </is>
-      </c>
-      <c r="F20" s="518" t="n"/>
-      <c r="G20" s="518" t="n"/>
-      <c r="H20" s="442" t="inlineStr">
-        <is>
-          <t>Lステップ_スタートプラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="437" t="n"/>
-      <c r="B21" s="438" t="inlineStr">
-        <is>
-          <t>Lステップ_スタンダードプラン</t>
-        </is>
-      </c>
-      <c r="C21" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0001844</t>
-        </is>
-      </c>
-      <c r="D21" s="444" t="n"/>
-      <c r="E21" s="438" t="inlineStr">
-        <is>
-          <t>Lステップ002</t>
-        </is>
-      </c>
-      <c r="F21" s="518" t="n"/>
-      <c r="G21" s="518" t="n"/>
-      <c r="H21" s="438" t="inlineStr">
-        <is>
-          <t>Lステップ_スタンダードプラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="437" t="n"/>
-      <c r="B22" s="442" t="inlineStr">
-        <is>
-          <t>Lステップ_プロプラン</t>
-        </is>
-      </c>
-      <c r="C22" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0001845</t>
-        </is>
-      </c>
-      <c r="D22" s="444" t="n"/>
-      <c r="E22" s="442" t="inlineStr">
-        <is>
-          <t>Lステップ003</t>
-        </is>
-      </c>
-      <c r="F22" s="518" t="n"/>
-      <c r="G22" s="518" t="n"/>
-      <c r="H22" s="442" t="inlineStr">
-        <is>
-          <t>Lステップ_プロプラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="437" t="n"/>
-      <c r="B23" s="438" t="inlineStr">
-        <is>
-          <t>UTAGE_ライトプラン</t>
-        </is>
-      </c>
-      <c r="C23" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0002368</t>
-        </is>
-      </c>
-      <c r="D23" s="444" t="n"/>
-      <c r="E23" s="438" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	UTAGE001</t>
-        </is>
-      </c>
-      <c r="F23" s="518" t="n"/>
-      <c r="G23" s="518" t="n"/>
-      <c r="H23" s="438" t="inlineStr">
-        <is>
-          <t>UTAGE_ライトプラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="437" t="n"/>
-      <c r="B24" s="442" t="inlineStr">
-        <is>
-          <t>UTAGE_スタンダードプラン</t>
-        </is>
-      </c>
-      <c r="C24" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0002376</t>
-        </is>
-      </c>
-      <c r="D24" s="444" t="n"/>
-      <c r="E24" s="442" t="inlineStr">
-        <is>
-          <t>UTAGE002</t>
-        </is>
-      </c>
-      <c r="F24" s="518" t="n"/>
-      <c r="G24" s="518" t="n"/>
-      <c r="H24" s="442" t="inlineStr">
-        <is>
-          <t>UTAGE_スタンダードプラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="437" t="n"/>
-      <c r="B25" s="438" t="inlineStr">
-        <is>
-          <t>せきなび_スタンダード</t>
-        </is>
-      </c>
-      <c r="C25" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0002760</t>
-        </is>
-      </c>
-      <c r="D25" s="444" t="n"/>
-      <c r="E25" s="438" t="inlineStr">
-        <is>
-          <t>seknavi01</t>
-        </is>
-      </c>
-      <c r="F25" s="518" t="n"/>
-      <c r="G25" s="518" t="n"/>
-      <c r="H25" s="438" t="inlineStr">
-        <is>
-          <t>せきなび_スタンダード</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="437" t="n"/>
-      <c r="B26" s="442" t="inlineStr">
-        <is>
-          <t>CRS人材募集管理システム_ベーシック</t>
-        </is>
-      </c>
-      <c r="C26" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0003676</t>
-        </is>
-      </c>
-      <c r="D26" s="444" t="n"/>
-      <c r="E26" s="442" t="inlineStr">
-        <is>
-          <t>CRS001</t>
-        </is>
-      </c>
-      <c r="F26" s="518" t="n"/>
-      <c r="G26" s="518" t="n"/>
-      <c r="H26" s="442" t="inlineStr">
-        <is>
-          <t>CRS人材募集管理システム_ベーシック</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="385" t="n"/>
-      <c r="B27" s="438" t="inlineStr">
-        <is>
-          <t>CRS人材募集管理システム_ベーシック_初期導入</t>
-        </is>
-      </c>
-      <c r="C27" s="439" t="inlineStr">
-        <is>
-          <t>DL06-0015862-001</t>
-        </is>
-      </c>
-      <c r="D27" s="444" t="n"/>
-      <c r="E27" s="438" t="inlineStr">
-        <is>
-          <t>CRS003</t>
-        </is>
-      </c>
-      <c r="F27" s="518" t="n"/>
-      <c r="G27" s="518" t="n"/>
-      <c r="H27" s="438" t="inlineStr">
-        <is>
-          <t>CRS人材募集管理システム_ベーシック_初期導入</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="385" t="n"/>
-      <c r="B28" s="442" t="inlineStr">
-        <is>
-          <t>CRS人材募集管理システム_ベーシック_保守・サポート</t>
-        </is>
-      </c>
-      <c r="C28" s="443" t="inlineStr">
-        <is>
-          <t>DL06-0015867-001</t>
-        </is>
-      </c>
-      <c r="D28" s="444" t="n"/>
-      <c r="E28" s="442" t="inlineStr">
-        <is>
-          <t>CRS004</t>
-        </is>
-      </c>
-      <c r="F28" s="518" t="n"/>
-      <c r="G28" s="518" t="n"/>
-      <c r="H28" s="442" t="inlineStr">
-        <is>
-          <t>CRS人材募集管理システム_ベーシック_保守・サポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="385" t="n"/>
-      <c r="B29" s="450" t="n"/>
-      <c r="C29" s="450" t="n"/>
-      <c r="D29" s="450" t="n"/>
-      <c r="E29" s="450" t="n"/>
-      <c r="F29" s="519" t="n"/>
-      <c r="G29" s="519" t="n"/>
-      <c r="H29" s="450" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="385" t="n"/>
-      <c r="B30" s="450" t="n"/>
-      <c r="C30" s="448" t="n"/>
-      <c r="D30" s="448" t="n"/>
-      <c r="E30" s="448" t="n"/>
-      <c r="F30" s="519" t="n"/>
-      <c r="G30" s="519" t="n"/>
-      <c r="H30" s="450" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="385" t="n"/>
-      <c r="B31" s="450" t="n"/>
-      <c r="C31" s="448" t="n"/>
-      <c r="D31" s="448" t="n"/>
-      <c r="E31" s="450" t="n"/>
-      <c r="F31" s="519" t="n"/>
-      <c r="G31" s="519" t="n"/>
-      <c r="H31" s="450" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="385" t="n"/>
-      <c r="B32" s="385" t="n"/>
-      <c r="C32" s="385" t="n"/>
-      <c r="D32" s="385" t="n"/>
-      <c r="E32" s="385" t="n"/>
-      <c r="F32" s="520" t="n"/>
-      <c r="G32" s="520" t="n"/>
-      <c r="H32" s="385" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="385" t="n"/>
-      <c r="B33" s="385" t="n"/>
-      <c r="C33" s="385" t="n"/>
-      <c r="D33" s="385" t="n"/>
-      <c r="E33" s="385" t="n"/>
-      <c r="F33" s="520" t="n"/>
-      <c r="G33" s="520" t="n"/>
-      <c r="H33" s="385" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="385" t="n"/>
-      <c r="B34" s="385" t="n"/>
-      <c r="C34" s="385" t="n"/>
-      <c r="D34" s="385" t="n"/>
-      <c r="E34" s="385" t="n"/>
-      <c r="F34" s="520" t="n"/>
-      <c r="G34" s="520" t="n"/>
-      <c r="H34" s="385" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="385" t="n"/>
-      <c r="B35" s="385" t="n"/>
-      <c r="C35" s="385" t="n"/>
-      <c r="D35" s="385" t="n"/>
-      <c r="E35" s="385" t="n"/>
-      <c r="F35" s="520" t="n"/>
-      <c r="G35" s="520" t="n"/>
-      <c r="H35" s="385" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="385" t="n"/>
-      <c r="B36" s="385" t="n"/>
-      <c r="C36" s="385" t="n"/>
-      <c r="D36" s="385" t="n"/>
-      <c r="E36" s="385" t="n"/>
-      <c r="F36" s="520" t="n"/>
-      <c r="G36" s="520" t="n"/>
-      <c r="H36" s="385" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="385" t="n"/>
-      <c r="B37" s="385" t="n"/>
-      <c r="C37" s="385" t="n"/>
-      <c r="D37" s="385" t="n"/>
-      <c r="E37" s="385" t="n"/>
-      <c r="F37" s="520" t="n"/>
-      <c r="G37" s="520" t="n"/>
       <c r="H37" s="385" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="385" t="n"/>
-      <c r="B38" s="385" t="n"/>
-      <c r="C38" s="385" t="n"/>
-      <c r="D38" s="385" t="n"/>
-      <c r="E38" s="385" t="n"/>
-      <c r="F38" s="520" t="n"/>
-      <c r="G38" s="520" t="n"/>
+      <c r="A38" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B38" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa ラージ</t>
+        </is>
+      </c>
+      <c r="C38" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019031</t>
+        </is>
+      </c>
+      <c r="D38" s="440" t="n"/>
+      <c r="E38" s="438" t="inlineStr">
+        <is>
+          <t>visa_l</t>
+        </is>
+      </c>
+      <c r="F38" s="514" t="n">
+        <v>597600</v>
+      </c>
+      <c r="G38" s="514" t="n">
+        <v>597600</v>
+      </c>
       <c r="H38" s="385" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="385" t="n"/>
-      <c r="B39" s="385" t="n"/>
-      <c r="C39" s="385" t="n"/>
-      <c r="D39" s="385" t="n"/>
-      <c r="E39" s="385" t="n"/>
-      <c r="F39" s="520" t="n"/>
-      <c r="G39" s="520" t="n"/>
+      <c r="A39" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B39" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa スモール導入設定等</t>
+        </is>
+      </c>
+      <c r="C39" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019034</t>
+        </is>
+      </c>
+      <c r="D39" s="440" t="n"/>
+      <c r="E39" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_visa_s</t>
+        </is>
+      </c>
+      <c r="F39" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G39" s="514" t="n">
+        <v>150000</v>
+      </c>
       <c r="H39" s="385" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="385" t="n"/>
-      <c r="B40" s="385" t="n"/>
-      <c r="C40" s="385" t="n"/>
-      <c r="D40" s="385" t="n"/>
-      <c r="E40" s="385" t="n"/>
-      <c r="F40" s="520" t="n"/>
-      <c r="G40" s="520" t="n"/>
+      <c r="A40" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B40" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa ラージ導入設定等</t>
+        </is>
+      </c>
+      <c r="C40" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0020470</t>
+        </is>
+      </c>
+      <c r="D40" s="440" t="n"/>
+      <c r="E40" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_visa_l</t>
+        </is>
+      </c>
+      <c r="F40" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G40" s="514" t="n">
+        <v>150000</v>
+      </c>
       <c r="H40" s="385" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="385" t="n"/>
-      <c r="B41" s="385" t="n"/>
-      <c r="C41" s="385" t="n"/>
-      <c r="D41" s="385" t="n"/>
-      <c r="E41" s="385" t="n"/>
-      <c r="F41" s="520" t="n"/>
-      <c r="G41" s="520" t="n"/>
+      <c r="A41" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B41" s="438" t="inlineStr">
+        <is>
+          <t>irohana study ラージ</t>
+        </is>
+      </c>
+      <c r="C41" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0027397</t>
+        </is>
+      </c>
+      <c r="D41" s="440" t="n"/>
+      <c r="E41" s="438" t="inlineStr">
+        <is>
+          <t>study_l</t>
+        </is>
+      </c>
+      <c r="F41" s="514" t="n">
+        <v>657600</v>
+      </c>
+      <c r="G41" s="514" t="n">
+        <v>777600</v>
+      </c>
       <c r="H41" s="385" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="385" t="n"/>
-      <c r="B42" s="385" t="n"/>
-      <c r="C42" s="385" t="n"/>
-      <c r="D42" s="385" t="n"/>
-      <c r="E42" s="385" t="n"/>
-      <c r="F42" s="520" t="n"/>
-      <c r="G42" s="520" t="n"/>
+      <c r="A42" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B42" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa スタンダード導入設定等</t>
+        </is>
+      </c>
+      <c r="C42" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0020466</t>
+        </is>
+      </c>
+      <c r="D42" s="440" t="n"/>
+      <c r="E42" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_visa_m</t>
+        </is>
+      </c>
+      <c r="F42" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G42" s="514" t="n">
+        <v>150000</v>
+      </c>
       <c r="H42" s="385" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="385" t="n"/>
-      <c r="B43" s="385" t="n"/>
-      <c r="C43" s="385" t="n"/>
-      <c r="D43" s="385" t="n"/>
-      <c r="E43" s="385" t="n"/>
-      <c r="F43" s="520" t="n"/>
-      <c r="G43" s="520" t="n"/>
+      <c r="A43" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B43" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa スタンダード</t>
+        </is>
+      </c>
+      <c r="C43" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019029</t>
+        </is>
+      </c>
+      <c r="D43" s="440" t="n"/>
+      <c r="E43" s="438" t="inlineStr">
+        <is>
+          <t>visa_m</t>
+        </is>
+      </c>
+      <c r="F43" s="514" t="n">
+        <v>477600</v>
+      </c>
+      <c r="G43" s="514" t="n">
+        <v>477600</v>
+      </c>
       <c r="H43" s="385" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="385" t="n"/>
-      <c r="B44" s="385" t="n"/>
-      <c r="C44" s="385" t="n"/>
-      <c r="D44" s="385" t="n"/>
-      <c r="E44" s="385" t="n"/>
-      <c r="F44" s="520" t="n"/>
-      <c r="G44" s="520" t="n"/>
+      <c r="A44" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B44" s="438" t="inlineStr">
+        <is>
+          <t>irohana study スタンダード導入設定等</t>
+        </is>
+      </c>
+      <c r="C44" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0028061</t>
+        </is>
+      </c>
+      <c r="D44" s="440" t="n"/>
+      <c r="E44" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_study_m</t>
+        </is>
+      </c>
+      <c r="F44" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G44" s="514" t="n">
+        <v>150000</v>
+      </c>
       <c r="H44" s="385" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="385" t="n"/>
-      <c r="B45" s="385" t="n"/>
-      <c r="C45" s="385" t="n"/>
-      <c r="D45" s="385" t="n"/>
-      <c r="E45" s="385" t="n"/>
-      <c r="F45" s="520" t="n"/>
-      <c r="G45" s="520" t="n"/>
+      <c r="A45" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B45" s="438" t="inlineStr">
+        <is>
+          <t>irohana study スモール導入設定等</t>
+        </is>
+      </c>
+      <c r="C45" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0028059</t>
+        </is>
+      </c>
+      <c r="D45" s="440" t="n"/>
+      <c r="E45" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_study_s</t>
+        </is>
+      </c>
+      <c r="F45" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G45" s="514" t="n">
+        <v>150000</v>
+      </c>
       <c r="H45" s="385" t="n"/>
     </row>
     <row r="46">

--- a/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
+++ b/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
@@ -36708,31 +36708,31 @@
     <dataValidation sqref="C61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"scale,クラフトバンクオフィス"</formula1>
     </dataValidation>
-    <dataValidation sqref="C108" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C117" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"くるみん認定,プラチナくるみん認定, トライくるみん認定 ,認定なし"</formula1>
     </dataValidation>
     <dataValidation sqref="C64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>'プルダウン用'!$A$2:$A$13</formula1>
     </dataValidation>
-    <dataValidation sqref="C103" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C112" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"あり,なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="C109 C121" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C118 C130" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"実施している,実施していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="C128" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C137" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>'プルダウン用'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="C107" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C116" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"えるぼし認定,プラチナえるぼし,認定なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="C189" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C198" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>'プルダウン用'!$B$2:$B$48</formula1>
     </dataValidation>
-    <dataValidation sqref="C48 C201" showDropDown="1" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="custom">
+    <dataValidation sqref="C48 C210" showDropDown="1" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="custom">
       <formula1>OR(NOT(ISERROR(DATEVALUE(C48))), AND(ISNUMBER(C48), LEFT(CELL("format", C48))="D"))</formula1>
     </dataValidation>
-    <dataValidation sqref="C199 C208" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C208 C217" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"賃上げを行わない,＋30円,＋50円"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">

--- a/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
+++ b/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
@@ -20478,7 +20478,7 @@
       <c r="E1" s="73" t="n"/>
       <c r="F1" s="69" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" s="477">
       <c r="A2" s="69" t="n"/>
       <c r="B2" s="72" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
       <c r="E2" s="73" t="n"/>
       <c r="F2" s="69" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" s="477">
       <c r="A3" s="69" t="n"/>
       <c r="B3" s="72" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
       <c r="E3" s="73" t="n"/>
       <c r="F3" s="69" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" s="477">
       <c r="A4" s="69" t="n"/>
       <c r="B4" s="72" t="n"/>
       <c r="C4" s="73" t="n"/>
@@ -20510,7 +20510,7 @@
       <c r="E4" s="73" t="n"/>
       <c r="F4" s="69" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" s="477">
       <c r="A5" s="94" t="n"/>
       <c r="B5" s="478" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
       <c r="Y26" s="462" t="n"/>
       <c r="Z26" s="462" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" s="477">
       <c r="A27" s="69" t="n"/>
       <c r="B27" s="124" t="n"/>
       <c r="C27" s="113" t="n"/>
@@ -21365,7 +21365,7 @@
       <c r="Y29" s="462" t="n"/>
       <c r="Z29" s="462" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" s="477">
       <c r="A30" s="69" t="n"/>
       <c r="B30" s="124" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
       <c r="Y31" s="462" t="n"/>
       <c r="Z31" s="462" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" s="477">
       <c r="A32" s="125" t="n"/>
       <c r="B32" s="496" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
       <c r="Y33" s="462" t="n"/>
       <c r="Z33" s="462" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" s="477">
       <c r="A34" s="129" t="n"/>
       <c r="B34" s="130" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
       <c r="Y34" s="135" t="n"/>
       <c r="Z34" s="135" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" s="477">
       <c r="A35" s="69" t="n"/>
       <c r="B35" s="265" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
       <c r="E37" s="73" t="n"/>
       <c r="F37" s="69" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" s="477">
       <c r="A38" s="69" t="n"/>
       <c r="B38" s="122" t="n"/>
       <c r="C38" s="73" t="n"/>
@@ -21616,7 +21616,7 @@
       <c r="Y38" s="462" t="n"/>
       <c r="Z38" s="462" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" s="477">
       <c r="A39" s="69" t="n"/>
       <c r="B39" s="497" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
       <c r="Y40" s="462" t="n"/>
       <c r="Z40" s="462" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" s="477">
       <c r="A41" s="69" t="n"/>
       <c r="B41" s="144" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
       <c r="Y41" s="462" t="n"/>
       <c r="Z41" s="462" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" s="477">
       <c r="A42" s="69" t="n"/>
       <c r="B42" s="150" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
       <c r="Y42" s="462" t="n"/>
       <c r="Z42" s="462" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" s="477">
       <c r="A43" s="69" t="n"/>
       <c r="B43" s="150" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
       <c r="Y43" s="462" t="n"/>
       <c r="Z43" s="462" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" s="477">
       <c r="A44" s="69" t="n"/>
       <c r="B44" s="150" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
       <c r="Y44" s="462" t="n"/>
       <c r="Z44" s="462" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" s="477">
       <c r="A45" s="69" t="n"/>
       <c r="B45" s="162" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
       <c r="Y45" s="462" t="n"/>
       <c r="Z45" s="462" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" s="477">
       <c r="A46" s="69" t="n"/>
       <c r="B46" s="155" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
       <c r="Y46" s="462" t="n"/>
       <c r="Z46" s="462" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" s="477">
       <c r="A47" s="69" t="n"/>
       <c r="B47" s="158" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
       <c r="Y47" s="462" t="n"/>
       <c r="Z47" s="462" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" s="477">
       <c r="A48" s="69" t="n"/>
       <c r="B48" s="162" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
       <c r="Y48" s="462" t="n"/>
       <c r="Z48" s="462" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" s="477">
       <c r="A49" s="69" t="n"/>
       <c r="B49" s="162" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
       <c r="Y49" s="462" t="n"/>
       <c r="Z49" s="462" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" s="477">
       <c r="A50" s="69" t="n"/>
       <c r="B50" s="230" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
       <c r="Y50" s="462" t="n"/>
       <c r="Z50" s="462" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" s="477">
       <c r="A51" s="69" t="n"/>
       <c r="B51" s="230" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
       <c r="Y51" s="462" t="n"/>
       <c r="Z51" s="462" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" s="477">
       <c r="A52" s="125" t="n"/>
       <c r="B52" s="167" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       <c r="Y62" s="462" t="n"/>
       <c r="Z62" s="462" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" s="477">
       <c r="A63" s="69" t="n"/>
       <c r="B63" s="176" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
       <c r="Y63" s="462" t="n"/>
       <c r="Z63" s="462" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" s="477">
       <c r="A64" s="69" t="n"/>
       <c r="B64" s="162" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
       <c r="Y64" s="462" t="n"/>
       <c r="Z64" s="462" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" s="477">
       <c r="A65" s="462" t="n"/>
       <c r="B65" s="182" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
       <c r="Y65" s="462" t="n"/>
       <c r="Z65" s="462" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" s="477">
       <c r="A66" s="69" t="n"/>
       <c r="B66" s="230" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
       <c r="Y66" s="462" t="n"/>
       <c r="Z66" s="462" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" s="477">
       <c r="A67" s="69" t="n"/>
       <c r="B67" s="230" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
       <c r="Y67" s="462" t="n"/>
       <c r="Z67" s="462" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" s="477">
       <c r="A68" s="125" t="n"/>
       <c r="B68" s="187" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
       <c r="Y68" s="169" t="n"/>
       <c r="Z68" s="169" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" s="477">
       <c r="A69" s="69" t="n"/>
       <c r="B69" s="230" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
       <c r="Y69" s="462" t="n"/>
       <c r="Z69" s="462" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" s="477">
       <c r="A70" s="69" t="n"/>
       <c r="B70" s="230" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
       <c r="Y70" s="462" t="n"/>
       <c r="Z70" s="462" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" s="477">
       <c r="A71" s="69" t="n"/>
       <c r="B71" s="162" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
       <c r="Y71" s="462" t="n"/>
       <c r="Z71" s="462" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" s="477">
       <c r="A72" s="69" t="n"/>
       <c r="B72" s="162" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
       <c r="Y72" s="462" t="n"/>
       <c r="Z72" s="462" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" s="477">
       <c r="A73" s="69" t="n"/>
       <c r="B73" s="192" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
       <c r="Y73" s="462" t="n"/>
       <c r="Z73" s="462" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" s="477">
       <c r="A74" s="69" t="n"/>
       <c r="B74" s="192" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
       <c r="Y74" s="462" t="n"/>
       <c r="Z74" s="462" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" s="477">
       <c r="A75" s="69" t="n"/>
       <c r="B75" s="192" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
       <c r="Y75" s="462" t="n"/>
       <c r="Z75" s="462" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" s="477">
       <c r="A76" s="123" t="n"/>
       <c r="B76" s="194" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
       <c r="Y76" s="462" t="n"/>
       <c r="Z76" s="462" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" s="477">
       <c r="A77" s="197" t="n"/>
       <c r="B77" s="498" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
       <c r="Y77" s="462" t="n"/>
       <c r="Z77" s="462" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" s="477">
       <c r="A78" s="200" t="n"/>
       <c r="B78" s="498" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
       <c r="Y78" s="462" t="n"/>
       <c r="Z78" s="462" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" s="477">
       <c r="A79" s="69" t="n"/>
       <c r="B79" s="498" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
       <c r="Y79" s="462" t="n"/>
       <c r="Z79" s="462" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" s="477">
       <c r="A80" s="69" t="n"/>
       <c r="B80" s="162" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
       <c r="Y80" s="462" t="n"/>
       <c r="Z80" s="462" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" s="477">
       <c r="A81" s="69" t="n"/>
       <c r="B81" s="162" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
       <c r="Y81" s="462" t="n"/>
       <c r="Z81" s="462" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" s="477">
       <c r="A82" s="69" t="n"/>
       <c r="B82" s="162" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
       <c r="Y82" s="462" t="n"/>
       <c r="Z82" s="462" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" s="477">
       <c r="A83" s="69" t="n"/>
       <c r="B83" s="498" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
       <c r="Y83" s="462" t="n"/>
       <c r="Z83" s="462" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" s="477">
       <c r="A84" s="69" t="n"/>
       <c r="B84" s="498" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
       <c r="Y84" s="462" t="n"/>
       <c r="Z84" s="462" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" s="477">
       <c r="A85" s="69" t="n"/>
       <c r="B85" s="498" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
       <c r="Y85" s="462" t="n"/>
       <c r="Z85" s="462" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" s="477">
       <c r="A86" s="69" t="n"/>
       <c r="B86" s="162" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
       <c r="Y86" s="462" t="n"/>
       <c r="Z86" s="462" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" s="477">
       <c r="A87" s="69" t="n"/>
       <c r="B87" s="162" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
       <c r="Y87" s="462" t="n"/>
       <c r="Z87" s="462" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" s="477">
       <c r="A88" s="69" t="n"/>
       <c r="B88" s="162" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
       <c r="Y88" s="462" t="n"/>
       <c r="Z88" s="462" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" s="477">
       <c r="A89" s="69" t="n"/>
       <c r="B89" s="498" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
       <c r="Y89" s="462" t="n"/>
       <c r="Z89" s="462" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" s="477">
       <c r="A90" s="69" t="n"/>
       <c r="B90" s="498" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
       <c r="Y90" s="462" t="n"/>
       <c r="Z90" s="462" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" s="477">
       <c r="A91" s="69" t="n"/>
       <c r="B91" s="498" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
       <c r="Y91" s="462" t="n"/>
       <c r="Z91" s="462" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" s="477">
       <c r="A92" s="69" t="n"/>
       <c r="B92" s="162" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       <c r="Y92" s="462" t="n"/>
       <c r="Z92" s="462" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" s="477">
       <c r="A93" s="69" t="n"/>
       <c r="B93" s="162" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
       <c r="Y93" s="462" t="n"/>
       <c r="Z93" s="462" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" s="477">
       <c r="A94" s="69" t="n"/>
       <c r="B94" s="162" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
       <c r="Y94" s="462" t="n"/>
       <c r="Z94" s="462" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" s="477">
       <c r="A95" s="69" t="n"/>
       <c r="B95" s="498" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
       <c r="Y95" s="462" t="n"/>
       <c r="Z95" s="462" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" s="477">
       <c r="A96" s="69" t="n"/>
       <c r="B96" s="498" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
       <c r="Y96" s="462" t="n"/>
       <c r="Z96" s="462" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" s="477">
       <c r="A97" s="69" t="n"/>
       <c r="B97" s="498" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
       <c r="Y97" s="462" t="n"/>
       <c r="Z97" s="462" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" s="477">
       <c r="A98" s="69" t="n"/>
       <c r="B98" s="498" t="inlineStr">
         <is>
@@ -23691,21 +23691,21 @@
       <c r="C98" s="499" t="n"/>
       <c r="D98" s="203" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" s="477">
       <c r="B99" s="0" t="inlineStr">
         <is>
           <t>役員（8）氏名</t>
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" s="477">
       <c r="B100" s="0" t="inlineStr">
         <is>
           <t>役員（8）氏名フリガナ</t>
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" s="477">
       <c r="A101" s="69" t="n"/>
       <c r="B101" s="498" t="inlineStr">
         <is>
@@ -23715,14 +23715,14 @@
       <c r="C101" s="499" t="n"/>
       <c r="D101" s="203" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" s="477">
       <c r="B102" s="0" t="inlineStr">
         <is>
           <t>役員（9）氏名</t>
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" s="477">
       <c r="B103" s="0" t="inlineStr">
         <is>
           <t>役員（9）氏名フリガナ</t>
@@ -23753,7 +23753,7 @@
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" s="477">
       <c r="A107" s="69" t="n"/>
       <c r="B107" s="230" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
       <c r="Y107" s="462" t="n"/>
       <c r="Z107" s="462" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" s="477">
       <c r="A108" s="69" t="n"/>
       <c r="B108" s="230" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
       <c r="Y108" s="462" t="n"/>
       <c r="Z108" s="462" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" s="477">
       <c r="A109" s="69" t="n"/>
       <c r="B109" s="230" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
       <c r="Y109" s="462" t="n"/>
       <c r="Z109" s="462" t="n"/>
     </row>
-    <row r="110" ht="9" customHeight="1" s="477">
+    <row r="110" s="477">
       <c r="A110" s="69" t="n"/>
       <c r="B110" s="230" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
       <c r="Y110" s="462" t="n"/>
       <c r="Z110" s="462" t="n"/>
     </row>
-    <row r="111" ht="25.5" customHeight="1" s="477">
+    <row r="111" s="477">
       <c r="A111" s="69" t="n"/>
       <c r="B111" s="230" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
       <c r="Y111" s="462" t="n"/>
       <c r="Z111" s="462" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" s="477">
       <c r="A112" s="69" t="n"/>
       <c r="B112" s="162" t="inlineStr">
         <is>
@@ -23988,16 +23988,17 @@
       <c r="Y112" s="462" t="n"/>
       <c r="Z112" s="462" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" s="477">
       <c r="A113" s="69" t="n"/>
       <c r="B113" s="209" t="inlineStr">
         <is>
           <t>申請年度</t>
         </is>
       </c>
-      <c r="C113" s="482" t="n"/>
-      <c r="D113" s="482" t="n"/>
-      <c r="E113" s="510" t="n"/>
+      <c r="C113" s="0">
+        <f>'転記'!B50</f>
+        <v/>
+      </c>
       <c r="F113" s="140" t="n"/>
       <c r="G113" s="462" t="n"/>
       <c r="H113" s="462" t="n"/>
@@ -24020,7 +24021,7 @@
       <c r="Y113" s="462" t="n"/>
       <c r="Z113" s="462" t="n"/>
     </row>
-    <row r="114" ht="6" customHeight="1" s="477">
+    <row r="114" s="477">
       <c r="A114" s="69" t="n"/>
       <c r="B114" s="212" t="inlineStr">
         <is>
@@ -24055,7 +24056,7 @@
       <c r="Y114" s="462" t="n"/>
       <c r="Z114" s="462" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" s="477">
       <c r="A115" s="69" t="n"/>
       <c r="B115" s="212" t="inlineStr">
         <is>
@@ -24090,7 +24091,7 @@
       <c r="Y115" s="462" t="n"/>
       <c r="Z115" s="462" t="n"/>
     </row>
-    <row r="116" ht="9" customHeight="1" s="477">
+    <row r="116" s="477">
       <c r="A116" s="69" t="n"/>
       <c r="B116" s="162" t="inlineStr">
         <is>
@@ -24126,7 +24127,7 @@
       <c r="Y116" s="462" t="n"/>
       <c r="Z116" s="462" t="n"/>
     </row>
-    <row r="117" ht="25.5" customHeight="1" s="477">
+    <row r="117" s="477">
       <c r="A117" s="69" t="n"/>
       <c r="B117" s="214" t="inlineStr">
         <is>
@@ -24162,7 +24163,7 @@
       <c r="Y117" s="462" t="n"/>
       <c r="Z117" s="462" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" s="477">
       <c r="A118" s="200" t="n"/>
       <c r="B118" s="162" t="inlineStr">
         <is>
@@ -24194,12 +24195,12 @@
       <c r="Y118" s="462" t="n"/>
       <c r="Z118" s="462" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" ht="9" customHeight="1" s="477">
       <c r="A119" s="69" t="n"/>
       <c r="B119" s="124" t="n"/>
       <c r="F119" s="69" t="n"/>
     </row>
-    <row r="120" ht="6" customHeight="1" s="477">
+    <row r="120" ht="25.5" customHeight="1" s="477">
       <c r="A120" s="69" t="n"/>
       <c r="B120" s="141" t="inlineStr">
         <is>
@@ -24215,7 +24216,7 @@
       <c r="E120" s="73" t="n"/>
       <c r="F120" s="69" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" s="477">
       <c r="A121" s="69" t="n"/>
       <c r="B121" s="72" t="n"/>
       <c r="C121" s="73" t="n"/>
@@ -24243,7 +24244,7 @@
       <c r="Y121" s="462" t="n"/>
       <c r="Z121" s="462" t="n"/>
     </row>
-    <row r="122" ht="28.5" customHeight="1" s="477">
+    <row r="122" s="477">
       <c r="A122" s="69" t="n"/>
       <c r="B122" s="497" t="inlineStr">
         <is>
@@ -24272,7 +24273,7 @@
       <c r="Y122" s="462" t="n"/>
       <c r="Z122" s="462" t="n"/>
     </row>
-    <row r="123" ht="9" customHeight="1" s="477">
+    <row r="123" ht="6" customHeight="1" s="477">
       <c r="A123" s="69" t="n"/>
       <c r="B123" s="72" t="n"/>
       <c r="C123" s="73" t="n"/>
@@ -24300,7 +24301,7 @@
       <c r="Y123" s="462" t="n"/>
       <c r="Z123" s="462" t="n"/>
     </row>
-    <row r="124" ht="25.5" customHeight="1" s="477">
+    <row r="124" s="477">
       <c r="A124" s="69" t="n"/>
       <c r="B124" s="230" t="inlineStr">
         <is>
@@ -24340,7 +24341,7 @@
       <c r="Y124" s="462" t="n"/>
       <c r="Z124" s="462" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="9" customHeight="1" s="477">
       <c r="A125" s="69" t="n"/>
       <c r="B125" s="72" t="n"/>
       <c r="C125" s="73" t="n"/>
@@ -24348,16 +24349,21 @@
       <c r="E125" s="73" t="n"/>
       <c r="F125" s="69" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="25.5" customHeight="1" s="477">
       <c r="A126" s="69" t="n"/>
       <c r="B126" s="521" t="inlineStr">
         <is>
           <t>『  次へ  』</t>
         </is>
       </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>をクリック</t>
+        </is>
+      </c>
       <c r="F126" s="69" t="n"/>
     </row>
-    <row r="127" ht="6" customHeight="1" s="477">
+    <row r="127" s="477">
       <c r="A127" s="69" t="n"/>
       <c r="B127" s="72" t="n"/>
       <c r="C127" s="73" t="n"/>
@@ -24385,7 +24391,7 @@
       <c r="Y127" s="462" t="n"/>
       <c r="Z127" s="462" t="n"/>
     </row>
-    <row r="128">
+    <row r="128" s="477">
       <c r="A128" s="69" t="n"/>
       <c r="B128" s="497" t="inlineStr">
         <is>
@@ -24414,7 +24420,7 @@
       <c r="Y128" s="462" t="n"/>
       <c r="Z128" s="462" t="n"/>
     </row>
-    <row r="129" ht="9" customHeight="1" s="477">
+    <row r="129" ht="6" customHeight="1" s="477">
       <c r="A129" s="69" t="n"/>
       <c r="B129" s="72" t="n"/>
       <c r="C129" s="73" t="n"/>
@@ -24442,7 +24448,7 @@
       <c r="Y129" s="462" t="n"/>
       <c r="Z129" s="462" t="n"/>
     </row>
-    <row r="130" ht="25.5" customHeight="1" s="477">
+    <row r="130" s="477">
       <c r="A130" s="69" t="n"/>
       <c r="B130" s="218" t="inlineStr">
         <is>
@@ -24475,7 +24481,7 @@
       <c r="Y130" s="462" t="n"/>
       <c r="Z130" s="462" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" ht="28.5" customHeight="1" s="477">
       <c r="A131" s="221" t="n"/>
       <c r="B131" s="222" t="inlineStr">
         <is>
@@ -24516,12 +24522,12 @@
       <c r="Y131" s="462" t="n"/>
       <c r="Z131" s="462" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" ht="9" customHeight="1" s="477">
       <c r="A132" s="69" t="n"/>
       <c r="B132" s="72" t="n"/>
       <c r="F132" s="69" t="n"/>
     </row>
-    <row r="133" ht="6" customHeight="1" s="477">
+    <row r="133" ht="25.5" customHeight="1" s="477">
       <c r="A133" s="69" t="n"/>
       <c r="B133" s="141" t="inlineStr">
         <is>
@@ -24537,7 +24543,7 @@
       <c r="E133" s="73" t="n"/>
       <c r="F133" s="69" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" s="477">
       <c r="A134" s="69" t="n"/>
       <c r="B134" s="72" t="n"/>
       <c r="C134" s="73" t="n"/>
@@ -24565,7 +24571,7 @@
       <c r="Y134" s="462" t="n"/>
       <c r="Z134" s="462" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" s="477">
       <c r="A135" s="69" t="n"/>
       <c r="B135" s="497" t="inlineStr">
         <is>
@@ -24594,7 +24600,7 @@
       <c r="Y135" s="462" t="n"/>
       <c r="Z135" s="462" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" ht="6" customHeight="1" s="477">
       <c r="A136" s="69" t="n"/>
       <c r="B136" s="72" t="n"/>
       <c r="C136" s="73" t="n"/>
@@ -24622,7 +24628,7 @@
       <c r="Y136" s="462" t="n"/>
       <c r="Z136" s="462" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" s="477">
       <c r="A137" s="69" t="n"/>
       <c r="B137" s="162" t="inlineStr">
         <is>
@@ -24658,7 +24664,7 @@
       <c r="Y137" s="462" t="n"/>
       <c r="Z137" s="462" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" ht="9" customHeight="1" s="477">
       <c r="A138" s="69" t="n"/>
       <c r="B138" s="72" t="n"/>
       <c r="C138" s="73" t="n"/>
@@ -24666,7 +24672,7 @@
       <c r="E138" s="73" t="n"/>
       <c r="F138" s="69" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" ht="25.5" customHeight="1" s="477">
       <c r="A139" s="69" t="n"/>
       <c r="B139" s="141" t="inlineStr">
         <is>
@@ -24682,7 +24688,7 @@
       <c r="E139" s="73" t="n"/>
       <c r="F139" s="69" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" s="477">
       <c r="A140" s="69" t="n"/>
       <c r="B140" s="72" t="n"/>
       <c r="C140" s="73" t="n"/>
@@ -24710,7 +24716,7 @@
       <c r="Y140" s="462" t="n"/>
       <c r="Z140" s="462" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" s="477">
       <c r="A141" s="69" t="n"/>
       <c r="B141" s="497" t="inlineStr">
         <is>
@@ -24740,7 +24746,7 @@
       <c r="Y141" s="462" t="n"/>
       <c r="Z141" s="462" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" ht="6" customHeight="1" s="477">
       <c r="A142" s="69" t="n"/>
       <c r="B142" s="72" t="n"/>
       <c r="C142" s="73" t="n"/>
@@ -24768,7 +24774,7 @@
       <c r="Y142" s="462" t="n"/>
       <c r="Z142" s="462" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" s="477">
       <c r="A143" s="69" t="n"/>
       <c r="B143" s="230" t="inlineStr">
         <is>
@@ -24803,7 +24809,7 @@
       <c r="Y143" s="462" t="n"/>
       <c r="Z143" s="462" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" s="477">
       <c r="A144" s="69" t="n"/>
       <c r="B144" s="230" t="inlineStr">
         <is>
@@ -24838,7 +24844,7 @@
       <c r="Y144" s="462" t="n"/>
       <c r="Z144" s="462" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" s="477">
       <c r="A145" s="69" t="n"/>
       <c r="B145" s="230" t="inlineStr">
         <is>
@@ -24873,7 +24879,7 @@
       <c r="Y145" s="462" t="n"/>
       <c r="Z145" s="462" t="n"/>
     </row>
-    <row r="146" ht="9" customHeight="1" s="477">
+    <row r="146" s="477">
       <c r="A146" s="69" t="n"/>
       <c r="B146" s="162" t="inlineStr">
         <is>
@@ -24909,7 +24915,7 @@
       <c r="Y146" s="462" t="n"/>
       <c r="Z146" s="462" t="n"/>
     </row>
-    <row r="147" ht="25.5" customHeight="1" s="477">
+    <row r="147" s="477">
       <c r="A147" s="69" t="n"/>
       <c r="B147" s="230" t="inlineStr">
         <is>
@@ -24950,7 +24956,7 @@
       <c r="Y147" s="462" t="n"/>
       <c r="Z147" s="462" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" s="477">
       <c r="A148" s="69" t="n"/>
       <c r="B148" s="230" t="inlineStr">
         <is>
@@ -24989,7 +24995,7 @@
       <c r="Y148" s="462" t="n"/>
       <c r="Z148" s="462" t="n"/>
     </row>
-    <row r="149">
+    <row r="149" s="477">
       <c r="A149" s="69" t="n"/>
       <c r="B149" s="230" t="inlineStr">
         <is>
@@ -25024,7 +25030,7 @@
       <c r="Y149" s="462" t="n"/>
       <c r="Z149" s="462" t="n"/>
     </row>
-    <row r="150" ht="6" customHeight="1" s="477">
+    <row r="150" s="477">
       <c r="A150" s="69" t="n"/>
       <c r="B150" s="230" t="inlineStr">
         <is>
@@ -25059,7 +25065,7 @@
       <c r="Y150" s="462" t="n"/>
       <c r="Z150" s="462" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" s="477">
       <c r="A151" s="69" t="n"/>
       <c r="B151" s="230" t="inlineStr">
         <is>
@@ -25094,7 +25100,7 @@
       <c r="Y151" s="462" t="n"/>
       <c r="Z151" s="462" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" s="477">
       <c r="A152" s="69" t="n"/>
       <c r="B152" s="230" t="inlineStr">
         <is>
@@ -25129,7 +25135,7 @@
       <c r="Y152" s="462" t="n"/>
       <c r="Z152" s="462" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" s="477">
       <c r="A153" s="69" t="n"/>
       <c r="B153" s="230" t="inlineStr">
         <is>
@@ -25164,7 +25170,7 @@
       <c r="Y153" s="462" t="n"/>
       <c r="Z153" s="462" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" s="477">
       <c r="A154" s="69" t="n"/>
       <c r="B154" s="230" t="inlineStr">
         <is>
@@ -25199,7 +25205,7 @@
       <c r="Y154" s="462" t="n"/>
       <c r="Z154" s="462" t="n"/>
     </row>
-    <row r="155">
+    <row r="155" ht="9" customHeight="1" s="477">
       <c r="A155" s="69" t="n"/>
       <c r="B155" s="72" t="n"/>
       <c r="C155" s="73" t="n"/>
@@ -25207,7 +25213,7 @@
       <c r="E155" s="73" t="n"/>
       <c r="F155" s="69" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" ht="25.5" customHeight="1" s="477">
       <c r="A156" s="69" t="n"/>
       <c r="B156" s="141" t="inlineStr">
         <is>
@@ -25223,7 +25229,7 @@
       <c r="E156" s="73" t="n"/>
       <c r="F156" s="69" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" s="477">
       <c r="A157" s="69" t="n"/>
       <c r="B157" s="72" t="n"/>
       <c r="C157" s="73" t="n"/>
@@ -25251,7 +25257,7 @@
       <c r="Y157" s="462" t="n"/>
       <c r="Z157" s="462" t="n"/>
     </row>
-    <row r="158" ht="9" customHeight="1" s="477">
+    <row r="158" s="477">
       <c r="A158" s="69" t="n"/>
       <c r="B158" s="497" t="inlineStr">
         <is>
@@ -25280,7 +25286,7 @@
       <c r="Y158" s="462" t="n"/>
       <c r="Z158" s="462" t="n"/>
     </row>
-    <row r="159" ht="25.5" customHeight="1" s="477">
+    <row r="159" ht="6" customHeight="1" s="477">
       <c r="A159" s="69" t="n"/>
       <c r="B159" s="72" t="n"/>
       <c r="C159" s="73" t="n"/>
@@ -25308,7 +25314,7 @@
       <c r="Y159" s="462" t="n"/>
       <c r="Z159" s="462" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" s="477">
       <c r="A160" s="69" t="n"/>
       <c r="B160" s="162" t="inlineStr">
         <is>
@@ -25352,7 +25358,7 @@
       <c r="Y160" s="462" t="n"/>
       <c r="Z160" s="462" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" s="477">
       <c r="A161" s="69" t="n"/>
       <c r="B161" s="162" t="inlineStr">
         <is>
@@ -25384,7 +25390,7 @@
       <c r="Y161" s="462" t="n"/>
       <c r="Z161" s="462" t="n"/>
     </row>
-    <row r="162" ht="6" customHeight="1" s="477">
+    <row r="162" s="477">
       <c r="A162" s="69" t="n"/>
       <c r="B162" s="162" t="inlineStr">
         <is>
@@ -25434,7 +25440,7 @@
       <c r="Y162" s="462" t="n"/>
       <c r="Z162" s="462" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" s="477">
       <c r="A163" s="69" t="n"/>
       <c r="B163" s="240" t="inlineStr">
         <is>
@@ -25477,7 +25483,7 @@
       <c r="Y163" s="462" t="n"/>
       <c r="Z163" s="462" t="n"/>
     </row>
-    <row r="164" ht="6" customHeight="1" s="477">
+    <row r="164" s="477">
       <c r="A164" s="69" t="n"/>
       <c r="B164" s="240" t="inlineStr">
         <is>
@@ -25527,7 +25533,7 @@
       <c r="Y164" s="462" t="n"/>
       <c r="Z164" s="462" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" s="477">
       <c r="A165" s="69" t="n"/>
       <c r="B165" s="240" t="inlineStr">
         <is>
@@ -25576,7 +25582,7 @@
       <c r="Y165" s="462" t="n"/>
       <c r="Z165" s="462" t="n"/>
     </row>
-    <row r="166" ht="6" customHeight="1" s="477">
+    <row r="166" s="477">
       <c r="A166" s="69" t="n"/>
       <c r="B166" s="246" t="inlineStr">
         <is>
@@ -25608,7 +25614,7 @@
       <c r="Y166" s="462" t="n"/>
       <c r="Z166" s="462" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" ht="9" customHeight="1" s="477">
       <c r="A167" s="69" t="n"/>
       <c r="B167" s="72" t="n"/>
       <c r="C167" s="73" t="n"/>
@@ -25616,7 +25622,7 @@
       <c r="E167" s="73" t="n"/>
       <c r="F167" s="69" t="n"/>
     </row>
-    <row r="168" ht="6" customHeight="1" s="477">
+    <row r="168" ht="25.5" customHeight="1" s="477">
       <c r="A168" s="69" t="n"/>
       <c r="B168" s="141" t="inlineStr">
         <is>
@@ -25632,7 +25638,7 @@
       <c r="E168" s="73" t="n"/>
       <c r="F168" s="69" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" s="477">
       <c r="A169" s="69" t="n"/>
       <c r="B169" s="72" t="n"/>
       <c r="C169" s="73" t="n"/>
@@ -25660,7 +25666,7 @@
       <c r="Y169" s="462" t="n"/>
       <c r="Z169" s="462" t="n"/>
     </row>
-    <row r="170" ht="9" customHeight="1" s="477">
+    <row r="170" s="477">
       <c r="A170" s="69" t="n"/>
       <c r="B170" s="497" t="inlineStr">
         <is>
@@ -25689,7 +25695,7 @@
       <c r="Y170" s="462" t="n"/>
       <c r="Z170" s="462" t="n"/>
     </row>
-    <row r="171" ht="25.5" customHeight="1" s="477">
+    <row r="171" ht="6" customHeight="1" s="477">
       <c r="A171" s="69" t="n"/>
       <c r="B171" s="72" t="n"/>
       <c r="C171" s="73" t="n"/>
@@ -25717,7 +25723,7 @@
       <c r="Y171" s="462" t="n"/>
       <c r="Z171" s="462" t="n"/>
     </row>
-    <row r="172">
+    <row r="172" s="477">
       <c r="A172" s="69" t="n"/>
       <c r="B172" s="249" t="inlineStr">
         <is>
@@ -25761,7 +25767,7 @@
       <c r="Y172" s="462" t="n"/>
       <c r="Z172" s="462" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" ht="6" customHeight="1" s="477">
       <c r="A173" s="69" t="n"/>
       <c r="B173" s="72" t="n"/>
       <c r="F173" s="69" t="n"/>
@@ -25786,7 +25792,7 @@
       <c r="Y173" s="462" t="n"/>
       <c r="Z173" s="462" t="n"/>
     </row>
-    <row r="174" ht="6" customHeight="1" s="477">
+    <row r="174" s="477">
       <c r="A174" s="69" t="n"/>
       <c r="B174" s="249" t="inlineStr">
         <is>
@@ -25830,7 +25836,7 @@
       <c r="Y174" s="462" t="n"/>
       <c r="Z174" s="462" t="n"/>
     </row>
-    <row r="175" ht="25.5" customHeight="1" s="477">
+    <row r="175" ht="6" customHeight="1" s="477">
       <c r="A175" s="69" t="n"/>
       <c r="B175" s="72" t="n"/>
       <c r="C175" s="73" t="n"/>
@@ -25858,7 +25864,7 @@
       <c r="Y175" s="462" t="n"/>
       <c r="Z175" s="462" t="n"/>
     </row>
-    <row r="176" ht="25.5" customHeight="1" s="477">
+    <row r="176" s="477">
       <c r="A176" s="69" t="n"/>
       <c r="B176" s="249" t="inlineStr">
         <is>
@@ -25902,7 +25908,7 @@
       <c r="Y176" s="462" t="n"/>
       <c r="Z176" s="462" t="n"/>
     </row>
-    <row r="177">
+    <row r="177" ht="6" customHeight="1" s="477">
       <c r="A177" s="69" t="n"/>
       <c r="B177" s="72" t="n"/>
       <c r="C177" s="73" t="n"/>
@@ -25930,7 +25936,7 @@
       <c r="Y177" s="462" t="n"/>
       <c r="Z177" s="462" t="n"/>
     </row>
-    <row r="178" ht="75.75" customHeight="1" s="477">
+    <row r="178" s="477">
       <c r="A178" s="69" t="n"/>
       <c r="B178" s="249" t="inlineStr">
         <is>
@@ -25970,7 +25976,7 @@
       <c r="Y178" s="462" t="n"/>
       <c r="Z178" s="462" t="n"/>
     </row>
-    <row r="179">
+    <row r="179" ht="9" customHeight="1" s="477">
       <c r="A179" s="69" t="n"/>
       <c r="B179" s="72" t="n"/>
       <c r="C179" s="73" t="n"/>
@@ -25978,7 +25984,7 @@
       <c r="E179" s="73" t="n"/>
       <c r="F179" s="69" t="n"/>
     </row>
-    <row r="180">
+    <row r="180" ht="25.5" customHeight="1" s="477">
       <c r="A180" s="69" t="n"/>
       <c r="B180" s="141" t="inlineStr">
         <is>
@@ -25994,7 +26000,7 @@
       <c r="E180" s="73" t="n"/>
       <c r="F180" s="69" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" s="477">
       <c r="A181" s="69" t="n"/>
       <c r="B181" s="258" t="n"/>
       <c r="F181" s="140" t="n"/>
@@ -26019,7 +26025,7 @@
       <c r="Y181" s="462" t="n"/>
       <c r="Z181" s="462" t="n"/>
     </row>
-    <row r="182" ht="6" customHeight="1" s="477">
+    <row r="182" s="477">
       <c r="A182" s="69" t="n"/>
       <c r="B182" s="497" t="inlineStr">
         <is>
@@ -26048,7 +26054,7 @@
       <c r="Y182" s="462" t="n"/>
       <c r="Z182" s="462" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" ht="6" customHeight="1" s="477">
       <c r="A183" s="69" t="n"/>
       <c r="B183" s="72" t="n"/>
       <c r="C183" s="73" t="n"/>
@@ -26076,7 +26082,7 @@
       <c r="Y183" s="462" t="n"/>
       <c r="Z183" s="462" t="n"/>
     </row>
-    <row r="184" ht="6" customHeight="1" s="477">
+    <row r="184" ht="25.5" customHeight="1" s="477">
       <c r="A184" s="69" t="n"/>
       <c r="B184" s="253" t="inlineStr">
         <is>
@@ -26104,7 +26110,7 @@
       <c r="E185" s="73" t="n"/>
       <c r="F185" s="69" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" s="477">
       <c r="A186" s="69" t="n"/>
       <c r="B186" s="72" t="n"/>
       <c r="C186" s="73" t="n"/>
@@ -26132,16 +26138,21 @@
       <c r="Y186" s="462" t="n"/>
       <c r="Z186" s="462" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" ht="75.75" customHeight="1" s="477">
       <c r="A187" s="69" t="n"/>
       <c r="B187" s="254" t="inlineStr">
         <is>
           <t>支援事業者入力</t>
         </is>
       </c>
-      <c r="C187" s="482" t="n"/>
-      <c r="D187" s="482" t="n"/>
-      <c r="E187" s="510" t="n"/>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>・申請者入力内容の確認
+①ITツールの選択、金額入力
+②入力した金額をお客様に画面共有し、確認
+③申請</t>
+        </is>
+      </c>
       <c r="F187" s="140" t="n"/>
       <c r="G187" s="462" t="n"/>
       <c r="H187" s="462" t="n"/>
@@ -26164,7 +26175,7 @@
       <c r="Y187" s="462" t="n"/>
       <c r="Z187" s="462" t="n"/>
     </row>
-    <row r="188" ht="6" customHeight="1" s="477">
+    <row r="188" s="477">
       <c r="A188" s="69" t="n"/>
       <c r="B188" s="258" t="inlineStr">
         <is>
@@ -26196,7 +26207,7 @@
       <c r="Y188" s="462" t="n"/>
       <c r="Z188" s="462" t="n"/>
     </row>
-    <row r="189">
+    <row r="189" s="477">
       <c r="A189" s="69" t="n"/>
       <c r="B189" s="72" t="n"/>
       <c r="C189" s="73" t="n"/>
@@ -26228,7 +26239,7 @@
       <c r="Y189" s="462" t="n"/>
       <c r="Z189" s="462" t="n"/>
     </row>
-    <row r="190" ht="22.5" customHeight="1" s="477">
+    <row r="190" s="477">
       <c r="A190" s="69" t="n"/>
       <c r="B190" s="497" t="inlineStr">
         <is>
@@ -26257,7 +26268,7 @@
       <c r="Y190" s="462" t="n"/>
       <c r="Z190" s="462" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" ht="6" customHeight="1" s="477">
       <c r="A191" s="69" t="n"/>
       <c r="B191" s="72" t="n"/>
       <c r="C191" s="73" t="n"/>
@@ -26285,7 +26296,7 @@
       <c r="Y191" s="462" t="n"/>
       <c r="Z191" s="462" t="n"/>
     </row>
-    <row r="192">
+    <row r="192" s="477">
       <c r="A192" s="69" t="n"/>
       <c r="B192" s="265" t="inlineStr">
         <is>
@@ -26321,7 +26332,7 @@
       <c r="Y192" s="462" t="n"/>
       <c r="Z192" s="462" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" ht="6" customHeight="1" s="477">
       <c r="A193" s="69" t="n"/>
       <c r="B193" s="72" t="n"/>
       <c r="C193" s="73" t="n"/>
@@ -26349,7 +26360,7 @@
       <c r="Y193" s="462" t="n"/>
       <c r="Z193" s="462" t="n"/>
     </row>
-    <row r="194">
+    <row r="194" ht="25.5" customHeight="1" s="477">
       <c r="A194" s="69" t="n"/>
       <c r="B194" s="141" t="inlineStr">
         <is>
@@ -26365,7 +26376,7 @@
       <c r="E194" s="73" t="n"/>
       <c r="F194" s="69" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" s="477">
       <c r="A195" s="260" t="n"/>
       <c r="B195" s="261" t="n"/>
       <c r="C195" s="247" t="n"/>
@@ -26393,7 +26404,7 @@
       <c r="Y195" s="462" t="n"/>
       <c r="Z195" s="462" t="n"/>
     </row>
-    <row r="196" ht="30.75" customHeight="1" s="477">
+    <row r="196" s="477">
       <c r="A196" s="69" t="n"/>
       <c r="B196" s="497" t="inlineStr">
         <is>
@@ -26422,7 +26433,7 @@
       <c r="Y196" s="462" t="n"/>
       <c r="Z196" s="462" t="n"/>
     </row>
-    <row r="197">
+    <row r="197" ht="6" customHeight="1" s="477">
       <c r="A197" s="69" t="n"/>
       <c r="B197" s="72" t="n"/>
       <c r="C197" s="73" t="n"/>
@@ -26450,7 +26461,7 @@
       <c r="Y197" s="462" t="n"/>
       <c r="Z197" s="462" t="n"/>
     </row>
-    <row r="198">
+    <row r="198" s="477">
       <c r="A198" s="69" t="n"/>
       <c r="B198" s="162" t="inlineStr">
         <is>
@@ -26487,7 +26498,7 @@
       <c r="Y198" s="462" t="n"/>
       <c r="Z198" s="462" t="n"/>
     </row>
-    <row r="199">
+    <row r="199" ht="22.5" customHeight="1" s="477">
       <c r="A199" s="69" t="n"/>
       <c r="B199" s="230" t="inlineStr">
         <is>
@@ -26526,7 +26537,7 @@
       <c r="Y199" s="462" t="n"/>
       <c r="Z199" s="462" t="n"/>
     </row>
-    <row r="200">
+    <row r="200" s="477">
       <c r="A200" s="69" t="n"/>
       <c r="B200" s="265" t="inlineStr">
         <is>
@@ -26558,7 +26569,7 @@
       <c r="Y200" s="462" t="n"/>
       <c r="Z200" s="462" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" s="477">
       <c r="A201" s="69" t="n"/>
       <c r="B201" s="265" t="inlineStr">
         <is>
@@ -26595,7 +26606,7 @@
       <c r="Y201" s="462" t="n"/>
       <c r="Z201" s="462" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" s="477">
       <c r="A202" s="69" t="n"/>
       <c r="B202" s="265" t="inlineStr">
         <is>
@@ -26628,7 +26639,7 @@
       <c r="Y202" s="462" t="n"/>
       <c r="Z202" s="462" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" s="477">
       <c r="A203" s="69" t="n"/>
       <c r="B203" s="265" t="inlineStr">
         <is>
@@ -26661,7 +26672,7 @@
       <c r="Y203" s="462" t="n"/>
       <c r="Z203" s="462" t="n"/>
     </row>
-    <row r="204">
+    <row r="204" s="477">
       <c r="A204" s="269" t="n"/>
       <c r="B204" s="265" t="inlineStr">
         <is>
@@ -26694,11 +26705,11 @@
       <c r="Y204" s="462" t="n"/>
       <c r="Z204" s="462" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" ht="30.75" customHeight="1" s="477">
       <c r="A205" s="271" t="n"/>
       <c r="B205" s="272" t="inlineStr">
         <is>
-          <t>⇨年平均成長率：上記4点記入後、「年平均成長率計算」をクリック（申請画面上で1.5％以上であることを確認）</t>
+          <t>⇨年平均成長率：上記4点記入後、「年平均成長率計算」をクリック（申請画面上で3.0％以上であることを確認）</t>
         </is>
       </c>
       <c r="C205" s="273" t="n"/>
@@ -26726,7 +26737,7 @@
       <c r="Y205" s="276" t="n"/>
       <c r="Z205" s="276" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" s="477">
       <c r="A206" s="277" t="n"/>
       <c r="B206" s="278" t="inlineStr">
         <is>
@@ -26762,7 +26773,7 @@
       <c r="Y206" s="169" t="n"/>
       <c r="Z206" s="169" t="n"/>
     </row>
-    <row r="207">
+    <row r="207" s="477">
       <c r="A207" s="200" t="n"/>
       <c r="B207" s="265" t="inlineStr">
         <is>
@@ -26799,7 +26810,7 @@
       <c r="Y207" s="462" t="n"/>
       <c r="Z207" s="462" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" s="477">
       <c r="A208" s="200" t="n"/>
       <c r="B208" s="265" t="inlineStr">
         <is>
@@ -26835,7 +26846,7 @@
       <c r="Y208" s="462" t="n"/>
       <c r="Z208" s="462" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" s="477">
       <c r="A209" s="200" t="n"/>
       <c r="B209" s="265" t="inlineStr">
         <is>
@@ -26878,7 +26889,7 @@
       <c r="Y209" s="462" t="n"/>
       <c r="Z209" s="462" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" s="477">
       <c r="A210" s="200" t="n"/>
       <c r="B210" s="162" t="inlineStr">
         <is>
@@ -26915,7 +26926,7 @@
       <c r="Y210" s="462" t="n"/>
       <c r="Z210" s="462" t="n"/>
     </row>
-    <row r="211" ht="6" customHeight="1" s="477">
+    <row r="211" s="477">
       <c r="A211" s="200" t="n"/>
       <c r="B211" s="265" t="inlineStr">
         <is>
@@ -26955,7 +26966,7 @@
       <c r="Y211" s="462" t="n"/>
       <c r="Z211" s="462" t="n"/>
     </row>
-    <row r="212" ht="6" customHeight="1" s="477">
+    <row r="212" s="477">
       <c r="A212" s="69" t="n"/>
       <c r="B212" s="265" t="inlineStr">
         <is>
@@ -26995,7 +27006,7 @@
       <c r="Y212" s="462" t="n"/>
       <c r="Z212" s="462" t="n"/>
     </row>
-    <row r="213" ht="6" customHeight="1" s="477">
+    <row r="213" s="477">
       <c r="A213" s="69" t="n"/>
       <c r="B213" s="265" t="inlineStr">
         <is>
@@ -27034,7 +27045,7 @@
       <c r="Y213" s="462" t="n"/>
       <c r="Z213" s="462" t="n"/>
     </row>
-    <row r="214" ht="6" customHeight="1" s="477">
+    <row r="214" s="477">
       <c r="A214" s="125" t="n"/>
       <c r="B214" s="291" t="n"/>
       <c r="C214" s="94" t="n"/>
@@ -27062,7 +27073,7 @@
       <c r="Y214" s="169" t="n"/>
       <c r="Z214" s="169" t="n"/>
     </row>
-    <row r="215">
+    <row r="215" s="477">
       <c r="A215" s="125" t="n"/>
       <c r="B215" s="291" t="inlineStr">
         <is>
@@ -27094,7 +27105,7 @@
       <c r="Y215" s="169" t="n"/>
       <c r="Z215" s="169" t="n"/>
     </row>
-    <row r="216" ht="6" customHeight="1" s="477">
+    <row r="216" s="477">
       <c r="A216" s="200" t="n"/>
       <c r="B216" s="265" t="inlineStr">
         <is>
@@ -27131,7 +27142,7 @@
       <c r="Y216" s="462" t="n"/>
       <c r="Z216" s="462" t="n"/>
     </row>
-    <row r="217">
+    <row r="217" s="477">
       <c r="A217" s="200" t="n"/>
       <c r="B217" s="265" t="inlineStr">
         <is>
@@ -27171,7 +27182,7 @@
       <c r="Y217" s="462" t="n"/>
       <c r="Z217" s="462" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" s="477">
       <c r="A218" s="125" t="n"/>
       <c r="B218" s="291" t="n"/>
       <c r="C218" s="94" t="n"/>
@@ -27199,7 +27210,7 @@
       <c r="Y218" s="169" t="n"/>
       <c r="Z218" s="169" t="n"/>
     </row>
-    <row r="219">
+    <row r="219" s="477">
       <c r="A219" s="125" t="n"/>
       <c r="B219" s="293" t="n"/>
       <c r="C219" s="125" t="n"/>
@@ -27227,7 +27238,7 @@
       <c r="Y219" s="169" t="n"/>
       <c r="Z219" s="169" t="n"/>
     </row>
-    <row r="220">
+    <row r="220" s="477">
       <c r="A220" s="125" t="n"/>
       <c r="B220" s="505" t="inlineStr">
         <is>
@@ -27256,7 +27267,7 @@
       <c r="Y220" s="169" t="n"/>
       <c r="Z220" s="169" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" ht="6" customHeight="1" s="477">
       <c r="A221" s="69" t="n"/>
       <c r="B221" s="72" t="n"/>
       <c r="C221" s="73" t="n"/>
@@ -27284,7 +27295,7 @@
       <c r="Y221" s="462" t="n"/>
       <c r="Z221" s="462" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" s="477">
       <c r="A222" s="125" t="n"/>
       <c r="B222" s="506" t="inlineStr">
         <is>
@@ -27342,16 +27353,19 @@
       <c r="Y223" s="462" t="n"/>
       <c r="Z223" s="462" t="n"/>
     </row>
-    <row r="224">
+    <row r="224" s="477">
       <c r="A224" s="296" t="n"/>
       <c r="B224" s="309" t="inlineStr">
         <is>
           <t>指定する一定期間において、3ヶ月以上、R7年度改定の地域別最低賃金未満で雇用していた従業員数が全従業員の30%以上であり、加点を希望する</t>
         </is>
       </c>
-      <c r="C224" s="482" t="n"/>
-      <c r="D224" s="482" t="n"/>
-      <c r="E224" s="510" t="n"/>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t>□はい
+□いいえ</t>
+        </is>
+      </c>
       <c r="F224" s="125" t="n"/>
       <c r="G224" s="169" t="n"/>
       <c r="H224" s="169" t="n"/>
@@ -27402,7 +27416,7 @@
       <c r="Y225" s="462" t="n"/>
       <c r="Z225" s="462" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" s="477">
       <c r="A226" s="300" t="n"/>
       <c r="B226" s="222" t="inlineStr">
         <is>
@@ -27443,7 +27457,7 @@
       <c r="Y226" s="169" t="n"/>
       <c r="Z226" s="169" t="n"/>
     </row>
-    <row r="227" ht="6" customHeight="1" s="477">
+    <row r="227" s="477">
       <c r="A227" s="125" t="n"/>
       <c r="B227" s="125" t="n"/>
       <c r="C227" s="304" t="inlineStr">
@@ -27475,7 +27489,7 @@
       <c r="Y227" s="169" t="n"/>
       <c r="Z227" s="169" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" s="477">
       <c r="A228" s="125" t="n"/>
       <c r="B228" s="293" t="n"/>
       <c r="C228" s="125" t="n"/>
@@ -27507,7 +27521,7 @@
       <c r="Y228" s="169" t="n"/>
       <c r="Z228" s="169" t="n"/>
     </row>
-    <row r="229">
+    <row r="229" s="477">
       <c r="A229" s="125" t="n"/>
       <c r="B229" s="305" t="inlineStr">
         <is>
@@ -27543,7 +27557,7 @@
       <c r="Y229" s="169" t="n"/>
       <c r="Z229" s="169" t="n"/>
     </row>
-    <row r="230" ht="6" customHeight="1" s="477">
+    <row r="230" s="477">
       <c r="A230" s="125" t="n"/>
       <c r="B230" s="291" t="n"/>
       <c r="C230" s="306" t="n"/>
@@ -27571,7 +27585,7 @@
       <c r="Y230" s="169" t="n"/>
       <c r="Z230" s="169" t="n"/>
     </row>
-    <row r="231" ht="25.5" customHeight="1" s="477">
+    <row r="231" s="477">
       <c r="A231" s="125" t="n"/>
       <c r="B231" s="505" t="inlineStr">
         <is>
@@ -27600,7 +27614,7 @@
       <c r="Y231" s="169" t="n"/>
       <c r="Z231" s="169" t="n"/>
     </row>
-    <row r="232">
+    <row r="232" ht="6" customHeight="1" s="477">
       <c r="A232" s="69" t="n"/>
       <c r="B232" s="72" t="n"/>
       <c r="C232" s="73" t="n"/>
@@ -27628,7 +27642,7 @@
       <c r="Y232" s="462" t="n"/>
       <c r="Z232" s="462" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" s="477">
       <c r="A233" s="125" t="n"/>
       <c r="B233" s="506" t="inlineStr">
         <is>
@@ -27686,7 +27700,7 @@
       <c r="Y234" s="462" t="n"/>
       <c r="Z234" s="462" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" s="477">
       <c r="A235" s="296" t="n"/>
       <c r="B235" s="309" t="inlineStr">
         <is>
@@ -27752,7 +27766,7 @@
       <c r="Y236" s="462" t="n"/>
       <c r="Z236" s="462" t="n"/>
     </row>
-    <row r="237" ht="25.5" customHeight="1" s="477">
+    <row r="237" s="477">
       <c r="A237" s="300" t="n"/>
       <c r="B237" s="222" t="inlineStr">
         <is>
@@ -27793,7 +27807,7 @@
       <c r="Y237" s="169" t="n"/>
       <c r="Z237" s="169" t="n"/>
     </row>
-    <row r="238">
+    <row r="238" s="477">
       <c r="A238" s="125" t="n"/>
       <c r="B238" s="125" t="n"/>
       <c r="C238" s="304" t="inlineStr">
@@ -27825,7 +27839,7 @@
       <c r="Y238" s="169" t="n"/>
       <c r="Z238" s="169" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" ht="6" customHeight="1" s="477">
       <c r="A239" s="69" t="n"/>
       <c r="B239" s="72" t="n"/>
       <c r="F239" s="69" t="n"/>
@@ -27850,7 +27864,7 @@
       <c r="Y239" s="462" t="n"/>
       <c r="Z239" s="462" t="n"/>
     </row>
-    <row r="240" ht="6" customHeight="1" s="477">
+    <row r="240" ht="25.5" customHeight="1" s="477">
       <c r="A240" s="69" t="n"/>
       <c r="B240" s="141" t="inlineStr">
         <is>
@@ -27866,7 +27880,7 @@
       <c r="E240" s="73" t="n"/>
       <c r="F240" s="69" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" s="477">
       <c r="A241" s="260" t="n"/>
       <c r="B241" s="261" t="n"/>
       <c r="C241" s="247" t="n"/>
@@ -27894,7 +27908,7 @@
       <c r="Y241" s="462" t="n"/>
       <c r="Z241" s="462" t="n"/>
     </row>
-    <row r="242" ht="6" customHeight="1" s="477">
+    <row r="242" s="477">
       <c r="A242" s="69" t="n"/>
       <c r="B242" s="497" t="inlineStr">
         <is>
@@ -27923,7 +27937,7 @@
       <c r="Y242" s="462" t="n"/>
       <c r="Z242" s="462" t="n"/>
     </row>
-    <row r="243" ht="25.5" customHeight="1" s="477">
+    <row r="243" ht="6" customHeight="1" s="477">
       <c r="A243" s="69" t="n"/>
       <c r="B243" s="72" t="n"/>
       <c r="C243" s="73" t="n"/>
@@ -27951,7 +27965,7 @@
       <c r="Y243" s="462" t="n"/>
       <c r="Z243" s="462" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" s="477">
       <c r="A244" s="69" t="n"/>
       <c r="B244" s="72" t="inlineStr">
         <is>
@@ -27983,7 +27997,7 @@
       <c r="Y244" s="462" t="n"/>
       <c r="Z244" s="462" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" ht="6" customHeight="1" s="477">
       <c r="A245" s="69" t="n"/>
       <c r="B245" s="72" t="n"/>
       <c r="C245" s="73" t="n"/>
@@ -28011,7 +28025,7 @@
       <c r="Y245" s="462" t="n"/>
       <c r="Z245" s="462" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" ht="25.5" customHeight="1" s="477">
       <c r="A246" s="69" t="n"/>
       <c r="B246" s="141" t="inlineStr">
         <is>
@@ -28027,7 +28041,7 @@
       <c r="E246" s="73" t="n"/>
       <c r="F246" s="69" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" s="477">
       <c r="A247" s="69" t="n"/>
       <c r="B247" s="72" t="n"/>
       <c r="C247" s="73" t="n"/>
@@ -28055,7 +28069,7 @@
       <c r="Y247" s="462" t="n"/>
       <c r="Z247" s="462" t="n"/>
     </row>
-    <row r="248">
+    <row r="248" s="477">
       <c r="A248" s="69" t="n"/>
       <c r="B248" s="497" t="inlineStr">
         <is>
@@ -28084,7 +28098,7 @@
       <c r="Y248" s="462" t="n"/>
       <c r="Z248" s="462" t="n"/>
     </row>
-    <row r="249">
+    <row r="249" ht="6" customHeight="1" s="477">
       <c r="A249" s="69" t="n"/>
       <c r="B249" s="72" t="n"/>
       <c r="C249" s="73" t="n"/>
@@ -28112,7 +28126,7 @@
       <c r="Y249" s="462" t="n"/>
       <c r="Z249" s="462" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" s="477">
       <c r="A250" s="125" t="n"/>
       <c r="B250" s="310" t="inlineStr">
         <is>
@@ -28144,7 +28158,7 @@
       <c r="Y250" s="169" t="n"/>
       <c r="Z250" s="169" t="n"/>
     </row>
-    <row r="251">
+    <row r="251" ht="6" customHeight="1" s="477">
       <c r="A251" s="69" t="n"/>
       <c r="B251" s="72" t="n"/>
       <c r="C251" s="73" t="n"/>
@@ -28172,7 +28186,7 @@
       <c r="Y251" s="462" t="n"/>
       <c r="Z251" s="462" t="n"/>
     </row>
-    <row r="252">
+    <row r="252" ht="25.5" customHeight="1" s="477">
       <c r="A252" s="69" t="n"/>
       <c r="B252" s="141" t="inlineStr">
         <is>
@@ -28188,7 +28202,7 @@
       <c r="E252" s="73" t="n"/>
       <c r="F252" s="69" t="n"/>
     </row>
-    <row r="253">
+    <row r="253" s="477">
       <c r="A253" s="69" t="n"/>
       <c r="B253" s="72" t="n"/>
       <c r="C253" s="73" t="n"/>
@@ -28216,7 +28230,7 @@
       <c r="Y253" s="462" t="n"/>
       <c r="Z253" s="462" t="n"/>
     </row>
-    <row r="254">
+    <row r="254" s="477">
       <c r="A254" s="69" t="n"/>
       <c r="B254" s="72" t="inlineStr">
         <is>
@@ -28248,7 +28262,7 @@
       <c r="Y254" s="462" t="n"/>
       <c r="Z254" s="462" t="n"/>
     </row>
-    <row r="255">
+    <row r="255" s="477">
       <c r="A255" s="69" t="n"/>
       <c r="B255" s="72" t="n"/>
       <c r="C255" s="73" t="n"/>
@@ -28276,7 +28290,8 @@
       <c r="Y255" s="462" t="n"/>
       <c r="Z255" s="462" t="n"/>
     </row>
-    <row r="257">
+    <row r="256" s="477"/>
+    <row r="257" s="477">
       <c r="A257" s="69" t="n"/>
       <c r="B257" s="72" t="n"/>
       <c r="C257" s="73" t="n"/>
@@ -28304,7 +28319,7 @@
       <c r="Y257" s="462" t="n"/>
       <c r="Z257" s="462" t="n"/>
     </row>
-    <row r="258">
+    <row r="258" s="477">
       <c r="A258" s="69" t="n"/>
       <c r="B258" s="72" t="n"/>
       <c r="C258" s="73" t="n"/>
@@ -28332,7 +28347,7 @@
       <c r="Y258" s="462" t="n"/>
       <c r="Z258" s="462" t="n"/>
     </row>
-    <row r="259">
+    <row r="259" s="477">
       <c r="A259" s="69" t="n"/>
       <c r="B259" s="72" t="n"/>
       <c r="C259" s="73" t="n"/>
@@ -28360,7 +28375,7 @@
       <c r="Y259" s="462" t="n"/>
       <c r="Z259" s="462" t="n"/>
     </row>
-    <row r="260">
+    <row r="260" s="477">
       <c r="A260" s="69" t="n"/>
       <c r="B260" s="72" t="n"/>
       <c r="C260" s="73" t="n"/>
@@ -28388,7 +28403,7 @@
       <c r="Y260" s="462" t="n"/>
       <c r="Z260" s="462" t="n"/>
     </row>
-    <row r="261">
+    <row r="261" s="477">
       <c r="A261" s="69" t="n"/>
       <c r="B261" s="72" t="n"/>
       <c r="C261" s="73" t="n"/>
@@ -28416,7 +28431,7 @@
       <c r="Y261" s="462" t="n"/>
       <c r="Z261" s="462" t="n"/>
     </row>
-    <row r="262">
+    <row r="262" s="477">
       <c r="A262" s="69" t="n"/>
       <c r="B262" s="72" t="n"/>
       <c r="C262" s="73" t="n"/>
@@ -28444,7 +28459,7 @@
       <c r="Y262" s="462" t="n"/>
       <c r="Z262" s="462" t="n"/>
     </row>
-    <row r="263">
+    <row r="263" s="477">
       <c r="A263" s="69" t="n"/>
       <c r="B263" s="72" t="n"/>
       <c r="C263" s="73" t="n"/>
@@ -28472,7 +28487,7 @@
       <c r="Y263" s="462" t="n"/>
       <c r="Z263" s="462" t="n"/>
     </row>
-    <row r="264">
+    <row r="264" s="477">
       <c r="A264" s="69" t="n"/>
       <c r="B264" s="72" t="n"/>
       <c r="C264" s="73" t="n"/>
@@ -28500,7 +28515,7 @@
       <c r="Y264" s="462" t="n"/>
       <c r="Z264" s="462" t="n"/>
     </row>
-    <row r="265">
+    <row r="265" s="477">
       <c r="A265" s="69" t="n"/>
       <c r="B265" s="72" t="n"/>
       <c r="C265" s="73" t="n"/>
@@ -28528,7 +28543,7 @@
       <c r="Y265" s="462" t="n"/>
       <c r="Z265" s="462" t="n"/>
     </row>
-    <row r="266">
+    <row r="266" s="477">
       <c r="A266" s="69" t="n"/>
       <c r="B266" s="72" t="n"/>
       <c r="C266" s="73" t="n"/>
@@ -28556,7 +28571,7 @@
       <c r="Y266" s="462" t="n"/>
       <c r="Z266" s="462" t="n"/>
     </row>
-    <row r="267">
+    <row r="267" s="477">
       <c r="A267" s="69" t="n"/>
       <c r="B267" s="72" t="n"/>
       <c r="C267" s="73" t="n"/>
@@ -28584,7 +28599,7 @@
       <c r="Y267" s="462" t="n"/>
       <c r="Z267" s="462" t="n"/>
     </row>
-    <row r="268">
+    <row r="268" s="477">
       <c r="A268" s="69" t="n"/>
       <c r="B268" s="72" t="n"/>
       <c r="C268" s="73" t="n"/>
@@ -28612,7 +28627,7 @@
       <c r="Y268" s="462" t="n"/>
       <c r="Z268" s="462" t="n"/>
     </row>
-    <row r="269">
+    <row r="269" s="477">
       <c r="A269" s="69" t="n"/>
       <c r="B269" s="72" t="n"/>
       <c r="C269" s="73" t="n"/>
@@ -28640,7 +28655,7 @@
       <c r="Y269" s="462" t="n"/>
       <c r="Z269" s="462" t="n"/>
     </row>
-    <row r="270">
+    <row r="270" s="477">
       <c r="A270" s="69" t="n"/>
       <c r="B270" s="72" t="n"/>
       <c r="C270" s="73" t="n"/>
@@ -28668,7 +28683,7 @@
       <c r="Y270" s="462" t="n"/>
       <c r="Z270" s="462" t="n"/>
     </row>
-    <row r="271">
+    <row r="271" s="477">
       <c r="A271" s="69" t="n"/>
       <c r="B271" s="72" t="n"/>
       <c r="C271" s="73" t="n"/>
@@ -28696,7 +28711,7 @@
       <c r="Y271" s="462" t="n"/>
       <c r="Z271" s="462" t="n"/>
     </row>
-    <row r="272">
+    <row r="272" s="477">
       <c r="A272" s="69" t="n"/>
       <c r="B272" s="72" t="n"/>
       <c r="C272" s="73" t="n"/>
@@ -28724,7 +28739,7 @@
       <c r="Y272" s="462" t="n"/>
       <c r="Z272" s="462" t="n"/>
     </row>
-    <row r="273">
+    <row r="273" s="477">
       <c r="A273" s="69" t="n"/>
       <c r="B273" s="72" t="n"/>
       <c r="C273" s="73" t="n"/>
@@ -28752,7 +28767,7 @@
       <c r="Y273" s="462" t="n"/>
       <c r="Z273" s="462" t="n"/>
     </row>
-    <row r="274">
+    <row r="274" s="477">
       <c r="A274" s="69" t="n"/>
       <c r="B274" s="72" t="n"/>
       <c r="C274" s="73" t="n"/>
@@ -28780,7 +28795,7 @@
       <c r="Y274" s="462" t="n"/>
       <c r="Z274" s="462" t="n"/>
     </row>
-    <row r="275">
+    <row r="275" s="477">
       <c r="A275" s="69" t="n"/>
       <c r="B275" s="72" t="n"/>
       <c r="C275" s="73" t="n"/>
@@ -28808,7 +28823,7 @@
       <c r="Y275" s="462" t="n"/>
       <c r="Z275" s="462" t="n"/>
     </row>
-    <row r="276">
+    <row r="276" s="477">
       <c r="A276" s="69" t="n"/>
       <c r="B276" s="72" t="n"/>
       <c r="C276" s="73" t="n"/>
@@ -28836,7 +28851,7 @@
       <c r="Y276" s="462" t="n"/>
       <c r="Z276" s="462" t="n"/>
     </row>
-    <row r="277">
+    <row r="277" s="477">
       <c r="A277" s="69" t="n"/>
       <c r="B277" s="72" t="n"/>
       <c r="C277" s="73" t="n"/>
@@ -28864,7 +28879,7 @@
       <c r="Y277" s="462" t="n"/>
       <c r="Z277" s="462" t="n"/>
     </row>
-    <row r="278">
+    <row r="278" s="477">
       <c r="A278" s="69" t="n"/>
       <c r="B278" s="72" t="n"/>
       <c r="C278" s="73" t="n"/>
@@ -28892,7 +28907,7 @@
       <c r="Y278" s="462" t="n"/>
       <c r="Z278" s="462" t="n"/>
     </row>
-    <row r="279">
+    <row r="279" s="477">
       <c r="A279" s="69" t="n"/>
       <c r="B279" s="72" t="n"/>
       <c r="C279" s="73" t="n"/>
@@ -28920,7 +28935,7 @@
       <c r="Y279" s="462" t="n"/>
       <c r="Z279" s="462" t="n"/>
     </row>
-    <row r="280">
+    <row r="280" s="477">
       <c r="A280" s="69" t="n"/>
       <c r="B280" s="72" t="n"/>
       <c r="C280" s="73" t="n"/>
@@ -28948,7 +28963,7 @@
       <c r="Y280" s="462" t="n"/>
       <c r="Z280" s="462" t="n"/>
     </row>
-    <row r="281">
+    <row r="281" s="477">
       <c r="A281" s="69" t="n"/>
       <c r="B281" s="72" t="n"/>
       <c r="C281" s="73" t="n"/>
@@ -28957,7 +28972,7 @@
       <c r="F281" s="69" t="n"/>
       <c r="G281" s="69" t="n"/>
     </row>
-    <row r="282">
+    <row r="282" s="477">
       <c r="A282" s="69" t="n"/>
       <c r="B282" s="72" t="n"/>
       <c r="C282" s="73" t="n"/>
@@ -28966,7 +28981,7 @@
       <c r="F282" s="69" t="n"/>
       <c r="G282" s="69" t="n"/>
     </row>
-    <row r="283">
+    <row r="283" s="477">
       <c r="A283" s="69" t="n"/>
       <c r="B283" s="72" t="n"/>
       <c r="C283" s="73" t="n"/>
@@ -28975,7 +28990,7 @@
       <c r="F283" s="69" t="n"/>
       <c r="G283" s="69" t="n"/>
     </row>
-    <row r="284">
+    <row r="284" s="477">
       <c r="A284" s="69" t="n"/>
       <c r="B284" s="72" t="n"/>
       <c r="C284" s="73" t="n"/>
@@ -28984,7 +28999,7 @@
       <c r="F284" s="69" t="n"/>
       <c r="G284" s="69" t="n"/>
     </row>
-    <row r="285">
+    <row r="285" s="477">
       <c r="A285" s="69" t="n"/>
       <c r="B285" s="72" t="n"/>
       <c r="C285" s="73" t="n"/>
@@ -28993,7 +29008,7 @@
       <c r="F285" s="69" t="n"/>
       <c r="G285" s="69" t="n"/>
     </row>
-    <row r="286">
+    <row r="286" s="477">
       <c r="A286" s="69" t="n"/>
       <c r="B286" s="72" t="n"/>
       <c r="C286" s="73" t="n"/>
@@ -29002,7 +29017,7 @@
       <c r="F286" s="69" t="n"/>
       <c r="G286" s="69" t="n"/>
     </row>
-    <row r="287">
+    <row r="287" s="477">
       <c r="A287" s="69" t="n"/>
       <c r="B287" s="72" t="n"/>
       <c r="C287" s="73" t="n"/>
@@ -29011,7 +29026,7 @@
       <c r="F287" s="69" t="n"/>
       <c r="G287" s="69" t="n"/>
     </row>
-    <row r="288">
+    <row r="288" s="477">
       <c r="A288" s="69" t="n"/>
       <c r="B288" s="72" t="n"/>
       <c r="C288" s="73" t="n"/>
@@ -29020,7 +29035,7 @@
       <c r="F288" s="69" t="n"/>
       <c r="G288" s="69" t="n"/>
     </row>
-    <row r="289">
+    <row r="289" s="477">
       <c r="A289" s="69" t="n"/>
       <c r="B289" s="72" t="n"/>
       <c r="C289" s="73" t="n"/>
@@ -29029,7 +29044,7 @@
       <c r="F289" s="69" t="n"/>
       <c r="G289" s="69" t="n"/>
     </row>
-    <row r="290">
+    <row r="290" s="477">
       <c r="A290" s="69" t="n"/>
       <c r="B290" s="72" t="n"/>
       <c r="C290" s="73" t="n"/>
@@ -29038,7 +29053,7 @@
       <c r="F290" s="69" t="n"/>
       <c r="G290" s="69" t="n"/>
     </row>
-    <row r="291">
+    <row r="291" s="477">
       <c r="A291" s="69" t="n"/>
       <c r="B291" s="72" t="n"/>
       <c r="C291" s="73" t="n"/>
@@ -29047,7 +29062,7 @@
       <c r="F291" s="69" t="n"/>
       <c r="G291" s="69" t="n"/>
     </row>
-    <row r="292">
+    <row r="292" s="477">
       <c r="A292" s="69" t="n"/>
       <c r="B292" s="72" t="n"/>
       <c r="C292" s="73" t="n"/>
@@ -29056,7 +29071,7 @@
       <c r="F292" s="69" t="n"/>
       <c r="G292" s="69" t="n"/>
     </row>
-    <row r="293">
+    <row r="293" s="477">
       <c r="A293" s="69" t="n"/>
       <c r="B293" s="72" t="n"/>
       <c r="C293" s="73" t="n"/>
@@ -29065,7 +29080,7 @@
       <c r="F293" s="69" t="n"/>
       <c r="G293" s="69" t="n"/>
     </row>
-    <row r="294">
+    <row r="294" s="477">
       <c r="A294" s="69" t="n"/>
       <c r="B294" s="72" t="n"/>
       <c r="C294" s="73" t="n"/>
@@ -29074,7 +29089,7 @@
       <c r="F294" s="69" t="n"/>
       <c r="G294" s="69" t="n"/>
     </row>
-    <row r="295">
+    <row r="295" s="477">
       <c r="A295" s="69" t="n"/>
       <c r="B295" s="72" t="n"/>
       <c r="C295" s="73" t="n"/>
@@ -29083,7 +29098,7 @@
       <c r="F295" s="69" t="n"/>
       <c r="G295" s="69" t="n"/>
     </row>
-    <row r="296">
+    <row r="296" s="477">
       <c r="A296" s="69" t="n"/>
       <c r="B296" s="72" t="n"/>
       <c r="C296" s="73" t="n"/>
@@ -29092,7 +29107,7 @@
       <c r="F296" s="69" t="n"/>
       <c r="G296" s="69" t="n"/>
     </row>
-    <row r="297">
+    <row r="297" s="477">
       <c r="A297" s="69" t="n"/>
       <c r="B297" s="72" t="n"/>
       <c r="C297" s="73" t="n"/>
@@ -29101,7 +29116,7 @@
       <c r="F297" s="69" t="n"/>
       <c r="G297" s="69" t="n"/>
     </row>
-    <row r="298">
+    <row r="298" s="477">
       <c r="A298" s="69" t="n"/>
       <c r="B298" s="72" t="n"/>
       <c r="C298" s="73" t="n"/>
@@ -29110,7 +29125,7 @@
       <c r="F298" s="69" t="n"/>
       <c r="G298" s="69" t="n"/>
     </row>
-    <row r="299">
+    <row r="299" s="477">
       <c r="A299" s="69" t="n"/>
       <c r="B299" s="72" t="n"/>
       <c r="C299" s="73" t="n"/>
@@ -29119,7 +29134,7 @@
       <c r="F299" s="69" t="n"/>
       <c r="G299" s="69" t="n"/>
     </row>
-    <row r="300">
+    <row r="300" s="477">
       <c r="A300" s="69" t="n"/>
       <c r="B300" s="72" t="n"/>
       <c r="C300" s="73" t="n"/>
@@ -29128,7 +29143,7 @@
       <c r="F300" s="69" t="n"/>
       <c r="G300" s="69" t="n"/>
     </row>
-    <row r="301">
+    <row r="301" s="477">
       <c r="A301" s="69" t="n"/>
       <c r="B301" s="72" t="n"/>
       <c r="C301" s="73" t="n"/>
@@ -29137,7 +29152,7 @@
       <c r="F301" s="69" t="n"/>
       <c r="G301" s="69" t="n"/>
     </row>
-    <row r="302">
+    <row r="302" s="477">
       <c r="A302" s="69" t="n"/>
       <c r="B302" s="72" t="n"/>
       <c r="C302" s="73" t="n"/>
@@ -29146,7 +29161,7 @@
       <c r="F302" s="69" t="n"/>
       <c r="G302" s="69" t="n"/>
     </row>
-    <row r="303">
+    <row r="303" s="477">
       <c r="A303" s="69" t="n"/>
       <c r="B303" s="72" t="n"/>
       <c r="C303" s="73" t="n"/>
@@ -29155,7 +29170,7 @@
       <c r="F303" s="69" t="n"/>
       <c r="G303" s="69" t="n"/>
     </row>
-    <row r="304">
+    <row r="304" s="477">
       <c r="A304" s="69" t="n"/>
       <c r="B304" s="72" t="n"/>
       <c r="C304" s="73" t="n"/>
@@ -29164,7 +29179,7 @@
       <c r="F304" s="69" t="n"/>
       <c r="G304" s="69" t="n"/>
     </row>
-    <row r="305">
+    <row r="305" s="477">
       <c r="A305" s="69" t="n"/>
       <c r="B305" s="72" t="n"/>
       <c r="C305" s="73" t="n"/>
@@ -29173,7 +29188,7 @@
       <c r="F305" s="69" t="n"/>
       <c r="G305" s="69" t="n"/>
     </row>
-    <row r="306">
+    <row r="306" s="477">
       <c r="A306" s="69" t="n"/>
       <c r="B306" s="72" t="n"/>
       <c r="C306" s="73" t="n"/>
@@ -29182,7 +29197,7 @@
       <c r="F306" s="69" t="n"/>
       <c r="G306" s="69" t="n"/>
     </row>
-    <row r="307">
+    <row r="307" s="477">
       <c r="A307" s="69" t="n"/>
       <c r="B307" s="72" t="n"/>
       <c r="C307" s="73" t="n"/>
@@ -29191,7 +29206,7 @@
       <c r="F307" s="69" t="n"/>
       <c r="G307" s="69" t="n"/>
     </row>
-    <row r="308">
+    <row r="308" s="477">
       <c r="A308" s="69" t="n"/>
       <c r="B308" s="72" t="n"/>
       <c r="C308" s="73" t="n"/>
@@ -29200,7 +29215,7 @@
       <c r="F308" s="69" t="n"/>
       <c r="G308" s="69" t="n"/>
     </row>
-    <row r="309">
+    <row r="309" s="477">
       <c r="A309" s="69" t="n"/>
       <c r="B309" s="72" t="n"/>
       <c r="C309" s="73" t="n"/>
@@ -29209,7 +29224,7 @@
       <c r="F309" s="69" t="n"/>
       <c r="G309" s="69" t="n"/>
     </row>
-    <row r="310">
+    <row r="310" s="477">
       <c r="A310" s="69" t="n"/>
       <c r="B310" s="72" t="n"/>
       <c r="C310" s="73" t="n"/>
@@ -29218,7 +29233,7 @@
       <c r="F310" s="69" t="n"/>
       <c r="G310" s="69" t="n"/>
     </row>
-    <row r="311">
+    <row r="311" s="477">
       <c r="A311" s="69" t="n"/>
       <c r="B311" s="72" t="n"/>
       <c r="C311" s="73" t="n"/>
@@ -29227,7 +29242,7 @@
       <c r="F311" s="69" t="n"/>
       <c r="G311" s="69" t="n"/>
     </row>
-    <row r="312">
+    <row r="312" s="477">
       <c r="A312" s="69" t="n"/>
       <c r="B312" s="72" t="n"/>
       <c r="C312" s="73" t="n"/>
@@ -29236,7 +29251,7 @@
       <c r="F312" s="69" t="n"/>
       <c r="G312" s="69" t="n"/>
     </row>
-    <row r="313">
+    <row r="313" s="477">
       <c r="A313" s="69" t="n"/>
       <c r="B313" s="72" t="n"/>
       <c r="C313" s="73" t="n"/>
@@ -29245,7 +29260,7 @@
       <c r="F313" s="69" t="n"/>
       <c r="G313" s="69" t="n"/>
     </row>
-    <row r="314">
+    <row r="314" s="477">
       <c r="A314" s="69" t="n"/>
       <c r="B314" s="72" t="n"/>
       <c r="C314" s="73" t="n"/>
@@ -29254,7 +29269,7 @@
       <c r="F314" s="69" t="n"/>
       <c r="G314" s="69" t="n"/>
     </row>
-    <row r="315">
+    <row r="315" s="477">
       <c r="A315" s="69" t="n"/>
       <c r="B315" s="72" t="n"/>
       <c r="C315" s="73" t="n"/>
@@ -29263,7 +29278,7 @@
       <c r="F315" s="69" t="n"/>
       <c r="G315" s="69" t="n"/>
     </row>
-    <row r="316">
+    <row r="316" s="477">
       <c r="A316" s="69" t="n"/>
       <c r="B316" s="72" t="n"/>
       <c r="C316" s="73" t="n"/>
@@ -29272,7 +29287,7 @@
       <c r="F316" s="69" t="n"/>
       <c r="G316" s="69" t="n"/>
     </row>
-    <row r="317">
+    <row r="317" s="477">
       <c r="A317" s="69" t="n"/>
       <c r="B317" s="72" t="n"/>
       <c r="C317" s="73" t="n"/>
@@ -29281,7 +29296,7 @@
       <c r="F317" s="69" t="n"/>
       <c r="G317" s="69" t="n"/>
     </row>
-    <row r="318">
+    <row r="318" s="477">
       <c r="A318" s="69" t="n"/>
       <c r="B318" s="72" t="n"/>
       <c r="C318" s="73" t="n"/>
@@ -29290,7 +29305,7 @@
       <c r="F318" s="69" t="n"/>
       <c r="G318" s="69" t="n"/>
     </row>
-    <row r="319">
+    <row r="319" s="477">
       <c r="A319" s="69" t="n"/>
       <c r="B319" s="72" t="n"/>
       <c r="C319" s="73" t="n"/>
@@ -29299,7 +29314,7 @@
       <c r="F319" s="69" t="n"/>
       <c r="G319" s="69" t="n"/>
     </row>
-    <row r="320">
+    <row r="320" s="477">
       <c r="A320" s="69" t="n"/>
       <c r="B320" s="72" t="n"/>
       <c r="C320" s="73" t="n"/>
@@ -29308,7 +29323,7 @@
       <c r="F320" s="69" t="n"/>
       <c r="G320" s="69" t="n"/>
     </row>
-    <row r="321">
+    <row r="321" s="477">
       <c r="A321" s="69" t="n"/>
       <c r="B321" s="72" t="n"/>
       <c r="C321" s="73" t="n"/>
@@ -29317,7 +29332,7 @@
       <c r="F321" s="69" t="n"/>
       <c r="G321" s="69" t="n"/>
     </row>
-    <row r="322">
+    <row r="322" s="477">
       <c r="A322" s="69" t="n"/>
       <c r="B322" s="72" t="n"/>
       <c r="C322" s="73" t="n"/>
@@ -29326,7 +29341,7 @@
       <c r="F322" s="69" t="n"/>
       <c r="G322" s="69" t="n"/>
     </row>
-    <row r="323">
+    <row r="323" s="477">
       <c r="A323" s="69" t="n"/>
       <c r="B323" s="72" t="n"/>
       <c r="C323" s="73" t="n"/>
@@ -29335,7 +29350,7 @@
       <c r="F323" s="69" t="n"/>
       <c r="G323" s="69" t="n"/>
     </row>
-    <row r="324">
+    <row r="324" s="477">
       <c r="A324" s="69" t="n"/>
       <c r="B324" s="72" t="n"/>
       <c r="C324" s="73" t="n"/>
@@ -29344,7 +29359,7 @@
       <c r="F324" s="69" t="n"/>
       <c r="G324" s="69" t="n"/>
     </row>
-    <row r="325">
+    <row r="325" s="477">
       <c r="A325" s="69" t="n"/>
       <c r="B325" s="72" t="n"/>
       <c r="C325" s="73" t="n"/>
@@ -29353,7 +29368,7 @@
       <c r="F325" s="69" t="n"/>
       <c r="G325" s="69" t="n"/>
     </row>
-    <row r="326">
+    <row r="326" s="477">
       <c r="A326" s="69" t="n"/>
       <c r="B326" s="72" t="n"/>
       <c r="C326" s="73" t="n"/>
@@ -29362,7 +29377,7 @@
       <c r="F326" s="69" t="n"/>
       <c r="G326" s="69" t="n"/>
     </row>
-    <row r="327">
+    <row r="327" s="477">
       <c r="A327" s="69" t="n"/>
       <c r="B327" s="72" t="n"/>
       <c r="C327" s="73" t="n"/>
@@ -29371,7 +29386,7 @@
       <c r="F327" s="69" t="n"/>
       <c r="G327" s="69" t="n"/>
     </row>
-    <row r="328">
+    <row r="328" s="477">
       <c r="A328" s="69" t="n"/>
       <c r="B328" s="72" t="n"/>
       <c r="C328" s="73" t="n"/>
@@ -29380,7 +29395,7 @@
       <c r="F328" s="69" t="n"/>
       <c r="G328" s="69" t="n"/>
     </row>
-    <row r="329">
+    <row r="329" s="477">
       <c r="A329" s="69" t="n"/>
       <c r="B329" s="72" t="n"/>
       <c r="C329" s="73" t="n"/>
@@ -29389,7 +29404,7 @@
       <c r="F329" s="69" t="n"/>
       <c r="G329" s="69" t="n"/>
     </row>
-    <row r="330">
+    <row r="330" s="477">
       <c r="A330" s="69" t="n"/>
       <c r="B330" s="72" t="n"/>
       <c r="C330" s="73" t="n"/>
@@ -29398,7 +29413,7 @@
       <c r="F330" s="69" t="n"/>
       <c r="G330" s="69" t="n"/>
     </row>
-    <row r="331">
+    <row r="331" s="477">
       <c r="A331" s="69" t="n"/>
       <c r="B331" s="72" t="n"/>
       <c r="C331" s="73" t="n"/>
@@ -29407,7 +29422,7 @@
       <c r="F331" s="69" t="n"/>
       <c r="G331" s="69" t="n"/>
     </row>
-    <row r="332">
+    <row r="332" s="477">
       <c r="A332" s="69" t="n"/>
       <c r="B332" s="72" t="n"/>
       <c r="C332" s="73" t="n"/>
@@ -29416,7 +29431,7 @@
       <c r="F332" s="69" t="n"/>
       <c r="G332" s="69" t="n"/>
     </row>
-    <row r="333">
+    <row r="333" s="477">
       <c r="A333" s="69" t="n"/>
       <c r="B333" s="72" t="n"/>
       <c r="C333" s="73" t="n"/>
@@ -29425,7 +29440,7 @@
       <c r="F333" s="69" t="n"/>
       <c r="G333" s="69" t="n"/>
     </row>
-    <row r="334">
+    <row r="334" s="477">
       <c r="A334" s="69" t="n"/>
       <c r="B334" s="72" t="n"/>
       <c r="C334" s="73" t="n"/>
@@ -29434,7 +29449,7 @@
       <c r="F334" s="69" t="n"/>
       <c r="G334" s="69" t="n"/>
     </row>
-    <row r="335">
+    <row r="335" s="477">
       <c r="A335" s="69" t="n"/>
       <c r="B335" s="72" t="n"/>
       <c r="C335" s="73" t="n"/>
@@ -29443,7 +29458,7 @@
       <c r="F335" s="69" t="n"/>
       <c r="G335" s="69" t="n"/>
     </row>
-    <row r="336">
+    <row r="336" s="477">
       <c r="A336" s="69" t="n"/>
       <c r="B336" s="72" t="n"/>
       <c r="C336" s="73" t="n"/>
@@ -29452,7 +29467,7 @@
       <c r="F336" s="69" t="n"/>
       <c r="G336" s="69" t="n"/>
     </row>
-    <row r="337">
+    <row r="337" s="477">
       <c r="A337" s="69" t="n"/>
       <c r="B337" s="72" t="n"/>
       <c r="C337" s="73" t="n"/>
@@ -29461,7 +29476,7 @@
       <c r="F337" s="69" t="n"/>
       <c r="G337" s="69" t="n"/>
     </row>
-    <row r="338">
+    <row r="338" s="477">
       <c r="A338" s="69" t="n"/>
       <c r="B338" s="72" t="n"/>
       <c r="C338" s="73" t="n"/>
@@ -29470,7 +29485,7 @@
       <c r="F338" s="69" t="n"/>
       <c r="G338" s="69" t="n"/>
     </row>
-    <row r="339">
+    <row r="339" s="477">
       <c r="A339" s="69" t="n"/>
       <c r="B339" s="72" t="n"/>
       <c r="C339" s="73" t="n"/>
@@ -29479,7 +29494,7 @@
       <c r="F339" s="69" t="n"/>
       <c r="G339" s="69" t="n"/>
     </row>
-    <row r="340">
+    <row r="340" s="477">
       <c r="A340" s="69" t="n"/>
       <c r="B340" s="72" t="n"/>
       <c r="C340" s="73" t="n"/>
@@ -29488,7 +29503,7 @@
       <c r="F340" s="69" t="n"/>
       <c r="G340" s="69" t="n"/>
     </row>
-    <row r="341">
+    <row r="341" s="477">
       <c r="A341" s="69" t="n"/>
       <c r="B341" s="72" t="n"/>
       <c r="C341" s="73" t="n"/>
@@ -29497,7 +29512,7 @@
       <c r="F341" s="69" t="n"/>
       <c r="G341" s="69" t="n"/>
     </row>
-    <row r="342">
+    <row r="342" s="477">
       <c r="A342" s="69" t="n"/>
       <c r="B342" s="72" t="n"/>
       <c r="C342" s="73" t="n"/>
@@ -29506,7 +29521,7 @@
       <c r="F342" s="69" t="n"/>
       <c r="G342" s="69" t="n"/>
     </row>
-    <row r="343">
+    <row r="343" s="477">
       <c r="A343" s="69" t="n"/>
       <c r="B343" s="72" t="n"/>
       <c r="C343" s="73" t="n"/>
@@ -29515,7 +29530,7 @@
       <c r="F343" s="69" t="n"/>
       <c r="G343" s="69" t="n"/>
     </row>
-    <row r="344">
+    <row r="344" s="477">
       <c r="A344" s="69" t="n"/>
       <c r="B344" s="72" t="n"/>
       <c r="C344" s="73" t="n"/>
@@ -29524,7 +29539,7 @@
       <c r="F344" s="69" t="n"/>
       <c r="G344" s="69" t="n"/>
     </row>
-    <row r="345">
+    <row r="345" s="477">
       <c r="A345" s="69" t="n"/>
       <c r="B345" s="72" t="n"/>
       <c r="C345" s="73" t="n"/>
@@ -29533,7 +29548,7 @@
       <c r="F345" s="69" t="n"/>
       <c r="G345" s="69" t="n"/>
     </row>
-    <row r="346">
+    <row r="346" s="477">
       <c r="A346" s="69" t="n"/>
       <c r="B346" s="72" t="n"/>
       <c r="C346" s="73" t="n"/>
@@ -29542,7 +29557,7 @@
       <c r="F346" s="69" t="n"/>
       <c r="G346" s="69" t="n"/>
     </row>
-    <row r="347">
+    <row r="347" s="477">
       <c r="A347" s="69" t="n"/>
       <c r="B347" s="72" t="n"/>
       <c r="C347" s="73" t="n"/>
@@ -29551,7 +29566,7 @@
       <c r="F347" s="69" t="n"/>
       <c r="G347" s="69" t="n"/>
     </row>
-    <row r="348">
+    <row r="348" s="477">
       <c r="A348" s="69" t="n"/>
       <c r="B348" s="72" t="n"/>
       <c r="C348" s="73" t="n"/>
@@ -29560,7 +29575,7 @@
       <c r="F348" s="69" t="n"/>
       <c r="G348" s="69" t="n"/>
     </row>
-    <row r="349">
+    <row r="349" s="477">
       <c r="A349" s="69" t="n"/>
       <c r="B349" s="72" t="n"/>
       <c r="C349" s="73" t="n"/>
@@ -29569,7 +29584,7 @@
       <c r="F349" s="69" t="n"/>
       <c r="G349" s="69" t="n"/>
     </row>
-    <row r="350">
+    <row r="350" s="477">
       <c r="A350" s="69" t="n"/>
       <c r="B350" s="72" t="n"/>
       <c r="C350" s="73" t="n"/>
@@ -29578,7 +29593,7 @@
       <c r="F350" s="69" t="n"/>
       <c r="G350" s="69" t="n"/>
     </row>
-    <row r="351">
+    <row r="351" s="477">
       <c r="A351" s="69" t="n"/>
       <c r="B351" s="72" t="n"/>
       <c r="C351" s="73" t="n"/>
@@ -29587,7 +29602,7 @@
       <c r="F351" s="69" t="n"/>
       <c r="G351" s="69" t="n"/>
     </row>
-    <row r="352">
+    <row r="352" s="477">
       <c r="A352" s="69" t="n"/>
       <c r="B352" s="72" t="n"/>
       <c r="C352" s="73" t="n"/>
@@ -29596,7 +29611,7 @@
       <c r="F352" s="69" t="n"/>
       <c r="G352" s="69" t="n"/>
     </row>
-    <row r="353">
+    <row r="353" s="477">
       <c r="A353" s="69" t="n"/>
       <c r="B353" s="72" t="n"/>
       <c r="C353" s="73" t="n"/>
@@ -29605,7 +29620,7 @@
       <c r="F353" s="69" t="n"/>
       <c r="G353" s="69" t="n"/>
     </row>
-    <row r="354">
+    <row r="354" s="477">
       <c r="A354" s="69" t="n"/>
       <c r="B354" s="72" t="n"/>
       <c r="C354" s="73" t="n"/>
@@ -29614,7 +29629,7 @@
       <c r="F354" s="69" t="n"/>
       <c r="G354" s="69" t="n"/>
     </row>
-    <row r="355">
+    <row r="355" s="477">
       <c r="A355" s="69" t="n"/>
       <c r="B355" s="72" t="n"/>
       <c r="C355" s="73" t="n"/>
@@ -29623,7 +29638,7 @@
       <c r="F355" s="69" t="n"/>
       <c r="G355" s="69" t="n"/>
     </row>
-    <row r="356">
+    <row r="356" s="477">
       <c r="A356" s="69" t="n"/>
       <c r="B356" s="72" t="n"/>
       <c r="C356" s="73" t="n"/>
@@ -29632,7 +29647,7 @@
       <c r="F356" s="69" t="n"/>
       <c r="G356" s="69" t="n"/>
     </row>
-    <row r="357">
+    <row r="357" s="477">
       <c r="A357" s="69" t="n"/>
       <c r="B357" s="72" t="n"/>
       <c r="C357" s="73" t="n"/>
@@ -29641,7 +29656,7 @@
       <c r="F357" s="69" t="n"/>
       <c r="G357" s="69" t="n"/>
     </row>
-    <row r="358">
+    <row r="358" s="477">
       <c r="A358" s="69" t="n"/>
       <c r="B358" s="72" t="n"/>
       <c r="C358" s="73" t="n"/>
@@ -29650,7 +29665,7 @@
       <c r="F358" s="69" t="n"/>
       <c r="G358" s="69" t="n"/>
     </row>
-    <row r="359">
+    <row r="359" s="477">
       <c r="A359" s="69" t="n"/>
       <c r="B359" s="72" t="n"/>
       <c r="C359" s="73" t="n"/>
@@ -29659,7 +29674,7 @@
       <c r="F359" s="69" t="n"/>
       <c r="G359" s="69" t="n"/>
     </row>
-    <row r="360">
+    <row r="360" s="477">
       <c r="A360" s="69" t="n"/>
       <c r="B360" s="72" t="n"/>
       <c r="C360" s="73" t="n"/>
@@ -29668,7 +29683,7 @@
       <c r="F360" s="69" t="n"/>
       <c r="G360" s="69" t="n"/>
     </row>
-    <row r="361">
+    <row r="361" s="477">
       <c r="A361" s="69" t="n"/>
       <c r="B361" s="72" t="n"/>
       <c r="C361" s="73" t="n"/>
@@ -29677,7 +29692,7 @@
       <c r="F361" s="69" t="n"/>
       <c r="G361" s="69" t="n"/>
     </row>
-    <row r="362">
+    <row r="362" s="477">
       <c r="A362" s="69" t="n"/>
       <c r="B362" s="72" t="n"/>
       <c r="C362" s="73" t="n"/>
@@ -29686,7 +29701,7 @@
       <c r="F362" s="69" t="n"/>
       <c r="G362" s="69" t="n"/>
     </row>
-    <row r="363">
+    <row r="363" s="477">
       <c r="A363" s="69" t="n"/>
       <c r="B363" s="72" t="n"/>
       <c r="C363" s="73" t="n"/>
@@ -29695,7 +29710,7 @@
       <c r="F363" s="69" t="n"/>
       <c r="G363" s="69" t="n"/>
     </row>
-    <row r="364">
+    <row r="364" s="477">
       <c r="A364" s="69" t="n"/>
       <c r="B364" s="72" t="n"/>
       <c r="C364" s="73" t="n"/>
@@ -29704,7 +29719,7 @@
       <c r="F364" s="69" t="n"/>
       <c r="G364" s="69" t="n"/>
     </row>
-    <row r="365">
+    <row r="365" s="477">
       <c r="A365" s="69" t="n"/>
       <c r="B365" s="72" t="n"/>
       <c r="C365" s="73" t="n"/>
@@ -29713,7 +29728,7 @@
       <c r="F365" s="69" t="n"/>
       <c r="G365" s="69" t="n"/>
     </row>
-    <row r="366">
+    <row r="366" s="477">
       <c r="A366" s="69" t="n"/>
       <c r="B366" s="72" t="n"/>
       <c r="C366" s="73" t="n"/>
@@ -29722,7 +29737,7 @@
       <c r="F366" s="69" t="n"/>
       <c r="G366" s="69" t="n"/>
     </row>
-    <row r="367">
+    <row r="367" s="477">
       <c r="A367" s="69" t="n"/>
       <c r="B367" s="72" t="n"/>
       <c r="C367" s="73" t="n"/>
@@ -29731,7 +29746,7 @@
       <c r="F367" s="69" t="n"/>
       <c r="G367" s="69" t="n"/>
     </row>
-    <row r="368">
+    <row r="368" s="477">
       <c r="A368" s="69" t="n"/>
       <c r="B368" s="72" t="n"/>
       <c r="C368" s="73" t="n"/>
@@ -29740,7 +29755,7 @@
       <c r="F368" s="69" t="n"/>
       <c r="G368" s="69" t="n"/>
     </row>
-    <row r="369">
+    <row r="369" s="477">
       <c r="A369" s="69" t="n"/>
       <c r="B369" s="72" t="n"/>
       <c r="C369" s="73" t="n"/>
@@ -29749,7 +29764,7 @@
       <c r="F369" s="69" t="n"/>
       <c r="G369" s="69" t="n"/>
     </row>
-    <row r="370">
+    <row r="370" s="477">
       <c r="A370" s="69" t="n"/>
       <c r="B370" s="72" t="n"/>
       <c r="C370" s="73" t="n"/>
@@ -29758,7 +29773,7 @@
       <c r="F370" s="69" t="n"/>
       <c r="G370" s="69" t="n"/>
     </row>
-    <row r="371">
+    <row r="371" s="477">
       <c r="A371" s="69" t="n"/>
       <c r="B371" s="72" t="n"/>
       <c r="C371" s="73" t="n"/>
@@ -29767,7 +29782,7 @@
       <c r="F371" s="69" t="n"/>
       <c r="G371" s="69" t="n"/>
     </row>
-    <row r="372">
+    <row r="372" s="477">
       <c r="A372" s="69" t="n"/>
       <c r="B372" s="72" t="n"/>
       <c r="C372" s="73" t="n"/>
@@ -29776,7 +29791,7 @@
       <c r="F372" s="69" t="n"/>
       <c r="G372" s="69" t="n"/>
     </row>
-    <row r="373">
+    <row r="373" s="477">
       <c r="A373" s="69" t="n"/>
       <c r="B373" s="72" t="n"/>
       <c r="C373" s="73" t="n"/>
@@ -29785,7 +29800,7 @@
       <c r="F373" s="69" t="n"/>
       <c r="G373" s="69" t="n"/>
     </row>
-    <row r="374">
+    <row r="374" s="477">
       <c r="A374" s="69" t="n"/>
       <c r="B374" s="72" t="n"/>
       <c r="C374" s="73" t="n"/>
@@ -29794,7 +29809,7 @@
       <c r="F374" s="69" t="n"/>
       <c r="G374" s="69" t="n"/>
     </row>
-    <row r="375">
+    <row r="375" s="477">
       <c r="A375" s="69" t="n"/>
       <c r="B375" s="72" t="n"/>
       <c r="C375" s="73" t="n"/>
@@ -29803,7 +29818,7 @@
       <c r="F375" s="69" t="n"/>
       <c r="G375" s="69" t="n"/>
     </row>
-    <row r="376">
+    <row r="376" s="477">
       <c r="A376" s="69" t="n"/>
       <c r="B376" s="72" t="n"/>
       <c r="C376" s="73" t="n"/>
@@ -29812,7 +29827,7 @@
       <c r="F376" s="69" t="n"/>
       <c r="G376" s="69" t="n"/>
     </row>
-    <row r="377">
+    <row r="377" s="477">
       <c r="A377" s="69" t="n"/>
       <c r="B377" s="72" t="n"/>
       <c r="C377" s="73" t="n"/>
@@ -29821,7 +29836,7 @@
       <c r="F377" s="69" t="n"/>
       <c r="G377" s="69" t="n"/>
     </row>
-    <row r="378">
+    <row r="378" s="477">
       <c r="A378" s="69" t="n"/>
       <c r="B378" s="72" t="n"/>
       <c r="C378" s="73" t="n"/>
@@ -29830,7 +29845,7 @@
       <c r="F378" s="69" t="n"/>
       <c r="G378" s="69" t="n"/>
     </row>
-    <row r="379">
+    <row r="379" s="477">
       <c r="A379" s="69" t="n"/>
       <c r="B379" s="72" t="n"/>
       <c r="C379" s="73" t="n"/>
@@ -29839,7 +29854,7 @@
       <c r="F379" s="69" t="n"/>
       <c r="G379" s="69" t="n"/>
     </row>
-    <row r="380">
+    <row r="380" s="477">
       <c r="A380" s="69" t="n"/>
       <c r="B380" s="72" t="n"/>
       <c r="C380" s="73" t="n"/>
@@ -29848,7 +29863,7 @@
       <c r="F380" s="69" t="n"/>
       <c r="G380" s="69" t="n"/>
     </row>
-    <row r="381">
+    <row r="381" s="477">
       <c r="A381" s="69" t="n"/>
       <c r="B381" s="72" t="n"/>
       <c r="C381" s="73" t="n"/>
@@ -29857,7 +29872,7 @@
       <c r="F381" s="69" t="n"/>
       <c r="G381" s="69" t="n"/>
     </row>
-    <row r="382">
+    <row r="382" s="477">
       <c r="A382" s="69" t="n"/>
       <c r="B382" s="72" t="n"/>
       <c r="C382" s="73" t="n"/>
@@ -29866,7 +29881,7 @@
       <c r="F382" s="69" t="n"/>
       <c r="G382" s="69" t="n"/>
     </row>
-    <row r="383">
+    <row r="383" s="477">
       <c r="A383" s="69" t="n"/>
       <c r="B383" s="72" t="n"/>
       <c r="C383" s="73" t="n"/>
@@ -29875,7 +29890,7 @@
       <c r="F383" s="69" t="n"/>
       <c r="G383" s="69" t="n"/>
     </row>
-    <row r="384">
+    <row r="384" s="477">
       <c r="A384" s="69" t="n"/>
       <c r="B384" s="72" t="n"/>
       <c r="C384" s="73" t="n"/>
@@ -29884,7 +29899,7 @@
       <c r="F384" s="69" t="n"/>
       <c r="G384" s="69" t="n"/>
     </row>
-    <row r="385">
+    <row r="385" s="477">
       <c r="A385" s="69" t="n"/>
       <c r="B385" s="72" t="n"/>
       <c r="C385" s="73" t="n"/>
@@ -29893,7 +29908,7 @@
       <c r="F385" s="69" t="n"/>
       <c r="G385" s="69" t="n"/>
     </row>
-    <row r="386">
+    <row r="386" s="477">
       <c r="A386" s="69" t="n"/>
       <c r="B386" s="72" t="n"/>
       <c r="C386" s="73" t="n"/>
@@ -29902,7 +29917,7 @@
       <c r="F386" s="69" t="n"/>
       <c r="G386" s="69" t="n"/>
     </row>
-    <row r="387">
+    <row r="387" s="477">
       <c r="A387" s="69" t="n"/>
       <c r="B387" s="72" t="n"/>
       <c r="C387" s="73" t="n"/>
@@ -29911,7 +29926,7 @@
       <c r="F387" s="69" t="n"/>
       <c r="G387" s="69" t="n"/>
     </row>
-    <row r="388">
+    <row r="388" s="477">
       <c r="A388" s="69" t="n"/>
       <c r="B388" s="72" t="n"/>
       <c r="C388" s="73" t="n"/>
@@ -29920,7 +29935,7 @@
       <c r="F388" s="69" t="n"/>
       <c r="G388" s="69" t="n"/>
     </row>
-    <row r="389">
+    <row r="389" s="477">
       <c r="A389" s="69" t="n"/>
       <c r="B389" s="72" t="n"/>
       <c r="C389" s="73" t="n"/>
@@ -29929,7 +29944,7 @@
       <c r="F389" s="69" t="n"/>
       <c r="G389" s="69" t="n"/>
     </row>
-    <row r="390">
+    <row r="390" s="477">
       <c r="A390" s="69" t="n"/>
       <c r="B390" s="72" t="n"/>
       <c r="C390" s="73" t="n"/>
@@ -29938,7 +29953,7 @@
       <c r="F390" s="69" t="n"/>
       <c r="G390" s="69" t="n"/>
     </row>
-    <row r="391">
+    <row r="391" s="477">
       <c r="A391" s="69" t="n"/>
       <c r="B391" s="72" t="n"/>
       <c r="C391" s="73" t="n"/>
@@ -29947,7 +29962,7 @@
       <c r="F391" s="69" t="n"/>
       <c r="G391" s="69" t="n"/>
     </row>
-    <row r="392">
+    <row r="392" s="477">
       <c r="A392" s="69" t="n"/>
       <c r="B392" s="72" t="n"/>
       <c r="C392" s="73" t="n"/>
@@ -29956,7 +29971,7 @@
       <c r="F392" s="69" t="n"/>
       <c r="G392" s="69" t="n"/>
     </row>
-    <row r="393">
+    <row r="393" s="477">
       <c r="A393" s="69" t="n"/>
       <c r="B393" s="72" t="n"/>
       <c r="C393" s="73" t="n"/>
@@ -29965,7 +29980,7 @@
       <c r="F393" s="69" t="n"/>
       <c r="G393" s="69" t="n"/>
     </row>
-    <row r="394">
+    <row r="394" s="477">
       <c r="A394" s="69" t="n"/>
       <c r="B394" s="72" t="n"/>
       <c r="C394" s="73" t="n"/>
@@ -29974,7 +29989,7 @@
       <c r="F394" s="69" t="n"/>
       <c r="G394" s="69" t="n"/>
     </row>
-    <row r="395">
+    <row r="395" s="477">
       <c r="A395" s="69" t="n"/>
       <c r="B395" s="72" t="n"/>
       <c r="C395" s="73" t="n"/>
@@ -29983,7 +29998,7 @@
       <c r="F395" s="69" t="n"/>
       <c r="G395" s="69" t="n"/>
     </row>
-    <row r="396">
+    <row r="396" s="477">
       <c r="A396" s="69" t="n"/>
       <c r="B396" s="72" t="n"/>
       <c r="C396" s="73" t="n"/>
@@ -29992,7 +30007,7 @@
       <c r="F396" s="69" t="n"/>
       <c r="G396" s="69" t="n"/>
     </row>
-    <row r="397">
+    <row r="397" s="477">
       <c r="A397" s="69" t="n"/>
       <c r="B397" s="72" t="n"/>
       <c r="C397" s="73" t="n"/>
@@ -30001,7 +30016,7 @@
       <c r="F397" s="69" t="n"/>
       <c r="G397" s="69" t="n"/>
     </row>
-    <row r="398">
+    <row r="398" s="477">
       <c r="A398" s="69" t="n"/>
       <c r="B398" s="72" t="n"/>
       <c r="C398" s="73" t="n"/>
@@ -30010,7 +30025,7 @@
       <c r="F398" s="69" t="n"/>
       <c r="G398" s="69" t="n"/>
     </row>
-    <row r="399">
+    <row r="399" s="477">
       <c r="A399" s="69" t="n"/>
       <c r="B399" s="72" t="n"/>
       <c r="C399" s="73" t="n"/>
@@ -30019,7 +30034,7 @@
       <c r="F399" s="69" t="n"/>
       <c r="G399" s="69" t="n"/>
     </row>
-    <row r="400">
+    <row r="400" s="477">
       <c r="A400" s="69" t="n"/>
       <c r="B400" s="72" t="n"/>
       <c r="C400" s="73" t="n"/>
@@ -30028,7 +30043,7 @@
       <c r="F400" s="69" t="n"/>
       <c r="G400" s="69" t="n"/>
     </row>
-    <row r="401">
+    <row r="401" s="477">
       <c r="A401" s="69" t="n"/>
       <c r="B401" s="72" t="n"/>
       <c r="C401" s="73" t="n"/>
@@ -30037,7 +30052,7 @@
       <c r="F401" s="69" t="n"/>
       <c r="G401" s="69" t="n"/>
     </row>
-    <row r="402">
+    <row r="402" s="477">
       <c r="A402" s="69" t="n"/>
       <c r="B402" s="72" t="n"/>
       <c r="C402" s="73" t="n"/>
@@ -30046,7 +30061,7 @@
       <c r="F402" s="69" t="n"/>
       <c r="G402" s="69" t="n"/>
     </row>
-    <row r="403">
+    <row r="403" s="477">
       <c r="A403" s="69" t="n"/>
       <c r="B403" s="72" t="n"/>
       <c r="C403" s="73" t="n"/>
@@ -30055,7 +30070,7 @@
       <c r="F403" s="69" t="n"/>
       <c r="G403" s="69" t="n"/>
     </row>
-    <row r="404">
+    <row r="404" s="477">
       <c r="A404" s="69" t="n"/>
       <c r="B404" s="72" t="n"/>
       <c r="C404" s="73" t="n"/>
@@ -30064,7 +30079,7 @@
       <c r="F404" s="69" t="n"/>
       <c r="G404" s="69" t="n"/>
     </row>
-    <row r="405">
+    <row r="405" s="477">
       <c r="A405" s="69" t="n"/>
       <c r="B405" s="72" t="n"/>
       <c r="C405" s="73" t="n"/>
@@ -30073,7 +30088,7 @@
       <c r="F405" s="69" t="n"/>
       <c r="G405" s="69" t="n"/>
     </row>
-    <row r="406">
+    <row r="406" s="477">
       <c r="A406" s="69" t="n"/>
       <c r="B406" s="72" t="n"/>
       <c r="C406" s="73" t="n"/>
@@ -30082,7 +30097,7 @@
       <c r="F406" s="69" t="n"/>
       <c r="G406" s="69" t="n"/>
     </row>
-    <row r="407">
+    <row r="407" s="477">
       <c r="A407" s="69" t="n"/>
       <c r="B407" s="72" t="n"/>
       <c r="C407" s="73" t="n"/>
@@ -30091,7 +30106,7 @@
       <c r="F407" s="69" t="n"/>
       <c r="G407" s="69" t="n"/>
     </row>
-    <row r="408">
+    <row r="408" s="477">
       <c r="A408" s="69" t="n"/>
       <c r="B408" s="72" t="n"/>
       <c r="C408" s="73" t="n"/>
@@ -30100,7 +30115,7 @@
       <c r="F408" s="69" t="n"/>
       <c r="G408" s="69" t="n"/>
     </row>
-    <row r="409">
+    <row r="409" s="477">
       <c r="A409" s="69" t="n"/>
       <c r="B409" s="72" t="n"/>
       <c r="C409" s="73" t="n"/>
@@ -30109,7 +30124,7 @@
       <c r="F409" s="69" t="n"/>
       <c r="G409" s="69" t="n"/>
     </row>
-    <row r="410">
+    <row r="410" s="477">
       <c r="A410" s="69" t="n"/>
       <c r="B410" s="72" t="n"/>
       <c r="C410" s="73" t="n"/>
@@ -30118,7 +30133,7 @@
       <c r="F410" s="69" t="n"/>
       <c r="G410" s="69" t="n"/>
     </row>
-    <row r="411">
+    <row r="411" s="477">
       <c r="A411" s="69" t="n"/>
       <c r="B411" s="72" t="n"/>
       <c r="C411" s="73" t="n"/>
@@ -30127,7 +30142,7 @@
       <c r="F411" s="69" t="n"/>
       <c r="G411" s="69" t="n"/>
     </row>
-    <row r="412">
+    <row r="412" s="477">
       <c r="A412" s="69" t="n"/>
       <c r="B412" s="72" t="n"/>
       <c r="C412" s="73" t="n"/>
@@ -30136,7 +30151,7 @@
       <c r="F412" s="69" t="n"/>
       <c r="G412" s="69" t="n"/>
     </row>
-    <row r="413">
+    <row r="413" s="477">
       <c r="A413" s="69" t="n"/>
       <c r="B413" s="72" t="n"/>
       <c r="C413" s="73" t="n"/>
@@ -30145,7 +30160,7 @@
       <c r="F413" s="69" t="n"/>
       <c r="G413" s="69" t="n"/>
     </row>
-    <row r="414">
+    <row r="414" s="477">
       <c r="A414" s="69" t="n"/>
       <c r="B414" s="72" t="n"/>
       <c r="C414" s="73" t="n"/>
@@ -30154,7 +30169,7 @@
       <c r="F414" s="69" t="n"/>
       <c r="G414" s="69" t="n"/>
     </row>
-    <row r="415">
+    <row r="415" s="477">
       <c r="A415" s="69" t="n"/>
       <c r="B415" s="72" t="n"/>
       <c r="C415" s="73" t="n"/>
@@ -30163,7 +30178,7 @@
       <c r="F415" s="69" t="n"/>
       <c r="G415" s="69" t="n"/>
     </row>
-    <row r="416">
+    <row r="416" s="477">
       <c r="A416" s="69" t="n"/>
       <c r="B416" s="72" t="n"/>
       <c r="C416" s="73" t="n"/>
@@ -30172,7 +30187,7 @@
       <c r="F416" s="69" t="n"/>
       <c r="G416" s="69" t="n"/>
     </row>
-    <row r="417">
+    <row r="417" s="477">
       <c r="A417" s="69" t="n"/>
       <c r="B417" s="72" t="n"/>
       <c r="C417" s="73" t="n"/>
@@ -30181,7 +30196,7 @@
       <c r="F417" s="69" t="n"/>
       <c r="G417" s="69" t="n"/>
     </row>
-    <row r="418">
+    <row r="418" s="477">
       <c r="A418" s="69" t="n"/>
       <c r="B418" s="72" t="n"/>
       <c r="C418" s="73" t="n"/>
@@ -30190,7 +30205,7 @@
       <c r="F418" s="69" t="n"/>
       <c r="G418" s="69" t="n"/>
     </row>
-    <row r="419">
+    <row r="419" s="477">
       <c r="A419" s="69" t="n"/>
       <c r="B419" s="72" t="n"/>
       <c r="C419" s="73" t="n"/>
@@ -30199,7 +30214,7 @@
       <c r="F419" s="69" t="n"/>
       <c r="G419" s="69" t="n"/>
     </row>
-    <row r="420">
+    <row r="420" s="477">
       <c r="A420" s="69" t="n"/>
       <c r="B420" s="72" t="n"/>
       <c r="C420" s="73" t="n"/>
@@ -30208,7 +30223,7 @@
       <c r="F420" s="69" t="n"/>
       <c r="G420" s="69" t="n"/>
     </row>
-    <row r="421">
+    <row r="421" s="477">
       <c r="A421" s="69" t="n"/>
       <c r="B421" s="72" t="n"/>
       <c r="C421" s="73" t="n"/>
@@ -30217,7 +30232,7 @@
       <c r="F421" s="69" t="n"/>
       <c r="G421" s="69" t="n"/>
     </row>
-    <row r="422">
+    <row r="422" s="477">
       <c r="A422" s="69" t="n"/>
       <c r="B422" s="72" t="n"/>
       <c r="C422" s="73" t="n"/>
@@ -30226,7 +30241,7 @@
       <c r="F422" s="69" t="n"/>
       <c r="G422" s="69" t="n"/>
     </row>
-    <row r="423">
+    <row r="423" s="477">
       <c r="A423" s="69" t="n"/>
       <c r="B423" s="72" t="n"/>
       <c r="C423" s="73" t="n"/>
@@ -30235,7 +30250,7 @@
       <c r="F423" s="69" t="n"/>
       <c r="G423" s="69" t="n"/>
     </row>
-    <row r="424">
+    <row r="424" s="477">
       <c r="A424" s="69" t="n"/>
       <c r="B424" s="72" t="n"/>
       <c r="C424" s="73" t="n"/>
@@ -30244,7 +30259,7 @@
       <c r="F424" s="69" t="n"/>
       <c r="G424" s="69" t="n"/>
     </row>
-    <row r="425">
+    <row r="425" s="477">
       <c r="A425" s="69" t="n"/>
       <c r="B425" s="72" t="n"/>
       <c r="C425" s="73" t="n"/>
@@ -30253,7 +30268,7 @@
       <c r="F425" s="69" t="n"/>
       <c r="G425" s="69" t="n"/>
     </row>
-    <row r="426">
+    <row r="426" s="477">
       <c r="A426" s="69" t="n"/>
       <c r="B426" s="72" t="n"/>
       <c r="C426" s="73" t="n"/>
@@ -30262,7 +30277,7 @@
       <c r="F426" s="69" t="n"/>
       <c r="G426" s="69" t="n"/>
     </row>
-    <row r="427">
+    <row r="427" s="477">
       <c r="A427" s="69" t="n"/>
       <c r="B427" s="72" t="n"/>
       <c r="C427" s="73" t="n"/>
@@ -30271,7 +30286,7 @@
       <c r="F427" s="69" t="n"/>
       <c r="G427" s="69" t="n"/>
     </row>
-    <row r="428">
+    <row r="428" s="477">
       <c r="A428" s="69" t="n"/>
       <c r="B428" s="72" t="n"/>
       <c r="C428" s="73" t="n"/>
@@ -30280,7 +30295,7 @@
       <c r="F428" s="69" t="n"/>
       <c r="G428" s="69" t="n"/>
     </row>
-    <row r="429">
+    <row r="429" s="477">
       <c r="A429" s="69" t="n"/>
       <c r="B429" s="72" t="n"/>
       <c r="C429" s="73" t="n"/>
@@ -30289,7 +30304,7 @@
       <c r="F429" s="69" t="n"/>
       <c r="G429" s="69" t="n"/>
     </row>
-    <row r="430">
+    <row r="430" s="477">
       <c r="A430" s="69" t="n"/>
       <c r="B430" s="72" t="n"/>
       <c r="C430" s="73" t="n"/>
@@ -30298,7 +30313,7 @@
       <c r="F430" s="69" t="n"/>
       <c r="G430" s="69" t="n"/>
     </row>
-    <row r="431">
+    <row r="431" s="477">
       <c r="A431" s="69" t="n"/>
       <c r="B431" s="72" t="n"/>
       <c r="C431" s="73" t="n"/>
@@ -30307,7 +30322,7 @@
       <c r="F431" s="69" t="n"/>
       <c r="G431" s="69" t="n"/>
     </row>
-    <row r="432">
+    <row r="432" s="477">
       <c r="A432" s="69" t="n"/>
       <c r="B432" s="72" t="n"/>
       <c r="C432" s="73" t="n"/>
@@ -30316,7 +30331,7 @@
       <c r="F432" s="69" t="n"/>
       <c r="G432" s="69" t="n"/>
     </row>
-    <row r="433">
+    <row r="433" s="477">
       <c r="A433" s="69" t="n"/>
       <c r="B433" s="72" t="n"/>
       <c r="C433" s="73" t="n"/>
@@ -30325,7 +30340,7 @@
       <c r="F433" s="69" t="n"/>
       <c r="G433" s="69" t="n"/>
     </row>
-    <row r="434">
+    <row r="434" s="477">
       <c r="A434" s="69" t="n"/>
       <c r="B434" s="72" t="n"/>
       <c r="C434" s="73" t="n"/>
@@ -30334,7 +30349,7 @@
       <c r="F434" s="69" t="n"/>
       <c r="G434" s="69" t="n"/>
     </row>
-    <row r="435">
+    <row r="435" s="477">
       <c r="A435" s="69" t="n"/>
       <c r="B435" s="72" t="n"/>
       <c r="C435" s="73" t="n"/>
@@ -30343,7 +30358,7 @@
       <c r="F435" s="69" t="n"/>
       <c r="G435" s="69" t="n"/>
     </row>
-    <row r="436">
+    <row r="436" s="477">
       <c r="A436" s="69" t="n"/>
       <c r="B436" s="72" t="n"/>
       <c r="C436" s="73" t="n"/>
@@ -30352,7 +30367,7 @@
       <c r="F436" s="69" t="n"/>
       <c r="G436" s="69" t="n"/>
     </row>
-    <row r="437">
+    <row r="437" s="477">
       <c r="A437" s="69" t="n"/>
       <c r="B437" s="72" t="n"/>
       <c r="C437" s="73" t="n"/>
@@ -30361,7 +30376,7 @@
       <c r="F437" s="69" t="n"/>
       <c r="G437" s="69" t="n"/>
     </row>
-    <row r="438">
+    <row r="438" s="477">
       <c r="A438" s="69" t="n"/>
       <c r="B438" s="72" t="n"/>
       <c r="C438" s="73" t="n"/>
@@ -30370,7 +30385,7 @@
       <c r="F438" s="69" t="n"/>
       <c r="G438" s="69" t="n"/>
     </row>
-    <row r="439">
+    <row r="439" s="477">
       <c r="A439" s="69" t="n"/>
       <c r="B439" s="72" t="n"/>
       <c r="C439" s="73" t="n"/>
@@ -30379,7 +30394,7 @@
       <c r="F439" s="69" t="n"/>
       <c r="G439" s="69" t="n"/>
     </row>
-    <row r="440">
+    <row r="440" s="477">
       <c r="A440" s="69" t="n"/>
       <c r="B440" s="72" t="n"/>
       <c r="C440" s="73" t="n"/>
@@ -30388,7 +30403,7 @@
       <c r="F440" s="69" t="n"/>
       <c r="G440" s="69" t="n"/>
     </row>
-    <row r="441">
+    <row r="441" s="477">
       <c r="A441" s="69" t="n"/>
       <c r="B441" s="72" t="n"/>
       <c r="C441" s="73" t="n"/>
@@ -30397,7 +30412,7 @@
       <c r="F441" s="69" t="n"/>
       <c r="G441" s="69" t="n"/>
     </row>
-    <row r="442">
+    <row r="442" s="477">
       <c r="A442" s="69" t="n"/>
       <c r="B442" s="72" t="n"/>
       <c r="C442" s="73" t="n"/>
@@ -30406,7 +30421,7 @@
       <c r="F442" s="69" t="n"/>
       <c r="G442" s="69" t="n"/>
     </row>
-    <row r="443">
+    <row r="443" s="477">
       <c r="A443" s="69" t="n"/>
       <c r="B443" s="72" t="n"/>
       <c r="C443" s="73" t="n"/>
@@ -30415,7 +30430,7 @@
       <c r="F443" s="69" t="n"/>
       <c r="G443" s="69" t="n"/>
     </row>
-    <row r="444">
+    <row r="444" s="477">
       <c r="A444" s="69" t="n"/>
       <c r="B444" s="72" t="n"/>
       <c r="C444" s="73" t="n"/>
@@ -30424,7 +30439,7 @@
       <c r="F444" s="69" t="n"/>
       <c r="G444" s="69" t="n"/>
     </row>
-    <row r="445">
+    <row r="445" s="477">
       <c r="A445" s="69" t="n"/>
       <c r="B445" s="72" t="n"/>
       <c r="C445" s="73" t="n"/>
@@ -30433,7 +30448,7 @@
       <c r="F445" s="69" t="n"/>
       <c r="G445" s="69" t="n"/>
     </row>
-    <row r="446">
+    <row r="446" s="477">
       <c r="A446" s="69" t="n"/>
       <c r="B446" s="72" t="n"/>
       <c r="C446" s="73" t="n"/>
@@ -30442,7 +30457,7 @@
       <c r="F446" s="69" t="n"/>
       <c r="G446" s="69" t="n"/>
     </row>
-    <row r="447">
+    <row r="447" s="477">
       <c r="A447" s="69" t="n"/>
       <c r="B447" s="72" t="n"/>
       <c r="C447" s="73" t="n"/>
@@ -30451,7 +30466,7 @@
       <c r="F447" s="69" t="n"/>
       <c r="G447" s="69" t="n"/>
     </row>
-    <row r="448">
+    <row r="448" s="477">
       <c r="A448" s="69" t="n"/>
       <c r="B448" s="72" t="n"/>
       <c r="C448" s="73" t="n"/>
@@ -30460,7 +30475,7 @@
       <c r="F448" s="69" t="n"/>
       <c r="G448" s="69" t="n"/>
     </row>
-    <row r="449">
+    <row r="449" s="477">
       <c r="A449" s="69" t="n"/>
       <c r="B449" s="72" t="n"/>
       <c r="C449" s="73" t="n"/>
@@ -30469,7 +30484,7 @@
       <c r="F449" s="69" t="n"/>
       <c r="G449" s="69" t="n"/>
     </row>
-    <row r="450">
+    <row r="450" s="477">
       <c r="A450" s="69" t="n"/>
       <c r="B450" s="72" t="n"/>
       <c r="C450" s="73" t="n"/>
@@ -30478,7 +30493,7 @@
       <c r="F450" s="69" t="n"/>
       <c r="G450" s="69" t="n"/>
     </row>
-    <row r="451">
+    <row r="451" s="477">
       <c r="A451" s="69" t="n"/>
       <c r="B451" s="72" t="n"/>
       <c r="C451" s="73" t="n"/>
@@ -30487,7 +30502,7 @@
       <c r="F451" s="69" t="n"/>
       <c r="G451" s="69" t="n"/>
     </row>
-    <row r="452">
+    <row r="452" s="477">
       <c r="A452" s="69" t="n"/>
       <c r="B452" s="72" t="n"/>
       <c r="C452" s="73" t="n"/>
@@ -30496,7 +30511,7 @@
       <c r="F452" s="69" t="n"/>
       <c r="G452" s="69" t="n"/>
     </row>
-    <row r="453">
+    <row r="453" s="477">
       <c r="A453" s="69" t="n"/>
       <c r="B453" s="72" t="n"/>
       <c r="C453" s="73" t="n"/>
@@ -30505,7 +30520,7 @@
       <c r="F453" s="69" t="n"/>
       <c r="G453" s="69" t="n"/>
     </row>
-    <row r="454">
+    <row r="454" s="477">
       <c r="A454" s="69" t="n"/>
       <c r="B454" s="72" t="n"/>
       <c r="C454" s="73" t="n"/>
@@ -30514,7 +30529,7 @@
       <c r="F454" s="69" t="n"/>
       <c r="G454" s="69" t="n"/>
     </row>
-    <row r="455">
+    <row r="455" s="477">
       <c r="A455" s="69" t="n"/>
       <c r="B455" s="72" t="n"/>
       <c r="C455" s="73" t="n"/>
@@ -30523,7 +30538,7 @@
       <c r="F455" s="69" t="n"/>
       <c r="G455" s="69" t="n"/>
     </row>
-    <row r="456">
+    <row r="456" s="477">
       <c r="A456" s="69" t="n"/>
       <c r="B456" s="72" t="n"/>
       <c r="C456" s="73" t="n"/>
@@ -30532,7 +30547,7 @@
       <c r="F456" s="69" t="n"/>
       <c r="G456" s="69" t="n"/>
     </row>
-    <row r="457">
+    <row r="457" s="477">
       <c r="A457" s="69" t="n"/>
       <c r="B457" s="72" t="n"/>
       <c r="C457" s="73" t="n"/>
@@ -30541,7 +30556,7 @@
       <c r="F457" s="69" t="n"/>
       <c r="G457" s="69" t="n"/>
     </row>
-    <row r="458">
+    <row r="458" s="477">
       <c r="A458" s="69" t="n"/>
       <c r="B458" s="72" t="n"/>
       <c r="C458" s="73" t="n"/>
@@ -30550,7 +30565,7 @@
       <c r="F458" s="69" t="n"/>
       <c r="G458" s="69" t="n"/>
     </row>
-    <row r="459">
+    <row r="459" s="477">
       <c r="A459" s="69" t="n"/>
       <c r="B459" s="72" t="n"/>
       <c r="C459" s="73" t="n"/>
@@ -30559,7 +30574,7 @@
       <c r="F459" s="69" t="n"/>
       <c r="G459" s="69" t="n"/>
     </row>
-    <row r="460">
+    <row r="460" s="477">
       <c r="A460" s="69" t="n"/>
       <c r="B460" s="72" t="n"/>
       <c r="C460" s="73" t="n"/>
@@ -30568,7 +30583,7 @@
       <c r="F460" s="69" t="n"/>
       <c r="G460" s="69" t="n"/>
     </row>
-    <row r="461">
+    <row r="461" s="477">
       <c r="A461" s="69" t="n"/>
       <c r="B461" s="72" t="n"/>
       <c r="C461" s="73" t="n"/>
@@ -30577,7 +30592,7 @@
       <c r="F461" s="69" t="n"/>
       <c r="G461" s="69" t="n"/>
     </row>
-    <row r="462">
+    <row r="462" s="477">
       <c r="A462" s="69" t="n"/>
       <c r="B462" s="72" t="n"/>
       <c r="C462" s="73" t="n"/>
@@ -30586,7 +30601,7 @@
       <c r="F462" s="69" t="n"/>
       <c r="G462" s="69" t="n"/>
     </row>
-    <row r="463">
+    <row r="463" s="477">
       <c r="A463" s="69" t="n"/>
       <c r="B463" s="72" t="n"/>
       <c r="C463" s="73" t="n"/>
@@ -30595,7 +30610,7 @@
       <c r="F463" s="69" t="n"/>
       <c r="G463" s="69" t="n"/>
     </row>
-    <row r="464">
+    <row r="464" s="477">
       <c r="A464" s="69" t="n"/>
       <c r="B464" s="72" t="n"/>
       <c r="C464" s="73" t="n"/>
@@ -30604,7 +30619,7 @@
       <c r="F464" s="69" t="n"/>
       <c r="G464" s="69" t="n"/>
     </row>
-    <row r="465">
+    <row r="465" s="477">
       <c r="A465" s="69" t="n"/>
       <c r="B465" s="72" t="n"/>
       <c r="C465" s="73" t="n"/>
@@ -30613,7 +30628,7 @@
       <c r="F465" s="69" t="n"/>
       <c r="G465" s="69" t="n"/>
     </row>
-    <row r="466">
+    <row r="466" s="477">
       <c r="A466" s="69" t="n"/>
       <c r="B466" s="72" t="n"/>
       <c r="C466" s="73" t="n"/>
@@ -30622,7 +30637,7 @@
       <c r="F466" s="69" t="n"/>
       <c r="G466" s="69" t="n"/>
     </row>
-    <row r="467">
+    <row r="467" s="477">
       <c r="A467" s="69" t="n"/>
       <c r="B467" s="72" t="n"/>
       <c r="C467" s="73" t="n"/>
@@ -30631,7 +30646,7 @@
       <c r="F467" s="69" t="n"/>
       <c r="G467" s="69" t="n"/>
     </row>
-    <row r="468">
+    <row r="468" s="477">
       <c r="A468" s="69" t="n"/>
       <c r="B468" s="72" t="n"/>
       <c r="C468" s="73" t="n"/>
@@ -30640,7 +30655,7 @@
       <c r="F468" s="69" t="n"/>
       <c r="G468" s="69" t="n"/>
     </row>
-    <row r="469">
+    <row r="469" s="477">
       <c r="A469" s="69" t="n"/>
       <c r="B469" s="72" t="n"/>
       <c r="C469" s="73" t="n"/>
@@ -30649,7 +30664,7 @@
       <c r="F469" s="69" t="n"/>
       <c r="G469" s="69" t="n"/>
     </row>
-    <row r="470">
+    <row r="470" s="477">
       <c r="A470" s="69" t="n"/>
       <c r="B470" s="72" t="n"/>
       <c r="C470" s="73" t="n"/>
@@ -30658,7 +30673,7 @@
       <c r="F470" s="69" t="n"/>
       <c r="G470" s="69" t="n"/>
     </row>
-    <row r="471">
+    <row r="471" s="477">
       <c r="A471" s="69" t="n"/>
       <c r="B471" s="72" t="n"/>
       <c r="C471" s="73" t="n"/>
@@ -30667,7 +30682,7 @@
       <c r="F471" s="69" t="n"/>
       <c r="G471" s="69" t="n"/>
     </row>
-    <row r="472">
+    <row r="472" s="477">
       <c r="A472" s="69" t="n"/>
       <c r="B472" s="72" t="n"/>
       <c r="C472" s="73" t="n"/>
@@ -30676,7 +30691,7 @@
       <c r="F472" s="69" t="n"/>
       <c r="G472" s="69" t="n"/>
     </row>
-    <row r="473">
+    <row r="473" s="477">
       <c r="A473" s="69" t="n"/>
       <c r="B473" s="72" t="n"/>
       <c r="C473" s="73" t="n"/>
@@ -30685,7 +30700,7 @@
       <c r="F473" s="69" t="n"/>
       <c r="G473" s="69" t="n"/>
     </row>
-    <row r="474">
+    <row r="474" s="477">
       <c r="A474" s="69" t="n"/>
       <c r="B474" s="72" t="n"/>
       <c r="C474" s="73" t="n"/>
@@ -30694,7 +30709,7 @@
       <c r="F474" s="69" t="n"/>
       <c r="G474" s="69" t="n"/>
     </row>
-    <row r="475">
+    <row r="475" s="477">
       <c r="A475" s="69" t="n"/>
       <c r="B475" s="72" t="n"/>
       <c r="C475" s="73" t="n"/>
@@ -30703,7 +30718,7 @@
       <c r="F475" s="69" t="n"/>
       <c r="G475" s="69" t="n"/>
     </row>
-    <row r="476">
+    <row r="476" s="477">
       <c r="A476" s="69" t="n"/>
       <c r="B476" s="72" t="n"/>
       <c r="C476" s="73" t="n"/>
@@ -30712,7 +30727,7 @@
       <c r="F476" s="69" t="n"/>
       <c r="G476" s="69" t="n"/>
     </row>
-    <row r="477">
+    <row r="477" s="477">
       <c r="A477" s="69" t="n"/>
       <c r="B477" s="72" t="n"/>
       <c r="C477" s="73" t="n"/>
@@ -30721,7 +30736,7 @@
       <c r="F477" s="69" t="n"/>
       <c r="G477" s="69" t="n"/>
     </row>
-    <row r="478">
+    <row r="478" s="477">
       <c r="A478" s="69" t="n"/>
       <c r="B478" s="72" t="n"/>
       <c r="C478" s="73" t="n"/>
@@ -30730,7 +30745,7 @@
       <c r="F478" s="69" t="n"/>
       <c r="G478" s="69" t="n"/>
     </row>
-    <row r="479">
+    <row r="479" s="477">
       <c r="A479" s="69" t="n"/>
       <c r="B479" s="72" t="n"/>
       <c r="C479" s="73" t="n"/>
@@ -30739,7 +30754,7 @@
       <c r="F479" s="69" t="n"/>
       <c r="G479" s="69" t="n"/>
     </row>
-    <row r="480">
+    <row r="480" s="477">
       <c r="A480" s="69" t="n"/>
       <c r="B480" s="72" t="n"/>
       <c r="C480" s="73" t="n"/>
@@ -30748,7 +30763,7 @@
       <c r="F480" s="69" t="n"/>
       <c r="G480" s="69" t="n"/>
     </row>
-    <row r="481">
+    <row r="481" s="477">
       <c r="A481" s="69" t="n"/>
       <c r="B481" s="72" t="n"/>
       <c r="C481" s="73" t="n"/>
@@ -30757,7 +30772,7 @@
       <c r="F481" s="69" t="n"/>
       <c r="G481" s="69" t="n"/>
     </row>
-    <row r="482">
+    <row r="482" s="477">
       <c r="A482" s="69" t="n"/>
       <c r="B482" s="72" t="n"/>
       <c r="C482" s="73" t="n"/>
@@ -30766,7 +30781,7 @@
       <c r="F482" s="69" t="n"/>
       <c r="G482" s="69" t="n"/>
     </row>
-    <row r="483">
+    <row r="483" s="477">
       <c r="A483" s="69" t="n"/>
       <c r="B483" s="72" t="n"/>
       <c r="C483" s="73" t="n"/>
@@ -30775,7 +30790,7 @@
       <c r="F483" s="69" t="n"/>
       <c r="G483" s="69" t="n"/>
     </row>
-    <row r="484">
+    <row r="484" s="477">
       <c r="A484" s="69" t="n"/>
       <c r="B484" s="72" t="n"/>
       <c r="C484" s="73" t="n"/>
@@ -30784,7 +30799,7 @@
       <c r="F484" s="69" t="n"/>
       <c r="G484" s="69" t="n"/>
     </row>
-    <row r="485">
+    <row r="485" s="477">
       <c r="A485" s="69" t="n"/>
       <c r="B485" s="72" t="n"/>
       <c r="C485" s="73" t="n"/>
@@ -30793,7 +30808,7 @@
       <c r="F485" s="69" t="n"/>
       <c r="G485" s="69" t="n"/>
     </row>
-    <row r="486">
+    <row r="486" s="477">
       <c r="A486" s="69" t="n"/>
       <c r="B486" s="72" t="n"/>
       <c r="C486" s="73" t="n"/>
@@ -30802,7 +30817,7 @@
       <c r="F486" s="69" t="n"/>
       <c r="G486" s="69" t="n"/>
     </row>
-    <row r="487">
+    <row r="487" s="477">
       <c r="A487" s="69" t="n"/>
       <c r="B487" s="72" t="n"/>
       <c r="C487" s="73" t="n"/>
@@ -30811,7 +30826,7 @@
       <c r="F487" s="69" t="n"/>
       <c r="G487" s="69" t="n"/>
     </row>
-    <row r="488">
+    <row r="488" s="477">
       <c r="A488" s="69" t="n"/>
       <c r="B488" s="72" t="n"/>
       <c r="C488" s="73" t="n"/>
@@ -30820,7 +30835,7 @@
       <c r="F488" s="69" t="n"/>
       <c r="G488" s="69" t="n"/>
     </row>
-    <row r="489">
+    <row r="489" s="477">
       <c r="A489" s="69" t="n"/>
       <c r="B489" s="72" t="n"/>
       <c r="C489" s="73" t="n"/>
@@ -30829,7 +30844,7 @@
       <c r="F489" s="69" t="n"/>
       <c r="G489" s="69" t="n"/>
     </row>
-    <row r="490">
+    <row r="490" s="477">
       <c r="A490" s="69" t="n"/>
       <c r="B490" s="72" t="n"/>
       <c r="C490" s="73" t="n"/>
@@ -30838,7 +30853,7 @@
       <c r="F490" s="69" t="n"/>
       <c r="G490" s="69" t="n"/>
     </row>
-    <row r="491">
+    <row r="491" s="477">
       <c r="A491" s="69" t="n"/>
       <c r="B491" s="72" t="n"/>
       <c r="C491" s="73" t="n"/>
@@ -30847,7 +30862,7 @@
       <c r="F491" s="69" t="n"/>
       <c r="G491" s="69" t="n"/>
     </row>
-    <row r="492">
+    <row r="492" s="477">
       <c r="A492" s="69" t="n"/>
       <c r="B492" s="72" t="n"/>
       <c r="C492" s="73" t="n"/>
@@ -30856,7 +30871,7 @@
       <c r="F492" s="69" t="n"/>
       <c r="G492" s="69" t="n"/>
     </row>
-    <row r="493">
+    <row r="493" s="477">
       <c r="A493" s="69" t="n"/>
       <c r="B493" s="72" t="n"/>
       <c r="C493" s="73" t="n"/>
@@ -30865,7 +30880,7 @@
       <c r="F493" s="69" t="n"/>
       <c r="G493" s="69" t="n"/>
     </row>
-    <row r="494">
+    <row r="494" s="477">
       <c r="A494" s="69" t="n"/>
       <c r="B494" s="72" t="n"/>
       <c r="C494" s="73" t="n"/>
@@ -30874,7 +30889,7 @@
       <c r="F494" s="69" t="n"/>
       <c r="G494" s="69" t="n"/>
     </row>
-    <row r="495">
+    <row r="495" s="477">
       <c r="A495" s="69" t="n"/>
       <c r="B495" s="72" t="n"/>
       <c r="C495" s="73" t="n"/>
@@ -30883,7 +30898,7 @@
       <c r="F495" s="69" t="n"/>
       <c r="G495" s="69" t="n"/>
     </row>
-    <row r="496">
+    <row r="496" s="477">
       <c r="A496" s="69" t="n"/>
       <c r="B496" s="72" t="n"/>
       <c r="C496" s="73" t="n"/>
@@ -30892,7 +30907,7 @@
       <c r="F496" s="69" t="n"/>
       <c r="G496" s="69" t="n"/>
     </row>
-    <row r="497">
+    <row r="497" s="477">
       <c r="A497" s="69" t="n"/>
       <c r="B497" s="72" t="n"/>
       <c r="C497" s="73" t="n"/>
@@ -30901,7 +30916,7 @@
       <c r="F497" s="69" t="n"/>
       <c r="G497" s="69" t="n"/>
     </row>
-    <row r="498">
+    <row r="498" s="477">
       <c r="A498" s="69" t="n"/>
       <c r="B498" s="72" t="n"/>
       <c r="C498" s="73" t="n"/>
@@ -30910,7 +30925,7 @@
       <c r="F498" s="69" t="n"/>
       <c r="G498" s="69" t="n"/>
     </row>
-    <row r="499">
+    <row r="499" s="477">
       <c r="A499" s="69" t="n"/>
       <c r="B499" s="72" t="n"/>
       <c r="C499" s="73" t="n"/>
@@ -30919,7 +30934,7 @@
       <c r="F499" s="69" t="n"/>
       <c r="G499" s="69" t="n"/>
     </row>
-    <row r="500">
+    <row r="500" s="477">
       <c r="A500" s="69" t="n"/>
       <c r="B500" s="72" t="n"/>
       <c r="C500" s="73" t="n"/>
@@ -30928,7 +30943,7 @@
       <c r="F500" s="69" t="n"/>
       <c r="G500" s="69" t="n"/>
     </row>
-    <row r="501">
+    <row r="501" s="477">
       <c r="A501" s="69" t="n"/>
       <c r="B501" s="72" t="n"/>
       <c r="C501" s="73" t="n"/>
@@ -30937,7 +30952,7 @@
       <c r="F501" s="69" t="n"/>
       <c r="G501" s="69" t="n"/>
     </row>
-    <row r="502">
+    <row r="502" s="477">
       <c r="A502" s="69" t="n"/>
       <c r="B502" s="72" t="n"/>
       <c r="C502" s="73" t="n"/>
@@ -30946,7 +30961,7 @@
       <c r="F502" s="69" t="n"/>
       <c r="G502" s="69" t="n"/>
     </row>
-    <row r="503">
+    <row r="503" s="477">
       <c r="A503" s="69" t="n"/>
       <c r="B503" s="72" t="n"/>
       <c r="C503" s="73" t="n"/>
@@ -30955,7 +30970,7 @@
       <c r="F503" s="69" t="n"/>
       <c r="G503" s="69" t="n"/>
     </row>
-    <row r="504">
+    <row r="504" s="477">
       <c r="A504" s="69" t="n"/>
       <c r="B504" s="72" t="n"/>
       <c r="C504" s="73" t="n"/>
@@ -30964,7 +30979,7 @@
       <c r="F504" s="69" t="n"/>
       <c r="G504" s="69" t="n"/>
     </row>
-    <row r="505">
+    <row r="505" s="477">
       <c r="A505" s="69" t="n"/>
       <c r="B505" s="72" t="n"/>
       <c r="C505" s="73" t="n"/>
@@ -30973,7 +30988,7 @@
       <c r="F505" s="69" t="n"/>
       <c r="G505" s="69" t="n"/>
     </row>
-    <row r="506">
+    <row r="506" s="477">
       <c r="A506" s="69" t="n"/>
       <c r="B506" s="72" t="n"/>
       <c r="C506" s="73" t="n"/>
@@ -30982,7 +30997,7 @@
       <c r="F506" s="69" t="n"/>
       <c r="G506" s="69" t="n"/>
     </row>
-    <row r="507">
+    <row r="507" s="477">
       <c r="A507" s="69" t="n"/>
       <c r="B507" s="72" t="n"/>
       <c r="C507" s="73" t="n"/>
@@ -30991,7 +31006,7 @@
       <c r="F507" s="69" t="n"/>
       <c r="G507" s="69" t="n"/>
     </row>
-    <row r="508">
+    <row r="508" s="477">
       <c r="A508" s="69" t="n"/>
       <c r="B508" s="72" t="n"/>
       <c r="C508" s="73" t="n"/>
@@ -31000,7 +31015,7 @@
       <c r="F508" s="69" t="n"/>
       <c r="G508" s="69" t="n"/>
     </row>
-    <row r="509">
+    <row r="509" s="477">
       <c r="A509" s="69" t="n"/>
       <c r="B509" s="72" t="n"/>
       <c r="C509" s="73" t="n"/>
@@ -31009,7 +31024,7 @@
       <c r="F509" s="69" t="n"/>
       <c r="G509" s="69" t="n"/>
     </row>
-    <row r="510">
+    <row r="510" s="477">
       <c r="A510" s="69" t="n"/>
       <c r="B510" s="72" t="n"/>
       <c r="C510" s="73" t="n"/>
@@ -31018,7 +31033,7 @@
       <c r="F510" s="69" t="n"/>
       <c r="G510" s="69" t="n"/>
     </row>
-    <row r="511">
+    <row r="511" s="477">
       <c r="A511" s="69" t="n"/>
       <c r="B511" s="72" t="n"/>
       <c r="C511" s="73" t="n"/>
@@ -31027,7 +31042,7 @@
       <c r="F511" s="69" t="n"/>
       <c r="G511" s="69" t="n"/>
     </row>
-    <row r="512">
+    <row r="512" s="477">
       <c r="A512" s="69" t="n"/>
       <c r="B512" s="72" t="n"/>
       <c r="C512" s="73" t="n"/>
@@ -31036,7 +31051,7 @@
       <c r="F512" s="69" t="n"/>
       <c r="G512" s="69" t="n"/>
     </row>
-    <row r="513">
+    <row r="513" s="477">
       <c r="A513" s="69" t="n"/>
       <c r="B513" s="72" t="n"/>
       <c r="C513" s="73" t="n"/>
@@ -31045,7 +31060,7 @@
       <c r="F513" s="69" t="n"/>
       <c r="G513" s="69" t="n"/>
     </row>
-    <row r="514">
+    <row r="514" s="477">
       <c r="A514" s="69" t="n"/>
       <c r="B514" s="72" t="n"/>
       <c r="C514" s="73" t="n"/>
@@ -31054,7 +31069,7 @@
       <c r="F514" s="69" t="n"/>
       <c r="G514" s="69" t="n"/>
     </row>
-    <row r="515">
+    <row r="515" s="477">
       <c r="A515" s="69" t="n"/>
       <c r="B515" s="72" t="n"/>
       <c r="C515" s="73" t="n"/>
@@ -31063,7 +31078,7 @@
       <c r="F515" s="69" t="n"/>
       <c r="G515" s="69" t="n"/>
     </row>
-    <row r="516">
+    <row r="516" s="477">
       <c r="A516" s="69" t="n"/>
       <c r="B516" s="72" t="n"/>
       <c r="C516" s="73" t="n"/>
@@ -31072,7 +31087,7 @@
       <c r="F516" s="69" t="n"/>
       <c r="G516" s="69" t="n"/>
     </row>
-    <row r="517">
+    <row r="517" s="477">
       <c r="A517" s="69" t="n"/>
       <c r="B517" s="72" t="n"/>
       <c r="C517" s="73" t="n"/>
@@ -31081,7 +31096,7 @@
       <c r="F517" s="69" t="n"/>
       <c r="G517" s="69" t="n"/>
     </row>
-    <row r="518">
+    <row r="518" s="477">
       <c r="A518" s="69" t="n"/>
       <c r="B518" s="72" t="n"/>
       <c r="C518" s="73" t="n"/>
@@ -31090,7 +31105,7 @@
       <c r="F518" s="69" t="n"/>
       <c r="G518" s="69" t="n"/>
     </row>
-    <row r="519">
+    <row r="519" s="477">
       <c r="A519" s="69" t="n"/>
       <c r="B519" s="72" t="n"/>
       <c r="C519" s="73" t="n"/>
@@ -31099,7 +31114,7 @@
       <c r="F519" s="69" t="n"/>
       <c r="G519" s="69" t="n"/>
     </row>
-    <row r="520">
+    <row r="520" s="477">
       <c r="A520" s="69" t="n"/>
       <c r="B520" s="72" t="n"/>
       <c r="C520" s="73" t="n"/>
@@ -31108,7 +31123,7 @@
       <c r="F520" s="69" t="n"/>
       <c r="G520" s="69" t="n"/>
     </row>
-    <row r="521">
+    <row r="521" s="477">
       <c r="A521" s="69" t="n"/>
       <c r="B521" s="72" t="n"/>
       <c r="C521" s="73" t="n"/>
@@ -31117,7 +31132,7 @@
       <c r="F521" s="69" t="n"/>
       <c r="G521" s="69" t="n"/>
     </row>
-    <row r="522">
+    <row r="522" s="477">
       <c r="A522" s="69" t="n"/>
       <c r="B522" s="72" t="n"/>
       <c r="C522" s="73" t="n"/>
@@ -31126,7 +31141,7 @@
       <c r="F522" s="69" t="n"/>
       <c r="G522" s="69" t="n"/>
     </row>
-    <row r="523">
+    <row r="523" s="477">
       <c r="A523" s="69" t="n"/>
       <c r="B523" s="72" t="n"/>
       <c r="C523" s="73" t="n"/>
@@ -31135,7 +31150,7 @@
       <c r="F523" s="69" t="n"/>
       <c r="G523" s="69" t="n"/>
     </row>
-    <row r="524">
+    <row r="524" s="477">
       <c r="A524" s="69" t="n"/>
       <c r="B524" s="72" t="n"/>
       <c r="C524" s="73" t="n"/>
@@ -31144,7 +31159,7 @@
       <c r="F524" s="69" t="n"/>
       <c r="G524" s="69" t="n"/>
     </row>
-    <row r="525">
+    <row r="525" s="477">
       <c r="A525" s="69" t="n"/>
       <c r="B525" s="72" t="n"/>
       <c r="C525" s="73" t="n"/>
@@ -31153,7 +31168,7 @@
       <c r="F525" s="69" t="n"/>
       <c r="G525" s="69" t="n"/>
     </row>
-    <row r="526">
+    <row r="526" s="477">
       <c r="A526" s="69" t="n"/>
       <c r="B526" s="72" t="n"/>
       <c r="C526" s="73" t="n"/>
@@ -31162,7 +31177,7 @@
       <c r="F526" s="69" t="n"/>
       <c r="G526" s="69" t="n"/>
     </row>
-    <row r="527">
+    <row r="527" s="477">
       <c r="A527" s="69" t="n"/>
       <c r="B527" s="72" t="n"/>
       <c r="C527" s="73" t="n"/>
@@ -31171,7 +31186,7 @@
       <c r="F527" s="69" t="n"/>
       <c r="G527" s="69" t="n"/>
     </row>
-    <row r="528">
+    <row r="528" s="477">
       <c r="A528" s="69" t="n"/>
       <c r="B528" s="72" t="n"/>
       <c r="C528" s="73" t="n"/>
@@ -31180,7 +31195,7 @@
       <c r="F528" s="69" t="n"/>
       <c r="G528" s="69" t="n"/>
     </row>
-    <row r="529">
+    <row r="529" s="477">
       <c r="A529" s="69" t="n"/>
       <c r="B529" s="72" t="n"/>
       <c r="C529" s="73" t="n"/>
@@ -31189,7 +31204,7 @@
       <c r="F529" s="69" t="n"/>
       <c r="G529" s="69" t="n"/>
     </row>
-    <row r="530">
+    <row r="530" s="477">
       <c r="A530" s="69" t="n"/>
       <c r="B530" s="72" t="n"/>
       <c r="C530" s="73" t="n"/>
@@ -31198,7 +31213,7 @@
       <c r="F530" s="69" t="n"/>
       <c r="G530" s="69" t="n"/>
     </row>
-    <row r="531">
+    <row r="531" s="477">
       <c r="A531" s="69" t="n"/>
       <c r="B531" s="72" t="n"/>
       <c r="C531" s="73" t="n"/>
@@ -31207,7 +31222,7 @@
       <c r="F531" s="69" t="n"/>
       <c r="G531" s="69" t="n"/>
     </row>
-    <row r="532">
+    <row r="532" s="477">
       <c r="A532" s="69" t="n"/>
       <c r="B532" s="72" t="n"/>
       <c r="C532" s="73" t="n"/>
@@ -31216,7 +31231,7 @@
       <c r="F532" s="69" t="n"/>
       <c r="G532" s="69" t="n"/>
     </row>
-    <row r="533">
+    <row r="533" s="477">
       <c r="A533" s="69" t="n"/>
       <c r="B533" s="72" t="n"/>
       <c r="C533" s="73" t="n"/>
@@ -31225,7 +31240,7 @@
       <c r="F533" s="69" t="n"/>
       <c r="G533" s="69" t="n"/>
     </row>
-    <row r="534">
+    <row r="534" s="477">
       <c r="A534" s="69" t="n"/>
       <c r="B534" s="72" t="n"/>
       <c r="C534" s="73" t="n"/>
@@ -31234,7 +31249,7 @@
       <c r="F534" s="69" t="n"/>
       <c r="G534" s="69" t="n"/>
     </row>
-    <row r="535">
+    <row r="535" s="477">
       <c r="A535" s="69" t="n"/>
       <c r="B535" s="72" t="n"/>
       <c r="C535" s="73" t="n"/>
@@ -31243,7 +31258,7 @@
       <c r="F535" s="69" t="n"/>
       <c r="G535" s="69" t="n"/>
     </row>
-    <row r="536">
+    <row r="536" s="477">
       <c r="A536" s="69" t="n"/>
       <c r="B536" s="72" t="n"/>
       <c r="C536" s="73" t="n"/>
@@ -31252,7 +31267,7 @@
       <c r="F536" s="69" t="n"/>
       <c r="G536" s="69" t="n"/>
     </row>
-    <row r="537">
+    <row r="537" s="477">
       <c r="A537" s="69" t="n"/>
       <c r="B537" s="72" t="n"/>
       <c r="C537" s="73" t="n"/>
@@ -31261,7 +31276,7 @@
       <c r="F537" s="69" t="n"/>
       <c r="G537" s="69" t="n"/>
     </row>
-    <row r="538">
+    <row r="538" s="477">
       <c r="A538" s="69" t="n"/>
       <c r="B538" s="72" t="n"/>
       <c r="C538" s="73" t="n"/>
@@ -31270,7 +31285,7 @@
       <c r="F538" s="69" t="n"/>
       <c r="G538" s="69" t="n"/>
     </row>
-    <row r="539">
+    <row r="539" s="477">
       <c r="A539" s="69" t="n"/>
       <c r="B539" s="72" t="n"/>
       <c r="C539" s="73" t="n"/>
@@ -31279,7 +31294,7 @@
       <c r="F539" s="69" t="n"/>
       <c r="G539" s="69" t="n"/>
     </row>
-    <row r="540">
+    <row r="540" s="477">
       <c r="A540" s="69" t="n"/>
       <c r="B540" s="72" t="n"/>
       <c r="C540" s="73" t="n"/>
@@ -31288,7 +31303,7 @@
       <c r="F540" s="69" t="n"/>
       <c r="G540" s="69" t="n"/>
     </row>
-    <row r="541">
+    <row r="541" s="477">
       <c r="A541" s="69" t="n"/>
       <c r="B541" s="72" t="n"/>
       <c r="C541" s="73" t="n"/>
@@ -31297,7 +31312,7 @@
       <c r="F541" s="69" t="n"/>
       <c r="G541" s="69" t="n"/>
     </row>
-    <row r="542">
+    <row r="542" s="477">
       <c r="A542" s="69" t="n"/>
       <c r="B542" s="72" t="n"/>
       <c r="C542" s="73" t="n"/>
@@ -31306,7 +31321,7 @@
       <c r="F542" s="69" t="n"/>
       <c r="G542" s="69" t="n"/>
     </row>
-    <row r="543">
+    <row r="543" s="477">
       <c r="A543" s="69" t="n"/>
       <c r="B543" s="72" t="n"/>
       <c r="C543" s="73" t="n"/>
@@ -31315,7 +31330,7 @@
       <c r="F543" s="69" t="n"/>
       <c r="G543" s="69" t="n"/>
     </row>
-    <row r="544">
+    <row r="544" s="477">
       <c r="A544" s="69" t="n"/>
       <c r="B544" s="72" t="n"/>
       <c r="C544" s="73" t="n"/>
@@ -31324,7 +31339,7 @@
       <c r="F544" s="69" t="n"/>
       <c r="G544" s="69" t="n"/>
     </row>
-    <row r="545">
+    <row r="545" s="477">
       <c r="A545" s="69" t="n"/>
       <c r="B545" s="72" t="n"/>
       <c r="C545" s="73" t="n"/>
@@ -31333,7 +31348,7 @@
       <c r="F545" s="69" t="n"/>
       <c r="G545" s="69" t="n"/>
     </row>
-    <row r="546">
+    <row r="546" s="477">
       <c r="A546" s="69" t="n"/>
       <c r="B546" s="72" t="n"/>
       <c r="C546" s="73" t="n"/>
@@ -31342,7 +31357,7 @@
       <c r="F546" s="69" t="n"/>
       <c r="G546" s="69" t="n"/>
     </row>
-    <row r="547">
+    <row r="547" s="477">
       <c r="A547" s="69" t="n"/>
       <c r="B547" s="72" t="n"/>
       <c r="C547" s="73" t="n"/>
@@ -31351,7 +31366,7 @@
       <c r="F547" s="69" t="n"/>
       <c r="G547" s="69" t="n"/>
     </row>
-    <row r="548">
+    <row r="548" s="477">
       <c r="A548" s="69" t="n"/>
       <c r="B548" s="72" t="n"/>
       <c r="C548" s="73" t="n"/>
@@ -31360,7 +31375,7 @@
       <c r="F548" s="69" t="n"/>
       <c r="G548" s="69" t="n"/>
     </row>
-    <row r="549">
+    <row r="549" s="477">
       <c r="A549" s="69" t="n"/>
       <c r="B549" s="72" t="n"/>
       <c r="C549" s="73" t="n"/>
@@ -31369,7 +31384,7 @@
       <c r="F549" s="69" t="n"/>
       <c r="G549" s="69" t="n"/>
     </row>
-    <row r="550">
+    <row r="550" s="477">
       <c r="A550" s="69" t="n"/>
       <c r="B550" s="72" t="n"/>
       <c r="C550" s="73" t="n"/>
@@ -31378,7 +31393,7 @@
       <c r="F550" s="69" t="n"/>
       <c r="G550" s="69" t="n"/>
     </row>
-    <row r="551">
+    <row r="551" s="477">
       <c r="A551" s="69" t="n"/>
       <c r="B551" s="72" t="n"/>
       <c r="C551" s="73" t="n"/>
@@ -31387,7 +31402,7 @@
       <c r="F551" s="69" t="n"/>
       <c r="G551" s="69" t="n"/>
     </row>
-    <row r="552">
+    <row r="552" s="477">
       <c r="A552" s="69" t="n"/>
       <c r="B552" s="72" t="n"/>
       <c r="C552" s="73" t="n"/>
@@ -31396,7 +31411,7 @@
       <c r="F552" s="69" t="n"/>
       <c r="G552" s="69" t="n"/>
     </row>
-    <row r="553">
+    <row r="553" s="477">
       <c r="A553" s="69" t="n"/>
       <c r="B553" s="72" t="n"/>
       <c r="C553" s="73" t="n"/>
@@ -31405,7 +31420,7 @@
       <c r="F553" s="69" t="n"/>
       <c r="G553" s="69" t="n"/>
     </row>
-    <row r="554">
+    <row r="554" s="477">
       <c r="A554" s="69" t="n"/>
       <c r="B554" s="72" t="n"/>
       <c r="C554" s="73" t="n"/>
@@ -31414,7 +31429,7 @@
       <c r="F554" s="69" t="n"/>
       <c r="G554" s="69" t="n"/>
     </row>
-    <row r="555">
+    <row r="555" s="477">
       <c r="A555" s="69" t="n"/>
       <c r="B555" s="72" t="n"/>
       <c r="C555" s="73" t="n"/>
@@ -31423,7 +31438,7 @@
       <c r="F555" s="69" t="n"/>
       <c r="G555" s="69" t="n"/>
     </row>
-    <row r="556">
+    <row r="556" s="477">
       <c r="A556" s="69" t="n"/>
       <c r="B556" s="72" t="n"/>
       <c r="C556" s="73" t="n"/>
@@ -31432,7 +31447,7 @@
       <c r="F556" s="69" t="n"/>
       <c r="G556" s="69" t="n"/>
     </row>
-    <row r="557">
+    <row r="557" s="477">
       <c r="A557" s="69" t="n"/>
       <c r="B557" s="72" t="n"/>
       <c r="C557" s="73" t="n"/>
@@ -31441,7 +31456,7 @@
       <c r="F557" s="69" t="n"/>
       <c r="G557" s="69" t="n"/>
     </row>
-    <row r="558">
+    <row r="558" s="477">
       <c r="A558" s="69" t="n"/>
       <c r="B558" s="72" t="n"/>
       <c r="C558" s="73" t="n"/>
@@ -31450,7 +31465,7 @@
       <c r="F558" s="69" t="n"/>
       <c r="G558" s="69" t="n"/>
     </row>
-    <row r="559">
+    <row r="559" s="477">
       <c r="A559" s="69" t="n"/>
       <c r="B559" s="72" t="n"/>
       <c r="C559" s="73" t="n"/>
@@ -31459,7 +31474,7 @@
       <c r="F559" s="69" t="n"/>
       <c r="G559" s="69" t="n"/>
     </row>
-    <row r="560">
+    <row r="560" s="477">
       <c r="A560" s="69" t="n"/>
       <c r="B560" s="72" t="n"/>
       <c r="C560" s="73" t="n"/>
@@ -31468,7 +31483,7 @@
       <c r="F560" s="69" t="n"/>
       <c r="G560" s="69" t="n"/>
     </row>
-    <row r="561">
+    <row r="561" s="477">
       <c r="A561" s="69" t="n"/>
       <c r="B561" s="72" t="n"/>
       <c r="C561" s="73" t="n"/>
@@ -31477,7 +31492,7 @@
       <c r="F561" s="69" t="n"/>
       <c r="G561" s="69" t="n"/>
     </row>
-    <row r="562">
+    <row r="562" s="477">
       <c r="A562" s="69" t="n"/>
       <c r="B562" s="72" t="n"/>
       <c r="C562" s="73" t="n"/>
@@ -31486,7 +31501,7 @@
       <c r="F562" s="69" t="n"/>
       <c r="G562" s="69" t="n"/>
     </row>
-    <row r="563">
+    <row r="563" s="477">
       <c r="A563" s="69" t="n"/>
       <c r="B563" s="72" t="n"/>
       <c r="C563" s="73" t="n"/>
@@ -31495,7 +31510,7 @@
       <c r="F563" s="69" t="n"/>
       <c r="G563" s="69" t="n"/>
     </row>
-    <row r="564">
+    <row r="564" s="477">
       <c r="A564" s="69" t="n"/>
       <c r="B564" s="72" t="n"/>
       <c r="C564" s="73" t="n"/>
@@ -31504,7 +31519,7 @@
       <c r="F564" s="69" t="n"/>
       <c r="G564" s="69" t="n"/>
     </row>
-    <row r="565">
+    <row r="565" s="477">
       <c r="A565" s="69" t="n"/>
       <c r="B565" s="72" t="n"/>
       <c r="C565" s="73" t="n"/>
@@ -31513,7 +31528,7 @@
       <c r="F565" s="69" t="n"/>
       <c r="G565" s="69" t="n"/>
     </row>
-    <row r="566">
+    <row r="566" s="477">
       <c r="A566" s="69" t="n"/>
       <c r="B566" s="72" t="n"/>
       <c r="C566" s="73" t="n"/>
@@ -31522,7 +31537,7 @@
       <c r="F566" s="69" t="n"/>
       <c r="G566" s="69" t="n"/>
     </row>
-    <row r="567">
+    <row r="567" s="477">
       <c r="A567" s="69" t="n"/>
       <c r="B567" s="72" t="n"/>
       <c r="C567" s="73" t="n"/>
@@ -31531,7 +31546,7 @@
       <c r="F567" s="69" t="n"/>
       <c r="G567" s="69" t="n"/>
     </row>
-    <row r="568">
+    <row r="568" s="477">
       <c r="A568" s="69" t="n"/>
       <c r="B568" s="72" t="n"/>
       <c r="C568" s="73" t="n"/>
@@ -31540,7 +31555,7 @@
       <c r="F568" s="69" t="n"/>
       <c r="G568" s="69" t="n"/>
     </row>
-    <row r="569">
+    <row r="569" s="477">
       <c r="A569" s="69" t="n"/>
       <c r="B569" s="72" t="n"/>
       <c r="C569" s="73" t="n"/>
@@ -31549,7 +31564,7 @@
       <c r="F569" s="69" t="n"/>
       <c r="G569" s="69" t="n"/>
     </row>
-    <row r="570">
+    <row r="570" s="477">
       <c r="A570" s="69" t="n"/>
       <c r="B570" s="72" t="n"/>
       <c r="C570" s="73" t="n"/>
@@ -31558,7 +31573,7 @@
       <c r="F570" s="69" t="n"/>
       <c r="G570" s="69" t="n"/>
     </row>
-    <row r="571">
+    <row r="571" s="477">
       <c r="A571" s="69" t="n"/>
       <c r="B571" s="72" t="n"/>
       <c r="C571" s="73" t="n"/>
@@ -31567,7 +31582,7 @@
       <c r="F571" s="69" t="n"/>
       <c r="G571" s="69" t="n"/>
     </row>
-    <row r="572">
+    <row r="572" s="477">
       <c r="A572" s="69" t="n"/>
       <c r="B572" s="72" t="n"/>
       <c r="C572" s="73" t="n"/>
@@ -31576,7 +31591,7 @@
       <c r="F572" s="69" t="n"/>
       <c r="G572" s="69" t="n"/>
     </row>
-    <row r="573">
+    <row r="573" s="477">
       <c r="A573" s="69" t="n"/>
       <c r="B573" s="72" t="n"/>
       <c r="C573" s="73" t="n"/>
@@ -31585,7 +31600,7 @@
       <c r="F573" s="69" t="n"/>
       <c r="G573" s="69" t="n"/>
     </row>
-    <row r="574">
+    <row r="574" s="477">
       <c r="A574" s="69" t="n"/>
       <c r="B574" s="72" t="n"/>
       <c r="C574" s="73" t="n"/>
@@ -31594,7 +31609,7 @@
       <c r="F574" s="69" t="n"/>
       <c r="G574" s="69" t="n"/>
     </row>
-    <row r="575">
+    <row r="575" s="477">
       <c r="A575" s="69" t="n"/>
       <c r="B575" s="72" t="n"/>
       <c r="C575" s="73" t="n"/>
@@ -31603,7 +31618,7 @@
       <c r="F575" s="69" t="n"/>
       <c r="G575" s="69" t="n"/>
     </row>
-    <row r="576">
+    <row r="576" s="477">
       <c r="A576" s="69" t="n"/>
       <c r="B576" s="72" t="n"/>
       <c r="C576" s="73" t="n"/>
@@ -31612,7 +31627,7 @@
       <c r="F576" s="69" t="n"/>
       <c r="G576" s="69" t="n"/>
     </row>
-    <row r="577">
+    <row r="577" s="477">
       <c r="A577" s="69" t="n"/>
       <c r="B577" s="72" t="n"/>
       <c r="C577" s="73" t="n"/>
@@ -31621,7 +31636,7 @@
       <c r="F577" s="69" t="n"/>
       <c r="G577" s="69" t="n"/>
     </row>
-    <row r="578">
+    <row r="578" s="477">
       <c r="A578" s="69" t="n"/>
       <c r="B578" s="72" t="n"/>
       <c r="C578" s="73" t="n"/>
@@ -31630,7 +31645,7 @@
       <c r="F578" s="69" t="n"/>
       <c r="G578" s="69" t="n"/>
     </row>
-    <row r="579">
+    <row r="579" s="477">
       <c r="A579" s="69" t="n"/>
       <c r="B579" s="72" t="n"/>
       <c r="C579" s="73" t="n"/>
@@ -31639,7 +31654,7 @@
       <c r="F579" s="69" t="n"/>
       <c r="G579" s="69" t="n"/>
     </row>
-    <row r="580">
+    <row r="580" s="477">
       <c r="A580" s="69" t="n"/>
       <c r="B580" s="72" t="n"/>
       <c r="C580" s="73" t="n"/>
@@ -31648,7 +31663,7 @@
       <c r="F580" s="69" t="n"/>
       <c r="G580" s="69" t="n"/>
     </row>
-    <row r="581">
+    <row r="581" s="477">
       <c r="A581" s="69" t="n"/>
       <c r="B581" s="72" t="n"/>
       <c r="C581" s="73" t="n"/>
@@ -31657,7 +31672,7 @@
       <c r="F581" s="69" t="n"/>
       <c r="G581" s="69" t="n"/>
     </row>
-    <row r="582">
+    <row r="582" s="477">
       <c r="A582" s="69" t="n"/>
       <c r="B582" s="72" t="n"/>
       <c r="C582" s="73" t="n"/>
@@ -31666,7 +31681,7 @@
       <c r="F582" s="69" t="n"/>
       <c r="G582" s="69" t="n"/>
     </row>
-    <row r="583">
+    <row r="583" s="477">
       <c r="A583" s="69" t="n"/>
       <c r="B583" s="72" t="n"/>
       <c r="C583" s="73" t="n"/>
@@ -31675,7 +31690,7 @@
       <c r="F583" s="69" t="n"/>
       <c r="G583" s="69" t="n"/>
     </row>
-    <row r="584">
+    <row r="584" s="477">
       <c r="A584" s="69" t="n"/>
       <c r="B584" s="72" t="n"/>
       <c r="C584" s="73" t="n"/>
@@ -31684,7 +31699,7 @@
       <c r="F584" s="69" t="n"/>
       <c r="G584" s="69" t="n"/>
     </row>
-    <row r="585">
+    <row r="585" s="477">
       <c r="A585" s="69" t="n"/>
       <c r="B585" s="72" t="n"/>
       <c r="C585" s="73" t="n"/>
@@ -31693,7 +31708,7 @@
       <c r="F585" s="69" t="n"/>
       <c r="G585" s="69" t="n"/>
     </row>
-    <row r="586">
+    <row r="586" s="477">
       <c r="A586" s="69" t="n"/>
       <c r="B586" s="72" t="n"/>
       <c r="C586" s="73" t="n"/>
@@ -31702,7 +31717,7 @@
       <c r="F586" s="69" t="n"/>
       <c r="G586" s="69" t="n"/>
     </row>
-    <row r="587">
+    <row r="587" s="477">
       <c r="A587" s="69" t="n"/>
       <c r="B587" s="72" t="n"/>
       <c r="C587" s="73" t="n"/>
@@ -31711,7 +31726,7 @@
       <c r="F587" s="69" t="n"/>
       <c r="G587" s="69" t="n"/>
     </row>
-    <row r="588">
+    <row r="588" s="477">
       <c r="A588" s="69" t="n"/>
       <c r="B588" s="72" t="n"/>
       <c r="C588" s="73" t="n"/>
@@ -31720,7 +31735,7 @@
       <c r="F588" s="69" t="n"/>
       <c r="G588" s="69" t="n"/>
     </row>
-    <row r="589">
+    <row r="589" s="477">
       <c r="A589" s="69" t="n"/>
       <c r="B589" s="72" t="n"/>
       <c r="C589" s="73" t="n"/>
@@ -31729,7 +31744,7 @@
       <c r="F589" s="69" t="n"/>
       <c r="G589" s="69" t="n"/>
     </row>
-    <row r="590">
+    <row r="590" s="477">
       <c r="A590" s="69" t="n"/>
       <c r="B590" s="72" t="n"/>
       <c r="C590" s="73" t="n"/>
@@ -31738,7 +31753,7 @@
       <c r="F590" s="69" t="n"/>
       <c r="G590" s="69" t="n"/>
     </row>
-    <row r="591">
+    <row r="591" s="477">
       <c r="A591" s="69" t="n"/>
       <c r="B591" s="72" t="n"/>
       <c r="C591" s="73" t="n"/>
@@ -31747,7 +31762,7 @@
       <c r="F591" s="69" t="n"/>
       <c r="G591" s="69" t="n"/>
     </row>
-    <row r="592">
+    <row r="592" s="477">
       <c r="A592" s="69" t="n"/>
       <c r="B592" s="72" t="n"/>
       <c r="C592" s="73" t="n"/>
@@ -31756,7 +31771,7 @@
       <c r="F592" s="69" t="n"/>
       <c r="G592" s="69" t="n"/>
     </row>
-    <row r="593">
+    <row r="593" s="477">
       <c r="A593" s="69" t="n"/>
       <c r="B593" s="72" t="n"/>
       <c r="C593" s="73" t="n"/>
@@ -31765,7 +31780,7 @@
       <c r="F593" s="69" t="n"/>
       <c r="G593" s="69" t="n"/>
     </row>
-    <row r="594">
+    <row r="594" s="477">
       <c r="A594" s="69" t="n"/>
       <c r="B594" s="72" t="n"/>
       <c r="C594" s="73" t="n"/>
@@ -31774,7 +31789,7 @@
       <c r="F594" s="69" t="n"/>
       <c r="G594" s="69" t="n"/>
     </row>
-    <row r="595">
+    <row r="595" s="477">
       <c r="A595" s="69" t="n"/>
       <c r="B595" s="72" t="n"/>
       <c r="C595" s="73" t="n"/>
@@ -31783,7 +31798,7 @@
       <c r="F595" s="69" t="n"/>
       <c r="G595" s="69" t="n"/>
     </row>
-    <row r="596">
+    <row r="596" s="477">
       <c r="A596" s="69" t="n"/>
       <c r="B596" s="72" t="n"/>
       <c r="C596" s="73" t="n"/>
@@ -31792,7 +31807,7 @@
       <c r="F596" s="69" t="n"/>
       <c r="G596" s="69" t="n"/>
     </row>
-    <row r="597">
+    <row r="597" s="477">
       <c r="A597" s="69" t="n"/>
       <c r="B597" s="72" t="n"/>
       <c r="C597" s="73" t="n"/>
@@ -31801,7 +31816,7 @@
       <c r="F597" s="69" t="n"/>
       <c r="G597" s="69" t="n"/>
     </row>
-    <row r="598">
+    <row r="598" s="477">
       <c r="A598" s="69" t="n"/>
       <c r="B598" s="72" t="n"/>
       <c r="C598" s="73" t="n"/>
@@ -31810,7 +31825,7 @@
       <c r="F598" s="69" t="n"/>
       <c r="G598" s="69" t="n"/>
     </row>
-    <row r="599">
+    <row r="599" s="477">
       <c r="A599" s="69" t="n"/>
       <c r="B599" s="72" t="n"/>
       <c r="C599" s="73" t="n"/>
@@ -31819,7 +31834,7 @@
       <c r="F599" s="69" t="n"/>
       <c r="G599" s="69" t="n"/>
     </row>
-    <row r="600">
+    <row r="600" s="477">
       <c r="A600" s="69" t="n"/>
       <c r="B600" s="72" t="n"/>
       <c r="C600" s="73" t="n"/>
@@ -31828,7 +31843,7 @@
       <c r="F600" s="69" t="n"/>
       <c r="G600" s="69" t="n"/>
     </row>
-    <row r="601">
+    <row r="601" s="477">
       <c r="A601" s="69" t="n"/>
       <c r="B601" s="72" t="n"/>
       <c r="C601" s="73" t="n"/>
@@ -31837,7 +31852,7 @@
       <c r="F601" s="69" t="n"/>
       <c r="G601" s="69" t="n"/>
     </row>
-    <row r="602">
+    <row r="602" s="477">
       <c r="A602" s="69" t="n"/>
       <c r="B602" s="72" t="n"/>
       <c r="C602" s="73" t="n"/>
@@ -31846,7 +31861,7 @@
       <c r="F602" s="69" t="n"/>
       <c r="G602" s="69" t="n"/>
     </row>
-    <row r="603">
+    <row r="603" s="477">
       <c r="A603" s="69" t="n"/>
       <c r="B603" s="72" t="n"/>
       <c r="C603" s="73" t="n"/>
@@ -31855,7 +31870,7 @@
       <c r="F603" s="69" t="n"/>
       <c r="G603" s="69" t="n"/>
     </row>
-    <row r="604">
+    <row r="604" s="477">
       <c r="A604" s="69" t="n"/>
       <c r="B604" s="72" t="n"/>
       <c r="C604" s="73" t="n"/>
@@ -31864,7 +31879,7 @@
       <c r="F604" s="69" t="n"/>
       <c r="G604" s="69" t="n"/>
     </row>
-    <row r="605">
+    <row r="605" s="477">
       <c r="A605" s="69" t="n"/>
       <c r="B605" s="72" t="n"/>
       <c r="C605" s="73" t="n"/>
@@ -31873,7 +31888,7 @@
       <c r="F605" s="69" t="n"/>
       <c r="G605" s="69" t="n"/>
     </row>
-    <row r="606">
+    <row r="606" s="477">
       <c r="A606" s="69" t="n"/>
       <c r="B606" s="72" t="n"/>
       <c r="C606" s="73" t="n"/>
@@ -31882,7 +31897,7 @@
       <c r="F606" s="69" t="n"/>
       <c r="G606" s="69" t="n"/>
     </row>
-    <row r="607">
+    <row r="607" s="477">
       <c r="A607" s="69" t="n"/>
       <c r="B607" s="72" t="n"/>
       <c r="C607" s="73" t="n"/>
@@ -31891,7 +31906,7 @@
       <c r="F607" s="69" t="n"/>
       <c r="G607" s="69" t="n"/>
     </row>
-    <row r="608">
+    <row r="608" s="477">
       <c r="A608" s="69" t="n"/>
       <c r="B608" s="72" t="n"/>
       <c r="C608" s="73" t="n"/>
@@ -31900,7 +31915,7 @@
       <c r="F608" s="69" t="n"/>
       <c r="G608" s="69" t="n"/>
     </row>
-    <row r="609">
+    <row r="609" s="477">
       <c r="A609" s="69" t="n"/>
       <c r="B609" s="72" t="n"/>
       <c r="C609" s="73" t="n"/>
@@ -31909,7 +31924,7 @@
       <c r="F609" s="69" t="n"/>
       <c r="G609" s="69" t="n"/>
     </row>
-    <row r="610">
+    <row r="610" s="477">
       <c r="A610" s="69" t="n"/>
       <c r="B610" s="72" t="n"/>
       <c r="C610" s="73" t="n"/>
@@ -31918,7 +31933,7 @@
       <c r="F610" s="69" t="n"/>
       <c r="G610" s="69" t="n"/>
     </row>
-    <row r="611">
+    <row r="611" s="477">
       <c r="A611" s="69" t="n"/>
       <c r="B611" s="72" t="n"/>
       <c r="C611" s="73" t="n"/>
@@ -31927,7 +31942,7 @@
       <c r="F611" s="69" t="n"/>
       <c r="G611" s="69" t="n"/>
     </row>
-    <row r="612">
+    <row r="612" s="477">
       <c r="A612" s="69" t="n"/>
       <c r="B612" s="72" t="n"/>
       <c r="C612" s="73" t="n"/>
@@ -31936,7 +31951,7 @@
       <c r="F612" s="69" t="n"/>
       <c r="G612" s="69" t="n"/>
     </row>
-    <row r="613">
+    <row r="613" s="477">
       <c r="A613" s="69" t="n"/>
       <c r="B613" s="72" t="n"/>
       <c r="C613" s="73" t="n"/>
@@ -31945,7 +31960,7 @@
       <c r="F613" s="69" t="n"/>
       <c r="G613" s="69" t="n"/>
     </row>
-    <row r="614">
+    <row r="614" s="477">
       <c r="A614" s="69" t="n"/>
       <c r="B614" s="72" t="n"/>
       <c r="C614" s="73" t="n"/>
@@ -31954,7 +31969,7 @@
       <c r="F614" s="69" t="n"/>
       <c r="G614" s="69" t="n"/>
     </row>
-    <row r="615">
+    <row r="615" s="477">
       <c r="A615" s="69" t="n"/>
       <c r="B615" s="72" t="n"/>
       <c r="C615" s="73" t="n"/>
@@ -31963,7 +31978,7 @@
       <c r="F615" s="69" t="n"/>
       <c r="G615" s="69" t="n"/>
     </row>
-    <row r="616">
+    <row r="616" s="477">
       <c r="A616" s="69" t="n"/>
       <c r="B616" s="72" t="n"/>
       <c r="C616" s="73" t="n"/>
@@ -31972,7 +31987,7 @@
       <c r="F616" s="69" t="n"/>
       <c r="G616" s="69" t="n"/>
     </row>
-    <row r="617">
+    <row r="617" s="477">
       <c r="A617" s="69" t="n"/>
       <c r="B617" s="72" t="n"/>
       <c r="C617" s="73" t="n"/>
@@ -31981,7 +31996,7 @@
       <c r="F617" s="69" t="n"/>
       <c r="G617" s="69" t="n"/>
     </row>
-    <row r="618">
+    <row r="618" s="477">
       <c r="A618" s="69" t="n"/>
       <c r="B618" s="72" t="n"/>
       <c r="C618" s="73" t="n"/>
@@ -31990,7 +32005,7 @@
       <c r="F618" s="69" t="n"/>
       <c r="G618" s="69" t="n"/>
     </row>
-    <row r="619">
+    <row r="619" s="477">
       <c r="A619" s="69" t="n"/>
       <c r="B619" s="72" t="n"/>
       <c r="C619" s="73" t="n"/>
@@ -31999,7 +32014,7 @@
       <c r="F619" s="69" t="n"/>
       <c r="G619" s="69" t="n"/>
     </row>
-    <row r="620">
+    <row r="620" s="477">
       <c r="A620" s="69" t="n"/>
       <c r="B620" s="72" t="n"/>
       <c r="C620" s="73" t="n"/>
@@ -32008,7 +32023,7 @@
       <c r="F620" s="69" t="n"/>
       <c r="G620" s="69" t="n"/>
     </row>
-    <row r="621">
+    <row r="621" s="477">
       <c r="A621" s="69" t="n"/>
       <c r="B621" s="72" t="n"/>
       <c r="C621" s="73" t="n"/>
@@ -32017,7 +32032,7 @@
       <c r="F621" s="69" t="n"/>
       <c r="G621" s="69" t="n"/>
     </row>
-    <row r="622">
+    <row r="622" s="477">
       <c r="A622" s="69" t="n"/>
       <c r="B622" s="72" t="n"/>
       <c r="C622" s="73" t="n"/>
@@ -32026,7 +32041,7 @@
       <c r="F622" s="69" t="n"/>
       <c r="G622" s="69" t="n"/>
     </row>
-    <row r="623">
+    <row r="623" s="477">
       <c r="A623" s="69" t="n"/>
       <c r="B623" s="72" t="n"/>
       <c r="C623" s="73" t="n"/>
@@ -32035,7 +32050,7 @@
       <c r="F623" s="69" t="n"/>
       <c r="G623" s="69" t="n"/>
     </row>
-    <row r="624">
+    <row r="624" s="477">
       <c r="A624" s="69" t="n"/>
       <c r="B624" s="72" t="n"/>
       <c r="C624" s="73" t="n"/>
@@ -32044,7 +32059,7 @@
       <c r="F624" s="69" t="n"/>
       <c r="G624" s="69" t="n"/>
     </row>
-    <row r="625">
+    <row r="625" s="477">
       <c r="A625" s="69" t="n"/>
       <c r="B625" s="72" t="n"/>
       <c r="C625" s="73" t="n"/>
@@ -32053,7 +32068,7 @@
       <c r="F625" s="69" t="n"/>
       <c r="G625" s="69" t="n"/>
     </row>
-    <row r="626">
+    <row r="626" s="477">
       <c r="A626" s="69" t="n"/>
       <c r="B626" s="72" t="n"/>
       <c r="C626" s="73" t="n"/>
@@ -32062,7 +32077,7 @@
       <c r="F626" s="69" t="n"/>
       <c r="G626" s="69" t="n"/>
     </row>
-    <row r="627">
+    <row r="627" s="477">
       <c r="A627" s="69" t="n"/>
       <c r="B627" s="72" t="n"/>
       <c r="C627" s="73" t="n"/>
@@ -32071,7 +32086,7 @@
       <c r="F627" s="69" t="n"/>
       <c r="G627" s="69" t="n"/>
     </row>
-    <row r="628">
+    <row r="628" s="477">
       <c r="A628" s="69" t="n"/>
       <c r="B628" s="72" t="n"/>
       <c r="C628" s="73" t="n"/>
@@ -32080,7 +32095,7 @@
       <c r="F628" s="69" t="n"/>
       <c r="G628" s="69" t="n"/>
     </row>
-    <row r="629">
+    <row r="629" s="477">
       <c r="A629" s="69" t="n"/>
       <c r="B629" s="72" t="n"/>
       <c r="C629" s="73" t="n"/>
@@ -32089,7 +32104,7 @@
       <c r="F629" s="69" t="n"/>
       <c r="G629" s="69" t="n"/>
     </row>
-    <row r="630">
+    <row r="630" s="477">
       <c r="A630" s="69" t="n"/>
       <c r="B630" s="72" t="n"/>
       <c r="C630" s="73" t="n"/>
@@ -32098,7 +32113,7 @@
       <c r="F630" s="69" t="n"/>
       <c r="G630" s="69" t="n"/>
     </row>
-    <row r="631">
+    <row r="631" s="477">
       <c r="A631" s="69" t="n"/>
       <c r="B631" s="72" t="n"/>
       <c r="C631" s="73" t="n"/>
@@ -32107,7 +32122,7 @@
       <c r="F631" s="69" t="n"/>
       <c r="G631" s="69" t="n"/>
     </row>
-    <row r="632">
+    <row r="632" s="477">
       <c r="A632" s="69" t="n"/>
       <c r="B632" s="72" t="n"/>
       <c r="C632" s="73" t="n"/>
@@ -32116,7 +32131,7 @@
       <c r="F632" s="69" t="n"/>
       <c r="G632" s="69" t="n"/>
     </row>
-    <row r="633">
+    <row r="633" s="477">
       <c r="A633" s="69" t="n"/>
       <c r="B633" s="72" t="n"/>
       <c r="C633" s="73" t="n"/>
@@ -32125,7 +32140,7 @@
       <c r="F633" s="69" t="n"/>
       <c r="G633" s="69" t="n"/>
     </row>
-    <row r="634">
+    <row r="634" s="477">
       <c r="A634" s="69" t="n"/>
       <c r="B634" s="72" t="n"/>
       <c r="C634" s="73" t="n"/>
@@ -32134,7 +32149,7 @@
       <c r="F634" s="69" t="n"/>
       <c r="G634" s="69" t="n"/>
     </row>
-    <row r="635">
+    <row r="635" s="477">
       <c r="A635" s="69" t="n"/>
       <c r="B635" s="72" t="n"/>
       <c r="C635" s="73" t="n"/>
@@ -32143,7 +32158,7 @@
       <c r="F635" s="69" t="n"/>
       <c r="G635" s="69" t="n"/>
     </row>
-    <row r="636">
+    <row r="636" s="477">
       <c r="A636" s="69" t="n"/>
       <c r="B636" s="72" t="n"/>
       <c r="C636" s="73" t="n"/>
@@ -32152,7 +32167,7 @@
       <c r="F636" s="69" t="n"/>
       <c r="G636" s="69" t="n"/>
     </row>
-    <row r="637">
+    <row r="637" s="477">
       <c r="A637" s="69" t="n"/>
       <c r="B637" s="72" t="n"/>
       <c r="C637" s="73" t="n"/>
@@ -32161,7 +32176,7 @@
       <c r="F637" s="69" t="n"/>
       <c r="G637" s="69" t="n"/>
     </row>
-    <row r="638">
+    <row r="638" s="477">
       <c r="A638" s="69" t="n"/>
       <c r="B638" s="72" t="n"/>
       <c r="C638" s="73" t="n"/>
@@ -32170,7 +32185,7 @@
       <c r="F638" s="69" t="n"/>
       <c r="G638" s="69" t="n"/>
     </row>
-    <row r="639">
+    <row r="639" s="477">
       <c r="A639" s="69" t="n"/>
       <c r="B639" s="72" t="n"/>
       <c r="C639" s="73" t="n"/>
@@ -32179,7 +32194,7 @@
       <c r="F639" s="69" t="n"/>
       <c r="G639" s="69" t="n"/>
     </row>
-    <row r="640">
+    <row r="640" s="477">
       <c r="A640" s="69" t="n"/>
       <c r="B640" s="72" t="n"/>
       <c r="C640" s="73" t="n"/>
@@ -32188,7 +32203,7 @@
       <c r="F640" s="69" t="n"/>
       <c r="G640" s="69" t="n"/>
     </row>
-    <row r="641">
+    <row r="641" s="477">
       <c r="A641" s="69" t="n"/>
       <c r="B641" s="72" t="n"/>
       <c r="C641" s="73" t="n"/>
@@ -32197,7 +32212,7 @@
       <c r="F641" s="69" t="n"/>
       <c r="G641" s="69" t="n"/>
     </row>
-    <row r="642">
+    <row r="642" s="477">
       <c r="A642" s="69" t="n"/>
       <c r="B642" s="72" t="n"/>
       <c r="C642" s="73" t="n"/>
@@ -32206,7 +32221,7 @@
       <c r="F642" s="69" t="n"/>
       <c r="G642" s="69" t="n"/>
     </row>
-    <row r="643">
+    <row r="643" s="477">
       <c r="A643" s="69" t="n"/>
       <c r="B643" s="72" t="n"/>
       <c r="C643" s="73" t="n"/>
@@ -32215,7 +32230,7 @@
       <c r="F643" s="69" t="n"/>
       <c r="G643" s="69" t="n"/>
     </row>
-    <row r="644">
+    <row r="644" s="477">
       <c r="A644" s="69" t="n"/>
       <c r="B644" s="72" t="n"/>
       <c r="C644" s="73" t="n"/>
@@ -32224,7 +32239,7 @@
       <c r="F644" s="69" t="n"/>
       <c r="G644" s="69" t="n"/>
     </row>
-    <row r="645">
+    <row r="645" s="477">
       <c r="A645" s="69" t="n"/>
       <c r="B645" s="72" t="n"/>
       <c r="C645" s="73" t="n"/>
@@ -32233,7 +32248,7 @@
       <c r="F645" s="69" t="n"/>
       <c r="G645" s="69" t="n"/>
     </row>
-    <row r="646">
+    <row r="646" s="477">
       <c r="A646" s="69" t="n"/>
       <c r="B646" s="72" t="n"/>
       <c r="C646" s="73" t="n"/>
@@ -32242,7 +32257,7 @@
       <c r="F646" s="69" t="n"/>
       <c r="G646" s="69" t="n"/>
     </row>
-    <row r="647">
+    <row r="647" s="477">
       <c r="A647" s="69" t="n"/>
       <c r="B647" s="72" t="n"/>
       <c r="C647" s="73" t="n"/>
@@ -32251,7 +32266,7 @@
       <c r="F647" s="69" t="n"/>
       <c r="G647" s="69" t="n"/>
     </row>
-    <row r="648">
+    <row r="648" s="477">
       <c r="A648" s="69" t="n"/>
       <c r="B648" s="72" t="n"/>
       <c r="C648" s="73" t="n"/>
@@ -32260,7 +32275,7 @@
       <c r="F648" s="69" t="n"/>
       <c r="G648" s="69" t="n"/>
     </row>
-    <row r="649">
+    <row r="649" s="477">
       <c r="A649" s="69" t="n"/>
       <c r="B649" s="72" t="n"/>
       <c r="C649" s="73" t="n"/>
@@ -32269,7 +32284,7 @@
       <c r="F649" s="69" t="n"/>
       <c r="G649" s="69" t="n"/>
     </row>
-    <row r="650">
+    <row r="650" s="477">
       <c r="A650" s="69" t="n"/>
       <c r="B650" s="72" t="n"/>
       <c r="C650" s="73" t="n"/>
@@ -32278,7 +32293,7 @@
       <c r="F650" s="69" t="n"/>
       <c r="G650" s="69" t="n"/>
     </row>
-    <row r="651">
+    <row r="651" s="477">
       <c r="A651" s="69" t="n"/>
       <c r="B651" s="72" t="n"/>
       <c r="C651" s="73" t="n"/>
@@ -32287,7 +32302,7 @@
       <c r="F651" s="69" t="n"/>
       <c r="G651" s="69" t="n"/>
     </row>
-    <row r="652">
+    <row r="652" s="477">
       <c r="A652" s="69" t="n"/>
       <c r="B652" s="72" t="n"/>
       <c r="C652" s="73" t="n"/>
@@ -32296,7 +32311,7 @@
       <c r="F652" s="69" t="n"/>
       <c r="G652" s="69" t="n"/>
     </row>
-    <row r="653">
+    <row r="653" s="477">
       <c r="A653" s="69" t="n"/>
       <c r="B653" s="72" t="n"/>
       <c r="C653" s="73" t="n"/>
@@ -32305,7 +32320,7 @@
       <c r="F653" s="69" t="n"/>
       <c r="G653" s="69" t="n"/>
     </row>
-    <row r="654">
+    <row r="654" s="477">
       <c r="A654" s="69" t="n"/>
       <c r="B654" s="72" t="n"/>
       <c r="C654" s="73" t="n"/>
@@ -32314,7 +32329,7 @@
       <c r="F654" s="69" t="n"/>
       <c r="G654" s="69" t="n"/>
     </row>
-    <row r="655">
+    <row r="655" s="477">
       <c r="A655" s="69" t="n"/>
       <c r="B655" s="72" t="n"/>
       <c r="C655" s="73" t="n"/>
@@ -32323,7 +32338,7 @@
       <c r="F655" s="69" t="n"/>
       <c r="G655" s="69" t="n"/>
     </row>
-    <row r="656">
+    <row r="656" s="477">
       <c r="A656" s="69" t="n"/>
       <c r="B656" s="72" t="n"/>
       <c r="C656" s="73" t="n"/>
@@ -32332,7 +32347,7 @@
       <c r="F656" s="69" t="n"/>
       <c r="G656" s="69" t="n"/>
     </row>
-    <row r="657">
+    <row r="657" s="477">
       <c r="A657" s="69" t="n"/>
       <c r="B657" s="72" t="n"/>
       <c r="C657" s="73" t="n"/>
@@ -32341,7 +32356,7 @@
       <c r="F657" s="69" t="n"/>
       <c r="G657" s="69" t="n"/>
     </row>
-    <row r="658">
+    <row r="658" s="477">
       <c r="A658" s="69" t="n"/>
       <c r="B658" s="72" t="n"/>
       <c r="C658" s="73" t="n"/>
@@ -32350,7 +32365,7 @@
       <c r="F658" s="69" t="n"/>
       <c r="G658" s="69" t="n"/>
     </row>
-    <row r="659">
+    <row r="659" s="477">
       <c r="A659" s="69" t="n"/>
       <c r="B659" s="72" t="n"/>
       <c r="C659" s="73" t="n"/>
@@ -32359,7 +32374,7 @@
       <c r="F659" s="69" t="n"/>
       <c r="G659" s="69" t="n"/>
     </row>
-    <row r="660">
+    <row r="660" s="477">
       <c r="A660" s="69" t="n"/>
       <c r="B660" s="72" t="n"/>
       <c r="C660" s="73" t="n"/>
@@ -32368,7 +32383,7 @@
       <c r="F660" s="69" t="n"/>
       <c r="G660" s="69" t="n"/>
     </row>
-    <row r="661">
+    <row r="661" s="477">
       <c r="A661" s="69" t="n"/>
       <c r="B661" s="72" t="n"/>
       <c r="C661" s="73" t="n"/>
@@ -32377,7 +32392,7 @@
       <c r="F661" s="69" t="n"/>
       <c r="G661" s="69" t="n"/>
     </row>
-    <row r="662">
+    <row r="662" s="477">
       <c r="A662" s="69" t="n"/>
       <c r="B662" s="72" t="n"/>
       <c r="C662" s="73" t="n"/>
@@ -32386,7 +32401,7 @@
       <c r="F662" s="69" t="n"/>
       <c r="G662" s="69" t="n"/>
     </row>
-    <row r="663">
+    <row r="663" s="477">
       <c r="A663" s="69" t="n"/>
       <c r="B663" s="72" t="n"/>
       <c r="C663" s="73" t="n"/>
@@ -32395,7 +32410,7 @@
       <c r="F663" s="69" t="n"/>
       <c r="G663" s="69" t="n"/>
     </row>
-    <row r="664">
+    <row r="664" s="477">
       <c r="A664" s="69" t="n"/>
       <c r="B664" s="72" t="n"/>
       <c r="C664" s="73" t="n"/>
@@ -32404,7 +32419,7 @@
       <c r="F664" s="69" t="n"/>
       <c r="G664" s="69" t="n"/>
     </row>
-    <row r="665">
+    <row r="665" s="477">
       <c r="A665" s="69" t="n"/>
       <c r="B665" s="72" t="n"/>
       <c r="C665" s="73" t="n"/>
@@ -32413,7 +32428,7 @@
       <c r="F665" s="69" t="n"/>
       <c r="G665" s="69" t="n"/>
     </row>
-    <row r="666">
+    <row r="666" s="477">
       <c r="A666" s="69" t="n"/>
       <c r="B666" s="72" t="n"/>
       <c r="C666" s="73" t="n"/>
@@ -32422,7 +32437,7 @@
       <c r="F666" s="69" t="n"/>
       <c r="G666" s="69" t="n"/>
     </row>
-    <row r="667">
+    <row r="667" s="477">
       <c r="A667" s="69" t="n"/>
       <c r="B667" s="72" t="n"/>
       <c r="C667" s="73" t="n"/>
@@ -32431,7 +32446,7 @@
       <c r="F667" s="69" t="n"/>
       <c r="G667" s="69" t="n"/>
     </row>
-    <row r="668">
+    <row r="668" s="477">
       <c r="A668" s="69" t="n"/>
       <c r="B668" s="72" t="n"/>
       <c r="C668" s="73" t="n"/>
@@ -32440,7 +32455,7 @@
       <c r="F668" s="69" t="n"/>
       <c r="G668" s="69" t="n"/>
     </row>
-    <row r="669">
+    <row r="669" s="477">
       <c r="A669" s="69" t="n"/>
       <c r="B669" s="72" t="n"/>
       <c r="C669" s="73" t="n"/>
@@ -32449,7 +32464,7 @@
       <c r="F669" s="69" t="n"/>
       <c r="G669" s="69" t="n"/>
     </row>
-    <row r="670">
+    <row r="670" s="477">
       <c r="A670" s="69" t="n"/>
       <c r="B670" s="72" t="n"/>
       <c r="C670" s="73" t="n"/>
@@ -32458,7 +32473,7 @@
       <c r="F670" s="69" t="n"/>
       <c r="G670" s="69" t="n"/>
     </row>
-    <row r="671">
+    <row r="671" s="477">
       <c r="A671" s="69" t="n"/>
       <c r="B671" s="72" t="n"/>
       <c r="C671" s="73" t="n"/>
@@ -32467,7 +32482,7 @@
       <c r="F671" s="69" t="n"/>
       <c r="G671" s="69" t="n"/>
     </row>
-    <row r="672">
+    <row r="672" s="477">
       <c r="A672" s="69" t="n"/>
       <c r="B672" s="72" t="n"/>
       <c r="C672" s="73" t="n"/>
@@ -32476,7 +32491,7 @@
       <c r="F672" s="69" t="n"/>
       <c r="G672" s="69" t="n"/>
     </row>
-    <row r="673">
+    <row r="673" s="477">
       <c r="A673" s="69" t="n"/>
       <c r="B673" s="72" t="n"/>
       <c r="C673" s="73" t="n"/>
@@ -32485,7 +32500,7 @@
       <c r="F673" s="69" t="n"/>
       <c r="G673" s="69" t="n"/>
     </row>
-    <row r="674">
+    <row r="674" s="477">
       <c r="A674" s="69" t="n"/>
       <c r="B674" s="72" t="n"/>
       <c r="C674" s="73" t="n"/>
@@ -32494,7 +32509,7 @@
       <c r="F674" s="69" t="n"/>
       <c r="G674" s="69" t="n"/>
     </row>
-    <row r="675">
+    <row r="675" s="477">
       <c r="A675" s="69" t="n"/>
       <c r="B675" s="72" t="n"/>
       <c r="C675" s="73" t="n"/>
@@ -32503,7 +32518,7 @@
       <c r="F675" s="69" t="n"/>
       <c r="G675" s="69" t="n"/>
     </row>
-    <row r="676">
+    <row r="676" s="477">
       <c r="A676" s="69" t="n"/>
       <c r="B676" s="72" t="n"/>
       <c r="C676" s="73" t="n"/>
@@ -32512,7 +32527,7 @@
       <c r="F676" s="69" t="n"/>
       <c r="G676" s="69" t="n"/>
     </row>
-    <row r="677">
+    <row r="677" s="477">
       <c r="A677" s="69" t="n"/>
       <c r="B677" s="72" t="n"/>
       <c r="C677" s="73" t="n"/>
@@ -32521,7 +32536,7 @@
       <c r="F677" s="69" t="n"/>
       <c r="G677" s="69" t="n"/>
     </row>
-    <row r="678">
+    <row r="678" s="477">
       <c r="A678" s="69" t="n"/>
       <c r="B678" s="72" t="n"/>
       <c r="C678" s="73" t="n"/>
@@ -32530,7 +32545,7 @@
       <c r="F678" s="69" t="n"/>
       <c r="G678" s="69" t="n"/>
     </row>
-    <row r="679">
+    <row r="679" s="477">
       <c r="A679" s="69" t="n"/>
       <c r="B679" s="72" t="n"/>
       <c r="C679" s="73" t="n"/>
@@ -32539,7 +32554,7 @@
       <c r="F679" s="69" t="n"/>
       <c r="G679" s="69" t="n"/>
     </row>
-    <row r="680">
+    <row r="680" s="477">
       <c r="A680" s="69" t="n"/>
       <c r="B680" s="72" t="n"/>
       <c r="C680" s="73" t="n"/>
@@ -32548,7 +32563,7 @@
       <c r="F680" s="69" t="n"/>
       <c r="G680" s="69" t="n"/>
     </row>
-    <row r="681">
+    <row r="681" s="477">
       <c r="A681" s="69" t="n"/>
       <c r="B681" s="72" t="n"/>
       <c r="C681" s="73" t="n"/>
@@ -32557,7 +32572,7 @@
       <c r="F681" s="69" t="n"/>
       <c r="G681" s="69" t="n"/>
     </row>
-    <row r="682">
+    <row r="682" s="477">
       <c r="A682" s="69" t="n"/>
       <c r="B682" s="72" t="n"/>
       <c r="C682" s="73" t="n"/>
@@ -32566,7 +32581,7 @@
       <c r="F682" s="69" t="n"/>
       <c r="G682" s="69" t="n"/>
     </row>
-    <row r="683">
+    <row r="683" s="477">
       <c r="A683" s="69" t="n"/>
       <c r="B683" s="72" t="n"/>
       <c r="C683" s="73" t="n"/>
@@ -32575,7 +32590,7 @@
       <c r="F683" s="69" t="n"/>
       <c r="G683" s="69" t="n"/>
     </row>
-    <row r="684">
+    <row r="684" s="477">
       <c r="A684" s="69" t="n"/>
       <c r="B684" s="72" t="n"/>
       <c r="C684" s="73" t="n"/>
@@ -32584,7 +32599,7 @@
       <c r="F684" s="69" t="n"/>
       <c r="G684" s="69" t="n"/>
     </row>
-    <row r="685">
+    <row r="685" s="477">
       <c r="A685" s="69" t="n"/>
       <c r="B685" s="72" t="n"/>
       <c r="C685" s="73" t="n"/>
@@ -32593,7 +32608,7 @@
       <c r="F685" s="69" t="n"/>
       <c r="G685" s="69" t="n"/>
     </row>
-    <row r="686">
+    <row r="686" s="477">
       <c r="A686" s="69" t="n"/>
       <c r="B686" s="72" t="n"/>
       <c r="C686" s="73" t="n"/>
@@ -32602,7 +32617,7 @@
       <c r="F686" s="69" t="n"/>
       <c r="G686" s="69" t="n"/>
     </row>
-    <row r="687">
+    <row r="687" s="477">
       <c r="A687" s="69" t="n"/>
       <c r="B687" s="72" t="n"/>
       <c r="C687" s="73" t="n"/>
@@ -32611,7 +32626,7 @@
       <c r="F687" s="69" t="n"/>
       <c r="G687" s="69" t="n"/>
     </row>
-    <row r="688">
+    <row r="688" s="477">
       <c r="A688" s="69" t="n"/>
       <c r="B688" s="72" t="n"/>
       <c r="C688" s="73" t="n"/>
@@ -32620,7 +32635,7 @@
       <c r="F688" s="69" t="n"/>
       <c r="G688" s="69" t="n"/>
     </row>
-    <row r="689">
+    <row r="689" s="477">
       <c r="A689" s="69" t="n"/>
       <c r="B689" s="72" t="n"/>
       <c r="C689" s="73" t="n"/>
@@ -32629,7 +32644,7 @@
       <c r="F689" s="69" t="n"/>
       <c r="G689" s="69" t="n"/>
     </row>
-    <row r="690">
+    <row r="690" s="477">
       <c r="A690" s="69" t="n"/>
       <c r="B690" s="72" t="n"/>
       <c r="C690" s="73" t="n"/>
@@ -32638,7 +32653,7 @@
       <c r="F690" s="69" t="n"/>
       <c r="G690" s="69" t="n"/>
     </row>
-    <row r="691">
+    <row r="691" s="477">
       <c r="A691" s="69" t="n"/>
       <c r="B691" s="72" t="n"/>
       <c r="C691" s="73" t="n"/>
@@ -32647,7 +32662,7 @@
       <c r="F691" s="69" t="n"/>
       <c r="G691" s="69" t="n"/>
     </row>
-    <row r="692">
+    <row r="692" s="477">
       <c r="A692" s="69" t="n"/>
       <c r="B692" s="72" t="n"/>
       <c r="C692" s="73" t="n"/>
@@ -32656,7 +32671,7 @@
       <c r="F692" s="69" t="n"/>
       <c r="G692" s="69" t="n"/>
     </row>
-    <row r="693">
+    <row r="693" s="477">
       <c r="A693" s="69" t="n"/>
       <c r="B693" s="72" t="n"/>
       <c r="C693" s="73" t="n"/>
@@ -32665,7 +32680,7 @@
       <c r="F693" s="69" t="n"/>
       <c r="G693" s="69" t="n"/>
     </row>
-    <row r="694">
+    <row r="694" s="477">
       <c r="A694" s="69" t="n"/>
       <c r="B694" s="72" t="n"/>
       <c r="C694" s="73" t="n"/>
@@ -32674,7 +32689,7 @@
       <c r="F694" s="69" t="n"/>
       <c r="G694" s="69" t="n"/>
     </row>
-    <row r="695">
+    <row r="695" s="477">
       <c r="A695" s="69" t="n"/>
       <c r="B695" s="72" t="n"/>
       <c r="C695" s="73" t="n"/>
@@ -32683,7 +32698,7 @@
       <c r="F695" s="69" t="n"/>
       <c r="G695" s="69" t="n"/>
     </row>
-    <row r="696">
+    <row r="696" s="477">
       <c r="A696" s="69" t="n"/>
       <c r="B696" s="72" t="n"/>
       <c r="C696" s="73" t="n"/>
@@ -32692,7 +32707,7 @@
       <c r="F696" s="69" t="n"/>
       <c r="G696" s="69" t="n"/>
     </row>
-    <row r="697">
+    <row r="697" s="477">
       <c r="A697" s="69" t="n"/>
       <c r="B697" s="72" t="n"/>
       <c r="C697" s="73" t="n"/>
@@ -32701,7 +32716,7 @@
       <c r="F697" s="69" t="n"/>
       <c r="G697" s="69" t="n"/>
     </row>
-    <row r="698">
+    <row r="698" s="477">
       <c r="A698" s="69" t="n"/>
       <c r="B698" s="72" t="n"/>
       <c r="C698" s="73" t="n"/>
@@ -32710,7 +32725,7 @@
       <c r="F698" s="69" t="n"/>
       <c r="G698" s="69" t="n"/>
     </row>
-    <row r="699">
+    <row r="699" s="477">
       <c r="A699" s="69" t="n"/>
       <c r="B699" s="72" t="n"/>
       <c r="C699" s="73" t="n"/>
@@ -32719,7 +32734,7 @@
       <c r="F699" s="69" t="n"/>
       <c r="G699" s="69" t="n"/>
     </row>
-    <row r="700">
+    <row r="700" s="477">
       <c r="A700" s="69" t="n"/>
       <c r="B700" s="72" t="n"/>
       <c r="C700" s="73" t="n"/>
@@ -32728,7 +32743,7 @@
       <c r="F700" s="69" t="n"/>
       <c r="G700" s="69" t="n"/>
     </row>
-    <row r="701">
+    <row r="701" s="477">
       <c r="A701" s="69" t="n"/>
       <c r="B701" s="72" t="n"/>
       <c r="C701" s="73" t="n"/>
@@ -32737,7 +32752,7 @@
       <c r="F701" s="69" t="n"/>
       <c r="G701" s="69" t="n"/>
     </row>
-    <row r="702">
+    <row r="702" s="477">
       <c r="A702" s="69" t="n"/>
       <c r="B702" s="72" t="n"/>
       <c r="C702" s="73" t="n"/>
@@ -32746,7 +32761,7 @@
       <c r="F702" s="69" t="n"/>
       <c r="G702" s="69" t="n"/>
     </row>
-    <row r="703">
+    <row r="703" s="477">
       <c r="A703" s="69" t="n"/>
       <c r="B703" s="72" t="n"/>
       <c r="C703" s="73" t="n"/>
@@ -32755,7 +32770,7 @@
       <c r="F703" s="69" t="n"/>
       <c r="G703" s="69" t="n"/>
     </row>
-    <row r="704">
+    <row r="704" s="477">
       <c r="A704" s="69" t="n"/>
       <c r="B704" s="72" t="n"/>
       <c r="C704" s="73" t="n"/>
@@ -32764,7 +32779,7 @@
       <c r="F704" s="69" t="n"/>
       <c r="G704" s="69" t="n"/>
     </row>
-    <row r="705">
+    <row r="705" s="477">
       <c r="A705" s="69" t="n"/>
       <c r="B705" s="72" t="n"/>
       <c r="C705" s="73" t="n"/>
@@ -32773,7 +32788,7 @@
       <c r="F705" s="69" t="n"/>
       <c r="G705" s="69" t="n"/>
     </row>
-    <row r="706">
+    <row r="706" s="477">
       <c r="A706" s="69" t="n"/>
       <c r="B706" s="72" t="n"/>
       <c r="C706" s="73" t="n"/>
@@ -32782,7 +32797,7 @@
       <c r="F706" s="69" t="n"/>
       <c r="G706" s="69" t="n"/>
     </row>
-    <row r="707">
+    <row r="707" s="477">
       <c r="A707" s="69" t="n"/>
       <c r="B707" s="72" t="n"/>
       <c r="C707" s="73" t="n"/>
@@ -32791,7 +32806,7 @@
       <c r="F707" s="69" t="n"/>
       <c r="G707" s="69" t="n"/>
     </row>
-    <row r="708">
+    <row r="708" s="477">
       <c r="A708" s="69" t="n"/>
       <c r="B708" s="72" t="n"/>
       <c r="C708" s="73" t="n"/>
@@ -32800,7 +32815,7 @@
       <c r="F708" s="69" t="n"/>
       <c r="G708" s="69" t="n"/>
     </row>
-    <row r="709">
+    <row r="709" s="477">
       <c r="A709" s="69" t="n"/>
       <c r="B709" s="72" t="n"/>
       <c r="C709" s="73" t="n"/>
@@ -32809,7 +32824,7 @@
       <c r="F709" s="69" t="n"/>
       <c r="G709" s="69" t="n"/>
     </row>
-    <row r="710">
+    <row r="710" s="477">
       <c r="A710" s="69" t="n"/>
       <c r="B710" s="72" t="n"/>
       <c r="C710" s="73" t="n"/>
@@ -32818,7 +32833,7 @@
       <c r="F710" s="69" t="n"/>
       <c r="G710" s="69" t="n"/>
     </row>
-    <row r="711">
+    <row r="711" s="477">
       <c r="A711" s="69" t="n"/>
       <c r="B711" s="72" t="n"/>
       <c r="C711" s="73" t="n"/>
@@ -32827,7 +32842,7 @@
       <c r="F711" s="69" t="n"/>
       <c r="G711" s="69" t="n"/>
     </row>
-    <row r="712">
+    <row r="712" s="477">
       <c r="A712" s="69" t="n"/>
       <c r="B712" s="72" t="n"/>
       <c r="C712" s="73" t="n"/>
@@ -32836,7 +32851,7 @@
       <c r="F712" s="69" t="n"/>
       <c r="G712" s="69" t="n"/>
     </row>
-    <row r="713">
+    <row r="713" s="477">
       <c r="A713" s="69" t="n"/>
       <c r="B713" s="72" t="n"/>
       <c r="C713" s="73" t="n"/>
@@ -32845,7 +32860,7 @@
       <c r="F713" s="69" t="n"/>
       <c r="G713" s="69" t="n"/>
     </row>
-    <row r="714">
+    <row r="714" s="477">
       <c r="A714" s="69" t="n"/>
       <c r="B714" s="72" t="n"/>
       <c r="C714" s="73" t="n"/>
@@ -32854,7 +32869,7 @@
       <c r="F714" s="69" t="n"/>
       <c r="G714" s="69" t="n"/>
     </row>
-    <row r="715">
+    <row r="715" s="477">
       <c r="A715" s="69" t="n"/>
       <c r="B715" s="72" t="n"/>
       <c r="C715" s="73" t="n"/>
@@ -32863,7 +32878,7 @@
       <c r="F715" s="69" t="n"/>
       <c r="G715" s="69" t="n"/>
     </row>
-    <row r="716">
+    <row r="716" s="477">
       <c r="A716" s="69" t="n"/>
       <c r="B716" s="72" t="n"/>
       <c r="C716" s="73" t="n"/>
@@ -32872,7 +32887,7 @@
       <c r="F716" s="69" t="n"/>
       <c r="G716" s="69" t="n"/>
     </row>
-    <row r="717">
+    <row r="717" s="477">
       <c r="A717" s="69" t="n"/>
       <c r="B717" s="72" t="n"/>
       <c r="C717" s="73" t="n"/>
@@ -32881,7 +32896,7 @@
       <c r="F717" s="69" t="n"/>
       <c r="G717" s="69" t="n"/>
     </row>
-    <row r="718">
+    <row r="718" s="477">
       <c r="A718" s="69" t="n"/>
       <c r="B718" s="72" t="n"/>
       <c r="C718" s="73" t="n"/>
@@ -32890,7 +32905,7 @@
       <c r="F718" s="69" t="n"/>
       <c r="G718" s="69" t="n"/>
     </row>
-    <row r="719">
+    <row r="719" s="477">
       <c r="A719" s="69" t="n"/>
       <c r="B719" s="72" t="n"/>
       <c r="C719" s="73" t="n"/>
@@ -32899,7 +32914,7 @@
       <c r="F719" s="69" t="n"/>
       <c r="G719" s="69" t="n"/>
     </row>
-    <row r="720">
+    <row r="720" s="477">
       <c r="A720" s="69" t="n"/>
       <c r="B720" s="72" t="n"/>
       <c r="C720" s="73" t="n"/>
@@ -32908,7 +32923,7 @@
       <c r="F720" s="69" t="n"/>
       <c r="G720" s="69" t="n"/>
     </row>
-    <row r="721">
+    <row r="721" s="477">
       <c r="A721" s="69" t="n"/>
       <c r="B721" s="72" t="n"/>
       <c r="C721" s="73" t="n"/>
@@ -32917,7 +32932,7 @@
       <c r="F721" s="69" t="n"/>
       <c r="G721" s="69" t="n"/>
     </row>
-    <row r="722">
+    <row r="722" s="477">
       <c r="A722" s="69" t="n"/>
       <c r="B722" s="72" t="n"/>
       <c r="C722" s="73" t="n"/>
@@ -32926,7 +32941,7 @@
       <c r="F722" s="69" t="n"/>
       <c r="G722" s="69" t="n"/>
     </row>
-    <row r="723">
+    <row r="723" s="477">
       <c r="A723" s="69" t="n"/>
       <c r="B723" s="72" t="n"/>
       <c r="C723" s="73" t="n"/>
@@ -32935,7 +32950,7 @@
       <c r="F723" s="69" t="n"/>
       <c r="G723" s="69" t="n"/>
     </row>
-    <row r="724">
+    <row r="724" s="477">
       <c r="A724" s="69" t="n"/>
       <c r="B724" s="72" t="n"/>
       <c r="C724" s="73" t="n"/>
@@ -32944,7 +32959,7 @@
       <c r="F724" s="69" t="n"/>
       <c r="G724" s="69" t="n"/>
     </row>
-    <row r="725">
+    <row r="725" s="477">
       <c r="A725" s="69" t="n"/>
       <c r="B725" s="72" t="n"/>
       <c r="C725" s="73" t="n"/>
@@ -32953,7 +32968,7 @@
       <c r="F725" s="69" t="n"/>
       <c r="G725" s="69" t="n"/>
     </row>
-    <row r="726">
+    <row r="726" s="477">
       <c r="A726" s="69" t="n"/>
       <c r="B726" s="72" t="n"/>
       <c r="C726" s="73" t="n"/>
@@ -32962,7 +32977,7 @@
       <c r="F726" s="69" t="n"/>
       <c r="G726" s="69" t="n"/>
     </row>
-    <row r="727">
+    <row r="727" s="477">
       <c r="A727" s="69" t="n"/>
       <c r="B727" s="72" t="n"/>
       <c r="C727" s="73" t="n"/>
@@ -32971,7 +32986,7 @@
       <c r="F727" s="69" t="n"/>
       <c r="G727" s="69" t="n"/>
     </row>
-    <row r="728">
+    <row r="728" s="477">
       <c r="A728" s="69" t="n"/>
       <c r="B728" s="72" t="n"/>
       <c r="C728" s="73" t="n"/>
@@ -32980,7 +32995,7 @@
       <c r="F728" s="69" t="n"/>
       <c r="G728" s="69" t="n"/>
     </row>
-    <row r="729">
+    <row r="729" s="477">
       <c r="A729" s="69" t="n"/>
       <c r="B729" s="72" t="n"/>
       <c r="C729" s="73" t="n"/>
@@ -32989,7 +33004,7 @@
       <c r="F729" s="69" t="n"/>
       <c r="G729" s="69" t="n"/>
     </row>
-    <row r="730">
+    <row r="730" s="477">
       <c r="A730" s="69" t="n"/>
       <c r="B730" s="72" t="n"/>
       <c r="C730" s="73" t="n"/>
@@ -32998,7 +33013,7 @@
       <c r="F730" s="69" t="n"/>
       <c r="G730" s="69" t="n"/>
     </row>
-    <row r="731">
+    <row r="731" s="477">
       <c r="A731" s="69" t="n"/>
       <c r="B731" s="72" t="n"/>
       <c r="C731" s="73" t="n"/>
@@ -33007,7 +33022,7 @@
       <c r="F731" s="69" t="n"/>
       <c r="G731" s="69" t="n"/>
     </row>
-    <row r="732">
+    <row r="732" s="477">
       <c r="A732" s="69" t="n"/>
       <c r="B732" s="72" t="n"/>
       <c r="C732" s="73" t="n"/>
@@ -33016,7 +33031,7 @@
       <c r="F732" s="69" t="n"/>
       <c r="G732" s="69" t="n"/>
     </row>
-    <row r="733">
+    <row r="733" s="477">
       <c r="A733" s="69" t="n"/>
       <c r="B733" s="72" t="n"/>
       <c r="C733" s="73" t="n"/>
@@ -33025,7 +33040,7 @@
       <c r="F733" s="69" t="n"/>
       <c r="G733" s="69" t="n"/>
     </row>
-    <row r="734">
+    <row r="734" s="477">
       <c r="A734" s="69" t="n"/>
       <c r="B734" s="72" t="n"/>
       <c r="C734" s="73" t="n"/>
@@ -33034,7 +33049,7 @@
       <c r="F734" s="69" t="n"/>
       <c r="G734" s="69" t="n"/>
     </row>
-    <row r="735">
+    <row r="735" s="477">
       <c r="A735" s="69" t="n"/>
       <c r="B735" s="72" t="n"/>
       <c r="C735" s="73" t="n"/>
@@ -33043,7 +33058,7 @@
       <c r="F735" s="69" t="n"/>
       <c r="G735" s="69" t="n"/>
     </row>
-    <row r="736">
+    <row r="736" s="477">
       <c r="A736" s="69" t="n"/>
       <c r="B736" s="72" t="n"/>
       <c r="C736" s="73" t="n"/>
@@ -33052,7 +33067,7 @@
       <c r="F736" s="69" t="n"/>
       <c r="G736" s="69" t="n"/>
     </row>
-    <row r="737">
+    <row r="737" s="477">
       <c r="A737" s="69" t="n"/>
       <c r="B737" s="72" t="n"/>
       <c r="C737" s="73" t="n"/>
@@ -33061,7 +33076,7 @@
       <c r="F737" s="69" t="n"/>
       <c r="G737" s="69" t="n"/>
     </row>
-    <row r="738">
+    <row r="738" s="477">
       <c r="A738" s="69" t="n"/>
       <c r="B738" s="72" t="n"/>
       <c r="C738" s="73" t="n"/>
@@ -33070,7 +33085,7 @@
       <c r="F738" s="69" t="n"/>
       <c r="G738" s="69" t="n"/>
     </row>
-    <row r="739">
+    <row r="739" s="477">
       <c r="A739" s="69" t="n"/>
       <c r="B739" s="72" t="n"/>
       <c r="C739" s="73" t="n"/>
@@ -33079,7 +33094,7 @@
       <c r="F739" s="69" t="n"/>
       <c r="G739" s="69" t="n"/>
     </row>
-    <row r="740">
+    <row r="740" s="477">
       <c r="A740" s="69" t="n"/>
       <c r="B740" s="72" t="n"/>
       <c r="C740" s="73" t="n"/>
@@ -33088,7 +33103,7 @@
       <c r="F740" s="69" t="n"/>
       <c r="G740" s="69" t="n"/>
     </row>
-    <row r="741">
+    <row r="741" s="477">
       <c r="A741" s="69" t="n"/>
       <c r="B741" s="72" t="n"/>
       <c r="C741" s="73" t="n"/>
@@ -33097,7 +33112,7 @@
       <c r="F741" s="69" t="n"/>
       <c r="G741" s="69" t="n"/>
     </row>
-    <row r="742">
+    <row r="742" s="477">
       <c r="A742" s="69" t="n"/>
       <c r="B742" s="72" t="n"/>
       <c r="C742" s="73" t="n"/>
@@ -33106,7 +33121,7 @@
       <c r="F742" s="69" t="n"/>
       <c r="G742" s="69" t="n"/>
     </row>
-    <row r="743">
+    <row r="743" s="477">
       <c r="A743" s="69" t="n"/>
       <c r="B743" s="72" t="n"/>
       <c r="C743" s="73" t="n"/>
@@ -33115,7 +33130,7 @@
       <c r="F743" s="69" t="n"/>
       <c r="G743" s="69" t="n"/>
     </row>
-    <row r="744">
+    <row r="744" s="477">
       <c r="A744" s="69" t="n"/>
       <c r="B744" s="72" t="n"/>
       <c r="C744" s="73" t="n"/>
@@ -33124,7 +33139,7 @@
       <c r="F744" s="69" t="n"/>
       <c r="G744" s="69" t="n"/>
     </row>
-    <row r="745">
+    <row r="745" s="477">
       <c r="A745" s="69" t="n"/>
       <c r="B745" s="72" t="n"/>
       <c r="C745" s="73" t="n"/>
@@ -33133,7 +33148,7 @@
       <c r="F745" s="69" t="n"/>
       <c r="G745" s="69" t="n"/>
     </row>
-    <row r="746">
+    <row r="746" s="477">
       <c r="A746" s="69" t="n"/>
       <c r="B746" s="72" t="n"/>
       <c r="C746" s="73" t="n"/>
@@ -33142,7 +33157,7 @@
       <c r="F746" s="69" t="n"/>
       <c r="G746" s="69" t="n"/>
     </row>
-    <row r="747">
+    <row r="747" s="477">
       <c r="A747" s="69" t="n"/>
       <c r="B747" s="72" t="n"/>
       <c r="C747" s="73" t="n"/>
@@ -33151,7 +33166,7 @@
       <c r="F747" s="69" t="n"/>
       <c r="G747" s="69" t="n"/>
     </row>
-    <row r="748">
+    <row r="748" s="477">
       <c r="A748" s="69" t="n"/>
       <c r="B748" s="72" t="n"/>
       <c r="C748" s="73" t="n"/>
@@ -33160,7 +33175,7 @@
       <c r="F748" s="69" t="n"/>
       <c r="G748" s="69" t="n"/>
     </row>
-    <row r="749">
+    <row r="749" s="477">
       <c r="A749" s="69" t="n"/>
       <c r="B749" s="72" t="n"/>
       <c r="C749" s="73" t="n"/>
@@ -33169,7 +33184,7 @@
       <c r="F749" s="69" t="n"/>
       <c r="G749" s="69" t="n"/>
     </row>
-    <row r="750">
+    <row r="750" s="477">
       <c r="A750" s="69" t="n"/>
       <c r="B750" s="72" t="n"/>
       <c r="C750" s="73" t="n"/>
@@ -33178,7 +33193,7 @@
       <c r="F750" s="69" t="n"/>
       <c r="G750" s="69" t="n"/>
     </row>
-    <row r="751">
+    <row r="751" s="477">
       <c r="A751" s="69" t="n"/>
       <c r="B751" s="72" t="n"/>
       <c r="C751" s="73" t="n"/>
@@ -33187,7 +33202,7 @@
       <c r="F751" s="69" t="n"/>
       <c r="G751" s="69" t="n"/>
     </row>
-    <row r="752">
+    <row r="752" s="477">
       <c r="A752" s="69" t="n"/>
       <c r="B752" s="72" t="n"/>
       <c r="C752" s="73" t="n"/>
@@ -33196,7 +33211,7 @@
       <c r="F752" s="69" t="n"/>
       <c r="G752" s="69" t="n"/>
     </row>
-    <row r="753">
+    <row r="753" s="477">
       <c r="A753" s="69" t="n"/>
       <c r="B753" s="72" t="n"/>
       <c r="C753" s="73" t="n"/>
@@ -33205,7 +33220,7 @@
       <c r="F753" s="69" t="n"/>
       <c r="G753" s="69" t="n"/>
     </row>
-    <row r="754">
+    <row r="754" s="477">
       <c r="A754" s="69" t="n"/>
       <c r="B754" s="72" t="n"/>
       <c r="C754" s="73" t="n"/>
@@ -33214,7 +33229,7 @@
       <c r="F754" s="69" t="n"/>
       <c r="G754" s="69" t="n"/>
     </row>
-    <row r="755">
+    <row r="755" s="477">
       <c r="A755" s="69" t="n"/>
       <c r="B755" s="72" t="n"/>
       <c r="C755" s="73" t="n"/>
@@ -33223,7 +33238,7 @@
       <c r="F755" s="69" t="n"/>
       <c r="G755" s="69" t="n"/>
     </row>
-    <row r="756">
+    <row r="756" s="477">
       <c r="A756" s="69" t="n"/>
       <c r="B756" s="72" t="n"/>
       <c r="C756" s="73" t="n"/>
@@ -33232,7 +33247,7 @@
       <c r="F756" s="69" t="n"/>
       <c r="G756" s="69" t="n"/>
     </row>
-    <row r="757">
+    <row r="757" s="477">
       <c r="A757" s="69" t="n"/>
       <c r="B757" s="72" t="n"/>
       <c r="C757" s="73" t="n"/>
@@ -33241,7 +33256,7 @@
       <c r="F757" s="69" t="n"/>
       <c r="G757" s="69" t="n"/>
     </row>
-    <row r="758">
+    <row r="758" s="477">
       <c r="A758" s="69" t="n"/>
       <c r="B758" s="72" t="n"/>
       <c r="C758" s="73" t="n"/>
@@ -33250,7 +33265,7 @@
       <c r="F758" s="69" t="n"/>
       <c r="G758" s="69" t="n"/>
     </row>
-    <row r="759">
+    <row r="759" s="477">
       <c r="A759" s="69" t="n"/>
       <c r="B759" s="72" t="n"/>
       <c r="C759" s="73" t="n"/>
@@ -33259,7 +33274,7 @@
       <c r="F759" s="69" t="n"/>
       <c r="G759" s="69" t="n"/>
     </row>
-    <row r="760">
+    <row r="760" s="477">
       <c r="A760" s="69" t="n"/>
       <c r="B760" s="72" t="n"/>
       <c r="C760" s="73" t="n"/>
@@ -33268,7 +33283,7 @@
       <c r="F760" s="69" t="n"/>
       <c r="G760" s="69" t="n"/>
     </row>
-    <row r="761">
+    <row r="761" s="477">
       <c r="A761" s="69" t="n"/>
       <c r="B761" s="72" t="n"/>
       <c r="C761" s="73" t="n"/>
@@ -33277,7 +33292,7 @@
       <c r="F761" s="69" t="n"/>
       <c r="G761" s="69" t="n"/>
     </row>
-    <row r="762">
+    <row r="762" s="477">
       <c r="A762" s="69" t="n"/>
       <c r="B762" s="72" t="n"/>
       <c r="C762" s="73" t="n"/>
@@ -33286,7 +33301,7 @@
       <c r="F762" s="69" t="n"/>
       <c r="G762" s="69" t="n"/>
     </row>
-    <row r="763">
+    <row r="763" s="477">
       <c r="A763" s="69" t="n"/>
       <c r="B763" s="72" t="n"/>
       <c r="C763" s="73" t="n"/>
@@ -33295,7 +33310,7 @@
       <c r="F763" s="69" t="n"/>
       <c r="G763" s="69" t="n"/>
     </row>
-    <row r="764">
+    <row r="764" s="477">
       <c r="A764" s="69" t="n"/>
       <c r="B764" s="72" t="n"/>
       <c r="C764" s="73" t="n"/>
@@ -33304,7 +33319,7 @@
       <c r="F764" s="69" t="n"/>
       <c r="G764" s="69" t="n"/>
     </row>
-    <row r="765">
+    <row r="765" s="477">
       <c r="A765" s="69" t="n"/>
       <c r="B765" s="72" t="n"/>
       <c r="C765" s="73" t="n"/>
@@ -33313,7 +33328,7 @@
       <c r="F765" s="69" t="n"/>
       <c r="G765" s="69" t="n"/>
     </row>
-    <row r="766">
+    <row r="766" s="477">
       <c r="A766" s="69" t="n"/>
       <c r="B766" s="72" t="n"/>
       <c r="C766" s="73" t="n"/>
@@ -33322,7 +33337,7 @@
       <c r="F766" s="69" t="n"/>
       <c r="G766" s="69" t="n"/>
     </row>
-    <row r="767">
+    <row r="767" s="477">
       <c r="A767" s="69" t="n"/>
       <c r="B767" s="72" t="n"/>
       <c r="C767" s="73" t="n"/>
@@ -33331,7 +33346,7 @@
       <c r="F767" s="69" t="n"/>
       <c r="G767" s="69" t="n"/>
     </row>
-    <row r="768">
+    <row r="768" s="477">
       <c r="A768" s="69" t="n"/>
       <c r="B768" s="72" t="n"/>
       <c r="C768" s="73" t="n"/>
@@ -33340,7 +33355,7 @@
       <c r="F768" s="69" t="n"/>
       <c r="G768" s="69" t="n"/>
     </row>
-    <row r="769">
+    <row r="769" s="477">
       <c r="A769" s="69" t="n"/>
       <c r="B769" s="72" t="n"/>
       <c r="C769" s="73" t="n"/>
@@ -33349,7 +33364,7 @@
       <c r="F769" s="69" t="n"/>
       <c r="G769" s="69" t="n"/>
     </row>
-    <row r="770">
+    <row r="770" s="477">
       <c r="A770" s="69" t="n"/>
       <c r="B770" s="72" t="n"/>
       <c r="C770" s="73" t="n"/>
@@ -33358,7 +33373,7 @@
       <c r="F770" s="69" t="n"/>
       <c r="G770" s="69" t="n"/>
     </row>
-    <row r="771">
+    <row r="771" s="477">
       <c r="A771" s="69" t="n"/>
       <c r="B771" s="72" t="n"/>
       <c r="C771" s="73" t="n"/>
@@ -33367,7 +33382,7 @@
       <c r="F771" s="69" t="n"/>
       <c r="G771" s="69" t="n"/>
     </row>
-    <row r="772">
+    <row r="772" s="477">
       <c r="A772" s="69" t="n"/>
       <c r="B772" s="72" t="n"/>
       <c r="C772" s="73" t="n"/>
@@ -33376,7 +33391,7 @@
       <c r="F772" s="69" t="n"/>
       <c r="G772" s="69" t="n"/>
     </row>
-    <row r="773">
+    <row r="773" s="477">
       <c r="A773" s="69" t="n"/>
       <c r="B773" s="72" t="n"/>
       <c r="C773" s="73" t="n"/>
@@ -33385,7 +33400,7 @@
       <c r="F773" s="69" t="n"/>
       <c r="G773" s="69" t="n"/>
     </row>
-    <row r="774">
+    <row r="774" s="477">
       <c r="A774" s="69" t="n"/>
       <c r="B774" s="72" t="n"/>
       <c r="C774" s="73" t="n"/>
@@ -33394,7 +33409,7 @@
       <c r="F774" s="69" t="n"/>
       <c r="G774" s="69" t="n"/>
     </row>
-    <row r="775">
+    <row r="775" s="477">
       <c r="A775" s="69" t="n"/>
       <c r="B775" s="72" t="n"/>
       <c r="C775" s="73" t="n"/>
@@ -33403,7 +33418,7 @@
       <c r="F775" s="69" t="n"/>
       <c r="G775" s="69" t="n"/>
     </row>
-    <row r="776">
+    <row r="776" s="477">
       <c r="A776" s="69" t="n"/>
       <c r="B776" s="72" t="n"/>
       <c r="C776" s="73" t="n"/>
@@ -33412,7 +33427,7 @@
       <c r="F776" s="69" t="n"/>
       <c r="G776" s="69" t="n"/>
     </row>
-    <row r="777">
+    <row r="777" s="477">
       <c r="A777" s="69" t="n"/>
       <c r="B777" s="72" t="n"/>
       <c r="C777" s="73" t="n"/>
@@ -33421,7 +33436,7 @@
       <c r="F777" s="69" t="n"/>
       <c r="G777" s="69" t="n"/>
     </row>
-    <row r="778">
+    <row r="778" s="477">
       <c r="A778" s="69" t="n"/>
       <c r="B778" s="72" t="n"/>
       <c r="C778" s="73" t="n"/>
@@ -33430,7 +33445,7 @@
       <c r="F778" s="69" t="n"/>
       <c r="G778" s="69" t="n"/>
     </row>
-    <row r="779">
+    <row r="779" s="477">
       <c r="A779" s="69" t="n"/>
       <c r="B779" s="72" t="n"/>
       <c r="C779" s="73" t="n"/>
@@ -33439,7 +33454,7 @@
       <c r="F779" s="69" t="n"/>
       <c r="G779" s="69" t="n"/>
     </row>
-    <row r="780">
+    <row r="780" s="477">
       <c r="A780" s="69" t="n"/>
       <c r="B780" s="72" t="n"/>
       <c r="C780" s="73" t="n"/>
@@ -33448,7 +33463,7 @@
       <c r="F780" s="69" t="n"/>
       <c r="G780" s="69" t="n"/>
     </row>
-    <row r="781">
+    <row r="781" s="477">
       <c r="A781" s="69" t="n"/>
       <c r="B781" s="72" t="n"/>
       <c r="C781" s="73" t="n"/>
@@ -33457,7 +33472,7 @@
       <c r="F781" s="69" t="n"/>
       <c r="G781" s="69" t="n"/>
     </row>
-    <row r="782">
+    <row r="782" s="477">
       <c r="A782" s="69" t="n"/>
       <c r="B782" s="72" t="n"/>
       <c r="C782" s="73" t="n"/>
@@ -33466,7 +33481,7 @@
       <c r="F782" s="69" t="n"/>
       <c r="G782" s="69" t="n"/>
     </row>
-    <row r="783">
+    <row r="783" s="477">
       <c r="A783" s="69" t="n"/>
       <c r="B783" s="72" t="n"/>
       <c r="C783" s="73" t="n"/>
@@ -33475,7 +33490,7 @@
       <c r="F783" s="69" t="n"/>
       <c r="G783" s="69" t="n"/>
     </row>
-    <row r="784">
+    <row r="784" s="477">
       <c r="A784" s="69" t="n"/>
       <c r="B784" s="72" t="n"/>
       <c r="C784" s="73" t="n"/>
@@ -33484,7 +33499,7 @@
       <c r="F784" s="69" t="n"/>
       <c r="G784" s="69" t="n"/>
     </row>
-    <row r="785">
+    <row r="785" s="477">
       <c r="A785" s="69" t="n"/>
       <c r="B785" s="72" t="n"/>
       <c r="C785" s="73" t="n"/>
@@ -33493,7 +33508,7 @@
       <c r="F785" s="69" t="n"/>
       <c r="G785" s="69" t="n"/>
     </row>
-    <row r="786">
+    <row r="786" s="477">
       <c r="A786" s="69" t="n"/>
       <c r="B786" s="72" t="n"/>
       <c r="C786" s="73" t="n"/>
@@ -33502,7 +33517,7 @@
       <c r="F786" s="69" t="n"/>
       <c r="G786" s="69" t="n"/>
     </row>
-    <row r="787">
+    <row r="787" s="477">
       <c r="A787" s="69" t="n"/>
       <c r="B787" s="72" t="n"/>
       <c r="C787" s="73" t="n"/>
@@ -33511,7 +33526,7 @@
       <c r="F787" s="69" t="n"/>
       <c r="G787" s="69" t="n"/>
     </row>
-    <row r="788">
+    <row r="788" s="477">
       <c r="A788" s="69" t="n"/>
       <c r="B788" s="72" t="n"/>
       <c r="C788" s="73" t="n"/>
@@ -33520,7 +33535,7 @@
       <c r="F788" s="69" t="n"/>
       <c r="G788" s="69" t="n"/>
     </row>
-    <row r="789">
+    <row r="789" s="477">
       <c r="A789" s="69" t="n"/>
       <c r="B789" s="72" t="n"/>
       <c r="C789" s="73" t="n"/>
@@ -33529,7 +33544,7 @@
       <c r="F789" s="69" t="n"/>
       <c r="G789" s="69" t="n"/>
     </row>
-    <row r="790">
+    <row r="790" s="477">
       <c r="A790" s="69" t="n"/>
       <c r="B790" s="72" t="n"/>
       <c r="C790" s="73" t="n"/>
@@ -33538,7 +33553,7 @@
       <c r="F790" s="69" t="n"/>
       <c r="G790" s="69" t="n"/>
     </row>
-    <row r="791">
+    <row r="791" s="477">
       <c r="A791" s="69" t="n"/>
       <c r="B791" s="72" t="n"/>
       <c r="C791" s="73" t="n"/>
@@ -33547,7 +33562,7 @@
       <c r="F791" s="69" t="n"/>
       <c r="G791" s="69" t="n"/>
     </row>
-    <row r="792">
+    <row r="792" s="477">
       <c r="A792" s="69" t="n"/>
       <c r="B792" s="72" t="n"/>
       <c r="C792" s="73" t="n"/>
@@ -33556,7 +33571,7 @@
       <c r="F792" s="69" t="n"/>
       <c r="G792" s="69" t="n"/>
     </row>
-    <row r="793">
+    <row r="793" s="477">
       <c r="A793" s="69" t="n"/>
       <c r="B793" s="72" t="n"/>
       <c r="C793" s="73" t="n"/>
@@ -33565,7 +33580,7 @@
       <c r="F793" s="69" t="n"/>
       <c r="G793" s="69" t="n"/>
     </row>
-    <row r="794">
+    <row r="794" s="477">
       <c r="A794" s="69" t="n"/>
       <c r="B794" s="72" t="n"/>
       <c r="C794" s="73" t="n"/>
@@ -33574,7 +33589,7 @@
       <c r="F794" s="69" t="n"/>
       <c r="G794" s="69" t="n"/>
     </row>
-    <row r="795">
+    <row r="795" s="477">
       <c r="A795" s="69" t="n"/>
       <c r="B795" s="72" t="n"/>
       <c r="C795" s="73" t="n"/>
@@ -33583,7 +33598,7 @@
       <c r="F795" s="69" t="n"/>
       <c r="G795" s="69" t="n"/>
     </row>
-    <row r="796">
+    <row r="796" s="477">
       <c r="A796" s="69" t="n"/>
       <c r="B796" s="72" t="n"/>
       <c r="C796" s="73" t="n"/>
@@ -33592,7 +33607,7 @@
       <c r="F796" s="69" t="n"/>
       <c r="G796" s="69" t="n"/>
     </row>
-    <row r="797">
+    <row r="797" s="477">
       <c r="A797" s="69" t="n"/>
       <c r="B797" s="72" t="n"/>
       <c r="C797" s="73" t="n"/>
@@ -33601,7 +33616,7 @@
       <c r="F797" s="69" t="n"/>
       <c r="G797" s="69" t="n"/>
     </row>
-    <row r="798">
+    <row r="798" s="477">
       <c r="A798" s="69" t="n"/>
       <c r="B798" s="72" t="n"/>
       <c r="C798" s="73" t="n"/>
@@ -33610,7 +33625,7 @@
       <c r="F798" s="69" t="n"/>
       <c r="G798" s="69" t="n"/>
     </row>
-    <row r="799">
+    <row r="799" s="477">
       <c r="A799" s="69" t="n"/>
       <c r="B799" s="72" t="n"/>
       <c r="C799" s="73" t="n"/>
@@ -33619,7 +33634,7 @@
       <c r="F799" s="69" t="n"/>
       <c r="G799" s="69" t="n"/>
     </row>
-    <row r="800">
+    <row r="800" s="477">
       <c r="A800" s="69" t="n"/>
       <c r="B800" s="72" t="n"/>
       <c r="C800" s="73" t="n"/>
@@ -33628,7 +33643,7 @@
       <c r="F800" s="69" t="n"/>
       <c r="G800" s="69" t="n"/>
     </row>
-    <row r="801">
+    <row r="801" s="477">
       <c r="A801" s="69" t="n"/>
       <c r="B801" s="72" t="n"/>
       <c r="C801" s="73" t="n"/>
@@ -33637,7 +33652,7 @@
       <c r="F801" s="69" t="n"/>
       <c r="G801" s="69" t="n"/>
     </row>
-    <row r="802">
+    <row r="802" s="477">
       <c r="A802" s="69" t="n"/>
       <c r="B802" s="72" t="n"/>
       <c r="C802" s="73" t="n"/>
@@ -33646,7 +33661,7 @@
       <c r="F802" s="69" t="n"/>
       <c r="G802" s="69" t="n"/>
     </row>
-    <row r="803">
+    <row r="803" s="477">
       <c r="A803" s="69" t="n"/>
       <c r="B803" s="72" t="n"/>
       <c r="C803" s="73" t="n"/>
@@ -33655,7 +33670,7 @@
       <c r="F803" s="69" t="n"/>
       <c r="G803" s="69" t="n"/>
     </row>
-    <row r="804">
+    <row r="804" s="477">
       <c r="A804" s="69" t="n"/>
       <c r="B804" s="72" t="n"/>
       <c r="C804" s="73" t="n"/>
@@ -33664,7 +33679,7 @@
       <c r="F804" s="69" t="n"/>
       <c r="G804" s="69" t="n"/>
     </row>
-    <row r="805">
+    <row r="805" s="477">
       <c r="A805" s="69" t="n"/>
       <c r="B805" s="72" t="n"/>
       <c r="C805" s="73" t="n"/>
@@ -33673,7 +33688,7 @@
       <c r="F805" s="69" t="n"/>
       <c r="G805" s="69" t="n"/>
     </row>
-    <row r="806">
+    <row r="806" s="477">
       <c r="A806" s="69" t="n"/>
       <c r="B806" s="72" t="n"/>
       <c r="C806" s="73" t="n"/>
@@ -33682,7 +33697,7 @@
       <c r="F806" s="69" t="n"/>
       <c r="G806" s="69" t="n"/>
     </row>
-    <row r="807">
+    <row r="807" s="477">
       <c r="A807" s="69" t="n"/>
       <c r="B807" s="72" t="n"/>
       <c r="C807" s="73" t="n"/>
@@ -33691,7 +33706,7 @@
       <c r="F807" s="69" t="n"/>
       <c r="G807" s="69" t="n"/>
     </row>
-    <row r="808">
+    <row r="808" s="477">
       <c r="A808" s="69" t="n"/>
       <c r="B808" s="72" t="n"/>
       <c r="C808" s="73" t="n"/>
@@ -33700,7 +33715,7 @@
       <c r="F808" s="69" t="n"/>
       <c r="G808" s="69" t="n"/>
     </row>
-    <row r="809">
+    <row r="809" s="477">
       <c r="A809" s="69" t="n"/>
       <c r="B809" s="72" t="n"/>
       <c r="C809" s="73" t="n"/>
@@ -33709,7 +33724,7 @@
       <c r="F809" s="69" t="n"/>
       <c r="G809" s="69" t="n"/>
     </row>
-    <row r="810">
+    <row r="810" s="477">
       <c r="A810" s="69" t="n"/>
       <c r="B810" s="72" t="n"/>
       <c r="C810" s="73" t="n"/>
@@ -33718,7 +33733,7 @@
       <c r="F810" s="69" t="n"/>
       <c r="G810" s="69" t="n"/>
     </row>
-    <row r="811">
+    <row r="811" s="477">
       <c r="A811" s="69" t="n"/>
       <c r="B811" s="72" t="n"/>
       <c r="C811" s="73" t="n"/>
@@ -33727,7 +33742,7 @@
       <c r="F811" s="69" t="n"/>
       <c r="G811" s="69" t="n"/>
     </row>
-    <row r="812">
+    <row r="812" s="477">
       <c r="A812" s="69" t="n"/>
       <c r="B812" s="72" t="n"/>
       <c r="C812" s="73" t="n"/>
@@ -33736,7 +33751,7 @@
       <c r="F812" s="69" t="n"/>
       <c r="G812" s="69" t="n"/>
     </row>
-    <row r="813">
+    <row r="813" s="477">
       <c r="A813" s="69" t="n"/>
       <c r="B813" s="72" t="n"/>
       <c r="C813" s="73" t="n"/>
@@ -33745,7 +33760,7 @@
       <c r="F813" s="69" t="n"/>
       <c r="G813" s="69" t="n"/>
     </row>
-    <row r="814">
+    <row r="814" s="477">
       <c r="A814" s="69" t="n"/>
       <c r="B814" s="72" t="n"/>
       <c r="C814" s="73" t="n"/>
@@ -33754,7 +33769,7 @@
       <c r="F814" s="69" t="n"/>
       <c r="G814" s="69" t="n"/>
     </row>
-    <row r="815">
+    <row r="815" s="477">
       <c r="A815" s="69" t="n"/>
       <c r="B815" s="72" t="n"/>
       <c r="C815" s="73" t="n"/>
@@ -33763,7 +33778,7 @@
       <c r="F815" s="69" t="n"/>
       <c r="G815" s="69" t="n"/>
     </row>
-    <row r="816">
+    <row r="816" s="477">
       <c r="A816" s="69" t="n"/>
       <c r="B816" s="72" t="n"/>
       <c r="C816" s="73" t="n"/>
@@ -33772,7 +33787,7 @@
       <c r="F816" s="69" t="n"/>
       <c r="G816" s="69" t="n"/>
     </row>
-    <row r="817">
+    <row r="817" s="477">
       <c r="A817" s="69" t="n"/>
       <c r="B817" s="72" t="n"/>
       <c r="C817" s="73" t="n"/>
@@ -33781,7 +33796,7 @@
       <c r="F817" s="69" t="n"/>
       <c r="G817" s="69" t="n"/>
     </row>
-    <row r="818">
+    <row r="818" s="477">
       <c r="A818" s="69" t="n"/>
       <c r="B818" s="72" t="n"/>
       <c r="C818" s="73" t="n"/>
@@ -33790,7 +33805,7 @@
       <c r="F818" s="69" t="n"/>
       <c r="G818" s="69" t="n"/>
     </row>
-    <row r="819">
+    <row r="819" s="477">
       <c r="A819" s="69" t="n"/>
       <c r="B819" s="72" t="n"/>
       <c r="C819" s="73" t="n"/>
@@ -33799,7 +33814,7 @@
       <c r="F819" s="69" t="n"/>
       <c r="G819" s="69" t="n"/>
     </row>
-    <row r="820">
+    <row r="820" s="477">
       <c r="A820" s="69" t="n"/>
       <c r="B820" s="72" t="n"/>
       <c r="C820" s="73" t="n"/>
@@ -33808,7 +33823,7 @@
       <c r="F820" s="69" t="n"/>
       <c r="G820" s="69" t="n"/>
     </row>
-    <row r="821">
+    <row r="821" s="477">
       <c r="A821" s="69" t="n"/>
       <c r="B821" s="72" t="n"/>
       <c r="C821" s="73" t="n"/>
@@ -33817,7 +33832,7 @@
       <c r="F821" s="69" t="n"/>
       <c r="G821" s="69" t="n"/>
     </row>
-    <row r="822">
+    <row r="822" s="477">
       <c r="A822" s="69" t="n"/>
       <c r="B822" s="72" t="n"/>
       <c r="C822" s="73" t="n"/>
@@ -33826,7 +33841,7 @@
       <c r="F822" s="69" t="n"/>
       <c r="G822" s="69" t="n"/>
     </row>
-    <row r="823">
+    <row r="823" s="477">
       <c r="A823" s="69" t="n"/>
       <c r="B823" s="72" t="n"/>
       <c r="C823" s="73" t="n"/>
@@ -33835,7 +33850,7 @@
       <c r="F823" s="69" t="n"/>
       <c r="G823" s="69" t="n"/>
     </row>
-    <row r="824">
+    <row r="824" s="477">
       <c r="A824" s="69" t="n"/>
       <c r="B824" s="72" t="n"/>
       <c r="C824" s="73" t="n"/>
@@ -33844,7 +33859,7 @@
       <c r="F824" s="69" t="n"/>
       <c r="G824" s="69" t="n"/>
     </row>
-    <row r="825">
+    <row r="825" s="477">
       <c r="A825" s="69" t="n"/>
       <c r="B825" s="72" t="n"/>
       <c r="C825" s="73" t="n"/>
@@ -33853,7 +33868,7 @@
       <c r="F825" s="69" t="n"/>
       <c r="G825" s="69" t="n"/>
     </row>
-    <row r="826">
+    <row r="826" s="477">
       <c r="A826" s="69" t="n"/>
       <c r="B826" s="72" t="n"/>
       <c r="C826" s="73" t="n"/>
@@ -33862,7 +33877,7 @@
       <c r="F826" s="69" t="n"/>
       <c r="G826" s="69" t="n"/>
     </row>
-    <row r="827">
+    <row r="827" s="477">
       <c r="A827" s="69" t="n"/>
       <c r="B827" s="72" t="n"/>
       <c r="C827" s="73" t="n"/>
@@ -33871,7 +33886,7 @@
       <c r="F827" s="69" t="n"/>
       <c r="G827" s="69" t="n"/>
     </row>
-    <row r="828">
+    <row r="828" s="477">
       <c r="A828" s="69" t="n"/>
       <c r="B828" s="72" t="n"/>
       <c r="C828" s="73" t="n"/>
@@ -33880,7 +33895,7 @@
       <c r="F828" s="69" t="n"/>
       <c r="G828" s="69" t="n"/>
     </row>
-    <row r="829">
+    <row r="829" s="477">
       <c r="A829" s="69" t="n"/>
       <c r="B829" s="72" t="n"/>
       <c r="C829" s="73" t="n"/>
@@ -33889,7 +33904,7 @@
       <c r="F829" s="69" t="n"/>
       <c r="G829" s="69" t="n"/>
     </row>
-    <row r="830">
+    <row r="830" s="477">
       <c r="A830" s="69" t="n"/>
       <c r="B830" s="72" t="n"/>
       <c r="C830" s="73" t="n"/>
@@ -33898,7 +33913,7 @@
       <c r="F830" s="69" t="n"/>
       <c r="G830" s="69" t="n"/>
     </row>
-    <row r="831">
+    <row r="831" s="477">
       <c r="A831" s="69" t="n"/>
       <c r="B831" s="72" t="n"/>
       <c r="C831" s="73" t="n"/>
@@ -33907,7 +33922,7 @@
       <c r="F831" s="69" t="n"/>
       <c r="G831" s="69" t="n"/>
     </row>
-    <row r="832">
+    <row r="832" s="477">
       <c r="A832" s="69" t="n"/>
       <c r="B832" s="72" t="n"/>
       <c r="C832" s="73" t="n"/>
@@ -33916,7 +33931,7 @@
       <c r="F832" s="69" t="n"/>
       <c r="G832" s="69" t="n"/>
     </row>
-    <row r="833">
+    <row r="833" s="477">
       <c r="A833" s="69" t="n"/>
       <c r="B833" s="72" t="n"/>
       <c r="C833" s="73" t="n"/>
@@ -33925,7 +33940,7 @@
       <c r="F833" s="69" t="n"/>
       <c r="G833" s="69" t="n"/>
     </row>
-    <row r="834">
+    <row r="834" s="477">
       <c r="A834" s="69" t="n"/>
       <c r="B834" s="72" t="n"/>
       <c r="C834" s="73" t="n"/>
@@ -33934,7 +33949,7 @@
       <c r="F834" s="69" t="n"/>
       <c r="G834" s="69" t="n"/>
     </row>
-    <row r="835">
+    <row r="835" s="477">
       <c r="A835" s="69" t="n"/>
       <c r="B835" s="72" t="n"/>
       <c r="C835" s="73" t="n"/>
@@ -33943,7 +33958,7 @@
       <c r="F835" s="69" t="n"/>
       <c r="G835" s="69" t="n"/>
     </row>
-    <row r="836">
+    <row r="836" s="477">
       <c r="A836" s="69" t="n"/>
       <c r="B836" s="72" t="n"/>
       <c r="C836" s="73" t="n"/>
@@ -33952,7 +33967,7 @@
       <c r="F836" s="69" t="n"/>
       <c r="G836" s="69" t="n"/>
     </row>
-    <row r="837">
+    <row r="837" s="477">
       <c r="A837" s="69" t="n"/>
       <c r="B837" s="72" t="n"/>
       <c r="C837" s="73" t="n"/>
@@ -33961,7 +33976,7 @@
       <c r="F837" s="69" t="n"/>
       <c r="G837" s="69" t="n"/>
     </row>
-    <row r="838">
+    <row r="838" s="477">
       <c r="A838" s="69" t="n"/>
       <c r="B838" s="72" t="n"/>
       <c r="C838" s="73" t="n"/>
@@ -33970,7 +33985,7 @@
       <c r="F838" s="69" t="n"/>
       <c r="G838" s="69" t="n"/>
     </row>
-    <row r="839">
+    <row r="839" s="477">
       <c r="A839" s="69" t="n"/>
       <c r="B839" s="72" t="n"/>
       <c r="C839" s="73" t="n"/>
@@ -33979,7 +33994,7 @@
       <c r="F839" s="69" t="n"/>
       <c r="G839" s="69" t="n"/>
     </row>
-    <row r="840">
+    <row r="840" s="477">
       <c r="A840" s="69" t="n"/>
       <c r="B840" s="72" t="n"/>
       <c r="C840" s="73" t="n"/>
@@ -33988,7 +34003,7 @@
       <c r="F840" s="69" t="n"/>
       <c r="G840" s="69" t="n"/>
     </row>
-    <row r="841">
+    <row r="841" s="477">
       <c r="A841" s="69" t="n"/>
       <c r="B841" s="72" t="n"/>
       <c r="C841" s="73" t="n"/>
@@ -33997,7 +34012,7 @@
       <c r="F841" s="69" t="n"/>
       <c r="G841" s="69" t="n"/>
     </row>
-    <row r="842">
+    <row r="842" s="477">
       <c r="A842" s="69" t="n"/>
       <c r="B842" s="72" t="n"/>
       <c r="C842" s="73" t="n"/>
@@ -34006,7 +34021,7 @@
       <c r="F842" s="69" t="n"/>
       <c r="G842" s="69" t="n"/>
     </row>
-    <row r="843">
+    <row r="843" s="477">
       <c r="A843" s="69" t="n"/>
       <c r="B843" s="72" t="n"/>
       <c r="C843" s="73" t="n"/>
@@ -34015,7 +34030,7 @@
       <c r="F843" s="69" t="n"/>
       <c r="G843" s="69" t="n"/>
     </row>
-    <row r="844">
+    <row r="844" s="477">
       <c r="A844" s="69" t="n"/>
       <c r="B844" s="72" t="n"/>
       <c r="C844" s="73" t="n"/>
@@ -34024,7 +34039,7 @@
       <c r="F844" s="69" t="n"/>
       <c r="G844" s="69" t="n"/>
     </row>
-    <row r="845">
+    <row r="845" s="477">
       <c r="A845" s="69" t="n"/>
       <c r="B845" s="72" t="n"/>
       <c r="C845" s="73" t="n"/>
@@ -34033,7 +34048,7 @@
       <c r="F845" s="69" t="n"/>
       <c r="G845" s="69" t="n"/>
     </row>
-    <row r="846">
+    <row r="846" s="477">
       <c r="A846" s="69" t="n"/>
       <c r="B846" s="72" t="n"/>
       <c r="C846" s="73" t="n"/>
@@ -34042,7 +34057,7 @@
       <c r="F846" s="69" t="n"/>
       <c r="G846" s="69" t="n"/>
     </row>
-    <row r="847">
+    <row r="847" s="477">
       <c r="A847" s="69" t="n"/>
       <c r="B847" s="72" t="n"/>
       <c r="C847" s="73" t="n"/>
@@ -34051,7 +34066,7 @@
       <c r="F847" s="69" t="n"/>
       <c r="G847" s="69" t="n"/>
     </row>
-    <row r="848">
+    <row r="848" s="477">
       <c r="A848" s="69" t="n"/>
       <c r="B848" s="72" t="n"/>
       <c r="C848" s="73" t="n"/>
@@ -34060,7 +34075,7 @@
       <c r="F848" s="69" t="n"/>
       <c r="G848" s="69" t="n"/>
     </row>
-    <row r="849">
+    <row r="849" s="477">
       <c r="A849" s="69" t="n"/>
       <c r="B849" s="72" t="n"/>
       <c r="C849" s="73" t="n"/>
@@ -34069,7 +34084,7 @@
       <c r="F849" s="69" t="n"/>
       <c r="G849" s="69" t="n"/>
     </row>
-    <row r="850">
+    <row r="850" s="477">
       <c r="A850" s="69" t="n"/>
       <c r="B850" s="72" t="n"/>
       <c r="C850" s="73" t="n"/>
@@ -34078,7 +34093,7 @@
       <c r="F850" s="69" t="n"/>
       <c r="G850" s="69" t="n"/>
     </row>
-    <row r="851">
+    <row r="851" s="477">
       <c r="A851" s="69" t="n"/>
       <c r="B851" s="72" t="n"/>
       <c r="C851" s="73" t="n"/>
@@ -34087,7 +34102,7 @@
       <c r="F851" s="69" t="n"/>
       <c r="G851" s="69" t="n"/>
     </row>
-    <row r="852">
+    <row r="852" s="477">
       <c r="A852" s="69" t="n"/>
       <c r="B852" s="72" t="n"/>
       <c r="C852" s="73" t="n"/>
@@ -34096,7 +34111,7 @@
       <c r="F852" s="69" t="n"/>
       <c r="G852" s="69" t="n"/>
     </row>
-    <row r="853">
+    <row r="853" s="477">
       <c r="A853" s="69" t="n"/>
       <c r="B853" s="72" t="n"/>
       <c r="C853" s="73" t="n"/>
@@ -34105,7 +34120,7 @@
       <c r="F853" s="69" t="n"/>
       <c r="G853" s="69" t="n"/>
     </row>
-    <row r="854">
+    <row r="854" s="477">
       <c r="A854" s="69" t="n"/>
       <c r="B854" s="72" t="n"/>
       <c r="C854" s="73" t="n"/>
@@ -34114,7 +34129,7 @@
       <c r="F854" s="69" t="n"/>
       <c r="G854" s="69" t="n"/>
     </row>
-    <row r="855">
+    <row r="855" s="477">
       <c r="A855" s="69" t="n"/>
       <c r="B855" s="72" t="n"/>
       <c r="C855" s="73" t="n"/>
@@ -34123,7 +34138,7 @@
       <c r="F855" s="69" t="n"/>
       <c r="G855" s="69" t="n"/>
     </row>
-    <row r="856">
+    <row r="856" s="477">
       <c r="A856" s="69" t="n"/>
       <c r="B856" s="72" t="n"/>
       <c r="C856" s="73" t="n"/>
@@ -34132,7 +34147,7 @@
       <c r="F856" s="69" t="n"/>
       <c r="G856" s="69" t="n"/>
     </row>
-    <row r="857">
+    <row r="857" s="477">
       <c r="A857" s="69" t="n"/>
       <c r="B857" s="72" t="n"/>
       <c r="C857" s="73" t="n"/>
@@ -34141,7 +34156,7 @@
       <c r="F857" s="69" t="n"/>
       <c r="G857" s="69" t="n"/>
     </row>
-    <row r="858">
+    <row r="858" s="477">
       <c r="A858" s="69" t="n"/>
       <c r="B858" s="72" t="n"/>
       <c r="C858" s="73" t="n"/>
@@ -34150,7 +34165,7 @@
       <c r="F858" s="69" t="n"/>
       <c r="G858" s="69" t="n"/>
     </row>
-    <row r="859">
+    <row r="859" s="477">
       <c r="A859" s="69" t="n"/>
       <c r="B859" s="72" t="n"/>
       <c r="C859" s="73" t="n"/>
@@ -34159,7 +34174,7 @@
       <c r="F859" s="69" t="n"/>
       <c r="G859" s="69" t="n"/>
     </row>
-    <row r="860">
+    <row r="860" s="477">
       <c r="A860" s="69" t="n"/>
       <c r="B860" s="72" t="n"/>
       <c r="C860" s="73" t="n"/>
@@ -34168,7 +34183,7 @@
       <c r="F860" s="69" t="n"/>
       <c r="G860" s="69" t="n"/>
     </row>
-    <row r="861">
+    <row r="861" s="477">
       <c r="A861" s="69" t="n"/>
       <c r="B861" s="72" t="n"/>
       <c r="C861" s="73" t="n"/>
@@ -34177,7 +34192,7 @@
       <c r="F861" s="69" t="n"/>
       <c r="G861" s="69" t="n"/>
     </row>
-    <row r="862">
+    <row r="862" s="477">
       <c r="A862" s="69" t="n"/>
       <c r="B862" s="72" t="n"/>
       <c r="C862" s="73" t="n"/>
@@ -34186,7 +34201,7 @@
       <c r="F862" s="69" t="n"/>
       <c r="G862" s="69" t="n"/>
     </row>
-    <row r="863">
+    <row r="863" s="477">
       <c r="A863" s="69" t="n"/>
       <c r="B863" s="72" t="n"/>
       <c r="C863" s="73" t="n"/>
@@ -34195,7 +34210,7 @@
       <c r="F863" s="69" t="n"/>
       <c r="G863" s="69" t="n"/>
     </row>
-    <row r="864">
+    <row r="864" s="477">
       <c r="A864" s="69" t="n"/>
       <c r="B864" s="72" t="n"/>
       <c r="C864" s="73" t="n"/>
@@ -34204,7 +34219,7 @@
       <c r="F864" s="69" t="n"/>
       <c r="G864" s="69" t="n"/>
     </row>
-    <row r="865">
+    <row r="865" s="477">
       <c r="A865" s="69" t="n"/>
       <c r="B865" s="72" t="n"/>
       <c r="C865" s="73" t="n"/>
@@ -34213,7 +34228,7 @@
       <c r="F865" s="69" t="n"/>
       <c r="G865" s="69" t="n"/>
     </row>
-    <row r="866">
+    <row r="866" s="477">
       <c r="A866" s="69" t="n"/>
       <c r="B866" s="72" t="n"/>
       <c r="C866" s="73" t="n"/>
@@ -34222,7 +34237,7 @@
       <c r="F866" s="69" t="n"/>
       <c r="G866" s="69" t="n"/>
     </row>
-    <row r="867">
+    <row r="867" s="477">
       <c r="A867" s="69" t="n"/>
       <c r="B867" s="72" t="n"/>
       <c r="C867" s="73" t="n"/>
@@ -34231,7 +34246,7 @@
       <c r="F867" s="69" t="n"/>
       <c r="G867" s="69" t="n"/>
     </row>
-    <row r="868">
+    <row r="868" s="477">
       <c r="A868" s="69" t="n"/>
       <c r="B868" s="72" t="n"/>
       <c r="C868" s="73" t="n"/>
@@ -34240,7 +34255,7 @@
       <c r="F868" s="69" t="n"/>
       <c r="G868" s="69" t="n"/>
     </row>
-    <row r="869">
+    <row r="869" s="477">
       <c r="A869" s="69" t="n"/>
       <c r="B869" s="72" t="n"/>
       <c r="C869" s="73" t="n"/>
@@ -34249,7 +34264,7 @@
       <c r="F869" s="69" t="n"/>
       <c r="G869" s="69" t="n"/>
     </row>
-    <row r="870">
+    <row r="870" s="477">
       <c r="A870" s="69" t="n"/>
       <c r="B870" s="72" t="n"/>
       <c r="C870" s="73" t="n"/>
@@ -34258,7 +34273,7 @@
       <c r="F870" s="69" t="n"/>
       <c r="G870" s="69" t="n"/>
     </row>
-    <row r="871">
+    <row r="871" s="477">
       <c r="A871" s="69" t="n"/>
       <c r="B871" s="72" t="n"/>
       <c r="C871" s="73" t="n"/>
@@ -34267,7 +34282,7 @@
       <c r="F871" s="69" t="n"/>
       <c r="G871" s="69" t="n"/>
     </row>
-    <row r="872">
+    <row r="872" s="477">
       <c r="A872" s="69" t="n"/>
       <c r="B872" s="72" t="n"/>
       <c r="C872" s="73" t="n"/>
@@ -34276,7 +34291,7 @@
       <c r="F872" s="69" t="n"/>
       <c r="G872" s="69" t="n"/>
     </row>
-    <row r="873">
+    <row r="873" s="477">
       <c r="A873" s="69" t="n"/>
       <c r="B873" s="72" t="n"/>
       <c r="C873" s="73" t="n"/>
@@ -34285,7 +34300,7 @@
       <c r="F873" s="69" t="n"/>
       <c r="G873" s="69" t="n"/>
     </row>
-    <row r="874">
+    <row r="874" s="477">
       <c r="A874" s="69" t="n"/>
       <c r="B874" s="72" t="n"/>
       <c r="C874" s="73" t="n"/>
@@ -34294,7 +34309,7 @@
       <c r="F874" s="69" t="n"/>
       <c r="G874" s="69" t="n"/>
     </row>
-    <row r="875">
+    <row r="875" s="477">
       <c r="A875" s="69" t="n"/>
       <c r="B875" s="72" t="n"/>
       <c r="C875" s="73" t="n"/>
@@ -34303,7 +34318,7 @@
       <c r="F875" s="69" t="n"/>
       <c r="G875" s="69" t="n"/>
     </row>
-    <row r="876">
+    <row r="876" s="477">
       <c r="A876" s="69" t="n"/>
       <c r="B876" s="72" t="n"/>
       <c r="C876" s="73" t="n"/>
@@ -34312,7 +34327,7 @@
       <c r="F876" s="69" t="n"/>
       <c r="G876" s="69" t="n"/>
     </row>
-    <row r="877">
+    <row r="877" s="477">
       <c r="A877" s="69" t="n"/>
       <c r="B877" s="72" t="n"/>
       <c r="C877" s="73" t="n"/>
@@ -34321,7 +34336,7 @@
       <c r="F877" s="69" t="n"/>
       <c r="G877" s="69" t="n"/>
     </row>
-    <row r="878">
+    <row r="878" s="477">
       <c r="A878" s="69" t="n"/>
       <c r="B878" s="72" t="n"/>
       <c r="C878" s="73" t="n"/>
@@ -34330,7 +34345,7 @@
       <c r="F878" s="69" t="n"/>
       <c r="G878" s="69" t="n"/>
     </row>
-    <row r="879">
+    <row r="879" s="477">
       <c r="A879" s="69" t="n"/>
       <c r="B879" s="72" t="n"/>
       <c r="C879" s="73" t="n"/>
@@ -34339,7 +34354,7 @@
       <c r="F879" s="69" t="n"/>
       <c r="G879" s="69" t="n"/>
     </row>
-    <row r="880">
+    <row r="880" s="477">
       <c r="A880" s="69" t="n"/>
       <c r="B880" s="72" t="n"/>
       <c r="C880" s="73" t="n"/>
@@ -34348,7 +34363,7 @@
       <c r="F880" s="69" t="n"/>
       <c r="G880" s="69" t="n"/>
     </row>
-    <row r="881">
+    <row r="881" s="477">
       <c r="A881" s="69" t="n"/>
       <c r="B881" s="72" t="n"/>
       <c r="C881" s="73" t="n"/>
@@ -34357,7 +34372,7 @@
       <c r="F881" s="69" t="n"/>
       <c r="G881" s="69" t="n"/>
     </row>
-    <row r="882">
+    <row r="882" s="477">
       <c r="A882" s="69" t="n"/>
       <c r="B882" s="72" t="n"/>
       <c r="C882" s="73" t="n"/>
@@ -34366,7 +34381,7 @@
       <c r="F882" s="69" t="n"/>
       <c r="G882" s="69" t="n"/>
     </row>
-    <row r="883">
+    <row r="883" s="477">
       <c r="A883" s="69" t="n"/>
       <c r="B883" s="72" t="n"/>
       <c r="C883" s="73" t="n"/>
@@ -34375,7 +34390,7 @@
       <c r="F883" s="69" t="n"/>
       <c r="G883" s="69" t="n"/>
     </row>
-    <row r="884">
+    <row r="884" s="477">
       <c r="A884" s="69" t="n"/>
       <c r="B884" s="72" t="n"/>
       <c r="C884" s="73" t="n"/>
@@ -34384,7 +34399,7 @@
       <c r="F884" s="69" t="n"/>
       <c r="G884" s="69" t="n"/>
     </row>
-    <row r="885">
+    <row r="885" s="477">
       <c r="A885" s="69" t="n"/>
       <c r="B885" s="72" t="n"/>
       <c r="C885" s="73" t="n"/>
@@ -34393,7 +34408,7 @@
       <c r="F885" s="69" t="n"/>
       <c r="G885" s="69" t="n"/>
     </row>
-    <row r="886">
+    <row r="886" s="477">
       <c r="A886" s="69" t="n"/>
       <c r="B886" s="72" t="n"/>
       <c r="C886" s="73" t="n"/>
@@ -34402,7 +34417,7 @@
       <c r="F886" s="69" t="n"/>
       <c r="G886" s="69" t="n"/>
     </row>
-    <row r="887">
+    <row r="887" s="477">
       <c r="A887" s="69" t="n"/>
       <c r="B887" s="72" t="n"/>
       <c r="C887" s="73" t="n"/>
@@ -34411,7 +34426,7 @@
       <c r="F887" s="69" t="n"/>
       <c r="G887" s="69" t="n"/>
     </row>
-    <row r="888">
+    <row r="888" s="477">
       <c r="A888" s="69" t="n"/>
       <c r="B888" s="72" t="n"/>
       <c r="C888" s="73" t="n"/>
@@ -34420,7 +34435,7 @@
       <c r="F888" s="69" t="n"/>
       <c r="G888" s="69" t="n"/>
     </row>
-    <row r="889">
+    <row r="889" s="477">
       <c r="A889" s="69" t="n"/>
       <c r="B889" s="72" t="n"/>
       <c r="C889" s="73" t="n"/>
@@ -34429,7 +34444,7 @@
       <c r="F889" s="69" t="n"/>
       <c r="G889" s="69" t="n"/>
     </row>
-    <row r="890">
+    <row r="890" s="477">
       <c r="A890" s="69" t="n"/>
       <c r="B890" s="72" t="n"/>
       <c r="C890" s="73" t="n"/>
@@ -34438,7 +34453,7 @@
       <c r="F890" s="69" t="n"/>
       <c r="G890" s="69" t="n"/>
     </row>
-    <row r="891">
+    <row r="891" s="477">
       <c r="A891" s="69" t="n"/>
       <c r="B891" s="72" t="n"/>
       <c r="C891" s="73" t="n"/>
@@ -34447,7 +34462,7 @@
       <c r="F891" s="69" t="n"/>
       <c r="G891" s="69" t="n"/>
     </row>
-    <row r="892">
+    <row r="892" s="477">
       <c r="A892" s="69" t="n"/>
       <c r="B892" s="72" t="n"/>
       <c r="C892" s="73" t="n"/>
@@ -34456,7 +34471,7 @@
       <c r="F892" s="69" t="n"/>
       <c r="G892" s="69" t="n"/>
     </row>
-    <row r="893">
+    <row r="893" s="477">
       <c r="A893" s="69" t="n"/>
       <c r="B893" s="72" t="n"/>
       <c r="C893" s="73" t="n"/>
@@ -34465,7 +34480,7 @@
       <c r="F893" s="69" t="n"/>
       <c r="G893" s="69" t="n"/>
     </row>
-    <row r="894">
+    <row r="894" s="477">
       <c r="A894" s="69" t="n"/>
       <c r="B894" s="72" t="n"/>
       <c r="C894" s="73" t="n"/>
@@ -34474,7 +34489,7 @@
       <c r="F894" s="69" t="n"/>
       <c r="G894" s="69" t="n"/>
     </row>
-    <row r="895">
+    <row r="895" s="477">
       <c r="A895" s="69" t="n"/>
       <c r="B895" s="72" t="n"/>
       <c r="C895" s="73" t="n"/>
@@ -34483,7 +34498,7 @@
       <c r="F895" s="69" t="n"/>
       <c r="G895" s="69" t="n"/>
     </row>
-    <row r="896">
+    <row r="896" s="477">
       <c r="A896" s="69" t="n"/>
       <c r="B896" s="72" t="n"/>
       <c r="C896" s="73" t="n"/>
@@ -34492,7 +34507,7 @@
       <c r="F896" s="69" t="n"/>
       <c r="G896" s="69" t="n"/>
     </row>
-    <row r="897">
+    <row r="897" s="477">
       <c r="A897" s="69" t="n"/>
       <c r="B897" s="72" t="n"/>
       <c r="C897" s="73" t="n"/>
@@ -34501,7 +34516,7 @@
       <c r="F897" s="69" t="n"/>
       <c r="G897" s="69" t="n"/>
     </row>
-    <row r="898">
+    <row r="898" s="477">
       <c r="A898" s="69" t="n"/>
       <c r="B898" s="72" t="n"/>
       <c r="C898" s="73" t="n"/>
@@ -34510,7 +34525,7 @@
       <c r="F898" s="69" t="n"/>
       <c r="G898" s="69" t="n"/>
     </row>
-    <row r="899">
+    <row r="899" s="477">
       <c r="A899" s="69" t="n"/>
       <c r="B899" s="72" t="n"/>
       <c r="C899" s="73" t="n"/>
@@ -34519,7 +34534,7 @@
       <c r="F899" s="69" t="n"/>
       <c r="G899" s="69" t="n"/>
     </row>
-    <row r="900">
+    <row r="900" s="477">
       <c r="A900" s="69" t="n"/>
       <c r="B900" s="72" t="n"/>
       <c r="C900" s="73" t="n"/>
@@ -34528,7 +34543,7 @@
       <c r="F900" s="69" t="n"/>
       <c r="G900" s="69" t="n"/>
     </row>
-    <row r="901">
+    <row r="901" s="477">
       <c r="A901" s="69" t="n"/>
       <c r="B901" s="72" t="n"/>
       <c r="C901" s="73" t="n"/>
@@ -34537,7 +34552,7 @@
       <c r="F901" s="69" t="n"/>
       <c r="G901" s="69" t="n"/>
     </row>
-    <row r="902">
+    <row r="902" s="477">
       <c r="A902" s="69" t="n"/>
       <c r="B902" s="72" t="n"/>
       <c r="C902" s="73" t="n"/>
@@ -34546,7 +34561,7 @@
       <c r="F902" s="69" t="n"/>
       <c r="G902" s="69" t="n"/>
     </row>
-    <row r="903">
+    <row r="903" s="477">
       <c r="A903" s="69" t="n"/>
       <c r="B903" s="72" t="n"/>
       <c r="C903" s="73" t="n"/>
@@ -34555,7 +34570,7 @@
       <c r="F903" s="69" t="n"/>
       <c r="G903" s="69" t="n"/>
     </row>
-    <row r="904">
+    <row r="904" s="477">
       <c r="A904" s="69" t="n"/>
       <c r="B904" s="72" t="n"/>
       <c r="C904" s="73" t="n"/>
@@ -34564,7 +34579,7 @@
       <c r="F904" s="69" t="n"/>
       <c r="G904" s="69" t="n"/>
     </row>
-    <row r="905">
+    <row r="905" s="477">
       <c r="A905" s="69" t="n"/>
       <c r="B905" s="72" t="n"/>
       <c r="C905" s="73" t="n"/>
@@ -34573,7 +34588,7 @@
       <c r="F905" s="69" t="n"/>
       <c r="G905" s="69" t="n"/>
     </row>
-    <row r="906">
+    <row r="906" s="477">
       <c r="A906" s="69" t="n"/>
       <c r="B906" s="72" t="n"/>
       <c r="C906" s="73" t="n"/>
@@ -34582,7 +34597,7 @@
       <c r="F906" s="69" t="n"/>
       <c r="G906" s="69" t="n"/>
     </row>
-    <row r="907">
+    <row r="907" s="477">
       <c r="A907" s="69" t="n"/>
       <c r="B907" s="72" t="n"/>
       <c r="C907" s="73" t="n"/>
@@ -34591,7 +34606,7 @@
       <c r="F907" s="69" t="n"/>
       <c r="G907" s="69" t="n"/>
     </row>
-    <row r="908">
+    <row r="908" s="477">
       <c r="A908" s="69" t="n"/>
       <c r="B908" s="72" t="n"/>
       <c r="C908" s="73" t="n"/>
@@ -34600,7 +34615,7 @@
       <c r="F908" s="69" t="n"/>
       <c r="G908" s="69" t="n"/>
     </row>
-    <row r="909">
+    <row r="909" s="477">
       <c r="A909" s="69" t="n"/>
       <c r="B909" s="72" t="n"/>
       <c r="C909" s="73" t="n"/>
@@ -34609,7 +34624,7 @@
       <c r="F909" s="69" t="n"/>
       <c r="G909" s="69" t="n"/>
     </row>
-    <row r="910">
+    <row r="910" s="477">
       <c r="A910" s="69" t="n"/>
       <c r="B910" s="72" t="n"/>
       <c r="C910" s="73" t="n"/>
@@ -34618,7 +34633,7 @@
       <c r="F910" s="69" t="n"/>
       <c r="G910" s="69" t="n"/>
     </row>
-    <row r="911">
+    <row r="911" s="477">
       <c r="A911" s="69" t="n"/>
       <c r="B911" s="72" t="n"/>
       <c r="C911" s="73" t="n"/>
@@ -34627,7 +34642,7 @@
       <c r="F911" s="69" t="n"/>
       <c r="G911" s="69" t="n"/>
     </row>
-    <row r="912">
+    <row r="912" s="477">
       <c r="A912" s="69" t="n"/>
       <c r="B912" s="72" t="n"/>
       <c r="C912" s="73" t="n"/>
@@ -34636,7 +34651,7 @@
       <c r="F912" s="69" t="n"/>
       <c r="G912" s="69" t="n"/>
     </row>
-    <row r="913">
+    <row r="913" s="477">
       <c r="A913" s="69" t="n"/>
       <c r="B913" s="72" t="n"/>
       <c r="C913" s="73" t="n"/>
@@ -34645,7 +34660,7 @@
       <c r="F913" s="69" t="n"/>
       <c r="G913" s="69" t="n"/>
     </row>
-    <row r="914">
+    <row r="914" s="477">
       <c r="A914" s="69" t="n"/>
       <c r="B914" s="72" t="n"/>
       <c r="C914" s="73" t="n"/>
@@ -34654,7 +34669,7 @@
       <c r="F914" s="69" t="n"/>
       <c r="G914" s="69" t="n"/>
     </row>
-    <row r="915">
+    <row r="915" s="477">
       <c r="A915" s="69" t="n"/>
       <c r="B915" s="72" t="n"/>
       <c r="C915" s="73" t="n"/>
@@ -34663,7 +34678,7 @@
       <c r="F915" s="69" t="n"/>
       <c r="G915" s="69" t="n"/>
     </row>
-    <row r="916">
+    <row r="916" s="477">
       <c r="A916" s="69" t="n"/>
       <c r="B916" s="72" t="n"/>
       <c r="C916" s="73" t="n"/>
@@ -34672,7 +34687,7 @@
       <c r="F916" s="69" t="n"/>
       <c r="G916" s="69" t="n"/>
     </row>
-    <row r="917">
+    <row r="917" s="477">
       <c r="A917" s="69" t="n"/>
       <c r="B917" s="72" t="n"/>
       <c r="C917" s="73" t="n"/>
@@ -34681,7 +34696,7 @@
       <c r="F917" s="69" t="n"/>
       <c r="G917" s="69" t="n"/>
     </row>
-    <row r="918">
+    <row r="918" s="477">
       <c r="A918" s="69" t="n"/>
       <c r="B918" s="72" t="n"/>
       <c r="C918" s="73" t="n"/>
@@ -34690,7 +34705,7 @@
       <c r="F918" s="69" t="n"/>
       <c r="G918" s="69" t="n"/>
     </row>
-    <row r="919">
+    <row r="919" s="477">
       <c r="A919" s="69" t="n"/>
       <c r="B919" s="72" t="n"/>
       <c r="C919" s="73" t="n"/>
@@ -34699,7 +34714,7 @@
       <c r="F919" s="69" t="n"/>
       <c r="G919" s="69" t="n"/>
     </row>
-    <row r="920">
+    <row r="920" s="477">
       <c r="A920" s="69" t="n"/>
       <c r="B920" s="72" t="n"/>
       <c r="C920" s="73" t="n"/>
@@ -34708,7 +34723,7 @@
       <c r="F920" s="69" t="n"/>
       <c r="G920" s="69" t="n"/>
     </row>
-    <row r="921">
+    <row r="921" s="477">
       <c r="A921" s="69" t="n"/>
       <c r="B921" s="72" t="n"/>
       <c r="C921" s="73" t="n"/>
@@ -34717,7 +34732,7 @@
       <c r="F921" s="69" t="n"/>
       <c r="G921" s="69" t="n"/>
     </row>
-    <row r="922">
+    <row r="922" s="477">
       <c r="A922" s="69" t="n"/>
       <c r="B922" s="72" t="n"/>
       <c r="C922" s="73" t="n"/>
@@ -34726,7 +34741,7 @@
       <c r="F922" s="69" t="n"/>
       <c r="G922" s="69" t="n"/>
     </row>
-    <row r="923">
+    <row r="923" s="477">
       <c r="A923" s="69" t="n"/>
       <c r="B923" s="72" t="n"/>
       <c r="C923" s="73" t="n"/>
@@ -34735,7 +34750,7 @@
       <c r="F923" s="69" t="n"/>
       <c r="G923" s="69" t="n"/>
     </row>
-    <row r="924">
+    <row r="924" s="477">
       <c r="A924" s="69" t="n"/>
       <c r="B924" s="72" t="n"/>
       <c r="C924" s="73" t="n"/>
@@ -34744,7 +34759,7 @@
       <c r="F924" s="69" t="n"/>
       <c r="G924" s="69" t="n"/>
     </row>
-    <row r="925">
+    <row r="925" s="477">
       <c r="A925" s="69" t="n"/>
       <c r="B925" s="72" t="n"/>
       <c r="C925" s="73" t="n"/>
@@ -34753,7 +34768,7 @@
       <c r="F925" s="69" t="n"/>
       <c r="G925" s="69" t="n"/>
     </row>
-    <row r="926">
+    <row r="926" s="477">
       <c r="A926" s="69" t="n"/>
       <c r="B926" s="72" t="n"/>
       <c r="C926" s="73" t="n"/>
@@ -34762,7 +34777,7 @@
       <c r="F926" s="69" t="n"/>
       <c r="G926" s="69" t="n"/>
     </row>
-    <row r="927">
+    <row r="927" s="477">
       <c r="A927" s="69" t="n"/>
       <c r="B927" s="72" t="n"/>
       <c r="C927" s="73" t="n"/>
@@ -34771,7 +34786,7 @@
       <c r="F927" s="69" t="n"/>
       <c r="G927" s="69" t="n"/>
     </row>
-    <row r="928">
+    <row r="928" s="477">
       <c r="A928" s="69" t="n"/>
       <c r="B928" s="72" t="n"/>
       <c r="C928" s="73" t="n"/>
@@ -34780,7 +34795,7 @@
       <c r="F928" s="69" t="n"/>
       <c r="G928" s="69" t="n"/>
     </row>
-    <row r="929">
+    <row r="929" s="477">
       <c r="A929" s="69" t="n"/>
       <c r="B929" s="72" t="n"/>
       <c r="C929" s="73" t="n"/>
@@ -34789,7 +34804,7 @@
       <c r="F929" s="69" t="n"/>
       <c r="G929" s="69" t="n"/>
     </row>
-    <row r="930">
+    <row r="930" s="477">
       <c r="A930" s="69" t="n"/>
       <c r="B930" s="72" t="n"/>
       <c r="C930" s="73" t="n"/>
@@ -34798,7 +34813,7 @@
       <c r="F930" s="69" t="n"/>
       <c r="G930" s="69" t="n"/>
     </row>
-    <row r="931">
+    <row r="931" s="477">
       <c r="A931" s="69" t="n"/>
       <c r="B931" s="72" t="n"/>
       <c r="C931" s="73" t="n"/>
@@ -34807,7 +34822,7 @@
       <c r="F931" s="69" t="n"/>
       <c r="G931" s="69" t="n"/>
     </row>
-    <row r="932">
+    <row r="932" s="477">
       <c r="A932" s="69" t="n"/>
       <c r="B932" s="72" t="n"/>
       <c r="C932" s="73" t="n"/>
@@ -34816,7 +34831,7 @@
       <c r="F932" s="69" t="n"/>
       <c r="G932" s="69" t="n"/>
     </row>
-    <row r="933">
+    <row r="933" s="477">
       <c r="A933" s="69" t="n"/>
       <c r="B933" s="72" t="n"/>
       <c r="C933" s="73" t="n"/>
@@ -34825,7 +34840,7 @@
       <c r="F933" s="69" t="n"/>
       <c r="G933" s="69" t="n"/>
     </row>
-    <row r="934">
+    <row r="934" s="477">
       <c r="A934" s="69" t="n"/>
       <c r="B934" s="72" t="n"/>
       <c r="C934" s="73" t="n"/>
@@ -34834,7 +34849,7 @@
       <c r="F934" s="69" t="n"/>
       <c r="G934" s="69" t="n"/>
     </row>
-    <row r="935">
+    <row r="935" s="477">
       <c r="A935" s="69" t="n"/>
       <c r="B935" s="72" t="n"/>
       <c r="C935" s="73" t="n"/>
@@ -34843,7 +34858,7 @@
       <c r="F935" s="69" t="n"/>
       <c r="G935" s="69" t="n"/>
     </row>
-    <row r="936">
+    <row r="936" s="477">
       <c r="A936" s="69" t="n"/>
       <c r="B936" s="72" t="n"/>
       <c r="C936" s="73" t="n"/>
@@ -34852,7 +34867,7 @@
       <c r="F936" s="69" t="n"/>
       <c r="G936" s="69" t="n"/>
     </row>
-    <row r="937">
+    <row r="937" s="477">
       <c r="A937" s="69" t="n"/>
       <c r="B937" s="72" t="n"/>
       <c r="C937" s="73" t="n"/>
@@ -34861,7 +34876,7 @@
       <c r="F937" s="69" t="n"/>
       <c r="G937" s="69" t="n"/>
     </row>
-    <row r="938">
+    <row r="938" s="477">
       <c r="A938" s="69" t="n"/>
       <c r="B938" s="72" t="n"/>
       <c r="C938" s="73" t="n"/>
@@ -34870,7 +34885,7 @@
       <c r="F938" s="69" t="n"/>
       <c r="G938" s="69" t="n"/>
     </row>
-    <row r="939">
+    <row r="939" s="477">
       <c r="A939" s="69" t="n"/>
       <c r="B939" s="72" t="n"/>
       <c r="C939" s="73" t="n"/>
@@ -34879,7 +34894,7 @@
       <c r="F939" s="69" t="n"/>
       <c r="G939" s="69" t="n"/>
     </row>
-    <row r="940">
+    <row r="940" s="477">
       <c r="A940" s="69" t="n"/>
       <c r="B940" s="72" t="n"/>
       <c r="C940" s="73" t="n"/>
@@ -34888,7 +34903,7 @@
       <c r="F940" s="69" t="n"/>
       <c r="G940" s="69" t="n"/>
     </row>
-    <row r="941">
+    <row r="941" s="477">
       <c r="A941" s="69" t="n"/>
       <c r="B941" s="72" t="n"/>
       <c r="C941" s="73" t="n"/>
@@ -34897,7 +34912,7 @@
       <c r="F941" s="69" t="n"/>
       <c r="G941" s="69" t="n"/>
     </row>
-    <row r="942">
+    <row r="942" s="477">
       <c r="A942" s="69" t="n"/>
       <c r="B942" s="72" t="n"/>
       <c r="C942" s="73" t="n"/>
@@ -34906,7 +34921,7 @@
       <c r="F942" s="69" t="n"/>
       <c r="G942" s="69" t="n"/>
     </row>
-    <row r="943">
+    <row r="943" s="477">
       <c r="A943" s="69" t="n"/>
       <c r="B943" s="72" t="n"/>
       <c r="C943" s="73" t="n"/>
@@ -34915,7 +34930,7 @@
       <c r="F943" s="69" t="n"/>
       <c r="G943" s="69" t="n"/>
     </row>
-    <row r="944">
+    <row r="944" s="477">
       <c r="A944" s="69" t="n"/>
       <c r="B944" s="72" t="n"/>
       <c r="C944" s="73" t="n"/>
@@ -34924,7 +34939,7 @@
       <c r="F944" s="69" t="n"/>
       <c r="G944" s="69" t="n"/>
     </row>
-    <row r="945">
+    <row r="945" s="477">
       <c r="A945" s="69" t="n"/>
       <c r="B945" s="72" t="n"/>
       <c r="C945" s="73" t="n"/>
@@ -34933,7 +34948,7 @@
       <c r="F945" s="69" t="n"/>
       <c r="G945" s="69" t="n"/>
     </row>
-    <row r="946">
+    <row r="946" s="477">
       <c r="A946" s="69" t="n"/>
       <c r="B946" s="72" t="n"/>
       <c r="C946" s="73" t="n"/>
@@ -34942,7 +34957,7 @@
       <c r="F946" s="69" t="n"/>
       <c r="G946" s="69" t="n"/>
     </row>
-    <row r="947">
+    <row r="947" s="477">
       <c r="A947" s="69" t="n"/>
       <c r="B947" s="72" t="n"/>
       <c r="C947" s="73" t="n"/>
@@ -34951,7 +34966,7 @@
       <c r="F947" s="69" t="n"/>
       <c r="G947" s="69" t="n"/>
     </row>
-    <row r="948">
+    <row r="948" s="477">
       <c r="A948" s="69" t="n"/>
       <c r="B948" s="72" t="n"/>
       <c r="C948" s="73" t="n"/>
@@ -34960,7 +34975,7 @@
       <c r="F948" s="69" t="n"/>
       <c r="G948" s="69" t="n"/>
     </row>
-    <row r="949">
+    <row r="949" s="477">
       <c r="A949" s="69" t="n"/>
       <c r="B949" s="72" t="n"/>
       <c r="C949" s="73" t="n"/>
@@ -34969,7 +34984,7 @@
       <c r="F949" s="69" t="n"/>
       <c r="G949" s="69" t="n"/>
     </row>
-    <row r="950">
+    <row r="950" s="477">
       <c r="A950" s="69" t="n"/>
       <c r="B950" s="72" t="n"/>
       <c r="C950" s="73" t="n"/>
@@ -34978,7 +34993,7 @@
       <c r="F950" s="69" t="n"/>
       <c r="G950" s="69" t="n"/>
     </row>
-    <row r="951">
+    <row r="951" s="477">
       <c r="A951" s="69" t="n"/>
       <c r="B951" s="72" t="n"/>
       <c r="C951" s="73" t="n"/>
@@ -34987,7 +35002,7 @@
       <c r="F951" s="69" t="n"/>
       <c r="G951" s="69" t="n"/>
     </row>
-    <row r="952">
+    <row r="952" s="477">
       <c r="A952" s="69" t="n"/>
       <c r="B952" s="72" t="n"/>
       <c r="C952" s="73" t="n"/>
@@ -34996,7 +35011,7 @@
       <c r="F952" s="69" t="n"/>
       <c r="G952" s="69" t="n"/>
     </row>
-    <row r="953">
+    <row r="953" s="477">
       <c r="A953" s="69" t="n"/>
       <c r="B953" s="72" t="n"/>
       <c r="C953" s="73" t="n"/>
@@ -35005,7 +35020,7 @@
       <c r="F953" s="69" t="n"/>
       <c r="G953" s="69" t="n"/>
     </row>
-    <row r="954">
+    <row r="954" s="477">
       <c r="A954" s="69" t="n"/>
       <c r="B954" s="72" t="n"/>
       <c r="C954" s="73" t="n"/>
@@ -35014,7 +35029,7 @@
       <c r="F954" s="69" t="n"/>
       <c r="G954" s="69" t="n"/>
     </row>
-    <row r="955">
+    <row r="955" s="477">
       <c r="A955" s="69" t="n"/>
       <c r="B955" s="72" t="n"/>
       <c r="C955" s="73" t="n"/>
@@ -35023,7 +35038,7 @@
       <c r="F955" s="69" t="n"/>
       <c r="G955" s="69" t="n"/>
     </row>
-    <row r="956">
+    <row r="956" s="477">
       <c r="A956" s="69" t="n"/>
       <c r="B956" s="72" t="n"/>
       <c r="C956" s="73" t="n"/>
@@ -35032,7 +35047,7 @@
       <c r="F956" s="69" t="n"/>
       <c r="G956" s="69" t="n"/>
     </row>
-    <row r="957">
+    <row r="957" s="477">
       <c r="A957" s="69" t="n"/>
       <c r="B957" s="72" t="n"/>
       <c r="C957" s="73" t="n"/>
@@ -35041,7 +35056,7 @@
       <c r="F957" s="69" t="n"/>
       <c r="G957" s="69" t="n"/>
     </row>
-    <row r="958">
+    <row r="958" s="477">
       <c r="A958" s="69" t="n"/>
       <c r="B958" s="72" t="n"/>
       <c r="C958" s="73" t="n"/>
@@ -35050,7 +35065,7 @@
       <c r="F958" s="69" t="n"/>
       <c r="G958" s="69" t="n"/>
     </row>
-    <row r="959">
+    <row r="959" s="477">
       <c r="A959" s="69" t="n"/>
       <c r="B959" s="72" t="n"/>
       <c r="C959" s="73" t="n"/>
@@ -35059,7 +35074,7 @@
       <c r="F959" s="69" t="n"/>
       <c r="G959" s="69" t="n"/>
     </row>
-    <row r="960">
+    <row r="960" s="477">
       <c r="A960" s="69" t="n"/>
       <c r="B960" s="72" t="n"/>
       <c r="C960" s="73" t="n"/>
@@ -35068,7 +35083,7 @@
       <c r="F960" s="69" t="n"/>
       <c r="G960" s="69" t="n"/>
     </row>
-    <row r="961">
+    <row r="961" s="477">
       <c r="A961" s="69" t="n"/>
       <c r="B961" s="72" t="n"/>
       <c r="C961" s="73" t="n"/>
@@ -35077,7 +35092,7 @@
       <c r="F961" s="69" t="n"/>
       <c r="G961" s="69" t="n"/>
     </row>
-    <row r="962">
+    <row r="962" s="477">
       <c r="A962" s="69" t="n"/>
       <c r="B962" s="72" t="n"/>
       <c r="C962" s="73" t="n"/>
@@ -35086,7 +35101,7 @@
       <c r="F962" s="69" t="n"/>
       <c r="G962" s="69" t="n"/>
     </row>
-    <row r="963">
+    <row r="963" s="477">
       <c r="A963" s="69" t="n"/>
       <c r="B963" s="72" t="n"/>
       <c r="C963" s="73" t="n"/>
@@ -35095,7 +35110,7 @@
       <c r="F963" s="69" t="n"/>
       <c r="G963" s="69" t="n"/>
     </row>
-    <row r="964">
+    <row r="964" s="477">
       <c r="A964" s="69" t="n"/>
       <c r="B964" s="72" t="n"/>
       <c r="C964" s="73" t="n"/>
@@ -35104,7 +35119,7 @@
       <c r="F964" s="69" t="n"/>
       <c r="G964" s="69" t="n"/>
     </row>
-    <row r="965">
+    <row r="965" s="477">
       <c r="A965" s="69" t="n"/>
       <c r="B965" s="72" t="n"/>
       <c r="C965" s="73" t="n"/>
@@ -35113,7 +35128,7 @@
       <c r="F965" s="69" t="n"/>
       <c r="G965" s="69" t="n"/>
     </row>
-    <row r="966">
+    <row r="966" s="477">
       <c r="A966" s="69" t="n"/>
       <c r="B966" s="72" t="n"/>
       <c r="C966" s="73" t="n"/>
@@ -35122,7 +35137,7 @@
       <c r="F966" s="69" t="n"/>
       <c r="G966" s="69" t="n"/>
     </row>
-    <row r="967">
+    <row r="967" s="477">
       <c r="A967" s="69" t="n"/>
       <c r="B967" s="72" t="n"/>
       <c r="C967" s="73" t="n"/>
@@ -35131,7 +35146,7 @@
       <c r="F967" s="69" t="n"/>
       <c r="G967" s="69" t="n"/>
     </row>
-    <row r="968">
+    <row r="968" s="477">
       <c r="A968" s="69" t="n"/>
       <c r="B968" s="72" t="n"/>
       <c r="C968" s="73" t="n"/>
@@ -35140,7 +35155,7 @@
       <c r="F968" s="69" t="n"/>
       <c r="G968" s="69" t="n"/>
     </row>
-    <row r="969">
+    <row r="969" s="477">
       <c r="A969" s="69" t="n"/>
       <c r="B969" s="72" t="n"/>
       <c r="C969" s="73" t="n"/>
@@ -35149,7 +35164,7 @@
       <c r="F969" s="69" t="n"/>
       <c r="G969" s="69" t="n"/>
     </row>
-    <row r="970">
+    <row r="970" s="477">
       <c r="A970" s="69" t="n"/>
       <c r="B970" s="72" t="n"/>
       <c r="C970" s="73" t="n"/>
@@ -35158,7 +35173,7 @@
       <c r="F970" s="69" t="n"/>
       <c r="G970" s="69" t="n"/>
     </row>
-    <row r="971">
+    <row r="971" s="477">
       <c r="A971" s="69" t="n"/>
       <c r="B971" s="72" t="n"/>
       <c r="C971" s="73" t="n"/>
@@ -35167,7 +35182,7 @@
       <c r="F971" s="69" t="n"/>
       <c r="G971" s="69" t="n"/>
     </row>
-    <row r="972">
+    <row r="972" s="477">
       <c r="A972" s="69" t="n"/>
       <c r="B972" s="72" t="n"/>
       <c r="C972" s="73" t="n"/>
@@ -35176,7 +35191,7 @@
       <c r="F972" s="69" t="n"/>
       <c r="G972" s="69" t="n"/>
     </row>
-    <row r="973">
+    <row r="973" s="477">
       <c r="A973" s="69" t="n"/>
       <c r="B973" s="72" t="n"/>
       <c r="C973" s="73" t="n"/>
@@ -35185,7 +35200,7 @@
       <c r="F973" s="69" t="n"/>
       <c r="G973" s="69" t="n"/>
     </row>
-    <row r="974">
+    <row r="974" s="477">
       <c r="A974" s="69" t="n"/>
       <c r="B974" s="72" t="n"/>
       <c r="C974" s="73" t="n"/>
@@ -35194,7 +35209,7 @@
       <c r="F974" s="69" t="n"/>
       <c r="G974" s="69" t="n"/>
     </row>
-    <row r="975">
+    <row r="975" s="477">
       <c r="A975" s="69" t="n"/>
       <c r="B975" s="72" t="n"/>
       <c r="C975" s="73" t="n"/>
@@ -35203,7 +35218,7 @@
       <c r="F975" s="69" t="n"/>
       <c r="G975" s="69" t="n"/>
     </row>
-    <row r="976">
+    <row r="976" s="477">
       <c r="A976" s="69" t="n"/>
       <c r="B976" s="72" t="n"/>
       <c r="C976" s="73" t="n"/>
@@ -35212,7 +35227,7 @@
       <c r="F976" s="69" t="n"/>
       <c r="G976" s="69" t="n"/>
     </row>
-    <row r="977">
+    <row r="977" s="477">
       <c r="A977" s="69" t="n"/>
       <c r="B977" s="72" t="n"/>
       <c r="C977" s="73" t="n"/>
@@ -35221,7 +35236,7 @@
       <c r="F977" s="69" t="n"/>
       <c r="G977" s="69" t="n"/>
     </row>
-    <row r="978">
+    <row r="978" s="477">
       <c r="A978" s="69" t="n"/>
       <c r="B978" s="72" t="n"/>
       <c r="C978" s="73" t="n"/>
@@ -35230,7 +35245,7 @@
       <c r="F978" s="69" t="n"/>
       <c r="G978" s="69" t="n"/>
     </row>
-    <row r="979">
+    <row r="979" s="477">
       <c r="A979" s="69" t="n"/>
       <c r="B979" s="72" t="n"/>
       <c r="C979" s="73" t="n"/>
@@ -35239,7 +35254,7 @@
       <c r="F979" s="69" t="n"/>
       <c r="G979" s="69" t="n"/>
     </row>
-    <row r="980">
+    <row r="980" s="477">
       <c r="A980" s="69" t="n"/>
       <c r="B980" s="72" t="n"/>
       <c r="C980" s="73" t="n"/>
@@ -35248,7 +35263,7 @@
       <c r="F980" s="69" t="n"/>
       <c r="G980" s="69" t="n"/>
     </row>
-    <row r="981">
+    <row r="981" s="477">
       <c r="A981" s="69" t="n"/>
       <c r="B981" s="72" t="n"/>
       <c r="C981" s="73" t="n"/>
@@ -35257,7 +35272,7 @@
       <c r="F981" s="69" t="n"/>
       <c r="G981" s="69" t="n"/>
     </row>
-    <row r="982">
+    <row r="982" s="477">
       <c r="A982" s="69" t="n"/>
       <c r="B982" s="72" t="n"/>
       <c r="C982" s="73" t="n"/>
@@ -35266,7 +35281,7 @@
       <c r="F982" s="69" t="n"/>
       <c r="G982" s="69" t="n"/>
     </row>
-    <row r="983">
+    <row r="983" s="477">
       <c r="A983" s="69" t="n"/>
       <c r="B983" s="72" t="n"/>
       <c r="C983" s="73" t="n"/>
@@ -35275,7 +35290,7 @@
       <c r="F983" s="69" t="n"/>
       <c r="G983" s="69" t="n"/>
     </row>
-    <row r="984">
+    <row r="984" s="477">
       <c r="A984" s="69" t="n"/>
       <c r="B984" s="72" t="n"/>
       <c r="C984" s="73" t="n"/>
@@ -35284,7 +35299,7 @@
       <c r="F984" s="69" t="n"/>
       <c r="G984" s="69" t="n"/>
     </row>
-    <row r="985">
+    <row r="985" s="477">
       <c r="A985" s="69" t="n"/>
       <c r="B985" s="72" t="n"/>
       <c r="C985" s="73" t="n"/>
@@ -35293,7 +35308,7 @@
       <c r="F985" s="69" t="n"/>
       <c r="G985" s="69" t="n"/>
     </row>
-    <row r="986">
+    <row r="986" s="477">
       <c r="A986" s="69" t="n"/>
       <c r="B986" s="72" t="n"/>
       <c r="C986" s="73" t="n"/>
@@ -35302,7 +35317,7 @@
       <c r="F986" s="69" t="n"/>
       <c r="G986" s="69" t="n"/>
     </row>
-    <row r="987">
+    <row r="987" s="477">
       <c r="A987" s="69" t="n"/>
       <c r="B987" s="72" t="n"/>
       <c r="C987" s="73" t="n"/>
@@ -35311,7 +35326,7 @@
       <c r="F987" s="69" t="n"/>
       <c r="G987" s="69" t="n"/>
     </row>
-    <row r="988">
+    <row r="988" s="477">
       <c r="A988" s="69" t="n"/>
       <c r="B988" s="72" t="n"/>
       <c r="C988" s="73" t="n"/>
@@ -35320,7 +35335,7 @@
       <c r="F988" s="69" t="n"/>
       <c r="G988" s="69" t="n"/>
     </row>
-    <row r="989">
+    <row r="989" s="477">
       <c r="A989" s="69" t="n"/>
       <c r="B989" s="72" t="n"/>
       <c r="C989" s="73" t="n"/>
@@ -35329,7 +35344,7 @@
       <c r="F989" s="69" t="n"/>
       <c r="G989" s="69" t="n"/>
     </row>
-    <row r="990">
+    <row r="990" s="477">
       <c r="A990" s="69" t="n"/>
       <c r="B990" s="72" t="n"/>
       <c r="C990" s="73" t="n"/>
@@ -35338,7 +35353,7 @@
       <c r="F990" s="69" t="n"/>
       <c r="G990" s="69" t="n"/>
     </row>
-    <row r="991">
+    <row r="991" s="477">
       <c r="A991" s="69" t="n"/>
       <c r="B991" s="72" t="n"/>
       <c r="C991" s="73" t="n"/>
@@ -35347,7 +35362,7 @@
       <c r="F991" s="69" t="n"/>
       <c r="G991" s="69" t="n"/>
     </row>
-    <row r="992">
+    <row r="992" s="477">
       <c r="A992" s="69" t="n"/>
       <c r="B992" s="72" t="n"/>
       <c r="C992" s="73" t="n"/>
@@ -35356,7 +35371,7 @@
       <c r="F992" s="69" t="n"/>
       <c r="G992" s="69" t="n"/>
     </row>
-    <row r="993">
+    <row r="993" s="477">
       <c r="A993" s="69" t="n"/>
       <c r="B993" s="72" t="n"/>
       <c r="C993" s="73" t="n"/>
@@ -35365,7 +35380,7 @@
       <c r="F993" s="69" t="n"/>
       <c r="G993" s="69" t="n"/>
     </row>
-    <row r="994">
+    <row r="994" s="477">
       <c r="A994" s="69" t="n"/>
       <c r="B994" s="72" t="n"/>
       <c r="C994" s="73" t="n"/>
@@ -35374,7 +35389,7 @@
       <c r="F994" s="69" t="n"/>
       <c r="G994" s="69" t="n"/>
     </row>
-    <row r="995">
+    <row r="995" s="477">
       <c r="A995" s="69" t="n"/>
       <c r="B995" s="72" t="n"/>
       <c r="C995" s="73" t="n"/>
@@ -35383,7 +35398,7 @@
       <c r="F995" s="69" t="n"/>
       <c r="G995" s="69" t="n"/>
     </row>
-    <row r="996">
+    <row r="996" s="477">
       <c r="A996" s="69" t="n"/>
       <c r="B996" s="72" t="n"/>
       <c r="C996" s="73" t="n"/>
@@ -35392,7 +35407,7 @@
       <c r="F996" s="69" t="n"/>
       <c r="G996" s="69" t="n"/>
     </row>
-    <row r="997">
+    <row r="997" s="477">
       <c r="A997" s="69" t="n"/>
       <c r="B997" s="72" t="n"/>
       <c r="C997" s="73" t="n"/>
@@ -35401,7 +35416,7 @@
       <c r="F997" s="69" t="n"/>
       <c r="G997" s="69" t="n"/>
     </row>
-    <row r="998">
+    <row r="998" s="477">
       <c r="A998" s="69" t="n"/>
       <c r="B998" s="72" t="n"/>
       <c r="C998" s="73" t="n"/>
@@ -35410,7 +35425,7 @@
       <c r="F998" s="69" t="n"/>
       <c r="G998" s="69" t="n"/>
     </row>
-    <row r="999">
+    <row r="999" s="477">
       <c r="A999" s="69" t="n"/>
       <c r="B999" s="72" t="n"/>
       <c r="C999" s="73" t="n"/>
@@ -35419,7 +35434,7 @@
       <c r="F999" s="69" t="n"/>
       <c r="G999" s="69" t="n"/>
     </row>
-    <row r="1000">
+    <row r="1000" s="477">
       <c r="A1000" s="69" t="n"/>
       <c r="B1000" s="72" t="n"/>
       <c r="C1000" s="73" t="n"/>
@@ -35428,7 +35443,7 @@
       <c r="F1000" s="69" t="n"/>
       <c r="G1000" s="69" t="n"/>
     </row>
-    <row r="1001">
+    <row r="1001" s="477">
       <c r="A1001" s="69" t="n"/>
       <c r="B1001" s="72" t="n"/>
       <c r="C1001" s="73" t="n"/>
@@ -35437,7 +35452,7 @@
       <c r="F1001" s="69" t="n"/>
       <c r="G1001" s="69" t="n"/>
     </row>
-    <row r="1002">
+    <row r="1002" s="477">
       <c r="A1002" s="69" t="n"/>
       <c r="B1002" s="72" t="n"/>
       <c r="C1002" s="73" t="n"/>
@@ -35446,7 +35461,7 @@
       <c r="F1002" s="69" t="n"/>
       <c r="G1002" s="69" t="n"/>
     </row>
-    <row r="1003">
+    <row r="1003" s="477">
       <c r="A1003" s="69" t="n"/>
       <c r="B1003" s="72" t="n"/>
       <c r="C1003" s="73" t="n"/>
@@ -35455,7 +35470,7 @@
       <c r="F1003" s="69" t="n"/>
       <c r="G1003" s="69" t="n"/>
     </row>
-    <row r="1004">
+    <row r="1004" s="477">
       <c r="A1004" s="69" t="n"/>
       <c r="B1004" s="72" t="n"/>
       <c r="C1004" s="73" t="n"/>
@@ -35464,7 +35479,7 @@
       <c r="F1004" s="69" t="n"/>
       <c r="G1004" s="69" t="n"/>
     </row>
-    <row r="1005">
+    <row r="1005" s="477">
       <c r="A1005" s="69" t="n"/>
       <c r="B1005" s="72" t="n"/>
       <c r="C1005" s="73" t="n"/>
@@ -35473,7 +35488,7 @@
       <c r="F1005" s="69" t="n"/>
       <c r="G1005" s="69" t="n"/>
     </row>
-    <row r="1006">
+    <row r="1006" s="477">
       <c r="A1006" s="69" t="n"/>
       <c r="B1006" s="72" t="n"/>
       <c r="C1006" s="73" t="n"/>
@@ -35482,7 +35497,7 @@
       <c r="F1006" s="69" t="n"/>
       <c r="G1006" s="69" t="n"/>
     </row>
-    <row r="1007">
+    <row r="1007" s="477">
       <c r="A1007" s="69" t="n"/>
       <c r="B1007" s="72" t="n"/>
       <c r="C1007" s="73" t="n"/>
@@ -35491,7 +35506,7 @@
       <c r="F1007" s="69" t="n"/>
       <c r="G1007" s="69" t="n"/>
     </row>
-    <row r="1008">
+    <row r="1008" s="477">
       <c r="A1008" s="69" t="n"/>
       <c r="B1008" s="72" t="n"/>
       <c r="C1008" s="73" t="n"/>
@@ -35500,7 +35515,7 @@
       <c r="F1008" s="69" t="n"/>
       <c r="G1008" s="69" t="n"/>
     </row>
-    <row r="1009">
+    <row r="1009" s="477">
       <c r="A1009" s="69" t="n"/>
       <c r="B1009" s="72" t="n"/>
       <c r="C1009" s="73" t="n"/>
@@ -35509,7 +35524,7 @@
       <c r="F1009" s="69" t="n"/>
       <c r="G1009" s="69" t="n"/>
     </row>
-    <row r="1010">
+    <row r="1010" s="477">
       <c r="A1010" s="69" t="n"/>
       <c r="B1010" s="72" t="n"/>
       <c r="C1010" s="73" t="n"/>
@@ -35518,7 +35533,7 @@
       <c r="F1010" s="69" t="n"/>
       <c r="G1010" s="69" t="n"/>
     </row>
-    <row r="1011">
+    <row r="1011" s="477">
       <c r="A1011" s="69" t="n"/>
       <c r="B1011" s="72" t="n"/>
       <c r="C1011" s="73" t="n"/>
@@ -35527,7 +35542,7 @@
       <c r="F1011" s="69" t="n"/>
       <c r="G1011" s="69" t="n"/>
     </row>
-    <row r="1012">
+    <row r="1012" s="477">
       <c r="A1012" s="69" t="n"/>
       <c r="B1012" s="72" t="n"/>
       <c r="C1012" s="73" t="n"/>
@@ -35536,7 +35551,7 @@
       <c r="F1012" s="69" t="n"/>
       <c r="G1012" s="69" t="n"/>
     </row>
-    <row r="1013">
+    <row r="1013" s="477">
       <c r="A1013" s="69" t="n"/>
       <c r="B1013" s="72" t="n"/>
       <c r="C1013" s="73" t="n"/>
@@ -35545,7 +35560,7 @@
       <c r="F1013" s="69" t="n"/>
       <c r="G1013" s="69" t="n"/>
     </row>
-    <row r="1014">
+    <row r="1014" s="477">
       <c r="A1014" s="69" t="n"/>
       <c r="B1014" s="72" t="n"/>
       <c r="C1014" s="73" t="n"/>
@@ -35554,7 +35569,7 @@
       <c r="F1014" s="69" t="n"/>
       <c r="G1014" s="69" t="n"/>
     </row>
-    <row r="1015">
+    <row r="1015" s="477">
       <c r="A1015" s="69" t="n"/>
       <c r="B1015" s="72" t="n"/>
       <c r="C1015" s="73" t="n"/>
@@ -35563,7 +35578,7 @@
       <c r="F1015" s="69" t="n"/>
       <c r="G1015" s="69" t="n"/>
     </row>
-    <row r="1016">
+    <row r="1016" s="477">
       <c r="A1016" s="69" t="n"/>
       <c r="B1016" s="72" t="n"/>
       <c r="C1016" s="73" t="n"/>
@@ -35572,7 +35587,7 @@
       <c r="F1016" s="69" t="n"/>
       <c r="G1016" s="69" t="n"/>
     </row>
-    <row r="1017">
+    <row r="1017" s="477">
       <c r="A1017" s="69" t="n"/>
       <c r="B1017" s="72" t="n"/>
       <c r="C1017" s="73" t="n"/>
@@ -35581,7 +35596,7 @@
       <c r="F1017" s="69" t="n"/>
       <c r="G1017" s="69" t="n"/>
     </row>
-    <row r="1018">
+    <row r="1018" s="477">
       <c r="A1018" s="69" t="n"/>
       <c r="B1018" s="72" t="n"/>
       <c r="C1018" s="73" t="n"/>
@@ -35590,7 +35605,7 @@
       <c r="F1018" s="69" t="n"/>
       <c r="G1018" s="69" t="n"/>
     </row>
-    <row r="1019">
+    <row r="1019" s="477">
       <c r="A1019" s="69" t="n"/>
       <c r="B1019" s="72" t="n"/>
       <c r="C1019" s="73" t="n"/>
@@ -35599,7 +35614,7 @@
       <c r="F1019" s="69" t="n"/>
       <c r="G1019" s="69" t="n"/>
     </row>
-    <row r="1020">
+    <row r="1020" s="477">
       <c r="A1020" s="69" t="n"/>
       <c r="B1020" s="72" t="n"/>
       <c r="C1020" s="73" t="n"/>
@@ -35608,7 +35623,7 @@
       <c r="F1020" s="69" t="n"/>
       <c r="G1020" s="69" t="n"/>
     </row>
-    <row r="1021">
+    <row r="1021" s="477">
       <c r="A1021" s="69" t="n"/>
       <c r="B1021" s="72" t="n"/>
       <c r="C1021" s="73" t="n"/>
@@ -35617,7 +35632,7 @@
       <c r="F1021" s="69" t="n"/>
       <c r="G1021" s="69" t="n"/>
     </row>
-    <row r="1022">
+    <row r="1022" s="477">
       <c r="A1022" s="69" t="n"/>
       <c r="B1022" s="72" t="n"/>
       <c r="C1022" s="73" t="n"/>
@@ -35626,7 +35641,7 @@
       <c r="F1022" s="69" t="n"/>
       <c r="G1022" s="69" t="n"/>
     </row>
-    <row r="1023">
+    <row r="1023" s="477">
       <c r="A1023" s="69" t="n"/>
       <c r="B1023" s="72" t="n"/>
       <c r="C1023" s="73" t="n"/>
@@ -35635,7 +35650,7 @@
       <c r="F1023" s="69" t="n"/>
       <c r="G1023" s="69" t="n"/>
     </row>
-    <row r="1024">
+    <row r="1024" s="477">
       <c r="A1024" s="69" t="n"/>
       <c r="B1024" s="72" t="n"/>
       <c r="C1024" s="73" t="n"/>
@@ -35644,7 +35659,7 @@
       <c r="F1024" s="69" t="n"/>
       <c r="G1024" s="69" t="n"/>
     </row>
-    <row r="1025">
+    <row r="1025" s="477">
       <c r="A1025" s="69" t="n"/>
       <c r="B1025" s="72" t="n"/>
       <c r="C1025" s="73" t="n"/>
@@ -35653,7 +35668,7 @@
       <c r="F1025" s="69" t="n"/>
       <c r="G1025" s="69" t="n"/>
     </row>
-    <row r="1026">
+    <row r="1026" s="477">
       <c r="A1026" s="69" t="n"/>
       <c r="B1026" s="72" t="n"/>
       <c r="C1026" s="73" t="n"/>
@@ -35662,7 +35677,7 @@
       <c r="F1026" s="69" t="n"/>
       <c r="G1026" s="69" t="n"/>
     </row>
-    <row r="1027">
+    <row r="1027" s="477">
       <c r="A1027" s="69" t="n"/>
       <c r="B1027" s="72" t="n"/>
       <c r="C1027" s="73" t="n"/>
@@ -35671,7 +35686,7 @@
       <c r="F1027" s="69" t="n"/>
       <c r="G1027" s="69" t="n"/>
     </row>
-    <row r="1028">
+    <row r="1028" s="477">
       <c r="A1028" s="69" t="n"/>
       <c r="B1028" s="72" t="n"/>
       <c r="C1028" s="73" t="n"/>
@@ -35680,7 +35695,7 @@
       <c r="F1028" s="69" t="n"/>
       <c r="G1028" s="69" t="n"/>
     </row>
-    <row r="1029">
+    <row r="1029" s="477">
       <c r="A1029" s="69" t="n"/>
       <c r="B1029" s="72" t="n"/>
       <c r="C1029" s="73" t="n"/>
@@ -35689,7 +35704,7 @@
       <c r="F1029" s="69" t="n"/>
       <c r="G1029" s="69" t="n"/>
     </row>
-    <row r="1030">
+    <row r="1030" s="477">
       <c r="A1030" s="69" t="n"/>
       <c r="B1030" s="72" t="n"/>
       <c r="C1030" s="73" t="n"/>
@@ -35698,7 +35713,7 @@
       <c r="F1030" s="69" t="n"/>
       <c r="G1030" s="69" t="n"/>
     </row>
-    <row r="1031">
+    <row r="1031" s="477">
       <c r="A1031" s="69" t="n"/>
       <c r="B1031" s="72" t="n"/>
       <c r="C1031" s="73" t="n"/>
@@ -35707,7 +35722,7 @@
       <c r="F1031" s="69" t="n"/>
       <c r="G1031" s="69" t="n"/>
     </row>
-    <row r="1032">
+    <row r="1032" s="477">
       <c r="A1032" s="69" t="n"/>
       <c r="B1032" s="72" t="n"/>
       <c r="C1032" s="73" t="n"/>
@@ -35716,7 +35731,7 @@
       <c r="F1032" s="69" t="n"/>
       <c r="G1032" s="69" t="n"/>
     </row>
-    <row r="1033">
+    <row r="1033" s="477">
       <c r="A1033" s="69" t="n"/>
       <c r="B1033" s="72" t="n"/>
       <c r="C1033" s="73" t="n"/>
@@ -35725,7 +35740,7 @@
       <c r="F1033" s="69" t="n"/>
       <c r="G1033" s="69" t="n"/>
     </row>
-    <row r="1034">
+    <row r="1034" s="477">
       <c r="A1034" s="69" t="n"/>
       <c r="B1034" s="72" t="n"/>
       <c r="C1034" s="73" t="n"/>
@@ -35734,7 +35749,7 @@
       <c r="F1034" s="69" t="n"/>
       <c r="G1034" s="69" t="n"/>
     </row>
-    <row r="1035">
+    <row r="1035" s="477">
       <c r="A1035" s="69" t="n"/>
       <c r="B1035" s="72" t="n"/>
       <c r="C1035" s="73" t="n"/>
@@ -35743,7 +35758,7 @@
       <c r="F1035" s="69" t="n"/>
       <c r="G1035" s="69" t="n"/>
     </row>
-    <row r="1036">
+    <row r="1036" s="477">
       <c r="A1036" s="69" t="n"/>
       <c r="B1036" s="72" t="n"/>
       <c r="C1036" s="73" t="n"/>
@@ -35752,7 +35767,7 @@
       <c r="F1036" s="69" t="n"/>
       <c r="G1036" s="69" t="n"/>
     </row>
-    <row r="1037">
+    <row r="1037" s="477">
       <c r="A1037" s="69" t="n"/>
       <c r="B1037" s="72" t="n"/>
       <c r="C1037" s="73" t="n"/>
@@ -35761,7 +35776,7 @@
       <c r="F1037" s="69" t="n"/>
       <c r="G1037" s="69" t="n"/>
     </row>
-    <row r="1038">
+    <row r="1038" s="477">
       <c r="A1038" s="69" t="n"/>
       <c r="B1038" s="72" t="n"/>
       <c r="C1038" s="73" t="n"/>
@@ -35770,7 +35785,7 @@
       <c r="F1038" s="69" t="n"/>
       <c r="G1038" s="69" t="n"/>
     </row>
-    <row r="1039">
+    <row r="1039" s="477">
       <c r="A1039" s="69" t="n"/>
       <c r="B1039" s="72" t="n"/>
       <c r="C1039" s="73" t="n"/>
@@ -35779,7 +35794,7 @@
       <c r="F1039" s="69" t="n"/>
       <c r="G1039" s="69" t="n"/>
     </row>
-    <row r="1040">
+    <row r="1040" s="477">
       <c r="A1040" s="69" t="n"/>
       <c r="B1040" s="72" t="n"/>
       <c r="C1040" s="73" t="n"/>
@@ -35788,7 +35803,7 @@
       <c r="F1040" s="69" t="n"/>
       <c r="G1040" s="69" t="n"/>
     </row>
-    <row r="1041">
+    <row r="1041" s="477">
       <c r="A1041" s="69" t="n"/>
       <c r="B1041" s="72" t="n"/>
       <c r="C1041" s="73" t="n"/>
@@ -35797,7 +35812,7 @@
       <c r="F1041" s="69" t="n"/>
       <c r="G1041" s="69" t="n"/>
     </row>
-    <row r="1042">
+    <row r="1042" s="477">
       <c r="A1042" s="69" t="n"/>
       <c r="B1042" s="72" t="n"/>
       <c r="C1042" s="73" t="n"/>
@@ -35806,7 +35821,7 @@
       <c r="F1042" s="69" t="n"/>
       <c r="G1042" s="69" t="n"/>
     </row>
-    <row r="1043">
+    <row r="1043" s="477">
       <c r="A1043" s="69" t="n"/>
       <c r="B1043" s="72" t="n"/>
       <c r="C1043" s="73" t="n"/>
@@ -35815,7 +35830,7 @@
       <c r="F1043" s="69" t="n"/>
       <c r="G1043" s="69" t="n"/>
     </row>
-    <row r="1044">
+    <row r="1044" s="477">
       <c r="A1044" s="69" t="n"/>
       <c r="B1044" s="72" t="n"/>
       <c r="C1044" s="73" t="n"/>
@@ -35824,7 +35839,7 @@
       <c r="F1044" s="69" t="n"/>
       <c r="G1044" s="69" t="n"/>
     </row>
-    <row r="1045">
+    <row r="1045" s="477">
       <c r="A1045" s="69" t="n"/>
       <c r="B1045" s="72" t="n"/>
       <c r="C1045" s="73" t="n"/>
@@ -35833,7 +35848,7 @@
       <c r="F1045" s="69" t="n"/>
       <c r="G1045" s="69" t="n"/>
     </row>
-    <row r="1046">
+    <row r="1046" s="477">
       <c r="A1046" s="69" t="n"/>
       <c r="B1046" s="72" t="n"/>
       <c r="C1046" s="73" t="n"/>
@@ -35842,7 +35857,7 @@
       <c r="F1046" s="69" t="n"/>
       <c r="G1046" s="69" t="n"/>
     </row>
-    <row r="1047">
+    <row r="1047" s="477">
       <c r="A1047" s="69" t="n"/>
       <c r="B1047" s="72" t="n"/>
       <c r="C1047" s="73" t="n"/>
@@ -35851,7 +35866,7 @@
       <c r="F1047" s="69" t="n"/>
       <c r="G1047" s="69" t="n"/>
     </row>
-    <row r="1048">
+    <row r="1048" s="477">
       <c r="A1048" s="69" t="n"/>
       <c r="B1048" s="72" t="n"/>
       <c r="C1048" s="73" t="n"/>
@@ -35860,7 +35875,7 @@
       <c r="F1048" s="69" t="n"/>
       <c r="G1048" s="69" t="n"/>
     </row>
-    <row r="1049">
+    <row r="1049" s="477">
       <c r="A1049" s="69" t="n"/>
       <c r="B1049" s="72" t="n"/>
       <c r="C1049" s="73" t="n"/>
@@ -35869,7 +35884,7 @@
       <c r="F1049" s="69" t="n"/>
       <c r="G1049" s="69" t="n"/>
     </row>
-    <row r="1050">
+    <row r="1050" s="477">
       <c r="A1050" s="69" t="n"/>
       <c r="B1050" s="72" t="n"/>
       <c r="C1050" s="73" t="n"/>
@@ -35878,7 +35893,7 @@
       <c r="F1050" s="69" t="n"/>
       <c r="G1050" s="69" t="n"/>
     </row>
-    <row r="1051">
+    <row r="1051" s="477">
       <c r="A1051" s="69" t="n"/>
       <c r="B1051" s="72" t="n"/>
       <c r="C1051" s="73" t="n"/>
@@ -35887,7 +35902,7 @@
       <c r="F1051" s="69" t="n"/>
       <c r="G1051" s="69" t="n"/>
     </row>
-    <row r="1052">
+    <row r="1052" s="477">
       <c r="A1052" s="69" t="n"/>
       <c r="B1052" s="72" t="n"/>
       <c r="C1052" s="73" t="n"/>
@@ -35896,7 +35911,7 @@
       <c r="F1052" s="69" t="n"/>
       <c r="G1052" s="69" t="n"/>
     </row>
-    <row r="1053">
+    <row r="1053" s="477">
       <c r="A1053" s="69" t="n"/>
       <c r="B1053" s="72" t="n"/>
       <c r="C1053" s="73" t="n"/>
@@ -35905,7 +35920,7 @@
       <c r="F1053" s="69" t="n"/>
       <c r="G1053" s="69" t="n"/>
     </row>
-    <row r="1054">
+    <row r="1054" s="477">
       <c r="A1054" s="69" t="n"/>
       <c r="B1054" s="72" t="n"/>
       <c r="C1054" s="73" t="n"/>
@@ -35914,7 +35929,7 @@
       <c r="F1054" s="69" t="n"/>
       <c r="G1054" s="69" t="n"/>
     </row>
-    <row r="1055">
+    <row r="1055" s="477">
       <c r="A1055" s="69" t="n"/>
       <c r="B1055" s="72" t="n"/>
       <c r="C1055" s="73" t="n"/>
@@ -35923,7 +35938,7 @@
       <c r="F1055" s="69" t="n"/>
       <c r="G1055" s="69" t="n"/>
     </row>
-    <row r="1056">
+    <row r="1056" s="477">
       <c r="A1056" s="69" t="n"/>
       <c r="B1056" s="72" t="n"/>
       <c r="C1056" s="73" t="n"/>
@@ -35932,7 +35947,7 @@
       <c r="F1056" s="69" t="n"/>
       <c r="G1056" s="69" t="n"/>
     </row>
-    <row r="1057">
+    <row r="1057" s="477">
       <c r="A1057" s="69" t="n"/>
       <c r="B1057" s="72" t="n"/>
       <c r="C1057" s="73" t="n"/>
@@ -35941,7 +35956,7 @@
       <c r="F1057" s="69" t="n"/>
       <c r="G1057" s="69" t="n"/>
     </row>
-    <row r="1058">
+    <row r="1058" s="477">
       <c r="A1058" s="69" t="n"/>
       <c r="B1058" s="72" t="n"/>
       <c r="C1058" s="73" t="n"/>
@@ -35950,7 +35965,7 @@
       <c r="F1058" s="69" t="n"/>
       <c r="G1058" s="69" t="n"/>
     </row>
-    <row r="1059">
+    <row r="1059" s="477">
       <c r="A1059" s="69" t="n"/>
       <c r="B1059" s="72" t="n"/>
       <c r="C1059" s="73" t="n"/>
@@ -35959,7 +35974,7 @@
       <c r="F1059" s="69" t="n"/>
       <c r="G1059" s="69" t="n"/>
     </row>
-    <row r="1060">
+    <row r="1060" s="477">
       <c r="A1060" s="69" t="n"/>
       <c r="B1060" s="72" t="n"/>
       <c r="C1060" s="73" t="n"/>
@@ -35968,7 +35983,7 @@
       <c r="F1060" s="69" t="n"/>
       <c r="G1060" s="69" t="n"/>
     </row>
-    <row r="1061">
+    <row r="1061" s="477">
       <c r="A1061" s="69" t="n"/>
       <c r="B1061" s="72" t="n"/>
       <c r="C1061" s="73" t="n"/>
@@ -35977,7 +35992,7 @@
       <c r="F1061" s="69" t="n"/>
       <c r="G1061" s="69" t="n"/>
     </row>
-    <row r="1062">
+    <row r="1062" s="477">
       <c r="A1062" s="69" t="n"/>
       <c r="B1062" s="72" t="n"/>
       <c r="C1062" s="73" t="n"/>
@@ -35986,7 +36001,7 @@
       <c r="F1062" s="69" t="n"/>
       <c r="G1062" s="69" t="n"/>
     </row>
-    <row r="1063">
+    <row r="1063" s="477">
       <c r="A1063" s="69" t="n"/>
       <c r="B1063" s="72" t="n"/>
       <c r="C1063" s="73" t="n"/>
@@ -35995,7 +36010,7 @@
       <c r="F1063" s="69" t="n"/>
       <c r="G1063" s="69" t="n"/>
     </row>
-    <row r="1064">
+    <row r="1064" s="477">
       <c r="A1064" s="69" t="n"/>
       <c r="B1064" s="72" t="n"/>
       <c r="C1064" s="73" t="n"/>
@@ -36004,7 +36019,7 @@
       <c r="F1064" s="69" t="n"/>
       <c r="G1064" s="69" t="n"/>
     </row>
-    <row r="1065">
+    <row r="1065" s="477">
       <c r="A1065" s="69" t="n"/>
       <c r="B1065" s="72" t="n"/>
       <c r="C1065" s="73" t="n"/>
@@ -36013,7 +36028,7 @@
       <c r="F1065" s="69" t="n"/>
       <c r="G1065" s="69" t="n"/>
     </row>
-    <row r="1066">
+    <row r="1066" s="477">
       <c r="A1066" s="69" t="n"/>
       <c r="B1066" s="72" t="n"/>
       <c r="C1066" s="73" t="n"/>
@@ -36022,7 +36037,7 @@
       <c r="F1066" s="69" t="n"/>
       <c r="G1066" s="69" t="n"/>
     </row>
-    <row r="1067">
+    <row r="1067" s="477">
       <c r="A1067" s="69" t="n"/>
       <c r="B1067" s="72" t="n"/>
       <c r="C1067" s="73" t="n"/>
@@ -36031,7 +36046,7 @@
       <c r="F1067" s="69" t="n"/>
       <c r="G1067" s="69" t="n"/>
     </row>
-    <row r="1068">
+    <row r="1068" s="477">
       <c r="A1068" s="69" t="n"/>
       <c r="B1068" s="72" t="n"/>
       <c r="C1068" s="73" t="n"/>
@@ -36040,7 +36055,7 @@
       <c r="F1068" s="69" t="n"/>
       <c r="G1068" s="69" t="n"/>
     </row>
-    <row r="1069">
+    <row r="1069" s="477">
       <c r="A1069" s="69" t="n"/>
       <c r="B1069" s="72" t="n"/>
       <c r="C1069" s="73" t="n"/>
@@ -36049,7 +36064,7 @@
       <c r="F1069" s="69" t="n"/>
       <c r="G1069" s="69" t="n"/>
     </row>
-    <row r="1070">
+    <row r="1070" s="477">
       <c r="A1070" s="69" t="n"/>
       <c r="B1070" s="72" t="n"/>
       <c r="C1070" s="73" t="n"/>
@@ -36058,7 +36073,7 @@
       <c r="F1070" s="69" t="n"/>
       <c r="G1070" s="69" t="n"/>
     </row>
-    <row r="1071">
+    <row r="1071" s="477">
       <c r="A1071" s="69" t="n"/>
       <c r="B1071" s="72" t="n"/>
       <c r="C1071" s="73" t="n"/>
@@ -36067,7 +36082,7 @@
       <c r="F1071" s="69" t="n"/>
       <c r="G1071" s="69" t="n"/>
     </row>
-    <row r="1072">
+    <row r="1072" s="477">
       <c r="A1072" s="69" t="n"/>
       <c r="B1072" s="72" t="n"/>
       <c r="C1072" s="73" t="n"/>
@@ -36076,7 +36091,7 @@
       <c r="F1072" s="69" t="n"/>
       <c r="G1072" s="69" t="n"/>
     </row>
-    <row r="1073">
+    <row r="1073" s="477">
       <c r="A1073" s="69" t="n"/>
       <c r="B1073" s="72" t="n"/>
       <c r="C1073" s="73" t="n"/>
@@ -36085,7 +36100,7 @@
       <c r="F1073" s="69" t="n"/>
       <c r="G1073" s="69" t="n"/>
     </row>
-    <row r="1074">
+    <row r="1074" s="477">
       <c r="A1074" s="69" t="n"/>
       <c r="B1074" s="72" t="n"/>
       <c r="C1074" s="73" t="n"/>
@@ -36094,7 +36109,7 @@
       <c r="F1074" s="69" t="n"/>
       <c r="G1074" s="69" t="n"/>
     </row>
-    <row r="1075">
+    <row r="1075" s="477">
       <c r="A1075" s="69" t="n"/>
       <c r="B1075" s="72" t="n"/>
       <c r="C1075" s="73" t="n"/>
@@ -36103,7 +36118,7 @@
       <c r="F1075" s="69" t="n"/>
       <c r="G1075" s="69" t="n"/>
     </row>
-    <row r="1076">
+    <row r="1076" s="477">
       <c r="A1076" s="69" t="n"/>
       <c r="B1076" s="72" t="n"/>
       <c r="C1076" s="73" t="n"/>
@@ -36112,7 +36127,7 @@
       <c r="F1076" s="69" t="n"/>
       <c r="G1076" s="69" t="n"/>
     </row>
-    <row r="1077">
+    <row r="1077" s="477">
       <c r="A1077" s="69" t="n"/>
       <c r="B1077" s="72" t="n"/>
       <c r="C1077" s="73" t="n"/>
@@ -36121,7 +36136,7 @@
       <c r="F1077" s="69" t="n"/>
       <c r="G1077" s="69" t="n"/>
     </row>
-    <row r="1078">
+    <row r="1078" s="477">
       <c r="A1078" s="69" t="n"/>
       <c r="B1078" s="72" t="n"/>
       <c r="C1078" s="73" t="n"/>
@@ -36130,7 +36145,7 @@
       <c r="F1078" s="69" t="n"/>
       <c r="G1078" s="69" t="n"/>
     </row>
-    <row r="1079">
+    <row r="1079" s="477">
       <c r="A1079" s="69" t="n"/>
       <c r="B1079" s="72" t="n"/>
       <c r="C1079" s="73" t="n"/>
@@ -36139,7 +36154,7 @@
       <c r="F1079" s="69" t="n"/>
       <c r="G1079" s="69" t="n"/>
     </row>
-    <row r="1080">
+    <row r="1080" s="477">
       <c r="A1080" s="69" t="n"/>
       <c r="B1080" s="72" t="n"/>
       <c r="C1080" s="73" t="n"/>
@@ -36148,7 +36163,7 @@
       <c r="F1080" s="69" t="n"/>
       <c r="G1080" s="69" t="n"/>
     </row>
-    <row r="1081">
+    <row r="1081" s="477">
       <c r="A1081" s="69" t="n"/>
       <c r="B1081" s="72" t="n"/>
       <c r="C1081" s="73" t="n"/>
@@ -36157,7 +36172,7 @@
       <c r="F1081" s="69" t="n"/>
       <c r="G1081" s="69" t="n"/>
     </row>
-    <row r="1082">
+    <row r="1082" s="477">
       <c r="A1082" s="69" t="n"/>
       <c r="B1082" s="72" t="n"/>
       <c r="C1082" s="73" t="n"/>
@@ -36166,7 +36181,7 @@
       <c r="F1082" s="69" t="n"/>
       <c r="G1082" s="69" t="n"/>
     </row>
-    <row r="1083">
+    <row r="1083" s="477">
       <c r="A1083" s="69" t="n"/>
       <c r="B1083" s="72" t="n"/>
       <c r="C1083" s="73" t="n"/>
@@ -36175,7 +36190,7 @@
       <c r="F1083" s="69" t="n"/>
       <c r="G1083" s="69" t="n"/>
     </row>
-    <row r="1084">
+    <row r="1084" s="477">
       <c r="A1084" s="69" t="n"/>
       <c r="B1084" s="72" t="n"/>
       <c r="C1084" s="73" t="n"/>
@@ -36184,7 +36199,7 @@
       <c r="F1084" s="69" t="n"/>
       <c r="G1084" s="69" t="n"/>
     </row>
-    <row r="1085">
+    <row r="1085" s="477">
       <c r="A1085" s="69" t="n"/>
       <c r="B1085" s="72" t="n"/>
       <c r="C1085" s="73" t="n"/>
@@ -36193,7 +36208,7 @@
       <c r="F1085" s="69" t="n"/>
       <c r="G1085" s="69" t="n"/>
     </row>
-    <row r="1086">
+    <row r="1086" s="477">
       <c r="A1086" s="69" t="n"/>
       <c r="B1086" s="72" t="n"/>
       <c r="C1086" s="73" t="n"/>
@@ -36202,7 +36217,7 @@
       <c r="F1086" s="69" t="n"/>
       <c r="G1086" s="69" t="n"/>
     </row>
-    <row r="1087">
+    <row r="1087" s="477">
       <c r="A1087" s="69" t="n"/>
       <c r="B1087" s="72" t="n"/>
       <c r="C1087" s="73" t="n"/>
@@ -36211,7 +36226,7 @@
       <c r="F1087" s="69" t="n"/>
       <c r="G1087" s="69" t="n"/>
     </row>
-    <row r="1088">
+    <row r="1088" s="477">
       <c r="A1088" s="69" t="n"/>
       <c r="B1088" s="72" t="n"/>
       <c r="C1088" s="73" t="n"/>
@@ -36220,7 +36235,7 @@
       <c r="F1088" s="69" t="n"/>
       <c r="G1088" s="69" t="n"/>
     </row>
-    <row r="1089">
+    <row r="1089" s="477">
       <c r="A1089" s="69" t="n"/>
       <c r="B1089" s="72" t="n"/>
       <c r="C1089" s="73" t="n"/>
@@ -36229,7 +36244,7 @@
       <c r="F1089" s="69" t="n"/>
       <c r="G1089" s="69" t="n"/>
     </row>
-    <row r="1090">
+    <row r="1090" s="477">
       <c r="A1090" s="69" t="n"/>
       <c r="B1090" s="72" t="n"/>
       <c r="C1090" s="73" t="n"/>
@@ -36238,7 +36253,7 @@
       <c r="F1090" s="69" t="n"/>
       <c r="G1090" s="69" t="n"/>
     </row>
-    <row r="1091">
+    <row r="1091" s="477">
       <c r="A1091" s="69" t="n"/>
       <c r="B1091" s="72" t="n"/>
       <c r="C1091" s="73" t="n"/>
@@ -36247,7 +36262,7 @@
       <c r="F1091" s="69" t="n"/>
       <c r="G1091" s="69" t="n"/>
     </row>
-    <row r="1092">
+    <row r="1092" s="477">
       <c r="A1092" s="69" t="n"/>
       <c r="B1092" s="72" t="n"/>
       <c r="C1092" s="73" t="n"/>
@@ -36256,7 +36271,7 @@
       <c r="F1092" s="69" t="n"/>
       <c r="G1092" s="69" t="n"/>
     </row>
-    <row r="1093">
+    <row r="1093" s="477">
       <c r="A1093" s="69" t="n"/>
       <c r="B1093" s="72" t="n"/>
       <c r="C1093" s="73" t="n"/>
@@ -36265,7 +36280,7 @@
       <c r="F1093" s="69" t="n"/>
       <c r="G1093" s="69" t="n"/>
     </row>
-    <row r="1094">
+    <row r="1094" s="477">
       <c r="A1094" s="69" t="n"/>
       <c r="B1094" s="72" t="n"/>
       <c r="C1094" s="73" t="n"/>
@@ -36274,7 +36289,7 @@
       <c r="F1094" s="69" t="n"/>
       <c r="G1094" s="69" t="n"/>
     </row>
-    <row r="1095">
+    <row r="1095" s="477">
       <c r="A1095" s="69" t="n"/>
       <c r="B1095" s="72" t="n"/>
       <c r="C1095" s="73" t="n"/>
@@ -36283,7 +36298,7 @@
       <c r="F1095" s="69" t="n"/>
       <c r="G1095" s="69" t="n"/>
     </row>
-    <row r="1096">
+    <row r="1096" s="477">
       <c r="A1096" s="69" t="n"/>
       <c r="B1096" s="72" t="n"/>
       <c r="C1096" s="73" t="n"/>
@@ -36292,7 +36307,7 @@
       <c r="F1096" s="69" t="n"/>
       <c r="G1096" s="69" t="n"/>
     </row>
-    <row r="1097">
+    <row r="1097" s="477">
       <c r="A1097" s="69" t="n"/>
       <c r="B1097" s="72" t="n"/>
       <c r="C1097" s="73" t="n"/>
@@ -36301,7 +36316,7 @@
       <c r="F1097" s="69" t="n"/>
       <c r="G1097" s="69" t="n"/>
     </row>
-    <row r="1098">
+    <row r="1098" s="477">
       <c r="A1098" s="69" t="n"/>
       <c r="B1098" s="72" t="n"/>
       <c r="C1098" s="73" t="n"/>
@@ -36310,7 +36325,7 @@
       <c r="F1098" s="69" t="n"/>
       <c r="G1098" s="69" t="n"/>
     </row>
-    <row r="1099">
+    <row r="1099" s="477">
       <c r="A1099" s="69" t="n"/>
       <c r="B1099" s="72" t="n"/>
       <c r="C1099" s="73" t="n"/>
@@ -36319,7 +36334,7 @@
       <c r="F1099" s="69" t="n"/>
       <c r="G1099" s="69" t="n"/>
     </row>
-    <row r="1100">
+    <row r="1100" s="477">
       <c r="A1100" s="69" t="n"/>
       <c r="B1100" s="72" t="n"/>
       <c r="C1100" s="73" t="n"/>
@@ -36328,7 +36343,7 @@
       <c r="F1100" s="69" t="n"/>
       <c r="G1100" s="69" t="n"/>
     </row>
-    <row r="1101">
+    <row r="1101" s="477">
       <c r="A1101" s="69" t="n"/>
       <c r="B1101" s="72" t="n"/>
       <c r="C1101" s="73" t="n"/>
@@ -36337,7 +36352,7 @@
       <c r="F1101" s="69" t="n"/>
       <c r="G1101" s="69" t="n"/>
     </row>
-    <row r="1102">
+    <row r="1102" s="477">
       <c r="A1102" s="69" t="n"/>
       <c r="B1102" s="72" t="n"/>
       <c r="C1102" s="73" t="n"/>
@@ -36346,7 +36361,7 @@
       <c r="F1102" s="69" t="n"/>
       <c r="G1102" s="69" t="n"/>
     </row>
-    <row r="1103">
+    <row r="1103" s="477">
       <c r="A1103" s="69" t="n"/>
       <c r="B1103" s="72" t="n"/>
       <c r="C1103" s="73" t="n"/>
@@ -36355,7 +36370,7 @@
       <c r="F1103" s="69" t="n"/>
       <c r="G1103" s="69" t="n"/>
     </row>
-    <row r="1104">
+    <row r="1104" s="477">
       <c r="A1104" s="69" t="n"/>
       <c r="B1104" s="72" t="n"/>
       <c r="C1104" s="73" t="n"/>
@@ -36364,7 +36379,7 @@
       <c r="F1104" s="69" t="n"/>
       <c r="G1104" s="69" t="n"/>
     </row>
-    <row r="1105">
+    <row r="1105" s="477">
       <c r="A1105" s="69" t="n"/>
       <c r="B1105" s="72" t="n"/>
       <c r="C1105" s="73" t="n"/>
@@ -36373,7 +36388,7 @@
       <c r="F1105" s="69" t="n"/>
       <c r="G1105" s="69" t="n"/>
     </row>
-    <row r="1106">
+    <row r="1106" s="477">
       <c r="A1106" s="69" t="n"/>
       <c r="B1106" s="72" t="n"/>
       <c r="C1106" s="73" t="n"/>
@@ -36382,7 +36397,7 @@
       <c r="F1106" s="69" t="n"/>
       <c r="G1106" s="69" t="n"/>
     </row>
-    <row r="1107">
+    <row r="1107" s="477">
       <c r="A1107" s="69" t="n"/>
       <c r="B1107" s="72" t="n"/>
       <c r="C1107" s="73" t="n"/>
@@ -36391,7 +36406,7 @@
       <c r="F1107" s="69" t="n"/>
       <c r="G1107" s="69" t="n"/>
     </row>
-    <row r="1108">
+    <row r="1108" s="477">
       <c r="A1108" s="69" t="n"/>
       <c r="B1108" s="72" t="n"/>
       <c r="C1108" s="73" t="n"/>
@@ -36400,7 +36415,7 @@
       <c r="F1108" s="69" t="n"/>
       <c r="G1108" s="69" t="n"/>
     </row>
-    <row r="1109">
+    <row r="1109" s="477">
       <c r="A1109" s="69" t="n"/>
       <c r="B1109" s="72" t="n"/>
       <c r="C1109" s="73" t="n"/>
@@ -36409,7 +36424,7 @@
       <c r="F1109" s="69" t="n"/>
       <c r="G1109" s="69" t="n"/>
     </row>
-    <row r="1110">
+    <row r="1110" s="477">
       <c r="A1110" s="69" t="n"/>
       <c r="B1110" s="72" t="n"/>
       <c r="C1110" s="73" t="n"/>
@@ -36418,7 +36433,7 @@
       <c r="F1110" s="69" t="n"/>
       <c r="G1110" s="69" t="n"/>
     </row>
-    <row r="1111">
+    <row r="1111" s="477">
       <c r="A1111" s="69" t="n"/>
       <c r="B1111" s="72" t="n"/>
       <c r="C1111" s="73" t="n"/>
@@ -36427,7 +36442,7 @@
       <c r="F1111" s="69" t="n"/>
       <c r="G1111" s="69" t="n"/>
     </row>
-    <row r="1112">
+    <row r="1112" s="477">
       <c r="A1112" s="69" t="n"/>
       <c r="B1112" s="72" t="n"/>
       <c r="C1112" s="73" t="n"/>
@@ -36436,7 +36451,7 @@
       <c r="F1112" s="69" t="n"/>
       <c r="G1112" s="69" t="n"/>
     </row>
-    <row r="1113">
+    <row r="1113" s="477">
       <c r="A1113" s="69" t="n"/>
       <c r="B1113" s="72" t="n"/>
       <c r="C1113" s="73" t="n"/>
@@ -36445,7 +36460,7 @@
       <c r="F1113" s="69" t="n"/>
       <c r="G1113" s="69" t="n"/>
     </row>
-    <row r="1114">
+    <row r="1114" s="477">
       <c r="A1114" s="69" t="n"/>
       <c r="B1114" s="72" t="n"/>
       <c r="C1114" s="73" t="n"/>
@@ -36454,7 +36469,7 @@
       <c r="F1114" s="69" t="n"/>
       <c r="G1114" s="69" t="n"/>
     </row>
-    <row r="1115">
+    <row r="1115" s="477">
       <c r="A1115" s="69" t="n"/>
       <c r="B1115" s="72" t="n"/>
       <c r="C1115" s="73" t="n"/>
@@ -36463,7 +36478,7 @@
       <c r="F1115" s="69" t="n"/>
       <c r="G1115" s="69" t="n"/>
     </row>
-    <row r="1116">
+    <row r="1116" s="477">
       <c r="A1116" s="69" t="n"/>
       <c r="B1116" s="72" t="n"/>
       <c r="C1116" s="73" t="n"/>
@@ -36472,7 +36487,7 @@
       <c r="F1116" s="69" t="n"/>
       <c r="G1116" s="69" t="n"/>
     </row>
-    <row r="1117">
+    <row r="1117" s="477">
       <c r="A1117" s="69" t="n"/>
       <c r="B1117" s="72" t="n"/>
       <c r="C1117" s="73" t="n"/>
@@ -36481,7 +36496,7 @@
       <c r="F1117" s="69" t="n"/>
       <c r="G1117" s="69" t="n"/>
     </row>
-    <row r="1118">
+    <row r="1118" s="477">
       <c r="A1118" s="69" t="n"/>
       <c r="B1118" s="72" t="n"/>
       <c r="C1118" s="73" t="n"/>
@@ -36490,7 +36505,7 @@
       <c r="F1118" s="69" t="n"/>
       <c r="G1118" s="69" t="n"/>
     </row>
-    <row r="1119">
+    <row r="1119" s="477">
       <c r="A1119" s="69" t="n"/>
       <c r="B1119" s="72" t="n"/>
       <c r="C1119" s="73" t="n"/>
@@ -36499,7 +36514,7 @@
       <c r="F1119" s="69" t="n"/>
       <c r="G1119" s="69" t="n"/>
     </row>
-    <row r="1120">
+    <row r="1120" s="477">
       <c r="A1120" s="69" t="n"/>
       <c r="B1120" s="72" t="n"/>
       <c r="C1120" s="73" t="n"/>
@@ -36508,7 +36523,7 @@
       <c r="F1120" s="69" t="n"/>
       <c r="G1120" s="69" t="n"/>
     </row>
-    <row r="1121">
+    <row r="1121" s="477">
       <c r="A1121" s="69" t="n"/>
       <c r="B1121" s="72" t="n"/>
       <c r="C1121" s="73" t="n"/>
@@ -36517,7 +36532,7 @@
       <c r="F1121" s="69" t="n"/>
       <c r="G1121" s="69" t="n"/>
     </row>
-    <row r="1122">
+    <row r="1122" s="477">
       <c r="A1122" s="69" t="n"/>
       <c r="B1122" s="72" t="n"/>
       <c r="C1122" s="73" t="n"/>
@@ -36526,7 +36541,7 @@
       <c r="F1122" s="69" t="n"/>
       <c r="G1122" s="69" t="n"/>
     </row>
-    <row r="1123">
+    <row r="1123" s="477">
       <c r="A1123" s="69" t="n"/>
       <c r="B1123" s="72" t="n"/>
       <c r="C1123" s="73" t="n"/>
@@ -36535,7 +36550,7 @@
       <c r="F1123" s="69" t="n"/>
       <c r="G1123" s="69" t="n"/>
     </row>
-    <row r="1124">
+    <row r="1124" s="477">
       <c r="A1124" s="69" t="n"/>
       <c r="B1124" s="72" t="n"/>
       <c r="C1124" s="73" t="n"/>
@@ -36544,7 +36559,7 @@
       <c r="F1124" s="69" t="n"/>
       <c r="G1124" s="69" t="n"/>
     </row>
-    <row r="1125">
+    <row r="1125" s="477">
       <c r="A1125" s="69" t="n"/>
       <c r="B1125" s="72" t="n"/>
       <c r="C1125" s="73" t="n"/>
@@ -36553,7 +36568,7 @@
       <c r="F1125" s="69" t="n"/>
       <c r="G1125" s="69" t="n"/>
     </row>
-    <row r="1126">
+    <row r="1126" s="477">
       <c r="A1126" s="69" t="n"/>
       <c r="B1126" s="72" t="n"/>
       <c r="C1126" s="73" t="n"/>
@@ -36562,7 +36577,7 @@
       <c r="F1126" s="69" t="n"/>
       <c r="G1126" s="69" t="n"/>
     </row>
-    <row r="1127">
+    <row r="1127" s="477">
       <c r="A1127" s="69" t="n"/>
       <c r="B1127" s="72" t="n"/>
       <c r="C1127" s="73" t="n"/>
@@ -36571,7 +36586,7 @@
       <c r="F1127" s="69" t="n"/>
       <c r="G1127" s="69" t="n"/>
     </row>
-    <row r="1128">
+    <row r="1128" s="477">
       <c r="A1128" s="69" t="n"/>
       <c r="B1128" s="72" t="n"/>
       <c r="C1128" s="73" t="n"/>
@@ -36580,7 +36595,7 @@
       <c r="F1128" s="69" t="n"/>
       <c r="G1128" s="69" t="n"/>
     </row>
-    <row r="1129">
+    <row r="1129" s="477">
       <c r="A1129" s="69" t="n"/>
       <c r="B1129" s="72" t="n"/>
       <c r="C1129" s="73" t="n"/>
@@ -36589,7 +36604,7 @@
       <c r="F1129" s="69" t="n"/>
       <c r="G1129" s="69" t="n"/>
     </row>
-    <row r="1130">
+    <row r="1130" s="477">
       <c r="A1130" s="69" t="n"/>
       <c r="B1130" s="72" t="n"/>
       <c r="C1130" s="73" t="n"/>
@@ -36598,7 +36613,7 @@
       <c r="F1130" s="69" t="n"/>
       <c r="G1130" s="69" t="n"/>
     </row>
-    <row r="1131">
+    <row r="1131" s="477">
       <c r="A1131" s="69" t="n"/>
       <c r="B1131" s="72" t="n"/>
       <c r="C1131" s="73" t="n"/>
@@ -36607,7 +36622,7 @@
       <c r="F1131" s="69" t="n"/>
       <c r="G1131" s="69" t="n"/>
     </row>
-    <row r="1132">
+    <row r="1132" s="477">
       <c r="A1132" s="69" t="n"/>
       <c r="B1132" s="72" t="n"/>
       <c r="C1132" s="73" t="n"/>
@@ -36616,7 +36631,7 @@
       <c r="F1132" s="69" t="n"/>
       <c r="G1132" s="69" t="n"/>
     </row>
-    <row r="1133">
+    <row r="1133" s="477">
       <c r="A1133" s="69" t="n"/>
       <c r="B1133" s="72" t="n"/>
       <c r="C1133" s="73" t="n"/>
@@ -36625,19 +36640,18 @@
       <c r="F1133" s="69" t="n"/>
       <c r="G1133" s="69" t="n"/>
     </row>
-    <row r="1134">
+    <row r="1134" s="477">
       <c r="A1134" s="69" t="n"/>
       <c r="C1134" s="355" t="n"/>
       <c r="E1134" s="355" t="n"/>
     </row>
-    <row r="1135">
+    <row r="1135" s="477">
       <c r="A1135" s="69" t="n"/>
       <c r="C1135" s="355" t="n"/>
       <c r="E1135" s="355" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B187:E187"/>
+  <mergeCells count="20">
     <mergeCell ref="B239:E239"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B6:E6"/>
@@ -36646,10 +36660,7 @@
     <mergeCell ref="B222:E222"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B113:E113"/>
     <mergeCell ref="B173:E173"/>
-    <mergeCell ref="B224:E224"/>
     <mergeCell ref="B233:E233"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="C15:E15"/>

--- a/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
+++ b/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
@@ -26153,6 +26153,11 @@
 ③申請</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>完了後、再度お客様に画面共有をしていただく</t>
+        </is>
+      </c>
       <c r="F187" s="140" t="n"/>
       <c r="G187" s="462" t="n"/>
       <c r="H187" s="462" t="n"/>

--- a/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
+++ b/ツール/【原本_法人】企業名_インボイス枠_法人2026_v2.xlsx
@@ -9,11 +9,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="給与支給総額計算 (旧)" sheetId="4" state="hidden" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="申請金額" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="小規模事業者確認" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分類表" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品マスタ" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プルダウン用" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実績報告" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="編集用" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ツールマスタ" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分類表" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品マスタ" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="費用内訳マスタ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プルダウン用" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実績報告" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="編集用" sheetId="13" state="hidden" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +33,7 @@
     <numFmt numFmtId="169" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
     <numFmt numFmtId="170" formatCode="[$¥-411]#,##0"/>
   </numFmts>
-  <fonts count="75">
+  <fonts count="81">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -437,8 +439,39 @@
       <b val="1"/>
       <color rgb="FF000000"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="&quot;ＭＳ ゴシック&quot;"/>
+      <b val="1"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -623,6 +656,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB7B7B7"/>
         <bgColor rgb="FFB7B7B7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEAF1"/>
+        <bgColor rgb="FFDEEAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -1259,7 +1304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="525">
+  <cellXfs count="537">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -2583,6 +2628,38 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7459,6 +7536,1415 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="454" t="inlineStr">
+        <is>
+          <t>商品名_金額キー</t>
+        </is>
+      </c>
+      <c r="B1" s="454" t="inlineStr">
+        <is>
+          <t>内訳項目1</t>
+        </is>
+      </c>
+      <c r="C1" s="454" t="inlineStr">
+        <is>
+          <t>金額1</t>
+        </is>
+      </c>
+      <c r="D1" s="454" t="inlineStr">
+        <is>
+          <t>内訳項目2</t>
+        </is>
+      </c>
+      <c r="E1" s="454" t="inlineStr">
+        <is>
+          <t>金額2</t>
+        </is>
+      </c>
+      <c r="F1" s="454" t="inlineStr">
+        <is>
+          <t>内訳項目3</t>
+        </is>
+      </c>
+      <c r="G1" s="454" t="inlineStr">
+        <is>
+          <t>金額3</t>
+        </is>
+      </c>
+      <c r="H1" s="454" t="inlineStr">
+        <is>
+          <t>内訳項目4</t>
+        </is>
+      </c>
+      <c r="I1" s="454" t="inlineStr">
+        <is>
+          <t>金額4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）_800000</t>
+        </is>
+      </c>
+      <c r="B2" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C2" s="454" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D2" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E2" s="454" t="n">
+        <v>480000</v>
+      </c>
+      <c r="F2" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G2" s="454" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）_720000</t>
+        </is>
+      </c>
+      <c r="B3" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C3" s="454" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D3" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E3" s="454" t="n">
+        <v>430000</v>
+      </c>
+      <c r="F3" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G3" s="454" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）_700000</t>
+        </is>
+      </c>
+      <c r="B4" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C4" s="454" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E4" s="454" t="n">
+        <v>410000</v>
+      </c>
+      <c r="F4" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G4" s="454" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）_640000</t>
+        </is>
+      </c>
+      <c r="B5" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C5" s="454" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D5" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E5" s="454" t="n">
+        <v>370000</v>
+      </c>
+      <c r="F5" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G5" s="454" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）_600000</t>
+        </is>
+      </c>
+      <c r="B6" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C6" s="454" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D6" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E6" s="454" t="n">
+        <v>330000</v>
+      </c>
+      <c r="F6" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G6" s="454" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）_480000</t>
+        </is>
+      </c>
+      <c r="B7" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C7" s="454" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D7" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E7" s="454" t="n">
+        <v>310000</v>
+      </c>
+      <c r="F7" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G7" s="454" t="n">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）_400000</t>
+        </is>
+      </c>
+      <c r="B8" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C8" s="454" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D8" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E8" s="454" t="n">
+        <v>280000</v>
+      </c>
+      <c r="F8" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G8" s="454" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）_1200000</t>
+        </is>
+      </c>
+      <c r="B9" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C9" s="454" t="n">
+        <v>340000</v>
+      </c>
+      <c r="D9" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E9" s="454" t="n">
+        <v>570000</v>
+      </c>
+      <c r="F9" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G9" s="454" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H9" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I9" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）_1080000</t>
+        </is>
+      </c>
+      <c r="B10" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C10" s="454" t="n">
+        <v>340000</v>
+      </c>
+      <c r="D10" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E10" s="454" t="n">
+        <v>480000</v>
+      </c>
+      <c r="F10" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G10" s="454" t="n">
+        <v>190000</v>
+      </c>
+      <c r="H10" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I10" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）_1050000</t>
+        </is>
+      </c>
+      <c r="B11" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C11" s="454" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D11" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E11" s="454" t="n">
+        <v>460000</v>
+      </c>
+      <c r="F11" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G11" s="454" t="n">
+        <v>190000</v>
+      </c>
+      <c r="H11" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I11" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）_960000</t>
+        </is>
+      </c>
+      <c r="B12" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C12" s="454" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D12" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E12" s="454" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F12" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G12" s="454" t="n">
+        <v>160000</v>
+      </c>
+      <c r="H12" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I12" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）_900000</t>
+        </is>
+      </c>
+      <c r="B13" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C13" s="454" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D13" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E13" s="454" t="n">
+        <v>370000</v>
+      </c>
+      <c r="F13" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G13" s="454" t="n">
+        <v>160000</v>
+      </c>
+      <c r="H13" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I13" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）_720000</t>
+        </is>
+      </c>
+      <c r="B14" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C14" s="454" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D14" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E14" s="454" t="n">
+        <v>330000</v>
+      </c>
+      <c r="F14" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G14" s="454" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H14" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I14" s="454" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）_600000</t>
+        </is>
+      </c>
+      <c r="B15" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C15" s="454" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D15" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E15" s="454" t="n">
+        <v>240000</v>
+      </c>
+      <c r="F15" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G15" s="454" t="n">
+        <v>110000</v>
+      </c>
+      <c r="H15" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I15" s="454" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）_1200000</t>
+        </is>
+      </c>
+      <c r="B16" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C16" s="454" t="n">
+        <v>135000</v>
+      </c>
+      <c r="D16" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E16" s="454" t="n">
+        <v>820000</v>
+      </c>
+      <c r="F16" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G16" s="454" t="n">
+        <v>245000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）_1000000</t>
+        </is>
+      </c>
+      <c r="B17" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C17" s="454" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D17" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E17" s="454" t="n">
+        <v>670000</v>
+      </c>
+      <c r="F17" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G17" s="454" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）_960000</t>
+        </is>
+      </c>
+      <c r="B18" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C18" s="454" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D18" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E18" s="454" t="n">
+        <v>630000</v>
+      </c>
+      <c r="F18" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G18" s="454" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）_880000</t>
+        </is>
+      </c>
+      <c r="B19" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C19" s="454" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D19" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E19" s="454" t="n">
+        <v>560000</v>
+      </c>
+      <c r="F19" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G19" s="454" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="454" t="inlineStr">
+        <is>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）_800000</t>
+        </is>
+      </c>
+      <c r="B20" s="454" t="inlineStr">
+        <is>
+          <t>マスタ類の設定項目洗い出しにかかる費用</t>
+        </is>
+      </c>
+      <c r="C20" s="454" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D20" s="454" t="inlineStr">
+        <is>
+          <t>業務移行計画(並行稼動)作成費用</t>
+        </is>
+      </c>
+      <c r="E20" s="454" t="n">
+        <v>480000</v>
+      </c>
+      <c r="F20" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ項目洗い出し費用</t>
+        </is>
+      </c>
+      <c r="G20" s="454" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）_1800000</t>
+        </is>
+      </c>
+      <c r="B21" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C21" s="454" t="n">
+        <v>470000</v>
+      </c>
+      <c r="D21" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E21" s="454" t="n">
+        <v>940000</v>
+      </c>
+      <c r="F21" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G21" s="454" t="n">
+        <v>290000</v>
+      </c>
+      <c r="H21" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I21" s="454" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）_1500000</t>
+        </is>
+      </c>
+      <c r="B22" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C22" s="454" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D22" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E22" s="454" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F22" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G22" s="454" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H22" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I22" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）_1440000</t>
+        </is>
+      </c>
+      <c r="B23" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C23" s="454" t="n">
+        <v>390000</v>
+      </c>
+      <c r="D23" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E23" s="454" t="n">
+        <v>750000</v>
+      </c>
+      <c r="F23" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G23" s="454" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H23" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I23" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）_1320000</t>
+        </is>
+      </c>
+      <c r="B24" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C24" s="454" t="n">
+        <v>360000</v>
+      </c>
+      <c r="D24" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E24" s="454" t="n">
+        <v>670000</v>
+      </c>
+      <c r="F24" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G24" s="454" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H24" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I24" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="454" t="inlineStr">
+        <is>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）_1200000</t>
+        </is>
+      </c>
+      <c r="B25" s="454" t="inlineStr">
+        <is>
+          <t>導入設定費用、テーブル設定費用等</t>
+        </is>
+      </c>
+      <c r="C25" s="454" t="n">
+        <v>340000</v>
+      </c>
+      <c r="D25" s="454" t="inlineStr">
+        <is>
+          <t>カスタマイズ作業にかかる費用</t>
+        </is>
+      </c>
+      <c r="E25" s="454" t="n">
+        <v>570000</v>
+      </c>
+      <c r="F25" s="454" t="inlineStr">
+        <is>
+          <t>研修資料作成、研修実施費用</t>
+        </is>
+      </c>
+      <c r="G25" s="454" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H25" s="454" t="inlineStr">
+        <is>
+          <t>運用マニュアル作成費用</t>
+        </is>
+      </c>
+      <c r="I25" s="454" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="453" t="inlineStr">
+        <is>
+          <t>都道府県名</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="454" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B2" s="454" t="inlineStr">
+        <is>
+          <t>北海道/1075円</t>
+        </is>
+      </c>
+      <c r="C2" s="348" t="inlineStr">
+        <is>
+          <t>A、農業林業</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="454" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B3" s="454" t="inlineStr">
+        <is>
+          <t>青森/1029円</t>
+        </is>
+      </c>
+      <c r="C3" s="348" t="inlineStr">
+        <is>
+          <t>B、漁業</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="454" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B4" s="454" t="inlineStr">
+        <is>
+          <t>岩手/1031円</t>
+        </is>
+      </c>
+      <c r="C4" s="348" t="inlineStr">
+        <is>
+          <t>C、鉱業、採石業、砂利採取業</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="454" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B5" s="454" t="inlineStr">
+        <is>
+          <t>宮城/1038円</t>
+        </is>
+      </c>
+      <c r="C5" s="348" t="inlineStr">
+        <is>
+          <t>D、建設業</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="454" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B6" s="454" t="inlineStr">
+        <is>
+          <t>秋田/1031円</t>
+        </is>
+      </c>
+      <c r="C6" s="348" t="inlineStr">
+        <is>
+          <t>E、製造業</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="454" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B7" s="454" t="inlineStr">
+        <is>
+          <t>山形/1032円</t>
+        </is>
+      </c>
+      <c r="C7" s="348" t="inlineStr">
+        <is>
+          <t>F、電気、ガス、熱供給・水道業</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="454" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B8" s="454" t="inlineStr">
+        <is>
+          <t>福島/1033円</t>
+        </is>
+      </c>
+      <c r="C8" s="348" t="inlineStr">
+        <is>
+          <t>G、情報通信業</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="454" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B9" s="454" t="inlineStr">
+        <is>
+          <t>茨城/1074円</t>
+        </is>
+      </c>
+      <c r="C9" s="348" t="inlineStr">
+        <is>
+          <t>H、運輸業、郵便業</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="454" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B10" s="454" t="inlineStr">
+        <is>
+          <t>栃木/1068円</t>
+        </is>
+      </c>
+      <c r="C10" s="348" t="inlineStr">
+        <is>
+          <t>I、卸売業、小売業</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="454" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="B11" s="454" t="inlineStr">
+        <is>
+          <t>群馬/1063円</t>
+        </is>
+      </c>
+      <c r="C11" s="348" t="inlineStr">
+        <is>
+          <t>J、金融業、保険業</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="454" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="B12" s="454" t="inlineStr">
+        <is>
+          <t>埼玉/1141円</t>
+        </is>
+      </c>
+      <c r="C12" s="348" t="inlineStr">
+        <is>
+          <t>K、不動産業、物品賃貸業</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="454" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="B13" s="454" t="inlineStr">
+        <is>
+          <t>千葉/1140円</t>
+        </is>
+      </c>
+      <c r="C13" s="348" t="inlineStr">
+        <is>
+          <t>L、学術研究、専門・技術サービス業</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="454" t="inlineStr">
+        <is>
+          <t>東京/1226円</t>
+        </is>
+      </c>
+      <c r="C14" s="348" t="inlineStr">
+        <is>
+          <t>M、宿泊業、飲食サービス業</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="454" t="inlineStr">
+        <is>
+          <t>神奈川/1225円</t>
+        </is>
+      </c>
+      <c r="C15" s="348" t="inlineStr">
+        <is>
+          <t>N、生活関連サービス業、娯楽業</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="454" t="inlineStr">
+        <is>
+          <t>新潟/1050円</t>
+        </is>
+      </c>
+      <c r="C16" s="348" t="inlineStr">
+        <is>
+          <t>O、教育、学習支援業</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="454" t="inlineStr">
+        <is>
+          <t>富山/1062円</t>
+        </is>
+      </c>
+      <c r="C17" s="348" t="inlineStr">
+        <is>
+          <t>P、医療 福祉</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="454" t="inlineStr">
+        <is>
+          <t>石川/1054円</t>
+        </is>
+      </c>
+      <c r="C18" s="348" t="inlineStr">
+        <is>
+          <t>Q、複合サービス事業</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="454" t="inlineStr">
+        <is>
+          <t>福井/1053円</t>
+        </is>
+      </c>
+      <c r="C19" s="348" t="inlineStr">
+        <is>
+          <t>R、サービス業（他に分類されないもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="454" t="inlineStr">
+        <is>
+          <t>山梨/1052円</t>
+        </is>
+      </c>
+      <c r="C20" s="348" t="inlineStr">
+        <is>
+          <t>S、公務（他に分類されるものを除く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="454" t="inlineStr">
+        <is>
+          <t>長野/1061円</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="454" t="inlineStr">
+        <is>
+          <t>岐阜/1065円</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="454" t="inlineStr">
+        <is>
+          <t>静岡/1097円</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="454" t="inlineStr">
+        <is>
+          <t>愛知/1140円</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="454" t="inlineStr">
+        <is>
+          <t>三重/1087円</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="454" t="inlineStr">
+        <is>
+          <t>滋賀/1080円</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="454" t="inlineStr">
+        <is>
+          <t>京都/1122円</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="454" t="inlineStr">
+        <is>
+          <t>大阪/1177円</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="454" t="inlineStr">
+        <is>
+          <t>兵庫/1116円</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="454" t="inlineStr">
+        <is>
+          <t>奈良/1051円</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="454" t="inlineStr">
+        <is>
+          <t>和歌山/1045円</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="454" t="inlineStr">
+        <is>
+          <t>鳥取/1030円</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="454" t="inlineStr">
+        <is>
+          <t>島根/1033円</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="454" t="inlineStr">
+        <is>
+          <t>岡山/1047円</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="454" t="inlineStr">
+        <is>
+          <t>広島/1085円</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="454" t="inlineStr">
+        <is>
+          <t>山口/1043円</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="454" t="inlineStr">
+        <is>
+          <t>徳島/1046円</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="454" t="inlineStr">
+        <is>
+          <t>香川/1036円</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="454" t="inlineStr">
+        <is>
+          <t>愛媛/1033円</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="454" t="inlineStr">
+        <is>
+          <t>高知/1023円</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="454" t="inlineStr">
+        <is>
+          <t>福岡/1057円</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="454" t="inlineStr">
+        <is>
+          <t>佐賀/1030円</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="454" t="inlineStr">
+        <is>
+          <t>長崎/1031円</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="454" t="inlineStr">
+        <is>
+          <t>熊本/1034円</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="454" t="inlineStr">
+        <is>
+          <t>大分/1035円</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="454" t="inlineStr">
+        <is>
+          <t>宮崎/1023円</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="454" t="inlineStr">
+        <is>
+          <t>鹿児島/1026円</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="454" t="inlineStr">
+        <is>
+          <t>沖縄/1023円</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="455" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -19310,7 +20796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -23685,7 +25171,7 @@
       <c r="A98" s="69" t="n"/>
       <c r="B98" s="498" t="inlineStr">
         <is>
-          <t>役員（8）役職</t>
+          <t>役員（８）役職</t>
         </is>
       </c>
       <c r="C98" s="499" t="n"/>
@@ -23694,14 +25180,14 @@
     <row r="99" s="477">
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>役員（8）氏名</t>
+          <t>役員（８）氏名</t>
         </is>
       </c>
     </row>
     <row r="100" s="477">
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>役員（8）氏名フリガナ</t>
+          <t>役員（８）氏名フリガナ</t>
         </is>
       </c>
     </row>
@@ -23709,7 +25195,7 @@
       <c r="A101" s="69" t="n"/>
       <c r="B101" s="498" t="inlineStr">
         <is>
-          <t>役員（9）役職</t>
+          <t>役員（９）役職</t>
         </is>
       </c>
       <c r="C101" s="499" t="n"/>
@@ -23718,14 +25204,14 @@
     <row r="102" s="477">
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>役員（9）氏名</t>
+          <t>役員（９）氏名</t>
         </is>
       </c>
     </row>
     <row r="103" s="477">
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>役員（9）氏名フリガナ</t>
+          <t>役員（９）氏名フリガナ</t>
         </is>
       </c>
     </row>
@@ -25365,7 +26851,14 @@
           <t>セキュリティの状況</t>
         </is>
       </c>
-      <c r="C161" s="235" t="n"/>
+      <c r="C161" s="235" t="inlineStr">
+        <is>
+          <t>□緊急時の対応マニュアルや手順を定め、定期的に訓練を行っている
+■パソコンやサーバなどには、IDやパスワードを設け情報セキュリティ管理を行っている
+□セキュリティ対策は講じていないため、対策を講じていく
+□セキュリティ対策を講じておらず、今後もその予定はない</t>
+        </is>
+      </c>
       <c r="D161" s="236" t="n"/>
       <c r="E161" s="159" t="n"/>
       <c r="F161" s="140" t="n"/>
@@ -25490,24 +26983,19 @@
           <t>ITツールの導入により電子化する事務の範囲</t>
         </is>
       </c>
-      <c r="C164" s="243" t="inlineStr">
-        <is>
-          <t>□自社の会計業務
+      <c r="C164" s="243">
+        <f>IFERROR(VLOOKUP($C$61,'ツールマスタ'!$A$4:$C$50,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D164" s="244" t="inlineStr">
+        <is>
+          <t>※ツールによって内容確認
+□自社の会計業務
 □自社の請求書発行業務
 □自社の受発注業務
 □取引先の受発注業務
 □取引先からの請求書受領業務
 □自社・取引先間の決済業務</t>
-        </is>
-      </c>
-      <c r="D164" s="244" t="inlineStr">
-        <is>
-          <t>※ツールによって内容確認
-（一例）
-【貿易クラウド】
-■自社の請求書発行業務■自社の受発注業務■自社・取引先間の決済業務
-【Cbox】【クラフトバンク】
-■自社の会計業務■自社の請求書発行業務■自社の受発注業務</t>
         </is>
       </c>
       <c r="E164" s="159" t="n"/>
@@ -25540,23 +27028,18 @@
           <t>ITツールの導入によりインボイス対応に資する業務</t>
         </is>
       </c>
-      <c r="C165" s="245" t="inlineStr">
-        <is>
-          <t>□スキャンした請求書の自動データ化
+      <c r="C165" s="245">
+        <f>IFERROR(VLOOKUP($C$61,'ツールマスタ'!$A$4:$C$50,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D165" s="244" t="inlineStr">
+        <is>
+          <t>※ツールによって内容確認
+□スキャンした請求書の自動データ化
 □仕入先が免税事業者かどうかの確認
 □免税事業者の控除率の自動化
 □請求書発行時の登録番号記載
 □税率ごとの区分表示</t>
-        </is>
-      </c>
-      <c r="D165" s="244" t="inlineStr">
-        <is>
-          <t>※ツールによって内容確認
-（一例）
-【貿易クラウド】【Cbox】
-■請求書発行時の登録番号記載■税率ごとの区分表示
-【クラフトバンク】
-■スキャンした請求書の自動化■請求書発行時の登録番号記載■税率ごとの区分表示</t>
         </is>
       </c>
       <c r="E165" s="159" t="n"/>
@@ -26153,7 +27636,7 @@
 ③申請</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D187" s="0" t="inlineStr">
         <is>
           <t>完了後、再度お客様に画面共有をしていただく</t>
         </is>
@@ -36721,9 +38204,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="11">
-    <dataValidation sqref="C61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"scale,クラフトバンクオフィス"</formula1>
-    </dataValidation>
     <dataValidation sqref="C117" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"くるみん認定,プラチナくるみん認定, トライくるみん認定 ,認定なし"</formula1>
     </dataValidation>
@@ -36753,6 +38233,9 @@
     </dataValidation>
     <dataValidation sqref="C2:C3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"村上,土屋,坂平"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'ツールマスタ'!$A$4:$A$11</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -37690,7 +39173,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="5.38" customWidth="1" style="477" min="1" max="1"/>
@@ -37805,6 +39288,38 @@
         <f>VLOOKUP(D3,'商品マスタ'!B:H,6,FALSE)</f>
         <v/>
       </c>
+      <c r="M3" s="525">
+        <f>IFERROR(VLOOKUP($D3&amp;"_"&amp;TEXT($H3,"0"),'費用内訳マスタ'!$A:$I,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="525">
+        <f>IFERROR(VLOOKUP($D3&amp;"_"&amp;TEXT($H3,"0"),'費用内訳マスタ'!$A:$I,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="525">
+        <f>IFERROR(VLOOKUP($D3&amp;"_"&amp;TEXT($H3,"0"),'費用内訳マスタ'!$A:$I,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="525">
+        <f>IFERROR(VLOOKUP($D3&amp;"_"&amp;TEXT($H3,"0"),'費用内訳マスタ'!$A:$I,5,0),"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="525">
+        <f>IFERROR(VLOOKUP($D3&amp;"_"&amp;TEXT($H3,"0"),'費用内訳マスタ'!$A:$I,6,0),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="525">
+        <f>IFERROR(VLOOKUP($D3&amp;"_"&amp;TEXT($H3,"0"),'費用内訳マスタ'!$A:$I,7,0),"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="525">
+        <f>IFERROR(VLOOKUP($D3&amp;"_"&amp;TEXT($H3,"0"),'費用内訳マスタ'!$A:$I,8,0),"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="525">
+        <f>IFERROR(VLOOKUP($D3&amp;"_"&amp;TEXT($H3,"0"),'費用内訳マスタ'!$A:$I,9,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="395" t="n">
@@ -37835,6 +39350,38 @@
         <f>VLOOKUP(D4,'商品マスタ'!B:H,6,FALSE)</f>
         <v/>
       </c>
+      <c r="M4" s="525">
+        <f>IFERROR(VLOOKUP($D4&amp;"_"&amp;TEXT($H4,"0"),'費用内訳マスタ'!$A:$I,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="525">
+        <f>IFERROR(VLOOKUP($D4&amp;"_"&amp;TEXT($H4,"0"),'費用内訳マスタ'!$A:$I,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="O4" s="525">
+        <f>IFERROR(VLOOKUP($D4&amp;"_"&amp;TEXT($H4,"0"),'費用内訳マスタ'!$A:$I,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="P4" s="525">
+        <f>IFERROR(VLOOKUP($D4&amp;"_"&amp;TEXT($H4,"0"),'費用内訳マスタ'!$A:$I,5,0),"")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="525">
+        <f>IFERROR(VLOOKUP($D4&amp;"_"&amp;TEXT($H4,"0"),'費用内訳マスタ'!$A:$I,6,0),"")</f>
+        <v/>
+      </c>
+      <c r="R4" s="525">
+        <f>IFERROR(VLOOKUP($D4&amp;"_"&amp;TEXT($H4,"0"),'費用内訳マスタ'!$A:$I,7,0),"")</f>
+        <v/>
+      </c>
+      <c r="S4" s="525">
+        <f>IFERROR(VLOOKUP($D4&amp;"_"&amp;TEXT($H4,"0"),'費用内訳マスタ'!$A:$I,8,0),"")</f>
+        <v/>
+      </c>
+      <c r="T4" s="525">
+        <f>IFERROR(VLOOKUP($D4&amp;"_"&amp;TEXT($H4,"0"),'費用内訳マスタ'!$A:$I,9,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="395" t="n">
@@ -37865,6 +39412,38 @@
         <f>VLOOKUP(D5,'商品マスタ'!B:H,6,FALSE)</f>
         <v/>
       </c>
+      <c r="M5" s="525">
+        <f>IFERROR(VLOOKUP($D5&amp;"_"&amp;TEXT($H5,"0"),'費用内訳マスタ'!$A:$I,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="N5" s="525">
+        <f>IFERROR(VLOOKUP($D5&amp;"_"&amp;TEXT($H5,"0"),'費用内訳マスタ'!$A:$I,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="O5" s="525">
+        <f>IFERROR(VLOOKUP($D5&amp;"_"&amp;TEXT($H5,"0"),'費用内訳マスタ'!$A:$I,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="P5" s="525">
+        <f>IFERROR(VLOOKUP($D5&amp;"_"&amp;TEXT($H5,"0"),'費用内訳マスタ'!$A:$I,5,0),"")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="525">
+        <f>IFERROR(VLOOKUP($D5&amp;"_"&amp;TEXT($H5,"0"),'費用内訳マスタ'!$A:$I,6,0),"")</f>
+        <v/>
+      </c>
+      <c r="R5" s="525">
+        <f>IFERROR(VLOOKUP($D5&amp;"_"&amp;TEXT($H5,"0"),'費用内訳マスタ'!$A:$I,7,0),"")</f>
+        <v/>
+      </c>
+      <c r="S5" s="525">
+        <f>IFERROR(VLOOKUP($D5&amp;"_"&amp;TEXT($H5,"0"),'費用内訳マスタ'!$A:$I,8,0),"")</f>
+        <v/>
+      </c>
+      <c r="T5" s="525">
+        <f>IFERROR(VLOOKUP($D5&amp;"_"&amp;TEXT($H5,"0"),'費用内訳マスタ'!$A:$I,9,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="395" t="n">
@@ -37893,6 +39472,38 @@
       </c>
       <c r="K6" s="394">
         <f>VLOOKUP(D6,'商品マスタ'!B:H,6,FALSE)</f>
+        <v/>
+      </c>
+      <c r="M6" s="525">
+        <f>IFERROR(VLOOKUP($D6&amp;"_"&amp;TEXT($H6,"0"),'費用内訳マスタ'!$A:$I,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="N6" s="525">
+        <f>IFERROR(VLOOKUP($D6&amp;"_"&amp;TEXT($H6,"0"),'費用内訳マスタ'!$A:$I,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="O6" s="525">
+        <f>IFERROR(VLOOKUP($D6&amp;"_"&amp;TEXT($H6,"0"),'費用内訳マスタ'!$A:$I,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="P6" s="525">
+        <f>IFERROR(VLOOKUP($D6&amp;"_"&amp;TEXT($H6,"0"),'費用内訳マスタ'!$A:$I,5,0),"")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="525">
+        <f>IFERROR(VLOOKUP($D6&amp;"_"&amp;TEXT($H6,"0"),'費用内訳マスタ'!$A:$I,6,0),"")</f>
+        <v/>
+      </c>
+      <c r="R6" s="525">
+        <f>IFERROR(VLOOKUP($D6&amp;"_"&amp;TEXT($H6,"0"),'費用内訳マスタ'!$A:$I,7,0),"")</f>
+        <v/>
+      </c>
+      <c r="S6" s="525">
+        <f>IFERROR(VLOOKUP($D6&amp;"_"&amp;TEXT($H6,"0"),'費用内訳マスタ'!$A:$I,8,0),"")</f>
+        <v/>
+      </c>
+      <c r="T6" s="525">
+        <f>IFERROR(VLOOKUP($D6&amp;"_"&amp;TEXT($H6,"0"),'費用内訳マスタ'!$A:$I,9,0),"")</f>
         <v/>
       </c>
     </row>
@@ -37917,6 +39528,38 @@
       </c>
       <c r="J7" s="394" t="n"/>
       <c r="K7" s="394" t="n"/>
+      <c r="M7" s="525">
+        <f>IFERROR(VLOOKUP($D7&amp;"_"&amp;TEXT($H7,"0"),'費用内訳マスタ'!$A:$I,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="525">
+        <f>IFERROR(VLOOKUP($D7&amp;"_"&amp;TEXT($H7,"0"),'費用内訳マスタ'!$A:$I,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="O7" s="525">
+        <f>IFERROR(VLOOKUP($D7&amp;"_"&amp;TEXT($H7,"0"),'費用内訳マスタ'!$A:$I,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="P7" s="525">
+        <f>IFERROR(VLOOKUP($D7&amp;"_"&amp;TEXT($H7,"0"),'費用内訳マスタ'!$A:$I,5,0),"")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="525">
+        <f>IFERROR(VLOOKUP($D7&amp;"_"&amp;TEXT($H7,"0"),'費用内訳マスタ'!$A:$I,6,0),"")</f>
+        <v/>
+      </c>
+      <c r="R7" s="525">
+        <f>IFERROR(VLOOKUP($D7&amp;"_"&amp;TEXT($H7,"0"),'費用内訳マスタ'!$A:$I,7,0),"")</f>
+        <v/>
+      </c>
+      <c r="S7" s="525">
+        <f>IFERROR(VLOOKUP($D7&amp;"_"&amp;TEXT($H7,"0"),'費用内訳マスタ'!$A:$I,8,0),"")</f>
+        <v/>
+      </c>
+      <c r="T7" s="525">
+        <f>IFERROR(VLOOKUP($D7&amp;"_"&amp;TEXT($H7,"0"),'費用内訳マスタ'!$A:$I,9,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="385" t="n"/>
@@ -38053,7 +39696,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="D3:D6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>'商品マスタ'!$B$3:$B$45</formula1>
+      <formula1>'商品マスタ'!$B$3:$B$61</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -38237,6 +39880,242 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22.63" customWidth="1" style="477" min="2" max="2"/>
+    <col width="25.25" customWidth="1" style="477" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="526" t="inlineStr">
+        <is>
+          <t>「申請内容」C61でツールを選ぶとC164・C165が自動入力されます</t>
+        </is>
+      </c>
+      <c r="C1" s="527" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="527" t="n"/>
+      <c r="B2" s="527" t="n"/>
+      <c r="C2" s="527" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="528" t="inlineStr">
+        <is>
+          <t>ツール名</t>
+        </is>
+      </c>
+      <c r="B3" s="529" t="inlineStr">
+        <is>
+          <t>電子化する事務の範囲（C164）</t>
+        </is>
+      </c>
+      <c r="C3" s="529" t="inlineStr">
+        <is>
+          <t>インボイス対応業務（C165）</t>
+        </is>
+      </c>
+      <c r="D3" s="530" t="inlineStr">
+        <is>
+          <t>資料リンク（C62プロンプトに指入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="531" t="inlineStr">
+        <is>
+          <t>貿易クラウド</t>
+        </is>
+      </c>
+      <c r="B4" s="532" t="n"/>
+      <c r="C4" s="532" t="n"/>
+      <c r="D4" s="531" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="454" t="inlineStr">
+        <is>
+          <t>クラフトバンクオフィス</t>
+        </is>
+      </c>
+      <c r="B5" s="532" t="inlineStr">
+        <is>
+          <t>□自社の会計業務, □自社の請求書発行業務, □自社の受発注業務, □取引先の受発注業務, □取引先からの請求書受領業務</t>
+        </is>
+      </c>
+      <c r="C5" s="532" t="inlineStr">
+        <is>
+          <t>□スキャンした請求書の自動データ化, □仕入先が免税事業者かどうかの確認, □免税事業者の控除率の自動化, □請求書発行時の登録番号記載, □税率ごとの区分表示</t>
+        </is>
+      </c>
+      <c r="D5" s="533" t="inlineStr">
+        <is>
+          <t>https://corp.craft-bank.com/cbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="532" t="n"/>
+      <c r="C6" s="532" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="532" t="n"/>
+      <c r="C7" s="532" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="532" t="n"/>
+      <c r="C8" s="532" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="532" t="n"/>
+      <c r="C9" s="532" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="531" t="n"/>
+      <c r="B10" s="532" t="n"/>
+      <c r="C10" s="532" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="531" t="n"/>
+      <c r="B11" s="532" t="n"/>
+      <c r="C11" s="532" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="531" t="n"/>
+      <c r="B12" s="531" t="n"/>
+      <c r="C12" s="531" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="531" t="n"/>
+      <c r="B13" s="531" t="n"/>
+      <c r="C13" s="531" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="527" t="n"/>
+      <c r="B14" s="527" t="n"/>
+      <c r="C14" s="527" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="534" t="inlineStr">
+        <is>
+          <t>【参考】選択肢一覧（テーブル入力時に使用してください）</t>
+        </is>
+      </c>
+      <c r="C15" s="527" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="535" t="inlineStr">
+        <is>
+          <t>C164の選択肢</t>
+        </is>
+      </c>
+      <c r="B16" s="535" t="inlineStr">
+        <is>
+          <t>C165の選択肢</t>
+        </is>
+      </c>
+      <c r="C16" s="527" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="536" t="inlineStr">
+        <is>
+          <t>□自社の会計業務</t>
+        </is>
+      </c>
+      <c r="B17" s="536" t="inlineStr">
+        <is>
+          <t>□スキャンした請求書の自動データ化</t>
+        </is>
+      </c>
+      <c r="C17" s="527" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="536" t="inlineStr">
+        <is>
+          <t>□自社の請求書発行業務</t>
+        </is>
+      </c>
+      <c r="B18" s="536" t="inlineStr">
+        <is>
+          <t>□仕入先が免税事業者かどうかの確認</t>
+        </is>
+      </c>
+      <c r="C18" s="527" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="536" t="inlineStr">
+        <is>
+          <t>□自社の受発注業務</t>
+        </is>
+      </c>
+      <c r="B19" s="536" t="inlineStr">
+        <is>
+          <t>□免税事業者の控除率の自動化</t>
+        </is>
+      </c>
+      <c r="C19" s="527" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="536" t="inlineStr">
+        <is>
+          <t>□取引先の受発注業務</t>
+        </is>
+      </c>
+      <c r="B20" s="536" t="inlineStr">
+        <is>
+          <t>□請求書発行時の登録番号記載</t>
+        </is>
+      </c>
+      <c r="C20" s="527" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="536" t="inlineStr">
+        <is>
+          <t>□取引先からの請求書受領業務</t>
+        </is>
+      </c>
+      <c r="B21" s="536" t="inlineStr">
+        <is>
+          <t>□税率ごとの区分表示</t>
+        </is>
+      </c>
+      <c r="C21" s="527" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="536" t="inlineStr">
+        <is>
+          <t>□自社・取引先間の決済業務</t>
+        </is>
+      </c>
+      <c r="B22" s="527" t="n"/>
+      <c r="C22" s="527" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B4:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'ツールマスタ'!$A$17:$A$22</formula1>
+    </dataValidation>
+    <dataValidation sqref="C4:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'ツールマスタ'!$B$17:$B$22</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -47011,7 +48890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -47079,25 +48958,25 @@
       </c>
       <c r="B3" s="438" t="inlineStr">
         <is>
-          <t>貿易クラウド_利用料</t>
+          <t>AI Works_保守・サポート</t>
         </is>
       </c>
       <c r="C3" s="439" t="inlineStr">
         <is>
-          <t>DL06-0000792-001</t>
+          <t>DL07-0001726</t>
         </is>
       </c>
       <c r="D3" s="440" t="n"/>
       <c r="E3" s="438" t="inlineStr">
         <is>
-          <t>貿易001</t>
+          <t>AIWorks005</t>
         </is>
       </c>
       <c r="F3" s="514" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G3" s="514" t="n">
         <v>600000</v>
-      </c>
-      <c r="G3" s="514" t="n">
-        <v>3000000</v>
       </c>
       <c r="H3" s="438" t="inlineStr">
         <is>
@@ -47113,25 +48992,25 @@
       </c>
       <c r="B4" s="438" t="inlineStr">
         <is>
-          <t>カンリル_利用料</t>
+          <t>貿易クラウド_利用料</t>
         </is>
       </c>
       <c r="C4" s="439" t="inlineStr">
         <is>
-          <t>DL06-0029228-001</t>
+          <t>DL06-0000792-001</t>
         </is>
       </c>
       <c r="D4" s="440" t="n"/>
       <c r="E4" s="438" t="inlineStr">
         <is>
-          <t>カンリル001</t>
+          <t>貿易001</t>
         </is>
       </c>
       <c r="F4" s="514" t="n">
-        <v>32509</v>
+        <v>600000</v>
       </c>
       <c r="G4" s="514" t="n">
-        <v>325091</v>
+        <v>3000000</v>
       </c>
       <c r="H4" s="442" t="inlineStr">
         <is>
@@ -47147,25 +49026,25 @@
       </c>
       <c r="B5" s="438" t="inlineStr">
         <is>
-          <t>社長メシ_スタンダードプラン</t>
+          <t>AI Works_利用料</t>
         </is>
       </c>
       <c r="C5" s="439" t="inlineStr">
         <is>
-          <t>DL06-0029652-001</t>
+          <t>DL06-0001191-001</t>
         </is>
       </c>
       <c r="D5" s="440" t="n"/>
       <c r="E5" s="438" t="inlineStr">
         <is>
-          <t>社長メシ001</t>
+          <t>AIWorks001</t>
         </is>
       </c>
       <c r="F5" s="514" t="n">
-        <v>1500000</v>
+        <v>120000</v>
       </c>
       <c r="G5" s="514" t="n">
-        <v>1500000</v>
+        <v>360000</v>
       </c>
       <c r="H5" s="438" t="inlineStr">
         <is>
@@ -47181,25 +49060,25 @@
       </c>
       <c r="B6" s="438" t="inlineStr">
         <is>
-          <t>せきなび_スタンダード</t>
+          <t>カンリル_初期設定</t>
         </is>
       </c>
       <c r="C6" s="439" t="inlineStr">
         <is>
-          <t>DL06-0002760-001</t>
+          <t>DL07-0001738</t>
         </is>
       </c>
       <c r="D6" s="440" t="n"/>
       <c r="E6" s="438" t="inlineStr">
         <is>
-          <t>seknavi01</t>
+          <t>カンリル002</t>
         </is>
       </c>
       <c r="F6" s="514" t="n">
-        <v>300000</v>
+        <v>50000</v>
       </c>
       <c r="G6" s="514" t="n">
-        <v>360000</v>
+        <v>150000</v>
       </c>
       <c r="H6" s="442" t="inlineStr">
         <is>
@@ -47215,25 +49094,25 @@
       </c>
       <c r="B7" s="438" t="inlineStr">
         <is>
-          <t>カンリル_導入・活用コンサルティング</t>
+          <t>カンリル_保守サポート</t>
         </is>
       </c>
       <c r="C7" s="439" t="inlineStr">
         <is>
-          <t>DL07-0001708</t>
+          <t>DL07-0001733</t>
         </is>
       </c>
       <c r="D7" s="440" t="n"/>
       <c r="E7" s="438" t="inlineStr">
         <is>
-          <t>カンリル003</t>
+          <t>カンリル004</t>
         </is>
       </c>
       <c r="F7" s="514" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="G7" s="514" t="n">
-        <v>150000</v>
+        <v>125000</v>
       </c>
       <c r="H7" s="438" t="inlineStr">
         <is>
@@ -47249,25 +49128,25 @@
       </c>
       <c r="B8" s="438" t="inlineStr">
         <is>
-          <t>カンリル_初期設定</t>
+          <t>カンリル_利用料</t>
         </is>
       </c>
       <c r="C8" s="439" t="inlineStr">
         <is>
-          <t>DL07-0001738</t>
+          <t>DL06-0029228-001</t>
         </is>
       </c>
       <c r="D8" s="440" t="n"/>
       <c r="E8" s="438" t="inlineStr">
         <is>
-          <t>カンリル002</t>
+          <t>カンリル001</t>
         </is>
       </c>
       <c r="F8" s="514" t="n">
-        <v>50000</v>
+        <v>32509</v>
       </c>
       <c r="G8" s="514" t="n">
-        <v>150000</v>
+        <v>325091</v>
       </c>
       <c r="H8" s="442" t="inlineStr">
         <is>
@@ -47283,25 +49162,25 @@
       </c>
       <c r="B9" s="438" t="inlineStr">
         <is>
-          <t>Scale人事評価_スタンダードプラン</t>
+          <t>カンリル_導入・活用コンサルティング</t>
         </is>
       </c>
       <c r="C9" s="439" t="inlineStr">
         <is>
-          <t>DL07-0002412</t>
+          <t>DL07-0001708</t>
         </is>
       </c>
       <c r="D9" s="440" t="n"/>
       <c r="E9" s="438" t="inlineStr">
         <is>
-          <t>Scale001</t>
+          <t>カンリル003</t>
         </is>
       </c>
       <c r="F9" s="514" t="n">
-        <v>1920</v>
+        <v>20000</v>
       </c>
       <c r="G9" s="514" t="n">
-        <v>12000</v>
+        <v>150000</v>
       </c>
       <c r="H9" s="438" t="inlineStr">
         <is>
@@ -47317,25 +49196,25 @@
       </c>
       <c r="B10" s="438" t="inlineStr">
         <is>
-          <t>AI Works_保守・サポート</t>
+          <t>社長メシ_スタンダードプラン</t>
         </is>
       </c>
       <c r="C10" s="439" t="inlineStr">
         <is>
-          <t>DL07-0001726</t>
+          <t>DL06-0029652-001</t>
         </is>
       </c>
       <c r="D10" s="440" t="n"/>
       <c r="E10" s="438" t="inlineStr">
         <is>
-          <t>AIWorks005</t>
+          <t>社長メシ001</t>
         </is>
       </c>
       <c r="F10" s="514" t="n">
-        <v>120000</v>
+        <v>1500000</v>
       </c>
       <c r="G10" s="514" t="n">
-        <v>600000</v>
+        <v>1500000</v>
       </c>
       <c r="H10" s="442" t="inlineStr">
         <is>
@@ -47351,25 +49230,25 @@
       </c>
       <c r="B11" s="438" t="inlineStr">
         <is>
-          <t>AI Works_利用料</t>
+          <t>Scale人事評価_スタンダードプラン</t>
         </is>
       </c>
       <c r="C11" s="439" t="inlineStr">
         <is>
-          <t>DL06-0001191-001</t>
+          <t>DL07-0002412</t>
         </is>
       </c>
       <c r="D11" s="440" t="n"/>
       <c r="E11" s="438" t="inlineStr">
         <is>
-          <t>AIWorks001</t>
+          <t>Scale001</t>
         </is>
       </c>
       <c r="F11" s="514" t="n">
-        <v>120000</v>
+        <v>1920</v>
       </c>
       <c r="G11" s="514" t="n">
-        <v>360000</v>
+        <v>12000</v>
       </c>
       <c r="H11" s="438" t="inlineStr">
         <is>
@@ -47385,25 +49264,25 @@
       </c>
       <c r="B12" s="438" t="inlineStr">
         <is>
-          <t>カンリル_保守サポート</t>
+          <t>せきなび_スタンダード</t>
         </is>
       </c>
       <c r="C12" s="439" t="inlineStr">
         <is>
-          <t>DL07-0001733</t>
+          <t>DL06-0002760-001</t>
         </is>
       </c>
       <c r="D12" s="440" t="n"/>
       <c r="E12" s="438" t="inlineStr">
         <is>
-          <t>カンリル004</t>
+          <t>seknavi01</t>
         </is>
       </c>
       <c r="F12" s="514" t="n">
-        <v>60000</v>
+        <v>300000</v>
       </c>
       <c r="G12" s="514" t="n">
-        <v>125000</v>
+        <v>360000</v>
       </c>
       <c r="H12" s="442" t="inlineStr">
         <is>
@@ -47419,25 +49298,25 @@
       </c>
       <c r="B13" s="438" t="inlineStr">
         <is>
-          <t>freee会計_スタータープラン</t>
+          <t>Scale人事評価スタンダードプラン_初期設定</t>
         </is>
       </c>
       <c r="C13" s="439" t="inlineStr">
         <is>
-          <t>DL07-0007357</t>
+          <t>DL07-0020657</t>
         </is>
       </c>
       <c r="D13" s="440" t="n"/>
       <c r="E13" s="438" t="inlineStr">
         <is>
-          <t>freee会計001</t>
+          <t>Scale002</t>
         </is>
       </c>
       <c r="F13" s="514" t="n">
-        <v>65760</v>
+        <v>80000</v>
       </c>
       <c r="G13" s="514" t="n">
-        <v>65760</v>
+        <v>160000</v>
       </c>
       <c r="H13" s="438" t="inlineStr">
         <is>
@@ -47453,25 +49332,25 @@
       </c>
       <c r="B14" s="438" t="inlineStr">
         <is>
-          <t>Scale人事評価スタンダードプラン_初期設定</t>
+          <t>Scale人事評価スタンダードプラン_保守サポート</t>
         </is>
       </c>
       <c r="C14" s="439" t="inlineStr">
         <is>
-          <t>DL07-0020657</t>
+          <t>DL07-0020660</t>
         </is>
       </c>
       <c r="D14" s="440" t="n"/>
       <c r="E14" s="438" t="inlineStr">
         <is>
-          <t>Scale002</t>
+          <t>Scale004</t>
         </is>
       </c>
       <c r="F14" s="514" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="G14" s="514" t="n">
-        <v>160000</v>
+        <v>480000</v>
       </c>
       <c r="H14" s="442" t="inlineStr">
         <is>
@@ -47487,25 +49366,25 @@
       </c>
       <c r="B15" s="438" t="inlineStr">
         <is>
-          <t>AI Works_初期設定</t>
+          <t>配車頭_利用料</t>
         </is>
       </c>
       <c r="C15" s="439" t="inlineStr">
         <is>
-          <t>DL07-0003894</t>
+          <t>DL07-0032513</t>
         </is>
       </c>
       <c r="D15" s="440" t="n"/>
       <c r="E15" s="438" t="inlineStr">
         <is>
-          <t>AIWorks003</t>
+          <t>配車頭01</t>
         </is>
       </c>
       <c r="F15" s="514" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G15" s="514" t="n">
-        <v>200000</v>
+        <v>240000</v>
       </c>
       <c r="H15" s="438" t="inlineStr">
         <is>
@@ -47521,22 +49400,26 @@
       </c>
       <c r="B16" s="438" t="inlineStr">
         <is>
-          <t>PCセキュリティみまもりパック</t>
+          <t>BENRINEKO_営業管理システム</t>
         </is>
       </c>
       <c r="C16" s="439" t="inlineStr">
         <is>
-          <t>DL07-0002804</t>
+          <t>DL07-0032695</t>
         </is>
       </c>
       <c r="D16" s="440" t="n"/>
       <c r="E16" s="438" t="inlineStr">
         <is>
-          <t>pcsecurity</t>
-        </is>
-      </c>
-      <c r="F16" s="514" t="n"/>
-      <c r="G16" s="514" t="n"/>
+          <t>BENRINEKO_01</t>
+        </is>
+      </c>
+      <c r="F16" s="514" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G16" s="514" t="n">
+        <v>1500000</v>
+      </c>
       <c r="H16" s="442" t="inlineStr">
         <is>
           <t>AI Works_利用料_保守・サポート</t>
@@ -47551,25 +49434,25 @@
       </c>
       <c r="B17" s="438" t="inlineStr">
         <is>
-          <t>Scale人事評価_導入・活用コンサルティング</t>
+          <t>AI Works_初期設定</t>
         </is>
       </c>
       <c r="C17" s="439" t="inlineStr">
         <is>
-          <t>DL07-0020659</t>
+          <t>DL07-0003894</t>
         </is>
       </c>
       <c r="D17" s="440" t="n"/>
       <c r="E17" s="438" t="inlineStr">
         <is>
-          <t>Scale003</t>
+          <t>AIWorks003</t>
         </is>
       </c>
       <c r="F17" s="514" t="n">
-        <v>300000</v>
+        <v>10000</v>
       </c>
       <c r="G17" s="514" t="n">
-        <v>900000</v>
+        <v>200000</v>
       </c>
       <c r="H17" s="438" t="inlineStr">
         <is>
@@ -47585,25 +49468,25 @@
       </c>
       <c r="B18" s="438" t="inlineStr">
         <is>
-          <t>AI Works_導入活用コンサルティング</t>
+          <t>Arole_利用料</t>
         </is>
       </c>
       <c r="C18" s="439" t="inlineStr">
         <is>
-          <t>DL07-0003887</t>
+          <t>DL07-0034331</t>
         </is>
       </c>
       <c r="D18" s="440" t="n"/>
       <c r="E18" s="438" t="inlineStr">
         <is>
-          <t>AIWorks002</t>
+          <t>ar001</t>
         </is>
       </c>
       <c r="F18" s="514" t="n">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="G18" s="514" t="n">
-        <v>450000</v>
+        <v>2640000</v>
       </c>
       <c r="H18" s="442" t="inlineStr">
         <is>
@@ -47619,25 +49502,25 @@
       </c>
       <c r="B19" s="438" t="inlineStr">
         <is>
-          <t>Scale人事評価スタンダードプラン_保守サポート</t>
+          <t>AI Works_導入活用コンサルティング</t>
         </is>
       </c>
       <c r="C19" s="439" t="inlineStr">
         <is>
-          <t>DL07-0020660</t>
+          <t>DL07-0003887</t>
         </is>
       </c>
       <c r="D19" s="440" t="n"/>
       <c r="E19" s="438" t="inlineStr">
         <is>
-          <t>Scale004</t>
+          <t>AIWorks002</t>
         </is>
       </c>
       <c r="F19" s="514" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="G19" s="514" t="n">
-        <v>480000</v>
+        <v>450000</v>
       </c>
       <c r="H19" s="438" t="inlineStr">
         <is>
@@ -47648,30 +49531,30 @@
     <row r="20">
       <c r="A20" s="437" t="inlineStr">
         <is>
-          <t>クラフトバンク</t>
+          <t>カラフルボックスコンソーシアム</t>
         </is>
       </c>
       <c r="B20" s="438" t="inlineStr">
         <is>
-          <t>クラフトバンクオフィス プロフェッショナルプラン</t>
+          <t>Scale人事評価_導入・活用コンサルティング</t>
         </is>
       </c>
       <c r="C20" s="439" t="inlineStr">
         <is>
-          <t>DL04-0029552-004</t>
+          <t>DL07-0020659</t>
         </is>
       </c>
       <c r="D20" s="440" t="n"/>
       <c r="E20" s="438" t="inlineStr">
         <is>
-          <t>クラフトバンクオフィス プロフェッショナルプラン</t>
+          <t>Scale003</t>
         </is>
       </c>
       <c r="F20" s="514" t="n">
-        <v>1080000</v>
+        <v>300000</v>
       </c>
       <c r="G20" s="514" t="n">
-        <v>2160000</v>
+        <v>900000</v>
       </c>
       <c r="H20" s="442" t="inlineStr">
         <is>
@@ -47682,30 +49565,30 @@
     <row r="21">
       <c r="A21" s="437" t="inlineStr">
         <is>
-          <t>クラフトバンク</t>
+          <t>カラフルボックスコンソーシアム</t>
         </is>
       </c>
       <c r="B21" s="438" t="inlineStr">
         <is>
-          <t>クラフトバンクオフィス エンタープライズプラン</t>
+          <t>freee会計_スタータープラン</t>
         </is>
       </c>
       <c r="C21" s="439" t="inlineStr">
         <is>
-          <t>DL04-0029554-004</t>
+          <t>DL07-0007357</t>
         </is>
       </c>
       <c r="D21" s="440" t="n"/>
       <c r="E21" s="438" t="inlineStr">
         <is>
-          <t>クラフトバンクオフィス エンタープライズプラン</t>
+          <t>freee会計001</t>
         </is>
       </c>
       <c r="F21" s="514" t="n">
-        <v>1350000</v>
+        <v>65760</v>
       </c>
       <c r="G21" s="514" t="n">
-        <v>2700000</v>
+        <v>65760</v>
       </c>
       <c r="H21" s="438" t="inlineStr">
         <is>
@@ -47716,31 +49599,27 @@
     <row r="22">
       <c r="A22" s="437" t="inlineStr">
         <is>
-          <t>クラフトバンク</t>
+          <t>カラフルボックスコンソーシアム</t>
         </is>
       </c>
       <c r="B22" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
+          <t>PCセキュリティみまもりパック</t>
         </is>
       </c>
       <c r="C22" s="439" t="inlineStr">
         <is>
-          <t>DL07-0000180</t>
+          <t>DL07-0002804</t>
         </is>
       </c>
       <c r="D22" s="440" t="n"/>
       <c r="E22" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
-        </is>
-      </c>
-      <c r="F22" s="514" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G22" s="514" t="n">
-        <v>1205000</v>
-      </c>
+          <t>pcsecurity</t>
+        </is>
+      </c>
+      <c r="F22" s="514" t="n"/>
+      <c r="G22" s="514" t="n"/>
       <c r="H22" s="442" t="inlineStr">
         <is>
           <t>Lステップ_プロプラン</t>
@@ -47755,25 +49634,25 @@
       </c>
       <c r="B23" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）</t>
+          <t>クラフトバンクオフィス プロフェッショナルプラン</t>
         </is>
       </c>
       <c r="C23" s="439" t="inlineStr">
         <is>
-          <t>DL07-0000059</t>
+          <t>DL04-0029552-004</t>
         </is>
       </c>
       <c r="D23" s="440" t="n"/>
       <c r="E23" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）</t>
+          <t>クラフトバンクオフィス プロフェッショナルプラン</t>
         </is>
       </c>
       <c r="F23" s="514" t="n">
-        <v>800000</v>
+        <v>1080000</v>
       </c>
       <c r="G23" s="514" t="n">
-        <v>1600000</v>
+        <v>2160000</v>
       </c>
       <c r="H23" s="438" t="inlineStr">
         <is>
@@ -47789,25 +49668,25 @@
       </c>
       <c r="B24" s="438" t="inlineStr">
         <is>
-          <t>クラフトバンクオフィス スタンダードプラン</t>
+          <t>クラフトバンクオフィス エンタープライズプラン</t>
         </is>
       </c>
       <c r="C24" s="439" t="inlineStr">
         <is>
-          <t>DL04-0029553-003</t>
+          <t>DL04-0029554-004</t>
         </is>
       </c>
       <c r="D24" s="440" t="n"/>
       <c r="E24" s="438" t="inlineStr">
         <is>
-          <t>クラフトバンクオフィス スタンダードプラン</t>
+          <t>クラフトバンクオフィス エンタープライズプラン</t>
         </is>
       </c>
       <c r="F24" s="514" t="n">
-        <v>600000</v>
+        <v>1350000</v>
       </c>
       <c r="G24" s="514" t="n">
-        <v>1200000</v>
+        <v>2700000</v>
       </c>
       <c r="H24" s="442" t="inlineStr">
         <is>
@@ -47823,25 +49702,25 @@
       </c>
       <c r="B25" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="C25" s="439" t="inlineStr">
         <is>
-          <t>DL07-0000025</t>
+          <t>DL07-0000180</t>
         </is>
       </c>
       <c r="D25" s="440" t="n"/>
       <c r="E25" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="F25" s="514" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="G25" s="514" t="n">
-        <v>800000</v>
+        <v>1205000</v>
       </c>
       <c r="H25" s="438" t="inlineStr">
         <is>
@@ -47857,25 +49736,25 @@
       </c>
       <c r="B26" s="438" t="inlineStr">
         <is>
-          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）</t>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="C26" s="439" t="inlineStr">
         <is>
-          <t>DL07-0000070</t>
+          <t>DL07-0000059</t>
         </is>
       </c>
       <c r="D26" s="440" t="n"/>
       <c r="E26" s="438" t="inlineStr">
         <is>
-          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）</t>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="F26" s="514" t="n">
-        <v>1200000</v>
+        <v>800000</v>
       </c>
       <c r="G26" s="514" t="n">
-        <v>1800000</v>
+        <v>1600000</v>
       </c>
       <c r="H26" s="442" t="inlineStr">
         <is>
@@ -47891,18 +49770,18 @@
       </c>
       <c r="B27" s="438" t="inlineStr">
         <is>
-          <t>初期設定（クラフトバンクオフィス スタンダードプラン）</t>
+          <t>クラフトバンクオフィス スタンダードプラン</t>
         </is>
       </c>
       <c r="C27" s="439" t="inlineStr">
         <is>
-          <t>DL07-0000036</t>
+          <t>DL04-0029553-003</t>
         </is>
       </c>
       <c r="D27" s="440" t="n"/>
       <c r="E27" s="438" t="inlineStr">
         <is>
-          <t>初期設定（クラフトバンクオフィス スタンダードプラン）</t>
+          <t>クラフトバンクオフィス スタンダードプラン</t>
         </is>
       </c>
       <c r="F27" s="514" t="n">
@@ -47925,25 +49804,25 @@
       </c>
       <c r="B28" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス プロフェッショナルプラン</t>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="C28" s="439" t="inlineStr">
         <is>
-          <t>DL07-0001646</t>
+          <t>DL07-0000025</t>
         </is>
       </c>
       <c r="D28" s="440" t="n"/>
       <c r="E28" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス プロフェッショナルプラン</t>
+          <t>導入コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="F28" s="514" t="n">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="G28" s="514" t="n">
-        <v>1805000</v>
+        <v>800000</v>
       </c>
       <c r="H28" s="442" t="inlineStr">
         <is>
@@ -47959,666 +49838,986 @@
       </c>
       <c r="B29" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング活用コンサルティング（プロフェッショナルプラン）</t>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="C29" s="439" t="inlineStr">
         <is>
-          <t>DL07-0004098</t>
+          <t>DL07-0000070</t>
         </is>
       </c>
       <c r="D29" s="440" t="n"/>
       <c r="E29" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング活用コンサルティング（プロフェッショナルプラン）</t>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="F29" s="514" t="n">
-        <v>1000000</v>
+        <v>1200000</v>
       </c>
       <c r="G29" s="514" t="n">
-        <v>1920000</v>
+        <v>1800000</v>
       </c>
       <c r="H29" s="450" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="437" t="inlineStr">
         <is>
-          <t>ピスケス</t>
+          <t>クラフトバンク</t>
         </is>
       </c>
       <c r="B30" s="438" t="inlineStr">
         <is>
-          <t>着信ポップアップCTI</t>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="C30" s="439" t="inlineStr">
         <is>
-          <t>DL06-0034655-001</t>
+          <t>DL07-0000036</t>
         </is>
       </c>
       <c r="D30" s="440" t="n"/>
       <c r="E30" s="438" t="inlineStr">
         <is>
-          <t>PSA003</t>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="F30" s="514" t="n">
-        <v>108000</v>
+        <v>600000</v>
       </c>
       <c r="G30" s="514" t="n">
-        <v>120000</v>
+        <v>1200000</v>
       </c>
       <c r="H30" s="450" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="437" t="inlineStr">
         <is>
-          <t>ピスケス</t>
+          <t>クラフトバンク</t>
         </is>
       </c>
       <c r="B31" s="438" t="inlineStr">
         <is>
-          <t>LINEコネクト</t>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス プロフェッショナルプラン</t>
         </is>
       </c>
       <c r="C31" s="439" t="inlineStr">
         <is>
-          <t>DL06-0033682-001</t>
+          <t>DL07-0001646</t>
         </is>
       </c>
       <c r="D31" s="440" t="n"/>
       <c r="E31" s="438" t="inlineStr">
         <is>
-          <t>PLINE</t>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス プロフェッショナルプラン</t>
         </is>
       </c>
       <c r="F31" s="514" t="n">
-        <v>64000</v>
+        <v>1000000</v>
       </c>
       <c r="G31" s="514" t="n">
-        <v>80000</v>
+        <v>1805000</v>
       </c>
       <c r="H31" s="450" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="437" t="inlineStr">
         <is>
-          <t>ピスケス</t>
+          <t>クラフトバンク</t>
         </is>
       </c>
       <c r="B32" s="438" t="inlineStr">
         <is>
-          <t>ピスケスアポ</t>
+          <t>導入コンサルティング活用コンサルティング（プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="C32" s="439" t="inlineStr">
         <is>
-          <t>DL05-0024072-002</t>
+          <t>DL07-0004098</t>
         </is>
       </c>
       <c r="D32" s="440" t="n"/>
       <c r="E32" s="438" t="inlineStr">
         <is>
-          <t>piscesapo2024</t>
+          <t>導入コンサルティング活用コンサルティング（プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="F32" s="514" t="n">
-        <v>408000</v>
+        <v>1000000</v>
       </c>
       <c r="G32" s="514" t="n">
-        <v>480000</v>
+        <v>1920000</v>
       </c>
       <c r="H32" s="385" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="437" t="inlineStr">
         <is>
-          <t>ピスケス</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B33" s="438" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>★導入コンサルティング活用コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="C33" s="439" t="inlineStr">
         <is>
-          <t>DL06-0034634-001</t>
+          <t>DL07-0001647</t>
         </is>
       </c>
       <c r="D33" s="440" t="n"/>
       <c r="E33" s="438" t="inlineStr">
         <is>
-          <t>PKA002</t>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="F33" s="514" t="n">
-        <v>64000</v>
+        <v>600000</v>
       </c>
       <c r="G33" s="514" t="n">
-        <v>80000</v>
+        <v>1205000</v>
       </c>
       <c r="H33" s="385" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B34" s="438" t="inlineStr">
         <is>
-          <t>irohana study スモール</t>
+          <t>★導入コンサルティング活用コンサルティング（クラフトバンクオフィス プロフェッショナルプラン</t>
         </is>
       </c>
       <c r="C34" s="439" t="inlineStr">
         <is>
-          <t>DL07-0024780</t>
+          <t>DL07-0001648</t>
         </is>
       </c>
       <c r="D34" s="440" t="n"/>
       <c r="E34" s="438" t="inlineStr">
         <is>
-          <t>study_s</t>
+          <t>導入コンサルティング活用コンサルティング（クラフトバンクオフィス プロフェッショナルプラン</t>
         </is>
       </c>
       <c r="F34" s="514" t="n">
-        <v>237600</v>
+        <v>1000000</v>
       </c>
       <c r="G34" s="514" t="n">
-        <v>357600</v>
+        <v>1805000</v>
       </c>
       <c r="H34" s="385" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B35" s="438" t="inlineStr">
         <is>
-          <t>irohana visa スモール</t>
+          <t>★初期設定（クラフトバンクオフィス プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="C35" s="439" t="inlineStr">
         <is>
-          <t>DL07-0014825</t>
+          <t>DL07-0000075</t>
         </is>
       </c>
       <c r="D35" s="440" t="n"/>
       <c r="E35" s="438" t="inlineStr">
         <is>
-          <t>visa_s</t>
+          <t>初期設定（クラフトバンクオフィス プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="F35" s="514" t="n">
-        <v>357600</v>
+        <v>1200000</v>
       </c>
       <c r="G35" s="514" t="n">
-        <v>357600</v>
+        <v>1800000</v>
       </c>
       <c r="H35" s="385" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B36" s="438" t="inlineStr">
         <is>
-          <t>irohana study スタンダード</t>
+          <t>★初期設定（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="C36" s="439" t="inlineStr">
         <is>
-          <t>DL07-0024781</t>
+          <t>DL07-0000044</t>
         </is>
       </c>
       <c r="D36" s="440" t="n"/>
       <c r="E36" s="438" t="inlineStr">
         <is>
-          <t>study_m</t>
+          <t>初期設定（クラフトバンクオフィス スタンダードプラン）</t>
         </is>
       </c>
       <c r="F36" s="514" t="n">
-        <v>357600</v>
+        <v>600000</v>
       </c>
       <c r="G36" s="514" t="n">
-        <v>477600</v>
+        <v>1200000</v>
       </c>
       <c r="H36" s="385" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B37" s="438" t="inlineStr">
         <is>
-          <t>irohana 導入コンサルティング等</t>
+          <t>★クラフトバンクオフィススタンダードプラン</t>
         </is>
       </c>
       <c r="C37" s="439" t="inlineStr">
         <is>
-          <t>DL07-0019039</t>
+          <t>DL06-0013205-001</t>
         </is>
       </c>
       <c r="D37" s="440" t="n"/>
       <c r="E37" s="438" t="inlineStr">
         <is>
-          <t>導入コンサルティング等</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F37" s="514" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G37" s="514" t="n">
-        <v>200000</v>
+        <v>1200000</v>
       </c>
       <c r="H37" s="385" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B38" s="438" t="inlineStr">
         <is>
-          <t>irohana visa ラージ</t>
+          <t>★導入コンサルティング活用コンサルティング（スタンダードプラン）</t>
         </is>
       </c>
       <c r="C38" s="439" t="inlineStr">
         <is>
-          <t>DL07-0019031</t>
+          <t>DL07-0004102</t>
         </is>
       </c>
       <c r="D38" s="440" t="n"/>
       <c r="E38" s="438" t="inlineStr">
         <is>
-          <t>visa_l</t>
+          <t>導入コンサルティング活用コンサルティング（スタンダードプラン）</t>
         </is>
       </c>
       <c r="F38" s="514" t="n">
-        <v>597600</v>
+        <v>600000</v>
       </c>
       <c r="G38" s="514" t="n">
-        <v>597600</v>
+        <v>1610000</v>
       </c>
       <c r="H38" s="385" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B39" s="438" t="inlineStr">
         <is>
-          <t>irohana visa スモール導入設定等</t>
+          <t>★導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="C39" s="439" t="inlineStr">
         <is>
-          <t>DL07-0019034</t>
+          <t>DL07-0000073</t>
         </is>
       </c>
       <c r="D39" s="440" t="n"/>
       <c r="E39" s="438" t="inlineStr">
         <is>
-          <t>導入設定等_visa_s</t>
+          <t>導入コンサルティング（クラフトバンクオフィス プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="F39" s="514" t="n">
-        <v>50000</v>
+        <v>800000</v>
       </c>
       <c r="G39" s="514" t="n">
-        <v>150000</v>
+        <v>1600000</v>
       </c>
       <c r="H39" s="385" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B40" s="438" t="inlineStr">
         <is>
-          <t>irohana visa ラージ導入設定等</t>
+          <t>★導入コンサルティング（クラフトバンクオフィススタンダードプラン）</t>
         </is>
       </c>
       <c r="C40" s="439" t="inlineStr">
         <is>
-          <t>DL07-0020470</t>
+          <t>DL07-0000042</t>
         </is>
       </c>
       <c r="D40" s="440" t="n"/>
       <c r="E40" s="438" t="inlineStr">
         <is>
-          <t>導入設定等_visa_l</t>
+          <t>導入コンサルティング（クラフトバンクオフィススタンダードプラン）</t>
         </is>
       </c>
       <c r="F40" s="514" t="n">
-        <v>50000</v>
+        <v>400000</v>
       </c>
       <c r="G40" s="514" t="n">
-        <v>150000</v>
+        <v>800000</v>
       </c>
       <c r="H40" s="385" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B41" s="438" t="inlineStr">
         <is>
-          <t>irohana study ラージ</t>
+          <t>★クラフトバンクオフィス プロフェッショナルプラン</t>
         </is>
       </c>
       <c r="C41" s="439" t="inlineStr">
         <is>
-          <t>DL07-0027397</t>
+          <t>DL06-0024445-001</t>
         </is>
       </c>
       <c r="D41" s="440" t="n"/>
       <c r="E41" s="438" t="inlineStr">
         <is>
-          <t>study_l</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F41" s="514" t="n">
-        <v>657600</v>
+        <v>1080000</v>
       </c>
       <c r="G41" s="514" t="n">
-        <v>777600</v>
+        <v>2160000</v>
       </c>
       <c r="H41" s="385" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B42" s="438" t="inlineStr">
         <is>
-          <t>irohana visa スタンダード導入設定等</t>
+          <t>★クラフトバンクオフィス エンタープライズプラン</t>
         </is>
       </c>
       <c r="C42" s="439" t="inlineStr">
         <is>
-          <t>DL07-0020466</t>
+          <t>DL06-0024554-001</t>
         </is>
       </c>
       <c r="D42" s="440" t="n"/>
       <c r="E42" s="438" t="inlineStr">
         <is>
-          <t>導入設定等_visa_m</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F42" s="514" t="n">
-        <v>50000</v>
+        <v>1350000</v>
       </c>
       <c r="G42" s="514" t="n">
-        <v>150000</v>
+        <v>2700000</v>
       </c>
       <c r="H42" s="385" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>クラフトバンクコンソーシアム</t>
         </is>
       </c>
       <c r="B43" s="438" t="inlineStr">
         <is>
-          <t>irohana visa スタンダード</t>
+          <t>★導入コンサルティング活用コンサルティング（プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="C43" s="439" t="inlineStr">
         <is>
-          <t>DL07-0019029</t>
+          <t>DL07-0004103</t>
         </is>
       </c>
       <c r="D43" s="440" t="n"/>
       <c r="E43" s="438" t="inlineStr">
         <is>
-          <t>visa_m</t>
+          <t>導入コンサルティング活用コンサルティング（プロフェッショナルプラン）</t>
         </is>
       </c>
       <c r="F43" s="514" t="n">
-        <v>477600</v>
+        <v>1000000</v>
       </c>
       <c r="G43" s="514" t="n">
-        <v>477600</v>
+        <v>1920000</v>
       </c>
       <c r="H43" s="385" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>ピスケス</t>
         </is>
       </c>
       <c r="B44" s="438" t="inlineStr">
         <is>
-          <t>irohana study スタンダード導入設定等</t>
+          <t>着信ポップアップCTI</t>
         </is>
       </c>
       <c r="C44" s="439" t="inlineStr">
         <is>
-          <t>DL07-0028061</t>
+          <t>DL06-0034655-001</t>
         </is>
       </c>
       <c r="D44" s="440" t="n"/>
       <c r="E44" s="438" t="inlineStr">
         <is>
-          <t>導入設定等_study_m</t>
+          <t>PSA003</t>
         </is>
       </c>
       <c r="F44" s="514" t="n">
-        <v>50000</v>
+        <v>108000</v>
       </c>
       <c r="G44" s="514" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="H44" s="385" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="437" t="inlineStr">
         <is>
-          <t>いろはな</t>
+          <t>ピスケス</t>
         </is>
       </c>
       <c r="B45" s="438" t="inlineStr">
         <is>
-          <t>irohana study スモール導入設定等</t>
+          <t>LINEコネクト</t>
         </is>
       </c>
       <c r="C45" s="439" t="inlineStr">
         <is>
-          <t>DL07-0028059</t>
+          <t>DL06-0033682-001</t>
         </is>
       </c>
       <c r="D45" s="440" t="n"/>
       <c r="E45" s="438" t="inlineStr">
         <is>
+          <t>PLINE</t>
+        </is>
+      </c>
+      <c r="F45" s="514" t="n">
+        <v>64000</v>
+      </c>
+      <c r="G45" s="514" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H45" s="385" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="437" t="inlineStr">
+        <is>
+          <t>ピスケス</t>
+        </is>
+      </c>
+      <c r="B46" s="438" t="inlineStr">
+        <is>
+          <t>ピスケスアポ</t>
+        </is>
+      </c>
+      <c r="C46" s="439" t="inlineStr">
+        <is>
+          <t>DL05-0024072-002</t>
+        </is>
+      </c>
+      <c r="D46" s="440" t="n"/>
+      <c r="E46" s="438" t="inlineStr">
+        <is>
+          <t>piscesapo2024</t>
+        </is>
+      </c>
+      <c r="F46" s="514" t="n">
+        <v>408000</v>
+      </c>
+      <c r="G46" s="514" t="n">
+        <v>480000</v>
+      </c>
+      <c r="H46" s="385" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="437" t="inlineStr">
+        <is>
+          <t>ピスケス</t>
+        </is>
+      </c>
+      <c r="B47" s="438" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="C47" s="439" t="inlineStr">
+        <is>
+          <t>DL06-0034634-001</t>
+        </is>
+      </c>
+      <c r="D47" s="440" t="n"/>
+      <c r="E47" s="438" t="inlineStr">
+        <is>
+          <t>PKA002</t>
+        </is>
+      </c>
+      <c r="F47" s="514" t="n">
+        <v>64000</v>
+      </c>
+      <c r="G47" s="514" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H47" s="385" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B48" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa ラージ</t>
+        </is>
+      </c>
+      <c r="C48" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019031</t>
+        </is>
+      </c>
+      <c r="D48" s="440" t="n"/>
+      <c r="E48" s="438" t="inlineStr">
+        <is>
+          <t>visa_l</t>
+        </is>
+      </c>
+      <c r="F48" s="514" t="n">
+        <v>597600</v>
+      </c>
+      <c r="G48" s="514" t="n">
+        <v>597600</v>
+      </c>
+      <c r="H48" s="385" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B49" s="438" t="inlineStr">
+        <is>
+          <t>irohana match</t>
+        </is>
+      </c>
+      <c r="C49" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019032</t>
+        </is>
+      </c>
+      <c r="D49" s="440" t="n"/>
+      <c r="E49" s="438" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="F49" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="G49" s="514" t="n">
+        <v>477600</v>
+      </c>
+      <c r="H49" s="385" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B50" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa スモール</t>
+        </is>
+      </c>
+      <c r="C50" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0014825</t>
+        </is>
+      </c>
+      <c r="D50" s="440" t="n"/>
+      <c r="E50" s="438" t="inlineStr">
+        <is>
+          <t>visa_s</t>
+        </is>
+      </c>
+      <c r="F50" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="G50" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="H50" s="385" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B51" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa スタンダード</t>
+        </is>
+      </c>
+      <c r="C51" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019029</t>
+        </is>
+      </c>
+      <c r="D51" s="440" t="n"/>
+      <c r="E51" s="438" t="inlineStr">
+        <is>
+          <t>visa_m</t>
+        </is>
+      </c>
+      <c r="F51" s="514" t="n">
+        <v>477600</v>
+      </c>
+      <c r="G51" s="514" t="n">
+        <v>477600</v>
+      </c>
+      <c r="H51" s="385" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B52" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa ラージ導入設定等</t>
+        </is>
+      </c>
+      <c r="C52" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0020470</t>
+        </is>
+      </c>
+      <c r="D52" s="440" t="n"/>
+      <c r="E52" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_visa_l</t>
+        </is>
+      </c>
+      <c r="F52" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G52" s="514" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H52" s="385" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B53" s="438" t="inlineStr">
+        <is>
+          <t>irohana study スモール</t>
+        </is>
+      </c>
+      <c r="C53" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0024780</t>
+        </is>
+      </c>
+      <c r="D53" s="440" t="n"/>
+      <c r="E53" s="438" t="inlineStr">
+        <is>
+          <t>study_s</t>
+        </is>
+      </c>
+      <c r="F53" s="514" t="n">
+        <v>237600</v>
+      </c>
+      <c r="G53" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="H53" s="385" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B54" s="438" t="inlineStr">
+        <is>
+          <t>irohana 導入コンサルティング等</t>
+        </is>
+      </c>
+      <c r="C54" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019039</t>
+        </is>
+      </c>
+      <c r="D54" s="440" t="n"/>
+      <c r="E54" s="438" t="inlineStr">
+        <is>
+          <t>導入コンサルティング等</t>
+        </is>
+      </c>
+      <c r="F54" s="514" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G54" s="514" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H54" s="385" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B55" s="438" t="inlineStr">
+        <is>
+          <t>irohana match導入設定等</t>
+        </is>
+      </c>
+      <c r="C55" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0024779</t>
+        </is>
+      </c>
+      <c r="D55" s="440" t="n"/>
+      <c r="E55" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_match</t>
+        </is>
+      </c>
+      <c r="F55" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G55" s="514" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H55" s="385" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B56" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa スタンダード導入設定等</t>
+        </is>
+      </c>
+      <c r="C56" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0020466</t>
+        </is>
+      </c>
+      <c r="D56" s="440" t="n"/>
+      <c r="E56" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_visa_m</t>
+        </is>
+      </c>
+      <c r="F56" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G56" s="514" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H56" s="385" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B57" s="438" t="inlineStr">
+        <is>
+          <t>irohana visa スモール導入設定等</t>
+        </is>
+      </c>
+      <c r="C57" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0019034</t>
+        </is>
+      </c>
+      <c r="D57" s="440" t="n"/>
+      <c r="E57" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_visa_s</t>
+        </is>
+      </c>
+      <c r="F57" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G57" s="514" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H57" s="385" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B58" s="438" t="inlineStr">
+        <is>
+          <t>irohana study スモール導入設定等</t>
+        </is>
+      </c>
+      <c r="C58" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0028059</t>
+        </is>
+      </c>
+      <c r="D58" s="440" t="n"/>
+      <c r="E58" s="438" t="inlineStr">
+        <is>
           <t>導入設定等_study_s</t>
         </is>
       </c>
-      <c r="F45" s="514" t="n">
+      <c r="F58" s="514" t="n">
         <v>50000</v>
       </c>
-      <c r="G45" s="514" t="n">
+      <c r="G58" s="514" t="n">
         <v>150000</v>
       </c>
-      <c r="H45" s="385" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="385" t="n"/>
-      <c r="B46" s="385" t="n"/>
-      <c r="C46" s="385" t="n"/>
-      <c r="D46" s="385" t="n"/>
-      <c r="E46" s="385" t="n"/>
-      <c r="F46" s="520" t="n"/>
-      <c r="G46" s="520" t="n"/>
-      <c r="H46" s="385" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="385" t="n"/>
-      <c r="B47" s="385" t="n"/>
-      <c r="C47" s="385" t="n"/>
-      <c r="D47" s="385" t="n"/>
-      <c r="E47" s="385" t="n"/>
-      <c r="F47" s="520" t="n"/>
-      <c r="G47" s="520" t="n"/>
-      <c r="H47" s="385" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="385" t="n"/>
-      <c r="B48" s="385" t="n"/>
-      <c r="C48" s="385" t="n"/>
-      <c r="D48" s="385" t="n"/>
-      <c r="E48" s="385" t="n"/>
-      <c r="F48" s="520" t="n"/>
-      <c r="G48" s="520" t="n"/>
-      <c r="H48" s="385" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="385" t="n"/>
-      <c r="B49" s="385" t="n"/>
-      <c r="C49" s="385" t="n"/>
-      <c r="D49" s="385" t="n"/>
-      <c r="E49" s="385" t="n"/>
-      <c r="F49" s="520" t="n"/>
-      <c r="G49" s="520" t="n"/>
-      <c r="H49" s="385" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="385" t="n"/>
-      <c r="B50" s="385" t="n"/>
-      <c r="C50" s="385" t="n"/>
-      <c r="D50" s="385" t="n"/>
-      <c r="E50" s="385" t="n"/>
-      <c r="F50" s="520" t="n"/>
-      <c r="G50" s="520" t="n"/>
-      <c r="H50" s="385" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="385" t="n"/>
-      <c r="B51" s="385" t="n"/>
-      <c r="C51" s="385" t="n"/>
-      <c r="D51" s="385" t="n"/>
-      <c r="E51" s="385" t="n"/>
-      <c r="F51" s="520" t="n"/>
-      <c r="G51" s="520" t="n"/>
-      <c r="H51" s="385" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="385" t="n"/>
-      <c r="B52" s="385" t="n"/>
-      <c r="C52" s="385" t="n"/>
-      <c r="D52" s="385" t="n"/>
-      <c r="E52" s="385" t="n"/>
-      <c r="F52" s="520" t="n"/>
-      <c r="G52" s="520" t="n"/>
-      <c r="H52" s="385" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="385" t="n"/>
-      <c r="B53" s="385" t="n"/>
-      <c r="C53" s="385" t="n"/>
-      <c r="D53" s="385" t="n"/>
-      <c r="E53" s="385" t="n"/>
-      <c r="F53" s="520" t="n"/>
-      <c r="G53" s="520" t="n"/>
-      <c r="H53" s="385" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="385" t="n"/>
-      <c r="B54" s="385" t="n"/>
-      <c r="C54" s="385" t="n"/>
-      <c r="D54" s="385" t="n"/>
-      <c r="E54" s="385" t="n"/>
-      <c r="F54" s="520" t="n"/>
-      <c r="G54" s="520" t="n"/>
-      <c r="H54" s="385" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="385" t="n"/>
-      <c r="B55" s="385" t="n"/>
-      <c r="C55" s="385" t="n"/>
-      <c r="D55" s="385" t="n"/>
-      <c r="E55" s="385" t="n"/>
-      <c r="F55" s="520" t="n"/>
-      <c r="G55" s="520" t="n"/>
-      <c r="H55" s="385" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="385" t="n"/>
-      <c r="B56" s="385" t="n"/>
-      <c r="C56" s="385" t="n"/>
-      <c r="D56" s="385" t="n"/>
-      <c r="E56" s="385" t="n"/>
-      <c r="F56" s="520" t="n"/>
-      <c r="G56" s="520" t="n"/>
-      <c r="H56" s="385" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="385" t="n"/>
-      <c r="B57" s="385" t="n"/>
-      <c r="C57" s="385" t="n"/>
-      <c r="D57" s="385" t="n"/>
-      <c r="E57" s="385" t="n"/>
-      <c r="F57" s="520" t="n"/>
-      <c r="G57" s="520" t="n"/>
-      <c r="H57" s="385" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="385" t="n"/>
-      <c r="B58" s="385" t="n"/>
-      <c r="C58" s="385" t="n"/>
-      <c r="D58" s="385" t="n"/>
-      <c r="E58" s="385" t="n"/>
-      <c r="F58" s="520" t="n"/>
-      <c r="G58" s="520" t="n"/>
       <c r="H58" s="385" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="385" t="n"/>
-      <c r="B59" s="385" t="n"/>
-      <c r="C59" s="385" t="n"/>
-      <c r="D59" s="385" t="n"/>
-      <c r="E59" s="385" t="n"/>
-      <c r="F59" s="520" t="n"/>
-      <c r="G59" s="520" t="n"/>
+      <c r="A59" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B59" s="438" t="inlineStr">
+        <is>
+          <t>irohana study スタンダード導入設定等</t>
+        </is>
+      </c>
+      <c r="C59" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0028061</t>
+        </is>
+      </c>
+      <c r="D59" s="440" t="n"/>
+      <c r="E59" s="438" t="inlineStr">
+        <is>
+          <t>導入設定等_study_m</t>
+        </is>
+      </c>
+      <c r="F59" s="514" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G59" s="514" t="n">
+        <v>150000</v>
+      </c>
       <c r="H59" s="385" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="385" t="n"/>
-      <c r="B60" s="385" t="n"/>
-      <c r="C60" s="385" t="n"/>
-      <c r="D60" s="385" t="n"/>
-      <c r="E60" s="385" t="n"/>
-      <c r="F60" s="520" t="n"/>
-      <c r="G60" s="520" t="n"/>
+      <c r="A60" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B60" s="438" t="inlineStr">
+        <is>
+          <t>irohana study スタンダード</t>
+        </is>
+      </c>
+      <c r="C60" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0024781</t>
+        </is>
+      </c>
+      <c r="D60" s="440" t="n"/>
+      <c r="E60" s="438" t="inlineStr">
+        <is>
+          <t>study_m</t>
+        </is>
+      </c>
+      <c r="F60" s="514" t="n">
+        <v>357600</v>
+      </c>
+      <c r="G60" s="514" t="n">
+        <v>477600</v>
+      </c>
       <c r="H60" s="385" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="385" t="n"/>
-      <c r="B61" s="385" t="n"/>
-      <c r="C61" s="385" t="n"/>
-      <c r="D61" s="385" t="n"/>
-      <c r="E61" s="385" t="n"/>
-      <c r="F61" s="520" t="n"/>
-      <c r="G61" s="520" t="n"/>
+      <c r="A61" s="437" t="inlineStr">
+        <is>
+          <t>いろはな</t>
+        </is>
+      </c>
+      <c r="B61" s="438" t="inlineStr">
+        <is>
+          <t>irohana study ラージ</t>
+        </is>
+      </c>
+      <c r="C61" s="439" t="inlineStr">
+        <is>
+          <t>DL07-0027397</t>
+        </is>
+      </c>
+      <c r="D61" s="440" t="n"/>
+      <c r="E61" s="438" t="inlineStr">
+        <is>
+          <t>study_l</t>
+        </is>
+      </c>
+      <c r="F61" s="514" t="n">
+        <v>657600</v>
+      </c>
+      <c r="G61" s="514" t="n">
+        <v>777600</v>
+      </c>
       <c r="H61" s="385" t="n"/>
     </row>
     <row r="62">
@@ -58022,512 +60221,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C49"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="453" t="inlineStr">
-        <is>
-          <t>都道府県名</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="454" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="B2" s="454" t="inlineStr">
-        <is>
-          <t>北海道/1075円</t>
-        </is>
-      </c>
-      <c r="C2" s="348" t="inlineStr">
-        <is>
-          <t>A、農業林業</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="454" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="B3" s="454" t="inlineStr">
-        <is>
-          <t>青森/1029円</t>
-        </is>
-      </c>
-      <c r="C3" s="348" t="inlineStr">
-        <is>
-          <t>B、漁業</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="454" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="B4" s="454" t="inlineStr">
-        <is>
-          <t>岩手/1031円</t>
-        </is>
-      </c>
-      <c r="C4" s="348" t="inlineStr">
-        <is>
-          <t>C、鉱業、採石業、砂利採取業</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="454" t="inlineStr">
-        <is>
-          <t>4月</t>
-        </is>
-      </c>
-      <c r="B5" s="454" t="inlineStr">
-        <is>
-          <t>宮城/1038円</t>
-        </is>
-      </c>
-      <c r="C5" s="348" t="inlineStr">
-        <is>
-          <t>D、建設業</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="454" t="inlineStr">
-        <is>
-          <t>5月</t>
-        </is>
-      </c>
-      <c r="B6" s="454" t="inlineStr">
-        <is>
-          <t>秋田/1031円</t>
-        </is>
-      </c>
-      <c r="C6" s="348" t="inlineStr">
-        <is>
-          <t>E、製造業</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="454" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="B7" s="454" t="inlineStr">
-        <is>
-          <t>山形/1032円</t>
-        </is>
-      </c>
-      <c r="C7" s="348" t="inlineStr">
-        <is>
-          <t>F、電気、ガス、熱供給・水道業</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="454" t="inlineStr">
-        <is>
-          <t>7月</t>
-        </is>
-      </c>
-      <c r="B8" s="454" t="inlineStr">
-        <is>
-          <t>福島/1033円</t>
-        </is>
-      </c>
-      <c r="C8" s="348" t="inlineStr">
-        <is>
-          <t>G、情報通信業</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="454" t="inlineStr">
-        <is>
-          <t>8月</t>
-        </is>
-      </c>
-      <c r="B9" s="454" t="inlineStr">
-        <is>
-          <t>茨城/1074円</t>
-        </is>
-      </c>
-      <c r="C9" s="348" t="inlineStr">
-        <is>
-          <t>H、運輸業、郵便業</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="454" t="inlineStr">
-        <is>
-          <t>9月</t>
-        </is>
-      </c>
-      <c r="B10" s="454" t="inlineStr">
-        <is>
-          <t>栃木/1068円</t>
-        </is>
-      </c>
-      <c r="C10" s="348" t="inlineStr">
-        <is>
-          <t>I、卸売業、小売業</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="454" t="inlineStr">
-        <is>
-          <t>10月</t>
-        </is>
-      </c>
-      <c r="B11" s="454" t="inlineStr">
-        <is>
-          <t>群馬/1063円</t>
-        </is>
-      </c>
-      <c r="C11" s="348" t="inlineStr">
-        <is>
-          <t>J、金融業、保険業</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="454" t="inlineStr">
-        <is>
-          <t>11月</t>
-        </is>
-      </c>
-      <c r="B12" s="454" t="inlineStr">
-        <is>
-          <t>埼玉/1141円</t>
-        </is>
-      </c>
-      <c r="C12" s="348" t="inlineStr">
-        <is>
-          <t>K、不動産業、物品賃貸業</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="454" t="inlineStr">
-        <is>
-          <t>12月</t>
-        </is>
-      </c>
-      <c r="B13" s="454" t="inlineStr">
-        <is>
-          <t>千葉/1140円</t>
-        </is>
-      </c>
-      <c r="C13" s="348" t="inlineStr">
-        <is>
-          <t>L、学術研究、専門・技術サービス業</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="454" t="inlineStr">
-        <is>
-          <t>東京/1226円</t>
-        </is>
-      </c>
-      <c r="C14" s="348" t="inlineStr">
-        <is>
-          <t>M、宿泊業、飲食サービス業</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="454" t="inlineStr">
-        <is>
-          <t>神奈川/1225円</t>
-        </is>
-      </c>
-      <c r="C15" s="348" t="inlineStr">
-        <is>
-          <t>N、生活関連サービス業、娯楽業</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="454" t="inlineStr">
-        <is>
-          <t>新潟/1050円</t>
-        </is>
-      </c>
-      <c r="C16" s="348" t="inlineStr">
-        <is>
-          <t>O、教育、学習支援業</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="454" t="inlineStr">
-        <is>
-          <t>富山/1062円</t>
-        </is>
-      </c>
-      <c r="C17" s="348" t="inlineStr">
-        <is>
-          <t>P、医療 福祉</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="454" t="inlineStr">
-        <is>
-          <t>石川/1054円</t>
-        </is>
-      </c>
-      <c r="C18" s="348" t="inlineStr">
-        <is>
-          <t>Q、複合サービス事業</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="454" t="inlineStr">
-        <is>
-          <t>福井/1053円</t>
-        </is>
-      </c>
-      <c r="C19" s="348" t="inlineStr">
-        <is>
-          <t>R、サービス業（他に分類されないもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="454" t="inlineStr">
-        <is>
-          <t>山梨/1052円</t>
-        </is>
-      </c>
-      <c r="C20" s="348" t="inlineStr">
-        <is>
-          <t>S、公務（他に分類されるものを除く）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="454" t="inlineStr">
-        <is>
-          <t>長野/1061円</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="454" t="inlineStr">
-        <is>
-          <t>岐阜/1065円</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="454" t="inlineStr">
-        <is>
-          <t>静岡/1097円</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="454" t="inlineStr">
-        <is>
-          <t>愛知/1140円</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="454" t="inlineStr">
-        <is>
-          <t>三重/1087円</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="454" t="inlineStr">
-        <is>
-          <t>滋賀/1080円</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="454" t="inlineStr">
-        <is>
-          <t>京都/1122円</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="454" t="inlineStr">
-        <is>
-          <t>大阪/1177円</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="454" t="inlineStr">
-        <is>
-          <t>兵庫/1116円</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="454" t="inlineStr">
-        <is>
-          <t>奈良/1051円</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="454" t="inlineStr">
-        <is>
-          <t>和歌山/1045円</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="454" t="inlineStr">
-        <is>
-          <t>鳥取/1030円</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="454" t="inlineStr">
-        <is>
-          <t>島根/1033円</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="454" t="inlineStr">
-        <is>
-          <t>岡山/1047円</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="454" t="inlineStr">
-        <is>
-          <t>広島/1085円</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="454" t="inlineStr">
-        <is>
-          <t>山口/1043円</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="454" t="inlineStr">
-        <is>
-          <t>徳島/1046円</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="454" t="inlineStr">
-        <is>
-          <t>香川/1036円</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="454" t="inlineStr">
-        <is>
-          <t>愛媛/1033円</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="454" t="inlineStr">
-        <is>
-          <t>高知/1023円</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="454" t="inlineStr">
-        <is>
-          <t>福岡/1057円</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="454" t="inlineStr">
-        <is>
-          <t>佐賀/1030円</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="454" t="inlineStr">
-        <is>
-          <t>長崎/1031円</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="454" t="inlineStr">
-        <is>
-          <t>熊本/1034円</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="454" t="inlineStr">
-        <is>
-          <t>大分/1035円</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="454" t="inlineStr">
-        <is>
-          <t>宮崎/1023円</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="454" t="inlineStr">
-        <is>
-          <t>鹿児島/1026円</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="454" t="inlineStr">
-        <is>
-          <t>沖縄/1023円</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="455" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>